--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -427,18 +427,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>БольшойКоэф</t>
+          <t>BigRatio</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>МалыйКоэф</t>
+          <t>SmallRatio</t>
         </is>
       </c>
     </row>
@@ -687,242 +687,6 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -934,23 +698,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Правило</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ВВЕРХ</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ВНИЗ</t>
+          <t>DOWN</t>
         </is>
       </c>
     </row>
@@ -1029,260 +793,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1294,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,265 +813,6 @@
         <v/>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1573,33 +824,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J260"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Тикет</t>
+          <t>Ticket</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Роль</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Лот</t>
+          <t>Lot</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ЦенаОткрытия</t>
+          <t>OpenPrice</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1664,6 +915,7 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1701,6 +953,7 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1786,261 +1039,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2052,23 +1050,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J260"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>СредняяЦенаBUY</t>
+          <t>AverageBuyPrice</t>
         </is>
       </c>
       <c r="E1">
@@ -2079,7 +1077,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ТекущаяЦена</t>
+          <t>CurrentPrice</t>
         </is>
       </c>
       <c r="B2">
@@ -2088,7 +1086,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>СредняяЦенаSELL</t>
+          <t>AverageSellPrice</t>
         </is>
       </c>
       <c r="E2">
@@ -2099,7 +1097,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ДвижениеВверхПункты</t>
+          <t>MoveUpPoints</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2107,7 +1105,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Центр</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="E3">
@@ -2118,7 +1116,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>СценарнаяЦена</t>
+          <t>ScenarioPrice</t>
         </is>
       </c>
       <c r="B4">
@@ -2127,7 +1125,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ВерхУровень1</t>
+          <t>UpperLevel1</t>
         </is>
       </c>
       <c r="E4">
@@ -2138,7 +1136,7 @@
     <row r="5">
       <c r="D5" t="inlineStr">
         <is>
-          <t>ВерхУровень2</t>
+          <t>UpperLevel2</t>
         </is>
       </c>
       <c r="E5">
@@ -2149,22 +1147,22 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Тикет</t>
+          <t>Ticket</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Роль</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>ВерхУровень3</t>
+          <t>UpperLevel3</t>
         </is>
       </c>
       <c r="E6" s="1">
@@ -2212,7 +1210,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ВерхУровень4</t>
+          <t>UpperLevel4</t>
         </is>
       </c>
       <c r="E7">
@@ -2297,7 +1295,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>НизУровень1</t>
+          <t>LowerLevel1</t>
         </is>
       </c>
       <c r="E9">
@@ -2340,7 +1338,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>НизУровень2</t>
+          <t>LowerLevel2</t>
         </is>
       </c>
       <c r="E10">
@@ -2383,7 +1381,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>НизУровень3</t>
+          <t>LowerLevel3</t>
         </is>
       </c>
       <c r="E11">
@@ -2426,7 +1424,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>НизУровень4</t>
+          <t>LowerLevel4</t>
         </is>
       </c>
       <c r="E12">
@@ -10602,23 +9600,10 @@
         <v/>
       </c>
     </row>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ТипХвоста</t>
+          <t>TailType</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10630,7 +9615,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ХудшийPnLХвоста</t>
+          <t>TailWorstPnL</t>
         </is>
       </c>
       <c r="B221">
@@ -10641,7 +9626,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ТикетХвоста</t>
+          <t>TailTicket</t>
         </is>
       </c>
       <c r="B222">
@@ -10652,7 +9637,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ЛотХвоста</t>
+          <t>TailLot</t>
         </is>
       </c>
       <c r="B223">
@@ -10663,7 +9648,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>УбытокХвостаДеньги</t>
+          <t>TailLossMoney</t>
         </is>
       </c>
       <c r="B224">
@@ -10674,7 +9659,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>УбытокНаЛот</t>
+          <t>TailLossPerLot</t>
         </is>
       </c>
       <c r="B225">
@@ -10682,41 +9667,6 @@
         <v/>
       </c>
     </row>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10728,23 +9678,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J260"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>СредняяЦенаBUY</t>
+          <t>AverageBuyPrice</t>
         </is>
       </c>
       <c r="E1">
@@ -10755,7 +9705,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ТекущаяЦена</t>
+          <t>CurrentPrice</t>
         </is>
       </c>
       <c r="B2">
@@ -10764,7 +9714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>СредняяЦенаSELL</t>
+          <t>AverageSellPrice</t>
         </is>
       </c>
       <c r="E2">
@@ -10775,7 +9725,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ДвижениеВнизПункты</t>
+          <t>MoveDownPoints</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -10783,7 +9733,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Центр</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="E3">
@@ -10794,7 +9744,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>СценарнаяЦена</t>
+          <t>ScenarioPrice</t>
         </is>
       </c>
       <c r="B4">
@@ -10803,7 +9753,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ВерхУровень1</t>
+          <t>UpperLevel1</t>
         </is>
       </c>
       <c r="E4">
@@ -10814,7 +9764,7 @@
     <row r="5">
       <c r="D5" t="inlineStr">
         <is>
-          <t>ВерхУровень2</t>
+          <t>UpperLevel2</t>
         </is>
       </c>
       <c r="E5">
@@ -10825,22 +9775,22 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Тикет</t>
+          <t>Ticket</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Роль</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>ВерхУровень3</t>
+          <t>UpperLevel3</t>
         </is>
       </c>
       <c r="E6" s="1">
@@ -10888,7 +9838,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ВерхУровень4</t>
+          <t>UpperLevel4</t>
         </is>
       </c>
       <c r="E7">
@@ -10973,7 +9923,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>НизУровень1</t>
+          <t>LowerLevel1</t>
         </is>
       </c>
       <c r="E9">
@@ -11016,7 +9966,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>НизУровень2</t>
+          <t>LowerLevel2</t>
         </is>
       </c>
       <c r="E10">
@@ -11059,7 +10009,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>НизУровень3</t>
+          <t>LowerLevel3</t>
         </is>
       </c>
       <c r="E11">
@@ -11102,7 +10052,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>НизУровень4</t>
+          <t>LowerLevel4</t>
         </is>
       </c>
       <c r="E12">
@@ -19278,23 +18228,10 @@
         <v/>
       </c>
     </row>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ТипХвоста</t>
+          <t>TailType</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19306,7 +18243,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ХудшийPnLХвоста</t>
+          <t>TailWorstPnL</t>
         </is>
       </c>
       <c r="B221">
@@ -19317,7 +18254,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ТикетХвоста</t>
+          <t>TailTicket</t>
         </is>
       </c>
       <c r="B222">
@@ -19328,7 +18265,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ЛотХвоста</t>
+          <t>TailLot</t>
         </is>
       </c>
       <c r="B223">
@@ -19339,7 +18276,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>УбытокХвостаДеньги</t>
+          <t>TailLossMoney</t>
         </is>
       </c>
       <c r="B224">
@@ -19350,7 +18287,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>УбытокНаЛот</t>
+          <t>TailLossPerLot</t>
         </is>
       </c>
       <c r="B225">
@@ -19358,41 +18295,6 @@
         <v/>
       </c>
     </row>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19404,25 +18306,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R260"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ТипХвоста</t>
+          <t>TailType</t>
         </is>
       </c>
       <c r="B2">
@@ -19433,7 +18335,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ЛотХвоста</t>
+          <t>TailLot</t>
         </is>
       </c>
       <c r="B3">
@@ -19444,7 +18346,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>СледующийУровень</t>
+          <t>NextLevel</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -19454,7 +18356,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>БольшойКоэф</t>
+          <t>BigRatio</t>
         </is>
       </c>
       <c r="B5">
@@ -19465,7 +18367,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>МалыйКоэф</t>
+          <t>SmallRatio</t>
         </is>
       </c>
       <c r="B6">
@@ -19476,7 +18378,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>БольшойЛот</t>
+          <t>BigLot</t>
         </is>
       </c>
       <c r="B7">
@@ -19487,7 +18389,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>МалыйЛот</t>
+          <t>SmallLot</t>
         </is>
       </c>
       <c r="B8">
@@ -19498,7 +18400,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>АктивныеСекции</t>
+          <t>ActiveSections</t>
         </is>
       </c>
       <c r="B9">
@@ -19509,7 +18411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ОбщийЛотПослеОткрытия</t>
+          <t>TotalLotAfterOpen</t>
         </is>
       </c>
       <c r="B10">
@@ -19520,7 +18422,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ЧистыйЛотПослеОткрытия</t>
+          <t>NetLotAfterOpen</t>
         </is>
       </c>
       <c r="B11">
@@ -19531,7 +18433,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>УровеньДостигнут</t>
+          <t>LevelReached</t>
         </is>
       </c>
       <c r="B12">
@@ -19542,7 +18444,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>НетВстречногоКаскада</t>
+          <t>NoOppositeCascade</t>
         </is>
       </c>
       <c r="B13">
@@ -19553,7 +18455,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>МожноОткрытьСекцию</t>
+          <t>CanOpenSection</t>
         </is>
       </c>
       <c r="B14">
@@ -19561,15 +18463,10 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>IDСекции</t>
+          <t>SectionID</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
@@ -19579,7 +18476,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>БольшойЛот</t>
+          <t>BigLot</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -19958,15 +18855,10 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ВыбраннаяСекция</t>
+          <t>SelectedSectionID</t>
         </is>
       </c>
       <c r="B30">
@@ -19977,7 +18869,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ПрибыльЦикла</t>
+          <t>CycleProfit</t>
         </is>
       </c>
       <c r="B31">
@@ -19988,7 +18880,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>МожноЗакрытьСекцию</t>
+          <t>CanCloseSection</t>
         </is>
       </c>
       <c r="B32">
@@ -19999,7 +18891,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ДобавкаРезерв</t>
+          <t>ReserveAdd</t>
         </is>
       </c>
       <c r="B33">
@@ -20010,7 +18902,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ДобавкаRecovery</t>
+          <t>RecoveryAdd</t>
         </is>
       </c>
       <c r="B34">
@@ -20021,7 +18913,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>НовыйГлобРезерв</t>
+          <t>NewGlobalReserve</t>
         </is>
       </c>
       <c r="B35">
@@ -20032,7 +18924,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>НовыйRecoveryFund</t>
+          <t>NewRecoveryFund</t>
         </is>
       </c>
       <c r="B36">
@@ -20040,230 +18932,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20275,25 +18943,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R260"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ТипХвоста</t>
+          <t>TailType</t>
         </is>
       </c>
       <c r="B2">
@@ -20304,7 +18972,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ЛотХвоста</t>
+          <t>TailLot</t>
         </is>
       </c>
       <c r="B3">
@@ -20315,7 +18983,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>СледующийУровень</t>
+          <t>NextLevel</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -20325,7 +18993,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>БольшойКоэф</t>
+          <t>BigRatio</t>
         </is>
       </c>
       <c r="B5">
@@ -20336,7 +19004,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>МалыйКоэф</t>
+          <t>SmallRatio</t>
         </is>
       </c>
       <c r="B6">
@@ -20347,7 +19015,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>БольшойЛот</t>
+          <t>BigLot</t>
         </is>
       </c>
       <c r="B7">
@@ -20358,7 +19026,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>МалыйЛот</t>
+          <t>SmallLot</t>
         </is>
       </c>
       <c r="B8">
@@ -20369,7 +19037,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>АктивныеСекции</t>
+          <t>ActiveSections</t>
         </is>
       </c>
       <c r="B9">
@@ -20380,7 +19048,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ОбщийЛотПослеОткрытия</t>
+          <t>TotalLotAfterOpen</t>
         </is>
       </c>
       <c r="B10">
@@ -20391,7 +19059,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ЧистыйЛотПослеОткрытия</t>
+          <t>NetLotAfterOpen</t>
         </is>
       </c>
       <c r="B11">
@@ -20402,7 +19070,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>УровеньДостигнут</t>
+          <t>LevelReached</t>
         </is>
       </c>
       <c r="B12">
@@ -20413,7 +19081,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>НетВстречногоКаскада</t>
+          <t>NoOppositeCascade</t>
         </is>
       </c>
       <c r="B13">
@@ -20424,7 +19092,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>МожноОткрытьСекцию</t>
+          <t>CanOpenSection</t>
         </is>
       </c>
       <c r="B14">
@@ -20432,15 +19100,10 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>IDСекции</t>
+          <t>SectionID</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
@@ -20450,7 +19113,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>БольшойЛот</t>
+          <t>BigLot</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -20829,15 +19492,10 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ВыбраннаяСекция</t>
+          <t>SelectedSectionID</t>
         </is>
       </c>
       <c r="B30">
@@ -20848,7 +19506,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ПрибыльЦикла</t>
+          <t>CycleProfit</t>
         </is>
       </c>
       <c r="B31">
@@ -20859,7 +19517,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>МожноЗакрытьСекцию</t>
+          <t>CanCloseSection</t>
         </is>
       </c>
       <c r="B32">
@@ -20870,7 +19528,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ДобавкаРезерв</t>
+          <t>ReserveAdd</t>
         </is>
       </c>
       <c r="B33">
@@ -20881,7 +19539,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ДобавкаRecovery</t>
+          <t>RecoveryAdd</t>
         </is>
       </c>
       <c r="B34">
@@ -20892,7 +19550,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>НовыйГлобРезерв</t>
+          <t>NewGlobalReserve</t>
         </is>
       </c>
       <c r="B35">
@@ -20903,7 +19561,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>НовыйRecoveryFund</t>
+          <t>NewRecoveryFund</t>
         </is>
       </c>
       <c r="B36">
@@ -20911,230 +19569,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21146,25 +19580,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ТипХвоста</t>
+          <t>TailType</t>
         </is>
       </c>
       <c r="B2">
@@ -21175,7 +19609,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ТикетХвоста</t>
+          <t>TailTicket</t>
         </is>
       </c>
       <c r="B3">
@@ -21186,7 +19620,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ЛотХвоста</t>
+          <t>TailLot</t>
         </is>
       </c>
       <c r="B4">
@@ -21197,7 +19631,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>УбытокНаЛот</t>
+          <t>TailLossPerLot</t>
         </is>
       </c>
       <c r="B5">
@@ -21208,7 +19642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>МожноЗакрытьСекцию</t>
+          <t>CanCloseSection</t>
         </is>
       </c>
       <c r="B6">
@@ -21219,7 +19653,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RecoveryПослеЦикла</t>
+          <t>RecoveryFundAfterCycle</t>
         </is>
       </c>
       <c r="B7">
@@ -21230,7 +19664,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ЛотЗакрытияСырой</t>
+          <t>CloseLotRaw</t>
         </is>
       </c>
       <c r="B8">
@@ -21241,7 +19675,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЛотЗакрытияОкругл</t>
+          <t>CloseLotRounded</t>
         </is>
       </c>
       <c r="B9">
@@ -21252,7 +19686,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЛотЗакрытияФинал</t>
+          <t>CloseLotFinal</t>
         </is>
       </c>
       <c r="B10">
@@ -21263,7 +19697,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ЗакрытиеРазрешено</t>
+          <t>CloseAllowed</t>
         </is>
       </c>
       <c r="B11">
@@ -21274,7 +19708,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>УбытокЗакрытияХвоста</t>
+          <t>TailCloseLoss</t>
         </is>
       </c>
       <c r="B12">
@@ -21285,7 +19719,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RecoveryПослеЗакрытия</t>
+          <t>RecoveryFundAfterClose</t>
         </is>
       </c>
       <c r="B13">
@@ -21296,7 +19730,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ЛотХвостаПослеЗакрытия</t>
+          <t>TailLotAfterClose</t>
         </is>
       </c>
       <c r="B14">
@@ -21307,7 +19741,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>СледующийУровень</t>
+          <t>NextLevel</t>
         </is>
       </c>
       <c r="B15">
@@ -21318,7 +19752,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>СледБольшойЛотПослеRecovery</t>
+          <t>NextBigLotAfterRecovery</t>
         </is>
       </c>
       <c r="B16">
@@ -21329,7 +19763,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>СледМалыйЛотПослеRecovery</t>
+          <t>NextSmallLotAfterRecovery</t>
         </is>
       </c>
       <c r="B17">
@@ -21337,249 +19771,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21591,25 +19782,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ТипХвоста</t>
+          <t>TailType</t>
         </is>
       </c>
       <c r="B2">
@@ -21620,7 +19811,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ТикетХвоста</t>
+          <t>TailTicket</t>
         </is>
       </c>
       <c r="B3">
@@ -21631,7 +19822,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ЛотХвоста</t>
+          <t>TailLot</t>
         </is>
       </c>
       <c r="B4">
@@ -21642,7 +19833,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>УбытокНаЛот</t>
+          <t>TailLossPerLot</t>
         </is>
       </c>
       <c r="B5">
@@ -21653,7 +19844,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>МожноЗакрытьСекцию</t>
+          <t>CanCloseSection</t>
         </is>
       </c>
       <c r="B6">
@@ -21664,7 +19855,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RecoveryПослеЦикла</t>
+          <t>RecoveryFundAfterCycle</t>
         </is>
       </c>
       <c r="B7">
@@ -21675,7 +19866,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ЛотЗакрытияСырой</t>
+          <t>CloseLotRaw</t>
         </is>
       </c>
       <c r="B8">
@@ -21686,7 +19877,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЛотЗакрытияОкругл</t>
+          <t>CloseLotRounded</t>
         </is>
       </c>
       <c r="B9">
@@ -21697,7 +19888,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЛотЗакрытияФинал</t>
+          <t>CloseLotFinal</t>
         </is>
       </c>
       <c r="B10">
@@ -21708,7 +19899,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ЗакрытиеРазрешено</t>
+          <t>CloseAllowed</t>
         </is>
       </c>
       <c r="B11">
@@ -21719,7 +19910,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>УбытокЗакрытияХвоста</t>
+          <t>TailCloseLoss</t>
         </is>
       </c>
       <c r="B12">
@@ -21730,7 +19921,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RecoveryПослеЗакрытия</t>
+          <t>RecoveryFundAfterClose</t>
         </is>
       </c>
       <c r="B13">
@@ -21741,7 +19932,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ЛотХвостаПослеЗакрытия</t>
+          <t>TailLotAfterClose</t>
         </is>
       </c>
       <c r="B14">
@@ -21752,7 +19943,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>СледующийУровень</t>
+          <t>NextLevel</t>
         </is>
       </c>
       <c r="B15">
@@ -21763,7 +19954,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>СледБольшойЛотПослеRecovery</t>
+          <t>NextBigLotAfterRecovery</t>
         </is>
       </c>
       <c r="B16">
@@ -21774,7 +19965,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>СледМалыйЛотПослеRecovery</t>
+          <t>NextSmallLotAfterRecovery</t>
         </is>
       </c>
       <c r="B17">
@@ -21782,249 +19973,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22036,30 +19984,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Поле</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ВВЕРХ</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ВНИЗ</t>
+          <t>DOWN</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>СценарнаяЦена</t>
+          <t>ScenarioPrice</t>
         </is>
       </c>
       <c r="B2">
@@ -22074,7 +20022,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ПлавающийИтогКорзины</t>
+          <t>BasketFloating</t>
         </is>
       </c>
       <c r="B3">
@@ -22089,7 +20037,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ГлобРезервПосле</t>
+          <t>GlobalReserveAfter</t>
         </is>
       </c>
       <c r="B4">
@@ -22104,7 +20052,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RecoveryПослеЦикла</t>
+          <t>RecoveryFundAfterCycle</t>
         </is>
       </c>
       <c r="B5">
@@ -22119,7 +20067,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ЛотХвостаПосле</t>
+          <t>TailLotAfter</t>
         </is>
       </c>
       <c r="B6">
@@ -22134,7 +20082,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ЛотЗакрытия</t>
+          <t>CloseLot</t>
         </is>
       </c>
       <c r="B7">
@@ -22149,7 +20097,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>МожноЗакрытьСекцию</t>
+          <t>CanCloseSection</t>
         </is>
       </c>
       <c r="B8">
@@ -22164,7 +20112,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>МожноЗакрытьХвост</t>
+          <t>CanCloseTail</t>
         </is>
       </c>
       <c r="B9">
@@ -22179,7 +20127,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>МожноЗакрытьКорзину</t>
+          <t>CanCloseBasket</t>
         </is>
       </c>
       <c r="B10">
@@ -22194,7 +20142,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>СледБольшойЛот</t>
+          <t>NextBigLot</t>
         </is>
       </c>
       <c r="B11">
@@ -22209,7 +20157,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>СледМалыйЛот</t>
+          <t>NextSmallLot</t>
         </is>
       </c>
       <c r="B12">
@@ -22224,7 +20172,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>СледДействие</t>
+          <t>NextAction</t>
         </is>
       </c>
       <c r="B13">
@@ -22236,253 +20184,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -18,6 +18,8 @@
     <sheet name="BasketSummary" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Validation" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="ScenarioText_UP" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ScenarioText_DOWN" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -804,12 +806,775 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1">
-        <f>"NEXT ACTION UP:"&amp;CHAR(10)&amp;BasketSummary!B13&amp;CHAR(10)&amp;"NEXT ACTION DOWN:"&amp;CHAR(10)&amp;BasketSummary!C13</f>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TailBefore</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TailClosed</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TailAfter</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RecoveryBefore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RecoveryAfter</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ReserveAfter</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>NOW()</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ScenarioText_UP</t>
+        </is>
+      </c>
+      <c r="D2">
+        <f>BasketSummary!B13</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>TailRecovery_UP!B3</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>TailRecovery_UP!B10</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>MAX(E2-F2,0)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>TailRecovery_UP!B5</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>TailRecovery_UP!B7</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>SectionCalculator_UP!B35</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>IF(OR(SectionCalculator_UP!B12&lt;&gt;"YES",SectionCalculator_UP!B13&lt;&gt;"YES"),"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>NOW()</f>
+        <v/>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ScenarioText_DOWN</t>
+        </is>
+      </c>
+      <c r="D3">
+        <f>BasketSummary!C13</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>TailRecovery_DOWN!B3</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>TailRecovery_DOWN!B10</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>MAX(E3-F3,0)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>TailRecovery_DOWN!B5</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>TailRecovery_DOWN!B7</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>SectionCalculator_DOWN!B35</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>IF(OR(SectionCalculator_DOWN!B12&lt;&gt;"YES",SectionCalculator_DOWN!B13&lt;&gt;"YES"),"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ScenarioTitle</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>"SCENARIO: PRICE MOVES UP"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CurrentPrice</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Scenario_UP!B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NextTriggerLevel</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>SectionCalculator_UP!B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DistancePoints</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>ROUND(ABS(B4-B3)*10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BigPosition</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>"SELL "&amp;TEXT(TailRecovery_UP!B16,"0.00")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SmallHedge</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>"BUY "&amp;TEXT(TailRecovery_UP!B17,"0.00")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SectionLevel</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>SectionCalculator_UP!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IF(SectionCalculator_UP!B12="YES","Reached level; tail found; risk limits OK","Waiting level/risk gate")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RiskChecks</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CanOpenSection</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>SectionCalculator_UP!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NoOppositeCascade</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>SectionCalculator_UP!B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CanCloseSection</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>SectionCalculator_UP!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CanCloseTail</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>TailRecovery_UP!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CycleProfit</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>SectionCalculator_UP!B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ReserveAdd</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>TailRecovery_UP!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RecoveryAdd</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>TailRecovery_UP!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DetectedTailType</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>TailRecovery_UP!B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TailLot</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>TailRecovery_UP!B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TailLoss</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>TailRecovery_UP!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RecoveryFundBefore</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>TailRecovery_UP!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CloseLotRaw</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>TailRecovery_UP!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CloseLotRounded</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>TailRecovery_UP!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CloseLotFinal</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>TailRecovery_UP!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TailLotAfter</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>MAX(B22-B27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RecoveryFundAfter</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>TailRecovery_UP!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HumanReadableAction</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>TEXTJOIN(CHAR(10),TRUE,B2,"Current Price: "&amp;TEXT(B3,"0.00000"),"Next trigger level: "&amp;TEXT(B4,"0.00000")&amp;" ("&amp;TEXT(B5,"0")&amp;" points)","Open section: "&amp;B6&amp;" + "&amp;B7,"Section level: "&amp;TEXT(B8,"0"),"CycleProfit: "&amp;TEXT(B17,"0.00"),"Reserve += "&amp;TEXT(B18,"0.00")&amp;"; Recovery += "&amp;TEXT(B19,"0.00"),"Tail: "&amp;B21&amp;" "&amp;TEXT(B22,"0.00")&amp;"; Close "&amp;TEXT(B27,"0.00")&amp;"; Remain "&amp;TEXT(B28,"0.00"),"CanCloseBasket: "&amp;BasketSummary!B10,"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ScenarioTitle</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>"SCENARIO: PRICE MOVES DOWN"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CurrentPrice</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Scenario_DOWN!B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NextTriggerLevel</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>SectionCalculator_DOWN!B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DistancePoints</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>ROUND(ABS(B4-B3)*10000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BigPosition</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>"SELL "&amp;TEXT(TailRecovery_DOWN!B16,"0.00")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SmallHedge</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>"BUY "&amp;TEXT(TailRecovery_DOWN!B17,"0.00")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SectionLevel</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>SectionCalculator_DOWN!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IF(SectionCalculator_DOWN!B12="YES","Reached level; tail found; risk limits OK","Waiting level/risk gate")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RiskChecks</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CanOpenSection</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>SectionCalculator_DOWN!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NoOppositeCascade</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>SectionCalculator_DOWN!B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CanCloseSection</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>SectionCalculator_DOWN!B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CanCloseTail</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>TailRecovery_DOWN!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CycleProfit</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>SectionCalculator_DOWN!B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ReserveAdd</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>TailRecovery_DOWN!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RecoveryAdd</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>TailRecovery_DOWN!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DetectedTailType</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>TailRecovery_DOWN!B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TailLot</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>TailRecovery_DOWN!B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TailLoss</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>TailRecovery_DOWN!B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RecoveryFundBefore</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>TailRecovery_DOWN!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CloseLotRaw</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>TailRecovery_DOWN!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CloseLotRounded</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>TailRecovery_DOWN!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CloseLotFinal</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>TailRecovery_DOWN!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TailLotAfter</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>MAX(B22-B27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RecoveryFundAfter</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>TailRecovery_DOWN!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HumanReadableAction</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>TEXTJOIN(CHAR(10),TRUE,B2,"Current Price: "&amp;TEXT(B3,"0.00000"),"Next trigger level: "&amp;TEXT(B4,"0.00000")&amp;" ("&amp;TEXT(B5,"0")&amp;" points)","Open section: "&amp;B6&amp;" + "&amp;B7,"Section level: "&amp;TEXT(B8,"0"),"CycleProfit: "&amp;TEXT(B17,"0.00"),"Reserve += "&amp;TEXT(B18,"0.00")&amp;"; Recovery += "&amp;TEXT(B19,"0.00"),"Tail: "&amp;B21&amp;" "&amp;TEXT(B22,"0.00")&amp;"; Close "&amp;TEXT(B27,"0.00")&amp;"; Remain "&amp;TEXT(B28,"0.00"),"CanCloseBasket: "&amp;BasketSummary!C10,"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
         <v/>
       </c>
     </row>
@@ -19984,7 +20749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20184,6 +20949,21 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HumanReadableAction</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>ScenarioText_UP!B31</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>ScenarioText_DOWN!B31</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,13 +40,23 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,9 +71,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -812,52 +825,52 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>Время</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Направление</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>Сценарий</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Действие</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TailBefore</t>
+          <t>Хвост до закрытия</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>TailClosed</t>
+          <t>Закрываемый лот хвоста</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>TailAfter</t>
+          <t>Хвост после закрытия</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>RecoveryBefore</t>
+          <t>RecoveryFund до</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>RecoveryAfter</t>
+          <t>RecoveryFund после</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ReserveAfter</t>
+          <t>Резерв после</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -873,7 +886,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UP</t>
+          <t>ВВЕРХ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -910,7 +923,7 @@
         <v/>
       </c>
       <c r="K2">
-        <f>IF(OR(SectionCalculator_UP!B12&lt;&gt;"YES",SectionCalculator_UP!B13&lt;&gt;"YES"),"YES","NO")</f>
+        <f>IF(OR(SectionCalculator_UP!B14&lt;&gt;"YES",SectionCalculator_UP!B13&lt;&gt;"YES"),"YES","NO")</f>
         <v/>
       </c>
     </row>
@@ -921,7 +934,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOWN</t>
+          <t>ВНИЗ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -958,7 +971,7 @@
         <v/>
       </c>
       <c r="K3">
-        <f>IF(OR(SectionCalculator_DOWN!B12&lt;&gt;"YES",SectionCalculator_DOWN!B13&lt;&gt;"YES"),"YES","NO")</f>
+        <f>IF(OR(SectionCalculator_DOWN!B14&lt;&gt;"YES",SectionCalculator_DOWN!B13&lt;&gt;"YES"),"YES","NO")</f>
         <v/>
       </c>
     </row>
@@ -973,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,113 +1004,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ScenarioTitle</t>
+          <t>Название сценария</t>
         </is>
       </c>
       <c r="B2">
-        <f>"SCENARIO: PRICE MOVES UP"</f>
+        <f>"СЦЕНАРИЙ: ЦЕНА ИДЕТ ВВЕРХ"</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CurrentPrice</t>
+          <t>Текущая цена</t>
         </is>
       </c>
       <c r="B3">
-        <f>Scenario_UP!B4</f>
+        <f>IFERROR(Scenario_UP!B4,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NextTriggerLevel</t>
+          <t>Следующий уровень</t>
         </is>
       </c>
       <c r="B4">
-        <f>SectionCalculator_UP!B15</f>
+        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!E4,IF(SectionCalculator_UP!B4=2,Scenario_UP!E5,IF(SectionCalculator_UP!B4=3,Scenario_UP!E6,IF(SectionCalculator_UP!B4=4,Scenario_UP!E7,"")))),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DistancePoints</t>
+          <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
       <c r="B5">
-        <f>ROUND(ABS(B4-B3)*10000,0)</f>
+        <f>IF(OR(B4="",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BigPosition</t>
+          <t>Большая позиция</t>
         </is>
       </c>
       <c r="B6">
-        <f>"SELL "&amp;TEXT(TailRecovery_UP!B16,"0.00")</f>
+        <f>IFERROR(IF(TailRecovery_UP!B16&gt;0,IF("UP"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_UP!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SmallHedge</t>
+          <t>Малая защитная позиция</t>
         </is>
       </c>
       <c r="B7">
-        <f>"BUY "&amp;TEXT(TailRecovery_UP!B17,"0.00")</f>
+        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SectionLevel</t>
+          <t>Уровень секции</t>
         </is>
       </c>
       <c r="B8">
-        <f>SectionCalculator_UP!B16</f>
+        <f>IFERROR(SectionCalculator_UP!B4,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Причина</t>
         </is>
       </c>
       <c r="B9">
-        <f>IF(SectionCalculator_UP!B12="YES","Reached level; tail found; risk limits OK","Waiting level/risk gate")</f>
+        <f>IF(SectionCalculator_UP!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция сейчас недоступна: уровень/риск-гейт/хвост")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RiskChecks</t>
+          <t>Проверки риска</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CanOpenSection</t>
+          <t>Можно открыть секцию</t>
         </is>
       </c>
       <c r="B12">
-        <f>SectionCalculator_UP!B12</f>
+        <f>SectionCalculator_UP!B14</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NoOppositeCascade</t>
+          <t>Нет встречного каскада</t>
         </is>
       </c>
       <c r="B13">
@@ -1108,7 +1121,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CanCloseSection</t>
+          <t>Можно закрыть секцию</t>
         </is>
       </c>
       <c r="B14">
@@ -1119,7 +1132,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CanCloseTail</t>
+          <t>Можно закрыть хвост</t>
         </is>
       </c>
       <c r="B15">
@@ -1130,132 +1143,132 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CycleProfit</t>
+          <t>Прибыль цикла</t>
         </is>
       </c>
       <c r="B17">
-        <f>SectionCalculator_UP!B31</f>
+        <f>IFERROR(SectionCalculator_UP!B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ReserveAdd</t>
+          <t>Добавить в резерв</t>
         </is>
       </c>
       <c r="B18">
-        <f>TailRecovery_UP!B6</f>
+        <f>IFERROR(TailRecovery_UP!B6,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RecoveryAdd</t>
+          <t>Добавить в RecoveryFund</t>
         </is>
       </c>
       <c r="B19">
-        <f>TailRecovery_UP!B8</f>
+        <f>IFERROR(TailRecovery_UP!B8,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DetectedTailType</t>
+          <t>Тип хвоста</t>
         </is>
       </c>
       <c r="B21">
-        <f>TailRecovery_UP!B2</f>
+        <f>IF(OR(TailRecovery_UP!B2="",TailRecovery_UP!B2="N/A"),"Хвост не найден",TailRecovery_UP!B2)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TailLot</t>
+          <t>Лот хвоста</t>
         </is>
       </c>
       <c r="B22">
-        <f>TailRecovery_UP!B3</f>
+        <f>IFERROR(IF(TailRecovery_UP!B3&gt;0,TailRecovery_UP!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TailLoss</t>
+          <t>Убыток хвоста</t>
         </is>
       </c>
       <c r="B23">
-        <f>TailRecovery_UP!B12</f>
+        <f>IFERROR(TailRecovery_UP!B12,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RecoveryFundBefore</t>
+          <t>RecoveryFund до закрытия</t>
         </is>
       </c>
       <c r="B24">
-        <f>TailRecovery_UP!B5</f>
+        <f>IFERROR(TailRecovery_UP!B5,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CloseLotRaw</t>
+          <t>Расчётный лот закрытия</t>
         </is>
       </c>
       <c r="B25">
-        <f>TailRecovery_UP!B9</f>
+        <f>IFERROR(TailRecovery_UP!B9,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CloseLotRounded</t>
+          <t>Округлённый лот закрытия</t>
         </is>
       </c>
       <c r="B26">
-        <f>TailRecovery_UP!B10</f>
+        <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CloseLotFinal</t>
+          <t>Итоговый лот закрытия</t>
         </is>
       </c>
       <c r="B27">
-        <f>TailRecovery_UP!B10</f>
+        <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TailLotAfter</t>
+          <t>Остаток хвоста</t>
         </is>
       </c>
       <c r="B28">
-        <f>MAX(B22-B27,0)</f>
+        <f>IF(OR(B22="Хвост не найден",NOT(ISNUMBER(B22))),"Хвост не найден",MAX(B22-B27,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RecoveryFundAfter</t>
+          <t>RecoveryFund после закрытия</t>
         </is>
       </c>
       <c r="B29">
-        <f>TailRecovery_UP!B7</f>
+        <f>IFERROR(TailRecovery_UP!B7,0)</f>
         <v/>
       </c>
     </row>
@@ -1266,11 +1279,33 @@
         </is>
       </c>
       <c r="B31">
-        <f>TEXTJOIN(CHAR(10),TRUE,B2,"Current Price: "&amp;TEXT(B3,"0.00000"),"Next trigger level: "&amp;TEXT(B4,"0.00000")&amp;" ("&amp;TEXT(B5,"0")&amp;" points)","Open section: "&amp;B6&amp;" + "&amp;B7,"Section level: "&amp;TEXT(B8,"0"),"CycleProfit: "&amp;TEXT(B17,"0.00"),"Reserve += "&amp;TEXT(B18,"0.00")&amp;"; Recovery += "&amp;TEXT(B19,"0.00"),"Tail: "&amp;B21&amp;" "&amp;TEXT(B22,"0.00")&amp;"; Close "&amp;TEXT(B27,"0.00")&amp;"; Remain "&amp;TEXT(B28,"0.00"),"CanCloseBasket: "&amp;BasketSummary!B10,"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
-        <v/>
-      </c>
-    </row>
+        <f>TEXTJOIN(CHAR(10),TRUE,"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ:",B2,"Если цена дойдет до: "&amp;IF(B4="","уровень не рассчитан",TEXT(B4,"0.00000")),"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5),"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7,"Прибыль цикла: "&amp;TEXT(B17,"0.00")&amp;"; Резерв +"&amp;TEXT(B18,"0.00")&amp;"; RecoveryFund +"&amp;TEXT(B19,"0.00"),"Хвост: "&amp;B21&amp;"; закрыть: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;"; останется: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28),"RecoveryFund после: "&amp;TEXT(B29,"0.00"),"Итоговое действие: "&amp;IF(BasketSummary!B10="YES","BASKET_CLOSE",IF(B12&lt;&gt;"YES","WAIT",IF(B14="YES",IF(B15="YES","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION"))),"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <f>B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A32:H45"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1281,7 +1316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,113 +1334,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ScenarioTitle</t>
+          <t>Название сценария</t>
         </is>
       </c>
       <c r="B2">
-        <f>"SCENARIO: PRICE MOVES DOWN"</f>
+        <f>"СЦЕНАРИЙ: ЦЕНА ИДЕТ ВНИЗ"</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CurrentPrice</t>
+          <t>Текущая цена</t>
         </is>
       </c>
       <c r="B3">
-        <f>Scenario_DOWN!B4</f>
+        <f>IFERROR(Scenario_DOWN!B4,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NextTriggerLevel</t>
+          <t>Следующий уровень</t>
         </is>
       </c>
       <c r="B4">
-        <f>SectionCalculator_DOWN!B15</f>
+        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!E9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!E10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!E11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!E12,"")))),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DistancePoints</t>
+          <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
       <c r="B5">
-        <f>ROUND(ABS(B4-B3)*10000,0)</f>
+        <f>IF(OR(B4="",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BigPosition</t>
+          <t>Большая позиция</t>
         </is>
       </c>
       <c r="B6">
-        <f>"SELL "&amp;TEXT(TailRecovery_DOWN!B16,"0.00")</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B16&gt;0,IF("DOWN"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_DOWN!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SmallHedge</t>
+          <t>Малая защитная позиция</t>
         </is>
       </c>
       <c r="B7">
-        <f>"BUY "&amp;TEXT(TailRecovery_DOWN!B17,"0.00")</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SectionLevel</t>
+          <t>Уровень секции</t>
         </is>
       </c>
       <c r="B8">
-        <f>SectionCalculator_DOWN!B16</f>
+        <f>IFERROR(SectionCalculator_DOWN!B4,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Причина</t>
         </is>
       </c>
       <c r="B9">
-        <f>IF(SectionCalculator_DOWN!B12="YES","Reached level; tail found; risk limits OK","Waiting level/risk gate")</f>
+        <f>IF(SectionCalculator_DOWN!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция сейчас недоступна: уровень/риск-гейт/хвост")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RiskChecks</t>
+          <t>Проверки риска</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CanOpenSection</t>
+          <t>Можно открыть секцию</t>
         </is>
       </c>
       <c r="B12">
-        <f>SectionCalculator_DOWN!B12</f>
+        <f>SectionCalculator_DOWN!B14</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NoOppositeCascade</t>
+          <t>Нет встречного каскада</t>
         </is>
       </c>
       <c r="B13">
@@ -1416,7 +1451,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CanCloseSection</t>
+          <t>Можно закрыть секцию</t>
         </is>
       </c>
       <c r="B14">
@@ -1427,7 +1462,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CanCloseTail</t>
+          <t>Можно закрыть хвост</t>
         </is>
       </c>
       <c r="B15">
@@ -1438,132 +1473,132 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CycleProfit</t>
+          <t>Прибыль цикла</t>
         </is>
       </c>
       <c r="B17">
-        <f>SectionCalculator_DOWN!B31</f>
+        <f>IFERROR(SectionCalculator_DOWN!B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ReserveAdd</t>
+          <t>Добавить в резерв</t>
         </is>
       </c>
       <c r="B18">
-        <f>TailRecovery_DOWN!B6</f>
+        <f>IFERROR(TailRecovery_DOWN!B6,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RecoveryAdd</t>
+          <t>Добавить в RecoveryFund</t>
         </is>
       </c>
       <c r="B19">
-        <f>TailRecovery_DOWN!B8</f>
+        <f>IFERROR(TailRecovery_DOWN!B8,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DetectedTailType</t>
+          <t>Тип хвоста</t>
         </is>
       </c>
       <c r="B21">
-        <f>TailRecovery_DOWN!B2</f>
+        <f>IF(OR(TailRecovery_DOWN!B2="",TailRecovery_DOWN!B2="N/A"),"Хвост не найден",TailRecovery_DOWN!B2)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TailLot</t>
+          <t>Лот хвоста</t>
         </is>
       </c>
       <c r="B22">
-        <f>TailRecovery_DOWN!B3</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B3&gt;0,TailRecovery_DOWN!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TailLoss</t>
+          <t>Убыток хвоста</t>
         </is>
       </c>
       <c r="B23">
-        <f>TailRecovery_DOWN!B12</f>
+        <f>IFERROR(TailRecovery_DOWN!B12,0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RecoveryFundBefore</t>
+          <t>RecoveryFund до закрытия</t>
         </is>
       </c>
       <c r="B24">
-        <f>TailRecovery_DOWN!B5</f>
+        <f>IFERROR(TailRecovery_DOWN!B5,0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CloseLotRaw</t>
+          <t>Расчётный лот закрытия</t>
         </is>
       </c>
       <c r="B25">
-        <f>TailRecovery_DOWN!B9</f>
+        <f>IFERROR(TailRecovery_DOWN!B9,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CloseLotRounded</t>
+          <t>Округлённый лот закрытия</t>
         </is>
       </c>
       <c r="B26">
-        <f>TailRecovery_DOWN!B10</f>
+        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CloseLotFinal</t>
+          <t>Итоговый лот закрытия</t>
         </is>
       </c>
       <c r="B27">
-        <f>TailRecovery_DOWN!B10</f>
+        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TailLotAfter</t>
+          <t>Остаток хвоста</t>
         </is>
       </c>
       <c r="B28">
-        <f>MAX(B22-B27,0)</f>
+        <f>IF(OR(B22="Хвост не найден",NOT(ISNUMBER(B22))),"Хвост не найден",MAX(B22-B27,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RecoveryFundAfter</t>
+          <t>RecoveryFund после закрытия</t>
         </is>
       </c>
       <c r="B29">
-        <f>TailRecovery_DOWN!B7</f>
+        <f>IFERROR(TailRecovery_DOWN!B7,0)</f>
         <v/>
       </c>
     </row>
@@ -1574,11 +1609,33 @@
         </is>
       </c>
       <c r="B31">
-        <f>TEXTJOIN(CHAR(10),TRUE,B2,"Current Price: "&amp;TEXT(B3,"0.00000"),"Next trigger level: "&amp;TEXT(B4,"0.00000")&amp;" ("&amp;TEXT(B5,"0")&amp;" points)","Open section: "&amp;B6&amp;" + "&amp;B7,"Section level: "&amp;TEXT(B8,"0"),"CycleProfit: "&amp;TEXT(B17,"0.00"),"Reserve += "&amp;TEXT(B18,"0.00")&amp;"; Recovery += "&amp;TEXT(B19,"0.00"),"Tail: "&amp;B21&amp;" "&amp;TEXT(B22,"0.00")&amp;"; Close "&amp;TEXT(B27,"0.00")&amp;"; Remain "&amp;TEXT(B28,"0.00"),"CanCloseBasket: "&amp;BasketSummary!C10,"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
-        <v/>
-      </c>
-    </row>
+        <f>TEXTJOIN(CHAR(10),TRUE,"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ:",B2,"Если цена дойдет до: "&amp;IF(B4="","уровень не рассчитан",TEXT(B4,"0.00000")),"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5),"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7,"Прибыль цикла: "&amp;TEXT(B17,"0.00")&amp;"; Резерв +"&amp;TEXT(B18,"0.00")&amp;"; RecoveryFund +"&amp;TEXT(B19,"0.00"),"Хвост: "&amp;B21&amp;"; закрыть: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;"; останется: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28),"RecoveryFund после: "&amp;TEXT(B29,"0.00"),"Итоговое действие: "&amp;IF(BasketSummary!C10="YES","BASKET_CLOSE",IF(B12&lt;&gt;"YES","WAIT",IF(B14="YES",IF(B15="YES","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION"))),"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <f>B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A32:H45"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!E4,IF(SectionCalculator_UP!B4=2,Scenario_UP!E5,IF(SectionCalculator_UP!B4=3,Scenario_UP!E6,IF(SectionCalculator_UP!B4=4,Scenario_UP!E7,"")))),"")</f>
+        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!E4,IF(SectionCalculator_UP!B4=2,Scenario_UP!E5,IF(SectionCalculator_UP!B4=3,Scenario_UP!E6,IF(SectionCalculator_UP!B4=4,Scenario_UP!E7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IF(OR(B4="",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
+        <f>IF(OR(B4="Уровень не рассчитан",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>SectionCalculator_UP!B14</f>
+        <f>IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>SectionCalculator_UP!B13</f>
+        <f>IF(SectionCalculator_UP!B13="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>SectionCalculator_UP!B32</f>
+        <f>IF(SectionCalculator_UP!B32="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>TailRecovery_UP!B11</f>
+        <f>IF(TailRecovery_UP!B11="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B31">
-        <f>TEXTJOIN(CHAR(10),TRUE,"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ:",B2,"Если цена дойдет до: "&amp;IF(B4="","уровень не рассчитан",TEXT(B4,"0.00000")),"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5),"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7,"Прибыль цикла: "&amp;TEXT(B17,"0.00")&amp;"; Резерв +"&amp;TEXT(B18,"0.00")&amp;"; RecoveryFund +"&amp;TEXT(B19,"0.00"),"Хвост: "&amp;B21&amp;"; закрыть: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;"; останется: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28),"RecoveryFund после: "&amp;TEXT(B29,"0.00"),"Итоговое действие: "&amp;IF(BasketSummary!B10="YES","BASKET_CLOSE",IF(B12&lt;&gt;"YES","WAIT",IF(B14="YES",IF(B15="YES","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION"))),"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B4),TEXT(B4,"0.00000"),B4)&amp;"."&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5)&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Проверки: открыть секцию="&amp;B12&amp;", встречный каскад="&amp;B13&amp;", закрыть секцию="&amp;B14&amp;", закрыть хвост="&amp;B15&amp;"."&amp;CHAR(10)&amp;"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7&amp;"."&amp;CHAR(10)&amp;"Хвост: "&amp;B21&amp;". Лот хвоста: "&amp;IF(ISNUMBER(B22),TEXT(B22,"0.00"),B22)&amp;"."&amp;CHAR(10)&amp;"Рекомендованный лот закрытия: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;". Остаток хвоста: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28)&amp;"."&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B29,"0.00")&amp;". Резерв после: "&amp;TEXT(B18,"0.00")&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Итоговое действие: "&amp;IF(BasketSummary!B10="YES","BASKET_CLOSE",IF(B12="НЕТ","WAIT",IF(B14="ДА",IF(B15="ДА","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION")))&amp;" / "&amp;IF(OR(B12="НЕТ",B13="НЕТ"),"SAFE","NORMAL")</f>
         <v/>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!E9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!E10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!E11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!E12,"")))),"")</f>
+        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!E9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!E10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!E11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!E12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IF(OR(B4="",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
+        <f>IF(OR(B4="Уровень не рассчитан",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
         <v/>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>SectionCalculator_DOWN!B14</f>
+        <f>IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>SectionCalculator_DOWN!B13</f>
+        <f>IF(SectionCalculator_DOWN!B13="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>SectionCalculator_DOWN!B32</f>
+        <f>IF(SectionCalculator_DOWN!B32="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>TailRecovery_DOWN!B11</f>
+        <f>IF(TailRecovery_DOWN!B11="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="B31">
-        <f>TEXTJOIN(CHAR(10),TRUE,"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ:",B2,"Если цена дойдет до: "&amp;IF(B4="","уровень не рассчитан",TEXT(B4,"0.00000")),"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5),"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7,"Прибыль цикла: "&amp;TEXT(B17,"0.00")&amp;"; Резерв +"&amp;TEXT(B18,"0.00")&amp;"; RecoveryFund +"&amp;TEXT(B19,"0.00"),"Хвост: "&amp;B21&amp;"; закрыть: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;"; останется: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28),"RecoveryFund после: "&amp;TEXT(B29,"0.00"),"Итоговое действие: "&amp;IF(BasketSummary!C10="YES","BASKET_CLOSE",IF(B12&lt;&gt;"YES","WAIT",IF(B14="YES",IF(B15="YES","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION"))),"SAFE: "&amp;IF(OR(B12&lt;&gt;"YES",B13&lt;&gt;"YES"),"YES","NO"))</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B4),TEXT(B4,"0.00000"),B4)&amp;"."&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5)&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Проверки: открыть секцию="&amp;B12&amp;", встречный каскад="&amp;B13&amp;", закрыть секцию="&amp;B14&amp;", закрыть хвост="&amp;B15&amp;"."&amp;CHAR(10)&amp;"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7&amp;"."&amp;CHAR(10)&amp;"Хвост: "&amp;B21&amp;". Лот хвоста: "&amp;IF(ISNUMBER(B22),TEXT(B22,"0.00"),B22)&amp;"."&amp;CHAR(10)&amp;"Рекомендованный лот закрытия: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;". Остаток хвоста: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28)&amp;"."&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B29,"0.00")&amp;". Резерв после: "&amp;TEXT(B18,"0.00")&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Итоговое действие: "&amp;IF(BasketSummary!C10="YES","BASKET_CLOSE",IF(B12="НЕТ","WAIT",IF(B14="ДА",IF(B15="ДА","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION")))&amp;" / "&amp;IF(OR(B12="НЕТ",B13="НЕТ"),"SAFE","NORMAL")</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -986,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,256 +1019,256 @@
         </is>
       </c>
       <c r="B3">
-        <f>IFERROR(Scenario_UP!B4,0)</f>
+        <f>IFERROR(CurrentPositions!F2,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Следующий уровень</t>
+          <t>Сценарная цена</t>
         </is>
       </c>
       <c r="B4">
-        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!E4,IF(SectionCalculator_UP!B4=2,Scenario_UP!E5,IF(SectionCalculator_UP!B4=3,Scenario_UP!E6,IF(SectionCalculator_UP!B4=4,Scenario_UP!E7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
+        <f>IFERROR(Scenario_UP!B4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Расстояние до уровня, пунктов</t>
+          <t>Следующий уровень открытия</t>
         </is>
       </c>
       <c r="B5">
-        <f>IF(OR(B4="Уровень не рассчитан",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
+        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!E4,IF(SectionCalculator_UP!B4=2,Scenario_UP!E5,IF(SectionCalculator_UP!B4=3,Scenario_UP!E6,IF(SectionCalculator_UP!B4=4,Scenario_UP!E7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Большая позиция</t>
+          <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
       <c r="B6">
-        <f>IFERROR(IF(TailRecovery_UP!B16&gt;0,IF("UP"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_UP!B16,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IF(OR(B5="Уровень не рассчитан",B4=""),"Расстояние не рассчитано",ROUND(ABS(B5-B4)*10000,0))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Малая защитная позиция</t>
+          <t>Большая позиция</t>
         </is>
       </c>
       <c r="B7">
-        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(IF(TailRecovery_UP!B16&gt;0,IF("UP"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_UP!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Уровень секции</t>
+          <t>Малая защитная позиция</t>
         </is>
       </c>
       <c r="B8">
-        <f>IFERROR(SectionCalculator_UP!B4,0)</f>
+        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Уровень секции</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IFERROR(SectionCalculator_UP!B4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Причина</t>
         </is>
       </c>
-      <c r="B9">
-        <f>IF(SectionCalculator_UP!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция сейчас недоступна: уровень/риск-гейт/хвост")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Проверки риска</t>
-        </is>
+      <c r="B10">
+        <f>IF(SectionCalculator_UP!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция недоступна: уровень/риск-гейт/хвост")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Можно открыть секцию</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")</f>
-        <v/>
+          <t>Проверки риска</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Нет встречного каскада</t>
+          <t>Можно открыть секцию</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(SectionCalculator_UP!B13="YES","ДА","НЕТ")</f>
+        <f>IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Можно закрыть секцию</t>
+          <t>Нет встречного каскада</t>
         </is>
       </c>
       <c r="B14">
-        <f>IF(SectionCalculator_UP!B32="YES","ДА","НЕТ")</f>
+        <f>IF(SectionCalculator_UP!B13="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Можно закрыть секцию</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>IF(SectionCalculator_UP!B32="YES","ДА","НЕТ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Можно закрыть хвост</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B16">
         <f>IF(TailRecovery_UP!B11="YES","ДА","НЕТ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Прибыль цикла</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>IFERROR(SectionCalculator_UP!B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Добавить в резерв</t>
+          <t>Прибыль цикла</t>
         </is>
       </c>
       <c r="B18">
-        <f>IFERROR(TailRecovery_UP!B6,0)</f>
+        <f>IFERROR(SectionCalculator_UP!B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Добавить в резерв</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>IFERROR(TailRecovery_UP!B6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Добавить в RecoveryFund</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B20">
         <f>IFERROR(TailRecovery_UP!B8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Тип хвоста</t>
-        </is>
-      </c>
-      <c r="B21">
-        <f>IF(OR(TailRecovery_UP!B2="",TailRecovery_UP!B2="N/A"),"Хвост не найден",TailRecovery_UP!B2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Лот хвоста</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>IFERROR(IF(TailRecovery_UP!B3&gt;0,TailRecovery_UP!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Убыток хвоста</t>
+          <t>Тип хвоста</t>
         </is>
       </c>
       <c r="B23">
-        <f>IFERROR(TailRecovery_UP!B12,0)</f>
+        <f>IF(OR(TailRecovery_UP!B2="",TailRecovery_UP!B2="N/A"),"Хвост не найден",TailRecovery_UP!B2)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RecoveryFund до закрытия</t>
+          <t>Лот хвоста</t>
         </is>
       </c>
       <c r="B24">
-        <f>IFERROR(TailRecovery_UP!B5,0)</f>
+        <f>IFERROR(IF(TailRecovery_UP!B3&gt;0,TailRecovery_UP!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Расчётный лот закрытия</t>
+          <t>Убыток хвоста</t>
         </is>
       </c>
       <c r="B25">
-        <f>IFERROR(TailRecovery_UP!B9,0)</f>
+        <f>IFERROR(TailRecovery_UP!B12,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Округлённый лот закрытия</t>
+          <t>RecoveryFund до закрытия</t>
         </is>
       </c>
       <c r="B26">
-        <f>IFERROR(TailRecovery_UP!B10,0)</f>
+        <f>IFERROR(TailRecovery_UP!B5,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Итоговый лот закрытия</t>
+          <t>Расчётный лот закрытия</t>
         </is>
       </c>
       <c r="B27">
-        <f>IFERROR(TailRecovery_UP!B10,0)</f>
+        <f>IFERROR(TailRecovery_UP!B9,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Остаток хвоста</t>
+          <t>Округлённый лот закрытия</t>
         </is>
       </c>
       <c r="B28">
-        <f>IF(OR(B22="Хвост не найден",NOT(ISNUMBER(B22))),"Хвост не найден",MAX(B22-B27,0))</f>
+        <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RecoveryFund после закрытия</t>
+          <t>Итоговый лот закрытия</t>
         </is>
       </c>
       <c r="B29">
-        <f>IFERROR(TailRecovery_UP!B7,0)</f>
+        <f>IFERROR(TailRecovery_UP!B10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Остаток хвоста</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>IF(OR(B24="Хвост не найден",NOT(ISNUMBER(B24))),"Хвост не найден",MAX(B24-B29,0))</f>
         <v/>
       </c>
     </row>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="B31">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B4),TEXT(B4,"0.00000"),B4)&amp;"."&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5)&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Проверки: открыть секцию="&amp;B12&amp;", встречный каскад="&amp;B13&amp;", закрыть секцию="&amp;B14&amp;", закрыть хвост="&amp;B15&amp;"."&amp;CHAR(10)&amp;"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7&amp;"."&amp;CHAR(10)&amp;"Хвост: "&amp;B21&amp;". Лот хвоста: "&amp;IF(ISNUMBER(B22),TEXT(B22,"0.00"),B22)&amp;"."&amp;CHAR(10)&amp;"Рекомендованный лот закрытия: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;". Остаток хвоста: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28)&amp;"."&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B29,"0.00")&amp;". Резерв после: "&amp;TEXT(B18,"0.00")&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Итоговое действие: "&amp;IF(BasketSummary!B10="YES","BASKET_CLOSE",IF(B12="НЕТ","WAIT",IF(B14="ДА",IF(B15="ДА","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION")))&amp;" / "&amp;IF(OR(B12="НЕТ",B13="НЕТ"),"SAFE","NORMAL")</f>
+        <f>IF(B13="ДА","ОТКРЫТЬ СЕКЦИЮ",IF(B15="ДА",IF(B16="ДА","ЗАКРЫТЬ СЕКЦИЮ + ЗАКРЫТЬ ХВОСТ","ЗАКРЫТЬ СЕКЦИЮ"),"ЖДАТЬ / НИЧЕГО НЕ ДЕЛАТЬ"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <f>B31</f>
+        <f>B46</f>
         <v/>
       </c>
     </row>
@@ -1302,6 +1302,12 @@
     <row r="43"/>
     <row r="44"/>
     <row r="45"/>
+    <row r="46">
+      <c r="B46">
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A32:H45"/>
@@ -1316,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,256 +1355,256 @@
         </is>
       </c>
       <c r="B3">
-        <f>IFERROR(Scenario_DOWN!B4,0)</f>
+        <f>IFERROR(CurrentPositions!F2,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Следующий уровень</t>
+          <t>Сценарная цена</t>
         </is>
       </c>
       <c r="B4">
-        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!E9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!E10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!E11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!E12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
+        <f>IFERROR(Scenario_DOWN!B4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Расстояние до уровня, пунктов</t>
+          <t>Следующий уровень открытия</t>
         </is>
       </c>
       <c r="B5">
-        <f>IF(OR(B4="Уровень не рассчитан",B3=""),"Уровень не рассчитан",ROUND(ABS(B4-B3)*10000,0))</f>
+        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!E9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!E10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!E11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!E12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Большая позиция</t>
+          <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
       <c r="B6">
-        <f>IFERROR(IF(TailRecovery_DOWN!B16&gt;0,IF("DOWN"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_DOWN!B16,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IF(OR(B5="Уровень не рассчитан",B4=""),"Расстояние не рассчитано",ROUND(ABS(B5-B4)*10000,0))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Малая защитная позиция</t>
+          <t>Большая позиция</t>
         </is>
       </c>
       <c r="B7">
-        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B16&gt;0,IF("DOWN"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_DOWN!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Уровень секции</t>
+          <t>Малая защитная позиция</t>
         </is>
       </c>
       <c r="B8">
-        <f>IFERROR(SectionCalculator_DOWN!B4,0)</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Уровень секции</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IFERROR(SectionCalculator_DOWN!B4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Причина</t>
         </is>
       </c>
-      <c r="B9">
-        <f>IF(SectionCalculator_DOWN!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция сейчас недоступна: уровень/риск-гейт/хвост")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Проверки риска</t>
-        </is>
+      <c r="B10">
+        <f>IF(SectionCalculator_DOWN!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция недоступна: уровень/риск-гейт/хвост")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Можно открыть секцию</t>
-        </is>
-      </c>
-      <c r="B12">
-        <f>IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")</f>
-        <v/>
+          <t>Проверки риска</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Нет встречного каскада</t>
+          <t>Можно открыть секцию</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(SectionCalculator_DOWN!B13="YES","ДА","НЕТ")</f>
+        <f>IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Можно закрыть секцию</t>
+          <t>Нет встречного каскада</t>
         </is>
       </c>
       <c r="B14">
-        <f>IF(SectionCalculator_DOWN!B32="YES","ДА","НЕТ")</f>
+        <f>IF(SectionCalculator_DOWN!B13="YES","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Можно закрыть секцию</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>IF(SectionCalculator_DOWN!B32="YES","ДА","НЕТ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Можно закрыть хвост</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="B16">
         <f>IF(TailRecovery_DOWN!B11="YES","ДА","НЕТ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Прибыль цикла</t>
-        </is>
-      </c>
-      <c r="B17">
-        <f>IFERROR(SectionCalculator_DOWN!B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Добавить в резерв</t>
+          <t>Прибыль цикла</t>
         </is>
       </c>
       <c r="B18">
-        <f>IFERROR(TailRecovery_DOWN!B6,0)</f>
+        <f>IFERROR(SectionCalculator_DOWN!B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Добавить в резерв</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>IFERROR(TailRecovery_DOWN!B6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Добавить в RecoveryFund</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B20">
         <f>IFERROR(TailRecovery_DOWN!B8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Тип хвоста</t>
-        </is>
-      </c>
-      <c r="B21">
-        <f>IF(OR(TailRecovery_DOWN!B2="",TailRecovery_DOWN!B2="N/A"),"Хвост не найден",TailRecovery_DOWN!B2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Лот хвоста</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>IFERROR(IF(TailRecovery_DOWN!B3&gt;0,TailRecovery_DOWN!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Убыток хвоста</t>
+          <t>Тип хвоста</t>
         </is>
       </c>
       <c r="B23">
-        <f>IFERROR(TailRecovery_DOWN!B12,0)</f>
+        <f>IF(OR(TailRecovery_DOWN!B2="",TailRecovery_DOWN!B2="N/A"),"Хвост не найден",TailRecovery_DOWN!B2)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RecoveryFund до закрытия</t>
+          <t>Лот хвоста</t>
         </is>
       </c>
       <c r="B24">
-        <f>IFERROR(TailRecovery_DOWN!B5,0)</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B3&gt;0,TailRecovery_DOWN!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Расчётный лот закрытия</t>
+          <t>Убыток хвоста</t>
         </is>
       </c>
       <c r="B25">
-        <f>IFERROR(TailRecovery_DOWN!B9,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B12,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Округлённый лот закрытия</t>
+          <t>RecoveryFund до закрытия</t>
         </is>
       </c>
       <c r="B26">
-        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B5,0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Итоговый лот закрытия</t>
+          <t>Расчётный лот закрытия</t>
         </is>
       </c>
       <c r="B27">
-        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B9,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Остаток хвоста</t>
+          <t>Округлённый лот закрытия</t>
         </is>
       </c>
       <c r="B28">
-        <f>IF(OR(B22="Хвост не найден",NOT(ISNUMBER(B22))),"Хвост не найден",MAX(B22-B27,0))</f>
+        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RecoveryFund после закрытия</t>
+          <t>Итоговый лот закрытия</t>
         </is>
       </c>
       <c r="B29">
-        <f>IFERROR(TailRecovery_DOWN!B7,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Остаток хвоста</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>IF(OR(B24="Хвост не найден",NOT(ISNUMBER(B24))),"Хвост не найден",MAX(B24-B29,0))</f>
         <v/>
       </c>
     </row>
@@ -1609,13 +1615,13 @@
         </is>
       </c>
       <c r="B31">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B4),TEXT(B4,"0.00000"),B4)&amp;"."&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0")&amp;" пунктов",B5)&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Проверки: открыть секцию="&amp;B12&amp;", встречный каскад="&amp;B13&amp;", закрыть секцию="&amp;B14&amp;", закрыть хвост="&amp;B15&amp;"."&amp;CHAR(10)&amp;"Рекомендация по открытию: "&amp;B6&amp;" и "&amp;B7&amp;"."&amp;CHAR(10)&amp;"Хвост: "&amp;B21&amp;". Лот хвоста: "&amp;IF(ISNUMBER(B22),TEXT(B22,"0.00"),B22)&amp;"."&amp;CHAR(10)&amp;"Рекомендованный лот закрытия: "&amp;IF(ISNUMBER(B27),TEXT(B27,"0.00"),"0.00")&amp;". Остаток хвоста: "&amp;IF(ISNUMBER(B28),TEXT(B28,"0.00"),B28)&amp;"."&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B29,"0.00")&amp;". Резерв после: "&amp;TEXT(B18,"0.00")&amp;"."&amp;CHAR(10)&amp;CHAR(10)&amp;"Итоговое действие: "&amp;IF(BasketSummary!C10="YES","BASKET_CLOSE",IF(B12="НЕТ","WAIT",IF(B14="ДА",IF(B15="ДА","CLOSE_SECTION+CLOSE_TAIL","CLOSE_SECTION"),"OPEN_SECTION")))&amp;" / "&amp;IF(OR(B12="НЕТ",B13="НЕТ"),"SAFE","NORMAL")</f>
+        <f>IF(B13="ДА","ОТКРЫТЬ СЕКЦИЮ",IF(B15="ДА",IF(B16="ДА","ЗАКРЫТЬ СЕКЦИЮ + ЗАКРЫТЬ ХВОСТ","ЗАКРЫТЬ СЕКЦИЮ"),"ЖДАТЬ / НИЧЕГО НЕ ДЕЛАТЬ"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <f>B31</f>
+        <f>B46</f>
         <v/>
       </c>
     </row>
@@ -1632,6 +1638,12 @@
     <row r="43"/>
     <row r="44"/>
     <row r="45"/>
+    <row r="46">
+      <c r="B46">
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A32:H45"/>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -785,11 +785,11 @@
         </is>
       </c>
       <c r="B5">
-        <f>IF(OR(SectionCalculator_UP!B14="NO",SectionCalculator_UP!B12="YES"),"OK","ERROR")</f>
+        <f>IF(SectionCalculator_UP!B12="YES","OK",IF(SectionCalculator_UP!B14="NO","BLOCKED","ERROR"))</f>
         <v/>
       </c>
       <c r="C5">
-        <f>IF(OR(SectionCalculator_DOWN!B14="NO",SectionCalculator_DOWN!B12="YES"),"OK","ERROR")</f>
+        <f>IF(SectionCalculator_DOWN!B12="YES","OK",IF(SectionCalculator_DOWN!B14="NO","BLOCKED","ERROR"))</f>
         <v/>
       </c>
     </row>
@@ -800,11 +800,11 @@
         </is>
       </c>
       <c r="B6">
-        <f>IF(SectionCalculator_UP!B13="YES","OK","ERROR")</f>
+        <f>IF(SectionCalculator_UP!B13="YES","OK","BLOCKED")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>IF(SectionCalculator_DOWN!B13="YES","OK","ERROR")</f>
+        <f>IF(SectionCalculator_DOWN!B13="YES","OK","BLOCKED")</f>
         <v/>
       </c>
     </row>
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="D2">
-        <f>BasketSummary!B13</f>
+        <f>IF(BasketSummary!B13="WAIT","ЖДАТЬ",IF(BasketSummary!B13="SAFE","SAFE",IF(BasketSummary!B13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(AND(TailRecovery_UP!B10&gt;0,TailRecovery_UP!B10&lt;TailRecovery_UP!B3),"ЗАКРЫТЬ ХВОСТ ЧАСТИЧНО","ЗАКРЫТЬ СЕКЦИЮ"))))</f>
         <v/>
       </c>
       <c r="E2">
-        <f>TailRecovery_UP!B3</f>
+        <f>IFERROR(TailRecovery_UP!B3,0)</f>
         <v/>
       </c>
       <c r="F2">
-        <f>TailRecovery_UP!B10</f>
+        <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
       <c r="G2">
-        <f>MAX(E2-F2,0)</f>
+        <f>IF(OR(NOT(ISNUMBER(E2)),NOT(ISNUMBER(F2))),"Хвост не найден",MAX(E2-F2,0))</f>
         <v/>
       </c>
       <c r="H2">
-        <f>TailRecovery_UP!B5</f>
+        <f>IFERROR(TailRecovery_UP!B5,0)</f>
         <v/>
       </c>
       <c r="I2">
-        <f>TailRecovery_UP!B7</f>
+        <f>IFERROR(TailRecovery_UP!B7,0)</f>
         <v/>
       </c>
       <c r="J2">
-        <f>SectionCalculator_UP!B35</f>
+        <f>IFERROR(SectionCalculator_UP!B35,0)</f>
         <v/>
       </c>
       <c r="K2">
@@ -943,31 +943,31 @@
         </is>
       </c>
       <c r="D3">
-        <f>BasketSummary!C13</f>
+        <f>IF(BasketSummary!C13="WAIT","ЖДАТЬ",IF(BasketSummary!C13="SAFE","SAFE",IF(BasketSummary!C13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(AND(TailRecovery_DOWN!B10&gt;0,TailRecovery_DOWN!B10&lt;TailRecovery_DOWN!B3),"ЗАКРЫТЬ ХВОСТ ЧАСТИЧНО","ЗАКРЫТЬ СЕКЦИЮ"))))</f>
         <v/>
       </c>
       <c r="E3">
-        <f>TailRecovery_DOWN!B3</f>
+        <f>IFERROR(TailRecovery_DOWN!B3,0)</f>
         <v/>
       </c>
       <c r="F3">
-        <f>TailRecovery_DOWN!B10</f>
+        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
       <c r="G3">
-        <f>MAX(E3-F3,0)</f>
+        <f>IF(OR(NOT(ISNUMBER(E3)),NOT(ISNUMBER(F3))),"Хвост не найден",MAX(E3-F3,0))</f>
         <v/>
       </c>
       <c r="H3">
-        <f>TailRecovery_DOWN!B5</f>
+        <f>IFERROR(TailRecovery_DOWN!B5,0)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>TailRecovery_DOWN!B7</f>
+        <f>IFERROR(TailRecovery_DOWN!B7,0)</f>
         <v/>
       </c>
       <c r="J3">
-        <f>SectionCalculator_DOWN!B35</f>
+        <f>IFERROR(SectionCalculator_DOWN!B35,0)</f>
         <v/>
       </c>
       <c r="K3">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E1">
-        <f>IFERROR(SUMPRODUCT((B7:B206="BUY")*E7:E206*D7:D206)/SUMIFS(D7:D206,B7:B206,"BUY"),0)</f>
+        <f>IFERROR(SUMPRODUCT((B7:B206="BUY")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"BUY")),0)</f>
         <v/>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="E2">
-        <f>IFERROR(SUMPRODUCT((B7:B206="SELL")*E7:E206*D7:D206)/SUMIFS(D7:D206,B7:B206,"SELL"),0)</f>
+        <f>IFERROR(SUMPRODUCT((B7:B206="SELL")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"SELL")),0)</f>
         <v/>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="E4">
-        <f>E3+1*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="E5">
-        <f>E3+2*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <f>E3+3*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+3*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="E7">
-        <f>E3+4*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F7">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="E9">
-        <f>E3-1*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F9">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="E10">
-        <f>E3-2*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F10">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="E11">
-        <f>E3-3*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-3*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F11">
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="E12">
-        <f>E3-4*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F12">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="E1">
-        <f>IFERROR(SUMPRODUCT((B7:B206="BUY")*E7:E206*D7:D206)/SUMIFS(D7:D206,B7:B206,"BUY"),0)</f>
+        <f>IFERROR(SUMPRODUCT((B7:B206="BUY")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"BUY")),0)</f>
         <v/>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="E2">
-        <f>IFERROR(SUMPRODUCT((B7:B206="SELL")*E7:E206*D7:D206)/SUMIFS(D7:D206,B7:B206,"SELL"),0)</f>
+        <f>IFERROR(SUMPRODUCT((B7:B206="SELL")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"SELL")),0)</f>
         <v/>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="E4">
-        <f>E3+1*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="E5">
-        <f>E3+2*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="E6" s="1">
-        <f>E3+3*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+3*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="E7">
-        <f>E3+4*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3+4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F7">
@@ -10761,7 +10761,7 @@
         </is>
       </c>
       <c r="E9">
-        <f>E3-1*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F9">
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="E10">
-        <f>E3-2*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F10">
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="E11">
-        <f>E3-3*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-3*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F11">
@@ -10890,7 +10890,7 @@
         </is>
       </c>
       <c r="E12">
-        <f>E3-4*Settings!$B$5*Settings!$B$3</f>
+        <f>IF(E3=0,"Уровень не рассчитан",E3-4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
       <c r="F12">
@@ -19216,7 +19216,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>FLOOR(B3*B5,Settings!$B$7)</f>
+        <f>IF(B3&lt;=0,0,FLOOR(B3*B5,Settings!$B$7))</f>
         <v/>
       </c>
     </row>
@@ -19227,7 +19227,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>FLOOR(B3*B6,Settings!$B$7)</f>
+        <f>IF(B3&lt;=0,0,FLOOR(B3*B6,Settings!$B$7))</f>
         <v/>
       </c>
     </row>
@@ -19293,7 +19293,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO")</f>
+        <f>IF(B3&lt;=0,"NO",IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO"))</f>
         <v/>
       </c>
     </row>
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>FLOOR(B3*B5,Settings!$B$7)</f>
+        <f>IF(B3&lt;=0,0,FLOOR(B3*B5,Settings!$B$7))</f>
         <v/>
       </c>
     </row>
@@ -19864,7 +19864,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>FLOOR(B3*B6,Settings!$B$7)</f>
+        <f>IF(B3&lt;=0,0,FLOOR(B3*B6,Settings!$B$7))</f>
         <v/>
       </c>
     </row>
@@ -19930,7 +19930,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO")</f>
+        <f>IF(B3&lt;=0,"NO",IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO"))</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Log" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="ScenarioText_UP" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="ScenarioText_DOWN" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="FormulaDependencyMap" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1041,7 +1042,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!E4,IF(SectionCalculator_UP!B4=2,Scenario_UP!E5,IF(SectionCalculator_UP!B4=3,Scenario_UP!E6,IF(SectionCalculator_UP!B4=4,Scenario_UP!E7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
+        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!N4,IF(SectionCalculator_UP!B4=2,Scenario_UP!N5,IF(SectionCalculator_UP!B4=3,Scenario_UP!N6,IF(SectionCalculator_UP!B4=4,Scenario_UP!N7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
@@ -1377,7 +1378,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!E9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!E10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!E11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!E12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
+        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!N9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!N10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!N11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!N12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
@@ -1652,6 +1653,105 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DependsOn</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>UsedBy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B4</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>Scenario_UP!B2+Scenario_UP!B3*Settings!B3</f>
+        <v/>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B2, Scenario_UP!B3, Settings!B3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B12, ScenarioText_UP!B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Scenario_DOWN!B4</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Scenario_DOWN!B2-Scenario_DOWN!B3*Settings!B3</f>
+        <v/>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Scenario_DOWN!B2, Scenario_DOWN!B3, Settings!B3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SectionCalculator_DOWN!B12, ScenarioText_DOWN!B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TailRecovery_UP!B10</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>IF(B6="YES",MIN(B9,B4),0)</f>
+        <v/>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TailRecovery_UP!B9, TailRecovery_UP!B4, TailRecovery_UP!B6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BasketSummary!B7, Log!F2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1884,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:N225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,12 +1998,12 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>AverageBuyPrice</t>
         </is>
       </c>
-      <c r="E1">
+      <c r="N1">
         <f>IFERROR(SUMPRODUCT((B7:B206="BUY")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"BUY")),0)</f>
         <v/>
       </c>
@@ -1918,12 +2018,12 @@
         <f>CurrentPositions!F2</f>
         <v/>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>AverageSellPrice</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="N2">
         <f>IFERROR(SUMPRODUCT((B7:B206="SELL")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"SELL")),0)</f>
         <v/>
       </c>
@@ -1937,13 +2037,13 @@
       <c r="B3" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Center</t>
         </is>
       </c>
-      <c r="E3">
-        <f>(E1+E2)/2</f>
+      <c r="N3">
+        <f>(N1+N2)/2</f>
         <v/>
       </c>
     </row>
@@ -1957,24 +2057,24 @@
         <f>B2+B3*Settings!$B$3</f>
         <v/>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>UpperLevel1</t>
         </is>
       </c>
-      <c r="E4">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+1*Settings!$B$5*Settings!$B$3)</f>
+      <c r="N4">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>UpperLevel2</t>
         </is>
       </c>
-      <c r="E5">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+2*Settings!$B$5*Settings!$B$3)</f>
+      <c r="N5">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -1996,37 +2096,47 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>OpenPrice</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>ScenarioPrice</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>ScenarioPointsPnL</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>ScenarioMoneyPnL</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>IsTail</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>SectionID</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>UpperLevel3</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+3*Settings!$B$5*Settings!$B$3)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>ScenarioPrice</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>ScenarioPointsPnL</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>ScenarioMoneyPnL</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>IsTail</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>SectionID</t>
-        </is>
+      <c r="N6">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+3*Settings!$B$5*Settings!$B$3)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2042,13 +2152,12 @@
         <f>CurrentPositions!C2</f>
         <v/>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UpperLevel4</t>
-        </is>
+      <c r="D7">
+        <f>CurrentPositions!D2</f>
+        <v/>
       </c>
       <c r="E7">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+4*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E2</f>
         <v/>
       </c>
       <c r="F7">
@@ -2069,6 +2178,15 @@
       </c>
       <c r="J7">
         <f>CurrentPositions!J2</f>
+        <v/>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UpperLevel4</t>
+        </is>
+      </c>
+      <c r="N7">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -2127,13 +2245,12 @@
         <f>CurrentPositions!C4</f>
         <v/>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LowerLevel1</t>
-        </is>
+      <c r="D9">
+        <f>CurrentPositions!D4</f>
+        <v/>
       </c>
       <c r="E9">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-1*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E4</f>
         <v/>
       </c>
       <c r="F9">
@@ -2154,6 +2271,15 @@
       </c>
       <c r="J9">
         <f>CurrentPositions!J4</f>
+        <v/>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>LowerLevel1</t>
+        </is>
+      </c>
+      <c r="N9">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -2170,13 +2296,12 @@
         <f>CurrentPositions!C5</f>
         <v/>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LowerLevel2</t>
-        </is>
+      <c r="D10">
+        <f>CurrentPositions!D5</f>
+        <v/>
       </c>
       <c r="E10">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-2*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E5</f>
         <v/>
       </c>
       <c r="F10">
@@ -2197,6 +2322,15 @@
       </c>
       <c r="J10">
         <f>CurrentPositions!J5</f>
+        <v/>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>LowerLevel2</t>
+        </is>
+      </c>
+      <c r="N10">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -2213,13 +2347,12 @@
         <f>CurrentPositions!C6</f>
         <v/>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LowerLevel3</t>
-        </is>
+      <c r="D11">
+        <f>CurrentPositions!D6</f>
+        <v/>
       </c>
       <c r="E11">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-3*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E6</f>
         <v/>
       </c>
       <c r="F11">
@@ -2240,6 +2373,15 @@
       </c>
       <c r="J11">
         <f>CurrentPositions!J6</f>
+        <v/>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>LowerLevel3</t>
+        </is>
+      </c>
+      <c r="N11">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-3*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -2256,13 +2398,12 @@
         <f>CurrentPositions!C7</f>
         <v/>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LowerLevel4</t>
-        </is>
+      <c r="D12">
+        <f>CurrentPositions!D7</f>
+        <v/>
       </c>
       <c r="E12">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-4*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E7</f>
         <v/>
       </c>
       <c r="F12">
@@ -2283,6 +2424,15 @@
       </c>
       <c r="J12">
         <f>CurrentPositions!J7</f>
+        <v/>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>LowerLevel4</t>
+        </is>
+      </c>
+      <c r="N12">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10512,7 +10662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:N225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10526,12 +10676,12 @@
           <t>Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>AverageBuyPrice</t>
         </is>
       </c>
-      <c r="E1">
+      <c r="N1">
         <f>IFERROR(SUMPRODUCT((B7:B206="BUY")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"BUY")),0)</f>
         <v/>
       </c>
@@ -10546,12 +10696,12 @@
         <f>CurrentPositions!F2</f>
         <v/>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>AverageSellPrice</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="N2">
         <f>IFERROR(SUMPRODUCT((B7:B206="SELL")*E7:E206*D7:D206)/MAX(0.0000001,SUMIFS(D7:D206,B7:B206,"SELL")),0)</f>
         <v/>
       </c>
@@ -10565,13 +10715,13 @@
       <c r="B3" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Center</t>
         </is>
       </c>
-      <c r="E3">
-        <f>(E1+E2)/2</f>
+      <c r="N3">
+        <f>(N1+N2)/2</f>
         <v/>
       </c>
     </row>
@@ -10585,24 +10735,24 @@
         <f>B2-B3*Settings!$B$3</f>
         <v/>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>UpperLevel1</t>
         </is>
       </c>
-      <c r="E4">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+1*Settings!$B$5*Settings!$B$3)</f>
+      <c r="N4">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>UpperLevel2</t>
         </is>
       </c>
-      <c r="E5">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+2*Settings!$B$5*Settings!$B$3)</f>
+      <c r="N5">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10624,37 +10774,47 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>OpenPrice</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>ScenarioPrice</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>ScenarioPointsPnL</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>ScenarioMoneyPnL</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>IsTail</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>SectionID</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>UpperLevel3</t>
         </is>
       </c>
-      <c r="E6" s="1">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+3*Settings!$B$5*Settings!$B$3)</f>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>ScenarioPrice</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>ScenarioPointsPnL</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>ScenarioMoneyPnL</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>IsTail</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>SectionID</t>
-        </is>
+      <c r="N6">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+3*Settings!$B$5*Settings!$B$3)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -10670,13 +10830,12 @@
         <f>CurrentPositions!C2</f>
         <v/>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UpperLevel4</t>
-        </is>
+      <c r="D7">
+        <f>CurrentPositions!D2</f>
+        <v/>
       </c>
       <c r="E7">
-        <f>IF(E3=0,"Уровень не рассчитан",E3+4*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E2</f>
         <v/>
       </c>
       <c r="F7">
@@ -10697,6 +10856,15 @@
       </c>
       <c r="J7">
         <f>CurrentPositions!J2</f>
+        <v/>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>UpperLevel4</t>
+        </is>
+      </c>
+      <c r="N7">
+        <f>IF(N3=0,"Уровень не рассчитан",N3+4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10755,13 +10923,12 @@
         <f>CurrentPositions!C4</f>
         <v/>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LowerLevel1</t>
-        </is>
+      <c r="D9">
+        <f>CurrentPositions!D4</f>
+        <v/>
       </c>
       <c r="E9">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-1*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E4</f>
         <v/>
       </c>
       <c r="F9">
@@ -10782,6 +10949,15 @@
       </c>
       <c r="J9">
         <f>CurrentPositions!J4</f>
+        <v/>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>LowerLevel1</t>
+        </is>
+      </c>
+      <c r="N9">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-1*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10798,13 +10974,12 @@
         <f>CurrentPositions!C5</f>
         <v/>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LowerLevel2</t>
-        </is>
+      <c r="D10">
+        <f>CurrentPositions!D5</f>
+        <v/>
       </c>
       <c r="E10">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-2*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E5</f>
         <v/>
       </c>
       <c r="F10">
@@ -10825,6 +11000,15 @@
       </c>
       <c r="J10">
         <f>CurrentPositions!J5</f>
+        <v/>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>LowerLevel2</t>
+        </is>
+      </c>
+      <c r="N10">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-2*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10841,13 +11025,12 @@
         <f>CurrentPositions!C6</f>
         <v/>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LowerLevel3</t>
-        </is>
+      <c r="D11">
+        <f>CurrentPositions!D6</f>
+        <v/>
       </c>
       <c r="E11">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-3*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E6</f>
         <v/>
       </c>
       <c r="F11">
@@ -10868,6 +11051,15 @@
       </c>
       <c r="J11">
         <f>CurrentPositions!J6</f>
+        <v/>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>LowerLevel3</t>
+        </is>
+      </c>
+      <c r="N11">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-3*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -10884,13 +11076,12 @@
         <f>CurrentPositions!C7</f>
         <v/>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LowerLevel4</t>
-        </is>
+      <c r="D12">
+        <f>CurrentPositions!D7</f>
+        <v/>
       </c>
       <c r="E12">
-        <f>IF(E3=0,"Уровень не рассчитан",E3-4*Settings!$B$5*Settings!$B$3)</f>
+        <f>CurrentPositions!E7</f>
         <v/>
       </c>
       <c r="F12">
@@ -10911,6 +11102,15 @@
       </c>
       <c r="J12">
         <f>CurrentPositions!J7</f>
+        <v/>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>LowerLevel4</t>
+        </is>
+      </c>
+      <c r="N12">
+        <f>IF(N3=0,"Уровень не рассчитан",N3-4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
     </row>
@@ -19271,7 +19471,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>IF(Scenario_UP!B4&gt;=IF(B4=1,Scenario_UP!E4,IF(B4=2,Scenario_UP!E5,IF(B4=3,Scenario_UP!E6,Scenario_UP!E7))),"YES","NO")</f>
+        <f>IF(Scenario_UP!B4&gt;=IF(B4=1,Scenario_UP!N4,IF(B4=2,Scenario_UP!N5,IF(B4=3,Scenario_UP!N6,Scenario_UP!N7))),"YES","NO")</f>
         <v/>
       </c>
     </row>
@@ -19908,7 +20108,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>IF(Scenario_DOWN!B4&lt;=IF(B4=1,Scenario_DOWN!E9,IF(B4=2,Scenario_DOWN!E10,IF(B4=3,Scenario_DOWN!E11,Scenario_DOWN!E12))),"YES","NO")</f>
+        <f>IF(Scenario_DOWN!B4&lt;=IF(B4=1,Scenario_DOWN!N9,IF(B4=2,Scenario_DOWN!N10,IF(B4=3,Scenario_DOWN!N11,Scenario_DOWN!N12))),"YES","NO")</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -29,7 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -72,9 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -714,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +811,81 @@
       </c>
       <c r="C6">
         <f>IF(SectionCalculator_DOWN!B13="YES","OK","BLOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tail exists when loss exists</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>IF(OR(Scenario_UP!B221&gt;=0,Scenario_UP!B222&lt;&gt;"N/A"),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>IF(OR(Scenario_DOWN!B221&gt;=0,Scenario_DOWN!B222&lt;&gt;"N/A"),"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ScenarioText action equals BasketSummary action</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>IF(OR(AND(BasketSummary!B13="BASKET_CLOSE",ScenarioText_UP!B31="ЗАКРЫТЬ ВСЮ КОРЗИНУ"),BasketSummary!B13&lt;&gt;"BASKET_CLOSE"),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IF(OR(AND(BasketSummary!C13="BASKET_CLOSE",ScenarioText_DOWN!B31="ЗАКРЫТЬ ВСЮ КОРЗИНУ"),BasketSummary!C13&lt;&gt;"BASKET_CLOSE"),"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NextTriggerLevel is numeric</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IF(OR(ISNUMBER(ScenarioText_UP!B5),ScenarioText_UP!B5="Уровень не рассчитан"),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>IF(OR(ISNUMBER(ScenarioText_DOWN!B5),ScenarioText_DOWN!B5="Уровень не рассчитан"),"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DistancePoints is numeric</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>IF(OR(ISNUMBER(ScenarioText_UP!B6),ScenarioText_UP!B6="Расстояние не рассчитано"),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>IF(OR(ISNUMBER(ScenarioText_DOWN!B6),ScenarioText_DOWN!B6="Расстояние не рассчитано"),"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HumanReadableAction not empty</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>IF(AND(ScenarioText_UP!B31&lt;&gt;"",ISNUMBER(ScenarioText_UP!B4)),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>IF(AND(ScenarioText_DOWN!B31&lt;&gt;"",ISNUMBER(ScenarioText_DOWN!B4)),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
@@ -1019,7 +1099,7 @@
           <t>Текущая цена</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <f>IFERROR(CurrentPositions!F2,0)</f>
         <v/>
       </c>
@@ -1030,7 +1110,7 @@
           <t>Сценарная цена</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <f>IFERROR(Scenario_UP!B4,0)</f>
         <v/>
       </c>
@@ -1041,7 +1121,7 @@
           <t>Следующий уровень открытия</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!N4,IF(SectionCalculator_UP!B4=2,Scenario_UP!N5,IF(SectionCalculator_UP!B4=3,Scenario_UP!N6,IF(SectionCalculator_UP!B4=4,Scenario_UP!N7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
@@ -1052,7 +1132,7 @@
           <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <f>IF(OR(B5="Уровень не рассчитан",B4=""),"Расстояние не рассчитано",ROUND(ABS(B5-B4)*10000,0))</f>
         <v/>
       </c>
@@ -1063,7 +1143,7 @@
           <t>Большая позиция</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <f>IFERROR(IF(TailRecovery_UP!B16&gt;0,IF("UP"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_UP!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
@@ -1074,7 +1154,7 @@
           <t>Малая защитная позиция</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
@@ -1202,7 +1282,7 @@
           <t>Лот хвоста</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <f>IFERROR(IF(TailRecovery_UP!B3&gt;0,TailRecovery_UP!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
@@ -1235,7 +1315,7 @@
           <t>Расчётный лот закрытия</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B27" s="4">
         <f>IFERROR(TailRecovery_UP!B9,0)</f>
         <v/>
       </c>
@@ -1246,7 +1326,7 @@
           <t>Округлённый лот закрытия</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
@@ -1257,7 +1337,7 @@
           <t>Итоговый лот закрытия</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B29" s="4">
         <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
@@ -1268,7 +1348,7 @@
           <t>Остаток хвоста</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B30" s="4">
         <f>IF(OR(B24="Хвост не найден",NOT(ISNUMBER(B24))),"Хвост не найден",MAX(B24-B29,0))</f>
         <v/>
       </c>
@@ -1280,18 +1360,20 @@
         </is>
       </c>
       <c r="B31">
-        <f>IF(B13="ДА","ОТКРЫТЬ СЕКЦИЮ",IF(B15="ДА",IF(B16="ДА","ЗАКРЫТЬ СЕКЦИЮ + ЗАКРЫТЬ ХВОСТ","ЗАКРЫТЬ СЕКЦИЮ"),"ЖДАТЬ / НИЧЕГО НЕ ДЕЛАТЬ"))</f>
+        <f>IF(BasketSummary!B13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(BasketSummary!B13="CLOSE_SECTION+CLOSE_TAIL","ЗАКРЫТЬ СЕКЦИЮ + ЗАКРЫТЬ ХВОСТ",IF(BasketSummary!B13="CLOSE_SECTION","ЗАКРЫТЬ СЕКЦИЮ",IF(BasketSummary!B13="OPEN_SECTION","ОТКРЫТЬ СЕКЦИЮ",IF(BasketSummary!B13="SAFE","SAFE",IF(BasketSummary!B13="WAIT","ЖДАТЬ","BLOCKED"))))))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="5">
         <f>B46</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
-    <row r="34"/>
+    <row r="34">
+      <c r="B34" s="4" t="n"/>
+    </row>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
@@ -1305,7 +1387,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1437,7 @@
           <t>Текущая цена</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <f>IFERROR(CurrentPositions!F2,0)</f>
         <v/>
       </c>
@@ -1366,7 +1448,7 @@
           <t>Сценарная цена</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <f>IFERROR(Scenario_DOWN!B4,0)</f>
         <v/>
       </c>
@@ -1377,7 +1459,7 @@
           <t>Следующий уровень открытия</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!N9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!N10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!N11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!N12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
@@ -1388,7 +1470,7 @@
           <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <f>IF(OR(B5="Уровень не рассчитан",B4=""),"Расстояние не рассчитано",ROUND(ABS(B5-B4)*10000,0))</f>
         <v/>
       </c>
@@ -1399,7 +1481,7 @@
           <t>Большая позиция</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <f>IFERROR(IF(TailRecovery_DOWN!B16&gt;0,IF("DOWN"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_DOWN!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
@@ -1410,7 +1492,7 @@
           <t>Малая защитная позиция</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
@@ -1538,7 +1620,7 @@
           <t>Лот хвоста</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <f>IFERROR(IF(TailRecovery_DOWN!B3&gt;0,TailRecovery_DOWN!B3,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
@@ -1571,7 +1653,7 @@
           <t>Расчётный лот закрытия</t>
         </is>
       </c>
-      <c r="B27">
+      <c r="B27" s="4">
         <f>IFERROR(TailRecovery_DOWN!B9,0)</f>
         <v/>
       </c>
@@ -1582,7 +1664,7 @@
           <t>Округлённый лот закрытия</t>
         </is>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
@@ -1593,7 +1675,7 @@
           <t>Итоговый лот закрытия</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B29" s="4">
         <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
@@ -1604,7 +1686,7 @@
           <t>Остаток хвоста</t>
         </is>
       </c>
-      <c r="B30">
+      <c r="B30" s="4">
         <f>IF(OR(B24="Хвост не найден",NOT(ISNUMBER(B24))),"Хвост не найден",MAX(B24-B29,0))</f>
         <v/>
       </c>
@@ -1616,18 +1698,20 @@
         </is>
       </c>
       <c r="B31">
-        <f>IF(B13="ДА","ОТКРЫТЬ СЕКЦИЮ",IF(B15="ДА",IF(B16="ДА","ЗАКРЫТЬ СЕКЦИЮ + ЗАКРЫТЬ ХВОСТ","ЗАКРЫТЬ СЕКЦИЮ"),"ЖДАТЬ / НИЧЕГО НЕ ДЕЛАТЬ"))</f>
+        <f>IF(BasketSummary!C13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(BasketSummary!C13="CLOSE_SECTION+CLOSE_TAIL","ЗАКРЫТЬ СЕКЦИЮ + ЗАКРЫТЬ ХВОСТ",IF(BasketSummary!C13="CLOSE_SECTION","ЗАКРЫТЬ СЕКЦИЮ",IF(BasketSummary!C13="OPEN_SECTION","ОТКРЫТЬ СЕКЦИЮ",IF(BasketSummary!C13="SAFE","SAFE",IF(BasketSummary!C13="WAIT","ЖДАТЬ","BLOCKED"))))))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
+      <c r="A32" s="5">
         <f>B46</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
-    <row r="34"/>
+    <row r="34">
+      <c r="B34" s="4" t="n"/>
+    </row>
     <row r="35"/>
     <row r="36"/>
     <row r="37"/>
@@ -1641,7 +1725,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1659,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,6 +1767,11 @@
           <t>UsedBy</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1729,21 +1818,338 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Scenario_UP!B2</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>CurrentPositions!F2</f>
+        <v/>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CurrentPositions!F2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CurrentPrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B4</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>B2+B3*Settings!B3</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B2,B3,Settings!B3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ScenarioPrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scenario_UP!N1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>...</f>
+        <v/>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Scenario_UP positions</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Scenario_UP!N3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AverageBuyPrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Scenario_UP!N2</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>...</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Scenario_UP positions</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Scenario_UP!N3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AverageSellPrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Scenario_UP!N3</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>(N1+N2)/2</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N1,N2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Scenario_UP!N4:N12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B221</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>MINIFS(...)</f>
+        <v/>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>H7:H206,B7:B206</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B222</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TailWorstPnL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B222</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>MINIFS(...)</f>
+        <v/>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A7:A206,H7:H206,B221</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Scenario_UP!B223</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TailTicket</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B7</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>IF(B3&lt;=0,0,FLOOR(...))</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B3,B5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BigLot</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B8</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>IF(B3&lt;=0,0,FLOOR(...))</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B3,B6</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SmallLot</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SectionCalculator_UP!B14</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>IF(...)</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B3,B7,B8,B12,B13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ScenarioText_UP!B13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CanOpenSection</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TailRecovery_UP!B10</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B14">
         <f>IF(B6="YES",MIN(B9,B4),0)</f>
         <v/>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TailRecovery_UP!B9, TailRecovery_UP!B4, TailRecovery_UP!B6</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>BasketSummary!B7, Log!F2</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B6,B9,B4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Log!F2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CloseLotFinal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BasketSummary!B13</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>IF(...)</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B8,B9,B10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ScenarioText_UP!B31</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NextAction</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ScenarioText_UP!B31</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>IF(BasketSummary!B13...)</f>
+        <v/>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BasketSummary!B13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ScenarioText_UP!B46</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HumanReadableAction</t>
         </is>
       </c>
     </row>
@@ -10603,7 +11009,7 @@
         </is>
       </c>
       <c r="B221">
-        <f>IFERROR(MIN(IF((B7:B206="SELL")*(H7:H206&lt;0),H7:H206)),0)</f>
+        <f>IFERROR(MINIFS(H7:H206,B7:B206,"SELL",H7:H206,"&lt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -10614,7 +11020,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IFERROR(MIN(IF((B7:B206="SELL")*(H7:H206=B221),A7:A206)),"N/A")</f>
+        <f>IFERROR(MINIFS(A7:A206,B7:B206,"SELL",H7:H206,B221),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -19281,7 +19687,7 @@
         </is>
       </c>
       <c r="B221">
-        <f>IFERROR(MIN(IF((B7:B206="BUY")*(H7:H206&lt;0),H7:H206)),0)</f>
+        <f>IFERROR(MINIFS(H7:H206,B7:B206,"BUY",H7:H206,"&lt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -19292,7 +19698,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IFERROR(MIN(IF((B7:B206="BUY")*(H7:H206=B221),A7:A206)),"N/A")</f>
+        <f>IFERROR(MINIFS(A7:A206,B7:B206,"BUY",H7:H206,B221),"N/A")</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -821,11 +821,11 @@
         </is>
       </c>
       <c r="B7">
-        <f>IF(OR(Scenario_UP!B221&gt;=0,Scenario_UP!B222&lt;&gt;"N/A"),"OK","ERROR")</f>
+        <f>IF(AND(COUNTIFS(Scenario_UP!B7:B206,"SELL",Scenario_UP!H7:H206,"&lt;0")&gt;0,Scenario_UP!B222="N/A"),"ERROR","OK")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>IF(OR(Scenario_DOWN!B221&gt;=0,Scenario_DOWN!B222&lt;&gt;"N/A"),"OK","ERROR")</f>
+        <f>IF(AND(COUNTIFS(Scenario_DOWN!B7:B206,"BUY",Scenario_DOWN!H7:H206,"&lt;0")&gt;0,Scenario_DOWN!B222="N/A"),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(B24="Хвост не найден","N/A",TEXT(Scenario_UP!B222,"0"))&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(B24="Хвост не найден","N/A",TEXT(Scenario_DOWN!B222,"0"))&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1779,9 +1779,10 @@
           <t>Scenario_UP!B4</t>
         </is>
       </c>
-      <c r="B2">
-        <f>Scenario_UP!B2+Scenario_UP!B3*Settings!B3</f>
-        <v/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>'=Scenario_UP!B2+Scenario_UP!B3*Settings!B3</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1800,9 +1801,10 @@
           <t>Scenario_DOWN!B4</t>
         </is>
       </c>
-      <c r="B3">
-        <f>Scenario_DOWN!B2-Scenario_DOWN!B3*Settings!B3</f>
-        <v/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'=Scenario_DOWN!B2-Scenario_DOWN!B3*Settings!B3</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1821,9 +1823,10 @@
           <t>Scenario_UP!B2</t>
         </is>
       </c>
-      <c r="B4">
-        <f>CurrentPositions!F2</f>
-        <v/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>'=CurrentPositions!F2</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1847,9 +1850,10 @@
           <t>Scenario_UP!B4</t>
         </is>
       </c>
-      <c r="B5">
-        <f>B2+B3*Settings!B3</f>
-        <v/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>'=B2+B3*Settings!B3</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1873,9 +1877,10 @@
           <t>Scenario_UP!N1</t>
         </is>
       </c>
-      <c r="B6">
-        <f>...</f>
-        <v/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>'=...</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1899,9 +1904,10 @@
           <t>Scenario_UP!N2</t>
         </is>
       </c>
-      <c r="B7">
-        <f>...</f>
-        <v/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>'=...</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1925,9 +1931,10 @@
           <t>Scenario_UP!N3</t>
         </is>
       </c>
-      <c r="B8">
-        <f>(N1+N2)/2</f>
-        <v/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>'=(N1+N2)/2</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1951,9 +1958,10 @@
           <t>Scenario_UP!B221</t>
         </is>
       </c>
-      <c r="B9">
-        <f>MINIFS(...)</f>
-        <v/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>'=MINIFS(...)</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1977,9 +1985,10 @@
           <t>Scenario_UP!B222</t>
         </is>
       </c>
-      <c r="B10">
-        <f>MINIFS(...)</f>
-        <v/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>'=MINIFS(...)</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2003,9 +2012,10 @@
           <t>SectionCalculator_UP!B7</t>
         </is>
       </c>
-      <c r="B11">
-        <f>IF(B3&lt;=0,0,FLOOR(...))</f>
-        <v/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>'=IF(B3&lt;=0,0,FLOOR(...))</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2029,9 +2039,10 @@
           <t>SectionCalculator_UP!B8</t>
         </is>
       </c>
-      <c r="B12">
-        <f>IF(B3&lt;=0,0,FLOOR(...))</f>
-        <v/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>'=IF(B3&lt;=0,0,FLOOR(...))</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2055,9 +2066,10 @@
           <t>SectionCalculator_UP!B14</t>
         </is>
       </c>
-      <c r="B13">
-        <f>IF(...)</f>
-        <v/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>'=IF(...)</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,9 +2093,10 @@
           <t>TailRecovery_UP!B10</t>
         </is>
       </c>
-      <c r="B14">
-        <f>IF(B6="YES",MIN(B9,B4),0)</f>
-        <v/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>'=IF(B6="YES",MIN(B9,B4),0)</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,9 +2120,10 @@
           <t>BasketSummary!B13</t>
         </is>
       </c>
-      <c r="B15">
-        <f>IF(...)</f>
-        <v/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>'=IF(...)</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,9 +2147,10 @@
           <t>ScenarioText_UP!B31</t>
         </is>
       </c>
-      <c r="B16">
-        <f>IF(BasketSummary!B13...)</f>
-        <v/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>'=IF(BasketSummary!B13...)</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2535,6 +2550,16 @@
           <t>SectionID</t>
         </is>
       </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>TailLossHelper</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>TailTicketHelper</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>UpperLevel3</t>
@@ -2586,6 +2611,14 @@
         <f>CurrentPositions!J2</f>
         <v/>
       </c>
+      <c r="K7">
+        <f>IF(AND(B7="SELL",H7&lt;0),H7,"")</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>IF(K7&lt;&gt;"",A7,"")</f>
+        <v/>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>UpperLevel4</t>
@@ -2637,6 +2670,14 @@
         <f>CurrentPositions!J3</f>
         <v/>
       </c>
+      <c r="K8">
+        <f>IF(AND(B8="SELL",H8&lt;0),H8,"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IF(K8&lt;&gt;"",A8,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -2679,6 +2720,14 @@
         <f>CurrentPositions!J4</f>
         <v/>
       </c>
+      <c r="K9">
+        <f>IF(AND(B9="SELL",H9&lt;0),H9,"")</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>IF(K9&lt;&gt;"",A9,"")</f>
+        <v/>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>LowerLevel1</t>
@@ -2730,6 +2779,14 @@
         <f>CurrentPositions!J5</f>
         <v/>
       </c>
+      <c r="K10">
+        <f>IF(AND(B10="SELL",H10&lt;0),H10,"")</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>IF(K10&lt;&gt;"",A10,"")</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>LowerLevel2</t>
@@ -2781,6 +2838,14 @@
         <f>CurrentPositions!J6</f>
         <v/>
       </c>
+      <c r="K11">
+        <f>IF(AND(B11="SELL",H11&lt;0),H11,"")</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>IF(K11&lt;&gt;"",A11,"")</f>
+        <v/>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>LowerLevel3</t>
@@ -2832,6 +2897,14 @@
         <f>CurrentPositions!J7</f>
         <v/>
       </c>
+      <c r="K12">
+        <f>IF(AND(B12="SELL",H12&lt;0),H12,"")</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>IF(K12&lt;&gt;"",A12,"")</f>
+        <v/>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>LowerLevel4</t>
@@ -2883,6 +2956,14 @@
         <f>CurrentPositions!J8</f>
         <v/>
       </c>
+      <c r="K13">
+        <f>IF(AND(B13="SELL",H13&lt;0),H13,"")</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>IF(K13&lt;&gt;"",A13,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -2925,6 +3006,14 @@
         <f>CurrentPositions!J9</f>
         <v/>
       </c>
+      <c r="K14">
+        <f>IF(AND(B14="SELL",H14&lt;0),H14,"")</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>IF(K14&lt;&gt;"",A14,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -2967,6 +3056,14 @@
         <f>CurrentPositions!J10</f>
         <v/>
       </c>
+      <c r="K15">
+        <f>IF(AND(B15="SELL",H15&lt;0),H15,"")</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>IF(K15&lt;&gt;"",A15,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -3009,6 +3106,14 @@
         <f>CurrentPositions!J11</f>
         <v/>
       </c>
+      <c r="K16">
+        <f>IF(AND(B16="SELL",H16&lt;0),H16,"")</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>IF(K16&lt;&gt;"",A16,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -3051,6 +3156,14 @@
         <f>CurrentPositions!J12</f>
         <v/>
       </c>
+      <c r="K17">
+        <f>IF(AND(B17="SELL",H17&lt;0),H17,"")</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>IF(K17&lt;&gt;"",A17,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -3093,6 +3206,14 @@
         <f>CurrentPositions!J13</f>
         <v/>
       </c>
+      <c r="K18">
+        <f>IF(AND(B18="SELL",H18&lt;0),H18,"")</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>IF(K18&lt;&gt;"",A18,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -3135,6 +3256,14 @@
         <f>CurrentPositions!J14</f>
         <v/>
       </c>
+      <c r="K19">
+        <f>IF(AND(B19="SELL",H19&lt;0),H19,"")</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>IF(K19&lt;&gt;"",A19,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -3177,6 +3306,14 @@
         <f>CurrentPositions!J15</f>
         <v/>
       </c>
+      <c r="K20">
+        <f>IF(AND(B20="SELL",H20&lt;0),H20,"")</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>IF(K20&lt;&gt;"",A20,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -3219,6 +3356,14 @@
         <f>CurrentPositions!J16</f>
         <v/>
       </c>
+      <c r="K21">
+        <f>IF(AND(B21="SELL",H21&lt;0),H21,"")</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>IF(K21&lt;&gt;"",A21,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -3261,6 +3406,14 @@
         <f>CurrentPositions!J17</f>
         <v/>
       </c>
+      <c r="K22">
+        <f>IF(AND(B22="SELL",H22&lt;0),H22,"")</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>IF(K22&lt;&gt;"",A22,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -3303,6 +3456,14 @@
         <f>CurrentPositions!J18</f>
         <v/>
       </c>
+      <c r="K23">
+        <f>IF(AND(B23="SELL",H23&lt;0),H23,"")</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>IF(K23&lt;&gt;"",A23,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -3345,6 +3506,14 @@
         <f>CurrentPositions!J19</f>
         <v/>
       </c>
+      <c r="K24">
+        <f>IF(AND(B24="SELL",H24&lt;0),H24,"")</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>IF(K24&lt;&gt;"",A24,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -3387,6 +3556,14 @@
         <f>CurrentPositions!J20</f>
         <v/>
       </c>
+      <c r="K25">
+        <f>IF(AND(B25="SELL",H25&lt;0),H25,"")</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>IF(K25&lt;&gt;"",A25,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -3429,6 +3606,14 @@
         <f>CurrentPositions!J21</f>
         <v/>
       </c>
+      <c r="K26">
+        <f>IF(AND(B26="SELL",H26&lt;0),H26,"")</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>IF(K26&lt;&gt;"",A26,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -3471,6 +3656,14 @@
         <f>CurrentPositions!J22</f>
         <v/>
       </c>
+      <c r="K27">
+        <f>IF(AND(B27="SELL",H27&lt;0),H27,"")</f>
+        <v/>
+      </c>
+      <c r="L27">
+        <f>IF(K27&lt;&gt;"",A27,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -3513,6 +3706,14 @@
         <f>CurrentPositions!J23</f>
         <v/>
       </c>
+      <c r="K28">
+        <f>IF(AND(B28="SELL",H28&lt;0),H28,"")</f>
+        <v/>
+      </c>
+      <c r="L28">
+        <f>IF(K28&lt;&gt;"",A28,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -3555,6 +3756,14 @@
         <f>CurrentPositions!J24</f>
         <v/>
       </c>
+      <c r="K29">
+        <f>IF(AND(B29="SELL",H29&lt;0),H29,"")</f>
+        <v/>
+      </c>
+      <c r="L29">
+        <f>IF(K29&lt;&gt;"",A29,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -3597,6 +3806,14 @@
         <f>CurrentPositions!J25</f>
         <v/>
       </c>
+      <c r="K30">
+        <f>IF(AND(B30="SELL",H30&lt;0),H30,"")</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>IF(K30&lt;&gt;"",A30,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -3639,6 +3856,14 @@
         <f>CurrentPositions!J26</f>
         <v/>
       </c>
+      <c r="K31">
+        <f>IF(AND(B31="SELL",H31&lt;0),H31,"")</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>IF(K31&lt;&gt;"",A31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -3681,6 +3906,14 @@
         <f>CurrentPositions!J27</f>
         <v/>
       </c>
+      <c r="K32">
+        <f>IF(AND(B32="SELL",H32&lt;0),H32,"")</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>IF(K32&lt;&gt;"",A32,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -3723,6 +3956,14 @@
         <f>CurrentPositions!J28</f>
         <v/>
       </c>
+      <c r="K33">
+        <f>IF(AND(B33="SELL",H33&lt;0),H33,"")</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>IF(K33&lt;&gt;"",A33,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -3765,6 +4006,14 @@
         <f>CurrentPositions!J29</f>
         <v/>
       </c>
+      <c r="K34">
+        <f>IF(AND(B34="SELL",H34&lt;0),H34,"")</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>IF(K34&lt;&gt;"",A34,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -3807,6 +4056,14 @@
         <f>CurrentPositions!J30</f>
         <v/>
       </c>
+      <c r="K35">
+        <f>IF(AND(B35="SELL",H35&lt;0),H35,"")</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>IF(K35&lt;&gt;"",A35,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -3849,6 +4106,14 @@
         <f>CurrentPositions!J31</f>
         <v/>
       </c>
+      <c r="K36">
+        <f>IF(AND(B36="SELL",H36&lt;0),H36,"")</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>IF(K36&lt;&gt;"",A36,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -3891,6 +4156,14 @@
         <f>CurrentPositions!J32</f>
         <v/>
       </c>
+      <c r="K37">
+        <f>IF(AND(B37="SELL",H37&lt;0),H37,"")</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>IF(K37&lt;&gt;"",A37,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -3933,6 +4206,14 @@
         <f>CurrentPositions!J33</f>
         <v/>
       </c>
+      <c r="K38">
+        <f>IF(AND(B38="SELL",H38&lt;0),H38,"")</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>IF(K38&lt;&gt;"",A38,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -3975,6 +4256,14 @@
         <f>CurrentPositions!J34</f>
         <v/>
       </c>
+      <c r="K39">
+        <f>IF(AND(B39="SELL",H39&lt;0),H39,"")</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>IF(K39&lt;&gt;"",A39,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -4017,6 +4306,14 @@
         <f>CurrentPositions!J35</f>
         <v/>
       </c>
+      <c r="K40">
+        <f>IF(AND(B40="SELL",H40&lt;0),H40,"")</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>IF(K40&lt;&gt;"",A40,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -4059,6 +4356,14 @@
         <f>CurrentPositions!J36</f>
         <v/>
       </c>
+      <c r="K41">
+        <f>IF(AND(B41="SELL",H41&lt;0),H41,"")</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>IF(K41&lt;&gt;"",A41,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -4101,6 +4406,14 @@
         <f>CurrentPositions!J37</f>
         <v/>
       </c>
+      <c r="K42">
+        <f>IF(AND(B42="SELL",H42&lt;0),H42,"")</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>IF(K42&lt;&gt;"",A42,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -4143,6 +4456,14 @@
         <f>CurrentPositions!J38</f>
         <v/>
       </c>
+      <c r="K43">
+        <f>IF(AND(B43="SELL",H43&lt;0),H43,"")</f>
+        <v/>
+      </c>
+      <c r="L43">
+        <f>IF(K43&lt;&gt;"",A43,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -4185,6 +4506,14 @@
         <f>CurrentPositions!J39</f>
         <v/>
       </c>
+      <c r="K44">
+        <f>IF(AND(B44="SELL",H44&lt;0),H44,"")</f>
+        <v/>
+      </c>
+      <c r="L44">
+        <f>IF(K44&lt;&gt;"",A44,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -4227,6 +4556,14 @@
         <f>CurrentPositions!J40</f>
         <v/>
       </c>
+      <c r="K45">
+        <f>IF(AND(B45="SELL",H45&lt;0),H45,"")</f>
+        <v/>
+      </c>
+      <c r="L45">
+        <f>IF(K45&lt;&gt;"",A45,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -4269,6 +4606,14 @@
         <f>CurrentPositions!J41</f>
         <v/>
       </c>
+      <c r="K46">
+        <f>IF(AND(B46="SELL",H46&lt;0),H46,"")</f>
+        <v/>
+      </c>
+      <c r="L46">
+        <f>IF(K46&lt;&gt;"",A46,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -4311,6 +4656,14 @@
         <f>CurrentPositions!J42</f>
         <v/>
       </c>
+      <c r="K47">
+        <f>IF(AND(B47="SELL",H47&lt;0),H47,"")</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>IF(K47&lt;&gt;"",A47,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -4353,6 +4706,14 @@
         <f>CurrentPositions!J43</f>
         <v/>
       </c>
+      <c r="K48">
+        <f>IF(AND(B48="SELL",H48&lt;0),H48,"")</f>
+        <v/>
+      </c>
+      <c r="L48">
+        <f>IF(K48&lt;&gt;"",A48,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -4395,6 +4756,14 @@
         <f>CurrentPositions!J44</f>
         <v/>
       </c>
+      <c r="K49">
+        <f>IF(AND(B49="SELL",H49&lt;0),H49,"")</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>IF(K49&lt;&gt;"",A49,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -4437,6 +4806,14 @@
         <f>CurrentPositions!J45</f>
         <v/>
       </c>
+      <c r="K50">
+        <f>IF(AND(B50="SELL",H50&lt;0),H50,"")</f>
+        <v/>
+      </c>
+      <c r="L50">
+        <f>IF(K50&lt;&gt;"",A50,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -4479,6 +4856,14 @@
         <f>CurrentPositions!J46</f>
         <v/>
       </c>
+      <c r="K51">
+        <f>IF(AND(B51="SELL",H51&lt;0),H51,"")</f>
+        <v/>
+      </c>
+      <c r="L51">
+        <f>IF(K51&lt;&gt;"",A51,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -4521,6 +4906,14 @@
         <f>CurrentPositions!J47</f>
         <v/>
       </c>
+      <c r="K52">
+        <f>IF(AND(B52="SELL",H52&lt;0),H52,"")</f>
+        <v/>
+      </c>
+      <c r="L52">
+        <f>IF(K52&lt;&gt;"",A52,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -4563,6 +4956,14 @@
         <f>CurrentPositions!J48</f>
         <v/>
       </c>
+      <c r="K53">
+        <f>IF(AND(B53="SELL",H53&lt;0),H53,"")</f>
+        <v/>
+      </c>
+      <c r="L53">
+        <f>IF(K53&lt;&gt;"",A53,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -4605,6 +5006,14 @@
         <f>CurrentPositions!J49</f>
         <v/>
       </c>
+      <c r="K54">
+        <f>IF(AND(B54="SELL",H54&lt;0),H54,"")</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>IF(K54&lt;&gt;"",A54,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -4647,6 +5056,14 @@
         <f>CurrentPositions!J50</f>
         <v/>
       </c>
+      <c r="K55">
+        <f>IF(AND(B55="SELL",H55&lt;0),H55,"")</f>
+        <v/>
+      </c>
+      <c r="L55">
+        <f>IF(K55&lt;&gt;"",A55,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -4689,6 +5106,14 @@
         <f>CurrentPositions!J51</f>
         <v/>
       </c>
+      <c r="K56">
+        <f>IF(AND(B56="SELL",H56&lt;0),H56,"")</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>IF(K56&lt;&gt;"",A56,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -4731,6 +5156,14 @@
         <f>CurrentPositions!J52</f>
         <v/>
       </c>
+      <c r="K57">
+        <f>IF(AND(B57="SELL",H57&lt;0),H57,"")</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>IF(K57&lt;&gt;"",A57,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -4773,6 +5206,14 @@
         <f>CurrentPositions!J53</f>
         <v/>
       </c>
+      <c r="K58">
+        <f>IF(AND(B58="SELL",H58&lt;0),H58,"")</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>IF(K58&lt;&gt;"",A58,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -4815,6 +5256,14 @@
         <f>CurrentPositions!J54</f>
         <v/>
       </c>
+      <c r="K59">
+        <f>IF(AND(B59="SELL",H59&lt;0),H59,"")</f>
+        <v/>
+      </c>
+      <c r="L59">
+        <f>IF(K59&lt;&gt;"",A59,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -4857,6 +5306,14 @@
         <f>CurrentPositions!J55</f>
         <v/>
       </c>
+      <c r="K60">
+        <f>IF(AND(B60="SELL",H60&lt;0),H60,"")</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>IF(K60&lt;&gt;"",A60,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -4899,6 +5356,14 @@
         <f>CurrentPositions!J56</f>
         <v/>
       </c>
+      <c r="K61">
+        <f>IF(AND(B61="SELL",H61&lt;0),H61,"")</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>IF(K61&lt;&gt;"",A61,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -4941,6 +5406,14 @@
         <f>CurrentPositions!J57</f>
         <v/>
       </c>
+      <c r="K62">
+        <f>IF(AND(B62="SELL",H62&lt;0),H62,"")</f>
+        <v/>
+      </c>
+      <c r="L62">
+        <f>IF(K62&lt;&gt;"",A62,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -4983,6 +5456,14 @@
         <f>CurrentPositions!J58</f>
         <v/>
       </c>
+      <c r="K63">
+        <f>IF(AND(B63="SELL",H63&lt;0),H63,"")</f>
+        <v/>
+      </c>
+      <c r="L63">
+        <f>IF(K63&lt;&gt;"",A63,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -5025,6 +5506,14 @@
         <f>CurrentPositions!J59</f>
         <v/>
       </c>
+      <c r="K64">
+        <f>IF(AND(B64="SELL",H64&lt;0),H64,"")</f>
+        <v/>
+      </c>
+      <c r="L64">
+        <f>IF(K64&lt;&gt;"",A64,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -5067,6 +5556,14 @@
         <f>CurrentPositions!J60</f>
         <v/>
       </c>
+      <c r="K65">
+        <f>IF(AND(B65="SELL",H65&lt;0),H65,"")</f>
+        <v/>
+      </c>
+      <c r="L65">
+        <f>IF(K65&lt;&gt;"",A65,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -5109,6 +5606,14 @@
         <f>CurrentPositions!J61</f>
         <v/>
       </c>
+      <c r="K66">
+        <f>IF(AND(B66="SELL",H66&lt;0),H66,"")</f>
+        <v/>
+      </c>
+      <c r="L66">
+        <f>IF(K66&lt;&gt;"",A66,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -5151,6 +5656,14 @@
         <f>CurrentPositions!J62</f>
         <v/>
       </c>
+      <c r="K67">
+        <f>IF(AND(B67="SELL",H67&lt;0),H67,"")</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>IF(K67&lt;&gt;"",A67,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -5193,6 +5706,14 @@
         <f>CurrentPositions!J63</f>
         <v/>
       </c>
+      <c r="K68">
+        <f>IF(AND(B68="SELL",H68&lt;0),H68,"")</f>
+        <v/>
+      </c>
+      <c r="L68">
+        <f>IF(K68&lt;&gt;"",A68,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -5235,6 +5756,14 @@
         <f>CurrentPositions!J64</f>
         <v/>
       </c>
+      <c r="K69">
+        <f>IF(AND(B69="SELL",H69&lt;0),H69,"")</f>
+        <v/>
+      </c>
+      <c r="L69">
+        <f>IF(K69&lt;&gt;"",A69,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -5277,6 +5806,14 @@
         <f>CurrentPositions!J65</f>
         <v/>
       </c>
+      <c r="K70">
+        <f>IF(AND(B70="SELL",H70&lt;0),H70,"")</f>
+        <v/>
+      </c>
+      <c r="L70">
+        <f>IF(K70&lt;&gt;"",A70,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -5319,6 +5856,14 @@
         <f>CurrentPositions!J66</f>
         <v/>
       </c>
+      <c r="K71">
+        <f>IF(AND(B71="SELL",H71&lt;0),H71,"")</f>
+        <v/>
+      </c>
+      <c r="L71">
+        <f>IF(K71&lt;&gt;"",A71,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -5361,6 +5906,14 @@
         <f>CurrentPositions!J67</f>
         <v/>
       </c>
+      <c r="K72">
+        <f>IF(AND(B72="SELL",H72&lt;0),H72,"")</f>
+        <v/>
+      </c>
+      <c r="L72">
+        <f>IF(K72&lt;&gt;"",A72,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -5403,6 +5956,14 @@
         <f>CurrentPositions!J68</f>
         <v/>
       </c>
+      <c r="K73">
+        <f>IF(AND(B73="SELL",H73&lt;0),H73,"")</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>IF(K73&lt;&gt;"",A73,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -5445,6 +6006,14 @@
         <f>CurrentPositions!J69</f>
         <v/>
       </c>
+      <c r="K74">
+        <f>IF(AND(B74="SELL",H74&lt;0),H74,"")</f>
+        <v/>
+      </c>
+      <c r="L74">
+        <f>IF(K74&lt;&gt;"",A74,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -5487,6 +6056,14 @@
         <f>CurrentPositions!J70</f>
         <v/>
       </c>
+      <c r="K75">
+        <f>IF(AND(B75="SELL",H75&lt;0),H75,"")</f>
+        <v/>
+      </c>
+      <c r="L75">
+        <f>IF(K75&lt;&gt;"",A75,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -5529,6 +6106,14 @@
         <f>CurrentPositions!J71</f>
         <v/>
       </c>
+      <c r="K76">
+        <f>IF(AND(B76="SELL",H76&lt;0),H76,"")</f>
+        <v/>
+      </c>
+      <c r="L76">
+        <f>IF(K76&lt;&gt;"",A76,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -5571,6 +6156,14 @@
         <f>CurrentPositions!J72</f>
         <v/>
       </c>
+      <c r="K77">
+        <f>IF(AND(B77="SELL",H77&lt;0),H77,"")</f>
+        <v/>
+      </c>
+      <c r="L77">
+        <f>IF(K77&lt;&gt;"",A77,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -5613,6 +6206,14 @@
         <f>CurrentPositions!J73</f>
         <v/>
       </c>
+      <c r="K78">
+        <f>IF(AND(B78="SELL",H78&lt;0),H78,"")</f>
+        <v/>
+      </c>
+      <c r="L78">
+        <f>IF(K78&lt;&gt;"",A78,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -5655,6 +6256,14 @@
         <f>CurrentPositions!J74</f>
         <v/>
       </c>
+      <c r="K79">
+        <f>IF(AND(B79="SELL",H79&lt;0),H79,"")</f>
+        <v/>
+      </c>
+      <c r="L79">
+        <f>IF(K79&lt;&gt;"",A79,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -5697,6 +6306,14 @@
         <f>CurrentPositions!J75</f>
         <v/>
       </c>
+      <c r="K80">
+        <f>IF(AND(B80="SELL",H80&lt;0),H80,"")</f>
+        <v/>
+      </c>
+      <c r="L80">
+        <f>IF(K80&lt;&gt;"",A80,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -5739,6 +6356,14 @@
         <f>CurrentPositions!J76</f>
         <v/>
       </c>
+      <c r="K81">
+        <f>IF(AND(B81="SELL",H81&lt;0),H81,"")</f>
+        <v/>
+      </c>
+      <c r="L81">
+        <f>IF(K81&lt;&gt;"",A81,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -5781,6 +6406,14 @@
         <f>CurrentPositions!J77</f>
         <v/>
       </c>
+      <c r="K82">
+        <f>IF(AND(B82="SELL",H82&lt;0),H82,"")</f>
+        <v/>
+      </c>
+      <c r="L82">
+        <f>IF(K82&lt;&gt;"",A82,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -5823,6 +6456,14 @@
         <f>CurrentPositions!J78</f>
         <v/>
       </c>
+      <c r="K83">
+        <f>IF(AND(B83="SELL",H83&lt;0),H83,"")</f>
+        <v/>
+      </c>
+      <c r="L83">
+        <f>IF(K83&lt;&gt;"",A83,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -5865,6 +6506,14 @@
         <f>CurrentPositions!J79</f>
         <v/>
       </c>
+      <c r="K84">
+        <f>IF(AND(B84="SELL",H84&lt;0),H84,"")</f>
+        <v/>
+      </c>
+      <c r="L84">
+        <f>IF(K84&lt;&gt;"",A84,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -5907,6 +6556,14 @@
         <f>CurrentPositions!J80</f>
         <v/>
       </c>
+      <c r="K85">
+        <f>IF(AND(B85="SELL",H85&lt;0),H85,"")</f>
+        <v/>
+      </c>
+      <c r="L85">
+        <f>IF(K85&lt;&gt;"",A85,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -5949,6 +6606,14 @@
         <f>CurrentPositions!J81</f>
         <v/>
       </c>
+      <c r="K86">
+        <f>IF(AND(B86="SELL",H86&lt;0),H86,"")</f>
+        <v/>
+      </c>
+      <c r="L86">
+        <f>IF(K86&lt;&gt;"",A86,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -5991,6 +6656,14 @@
         <f>CurrentPositions!J82</f>
         <v/>
       </c>
+      <c r="K87">
+        <f>IF(AND(B87="SELL",H87&lt;0),H87,"")</f>
+        <v/>
+      </c>
+      <c r="L87">
+        <f>IF(K87&lt;&gt;"",A87,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -6033,6 +6706,14 @@
         <f>CurrentPositions!J83</f>
         <v/>
       </c>
+      <c r="K88">
+        <f>IF(AND(B88="SELL",H88&lt;0),H88,"")</f>
+        <v/>
+      </c>
+      <c r="L88">
+        <f>IF(K88&lt;&gt;"",A88,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -6075,6 +6756,14 @@
         <f>CurrentPositions!J84</f>
         <v/>
       </c>
+      <c r="K89">
+        <f>IF(AND(B89="SELL",H89&lt;0),H89,"")</f>
+        <v/>
+      </c>
+      <c r="L89">
+        <f>IF(K89&lt;&gt;"",A89,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -6117,6 +6806,14 @@
         <f>CurrentPositions!J85</f>
         <v/>
       </c>
+      <c r="K90">
+        <f>IF(AND(B90="SELL",H90&lt;0),H90,"")</f>
+        <v/>
+      </c>
+      <c r="L90">
+        <f>IF(K90&lt;&gt;"",A90,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -6159,6 +6856,14 @@
         <f>CurrentPositions!J86</f>
         <v/>
       </c>
+      <c r="K91">
+        <f>IF(AND(B91="SELL",H91&lt;0),H91,"")</f>
+        <v/>
+      </c>
+      <c r="L91">
+        <f>IF(K91&lt;&gt;"",A91,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -6201,6 +6906,14 @@
         <f>CurrentPositions!J87</f>
         <v/>
       </c>
+      <c r="K92">
+        <f>IF(AND(B92="SELL",H92&lt;0),H92,"")</f>
+        <v/>
+      </c>
+      <c r="L92">
+        <f>IF(K92&lt;&gt;"",A92,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -6243,6 +6956,14 @@
         <f>CurrentPositions!J88</f>
         <v/>
       </c>
+      <c r="K93">
+        <f>IF(AND(B93="SELL",H93&lt;0),H93,"")</f>
+        <v/>
+      </c>
+      <c r="L93">
+        <f>IF(K93&lt;&gt;"",A93,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -6285,6 +7006,14 @@
         <f>CurrentPositions!J89</f>
         <v/>
       </c>
+      <c r="K94">
+        <f>IF(AND(B94="SELL",H94&lt;0),H94,"")</f>
+        <v/>
+      </c>
+      <c r="L94">
+        <f>IF(K94&lt;&gt;"",A94,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -6327,6 +7056,14 @@
         <f>CurrentPositions!J90</f>
         <v/>
       </c>
+      <c r="K95">
+        <f>IF(AND(B95="SELL",H95&lt;0),H95,"")</f>
+        <v/>
+      </c>
+      <c r="L95">
+        <f>IF(K95&lt;&gt;"",A95,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -6369,6 +7106,14 @@
         <f>CurrentPositions!J91</f>
         <v/>
       </c>
+      <c r="K96">
+        <f>IF(AND(B96="SELL",H96&lt;0),H96,"")</f>
+        <v/>
+      </c>
+      <c r="L96">
+        <f>IF(K96&lt;&gt;"",A96,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -6411,6 +7156,14 @@
         <f>CurrentPositions!J92</f>
         <v/>
       </c>
+      <c r="K97">
+        <f>IF(AND(B97="SELL",H97&lt;0),H97,"")</f>
+        <v/>
+      </c>
+      <c r="L97">
+        <f>IF(K97&lt;&gt;"",A97,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -6453,6 +7206,14 @@
         <f>CurrentPositions!J93</f>
         <v/>
       </c>
+      <c r="K98">
+        <f>IF(AND(B98="SELL",H98&lt;0),H98,"")</f>
+        <v/>
+      </c>
+      <c r="L98">
+        <f>IF(K98&lt;&gt;"",A98,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -6495,6 +7256,14 @@
         <f>CurrentPositions!J94</f>
         <v/>
       </c>
+      <c r="K99">
+        <f>IF(AND(B99="SELL",H99&lt;0),H99,"")</f>
+        <v/>
+      </c>
+      <c r="L99">
+        <f>IF(K99&lt;&gt;"",A99,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -6537,6 +7306,14 @@
         <f>CurrentPositions!J95</f>
         <v/>
       </c>
+      <c r="K100">
+        <f>IF(AND(B100="SELL",H100&lt;0),H100,"")</f>
+        <v/>
+      </c>
+      <c r="L100">
+        <f>IF(K100&lt;&gt;"",A100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -6579,6 +7356,14 @@
         <f>CurrentPositions!J96</f>
         <v/>
       </c>
+      <c r="K101">
+        <f>IF(AND(B101="SELL",H101&lt;0),H101,"")</f>
+        <v/>
+      </c>
+      <c r="L101">
+        <f>IF(K101&lt;&gt;"",A101,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -6621,6 +7406,14 @@
         <f>CurrentPositions!J97</f>
         <v/>
       </c>
+      <c r="K102">
+        <f>IF(AND(B102="SELL",H102&lt;0),H102,"")</f>
+        <v/>
+      </c>
+      <c r="L102">
+        <f>IF(K102&lt;&gt;"",A102,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -6663,6 +7456,14 @@
         <f>CurrentPositions!J98</f>
         <v/>
       </c>
+      <c r="K103">
+        <f>IF(AND(B103="SELL",H103&lt;0),H103,"")</f>
+        <v/>
+      </c>
+      <c r="L103">
+        <f>IF(K103&lt;&gt;"",A103,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -6705,6 +7506,14 @@
         <f>CurrentPositions!J99</f>
         <v/>
       </c>
+      <c r="K104">
+        <f>IF(AND(B104="SELL",H104&lt;0),H104,"")</f>
+        <v/>
+      </c>
+      <c r="L104">
+        <f>IF(K104&lt;&gt;"",A104,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -6747,6 +7556,14 @@
         <f>CurrentPositions!J100</f>
         <v/>
       </c>
+      <c r="K105">
+        <f>IF(AND(B105="SELL",H105&lt;0),H105,"")</f>
+        <v/>
+      </c>
+      <c r="L105">
+        <f>IF(K105&lt;&gt;"",A105,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -6789,6 +7606,14 @@
         <f>CurrentPositions!J101</f>
         <v/>
       </c>
+      <c r="K106">
+        <f>IF(AND(B106="SELL",H106&lt;0),H106,"")</f>
+        <v/>
+      </c>
+      <c r="L106">
+        <f>IF(K106&lt;&gt;"",A106,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -6831,6 +7656,14 @@
         <f>CurrentPositions!J102</f>
         <v/>
       </c>
+      <c r="K107">
+        <f>IF(AND(B107="SELL",H107&lt;0),H107,"")</f>
+        <v/>
+      </c>
+      <c r="L107">
+        <f>IF(K107&lt;&gt;"",A107,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -6873,6 +7706,14 @@
         <f>CurrentPositions!J103</f>
         <v/>
       </c>
+      <c r="K108">
+        <f>IF(AND(B108="SELL",H108&lt;0),H108,"")</f>
+        <v/>
+      </c>
+      <c r="L108">
+        <f>IF(K108&lt;&gt;"",A108,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -6915,6 +7756,14 @@
         <f>CurrentPositions!J104</f>
         <v/>
       </c>
+      <c r="K109">
+        <f>IF(AND(B109="SELL",H109&lt;0),H109,"")</f>
+        <v/>
+      </c>
+      <c r="L109">
+        <f>IF(K109&lt;&gt;"",A109,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -6957,6 +7806,14 @@
         <f>CurrentPositions!J105</f>
         <v/>
       </c>
+      <c r="K110">
+        <f>IF(AND(B110="SELL",H110&lt;0),H110,"")</f>
+        <v/>
+      </c>
+      <c r="L110">
+        <f>IF(K110&lt;&gt;"",A110,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -6999,6 +7856,14 @@
         <f>CurrentPositions!J106</f>
         <v/>
       </c>
+      <c r="K111">
+        <f>IF(AND(B111="SELL",H111&lt;0),H111,"")</f>
+        <v/>
+      </c>
+      <c r="L111">
+        <f>IF(K111&lt;&gt;"",A111,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -7041,6 +7906,14 @@
         <f>CurrentPositions!J107</f>
         <v/>
       </c>
+      <c r="K112">
+        <f>IF(AND(B112="SELL",H112&lt;0),H112,"")</f>
+        <v/>
+      </c>
+      <c r="L112">
+        <f>IF(K112&lt;&gt;"",A112,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -7083,6 +7956,14 @@
         <f>CurrentPositions!J108</f>
         <v/>
       </c>
+      <c r="K113">
+        <f>IF(AND(B113="SELL",H113&lt;0),H113,"")</f>
+        <v/>
+      </c>
+      <c r="L113">
+        <f>IF(K113&lt;&gt;"",A113,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -7125,6 +8006,14 @@
         <f>CurrentPositions!J109</f>
         <v/>
       </c>
+      <c r="K114">
+        <f>IF(AND(B114="SELL",H114&lt;0),H114,"")</f>
+        <v/>
+      </c>
+      <c r="L114">
+        <f>IF(K114&lt;&gt;"",A114,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -7167,6 +8056,14 @@
         <f>CurrentPositions!J110</f>
         <v/>
       </c>
+      <c r="K115">
+        <f>IF(AND(B115="SELL",H115&lt;0),H115,"")</f>
+        <v/>
+      </c>
+      <c r="L115">
+        <f>IF(K115&lt;&gt;"",A115,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -7209,6 +8106,14 @@
         <f>CurrentPositions!J111</f>
         <v/>
       </c>
+      <c r="K116">
+        <f>IF(AND(B116="SELL",H116&lt;0),H116,"")</f>
+        <v/>
+      </c>
+      <c r="L116">
+        <f>IF(K116&lt;&gt;"",A116,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -7251,6 +8156,14 @@
         <f>CurrentPositions!J112</f>
         <v/>
       </c>
+      <c r="K117">
+        <f>IF(AND(B117="SELL",H117&lt;0),H117,"")</f>
+        <v/>
+      </c>
+      <c r="L117">
+        <f>IF(K117&lt;&gt;"",A117,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -7293,6 +8206,14 @@
         <f>CurrentPositions!J113</f>
         <v/>
       </c>
+      <c r="K118">
+        <f>IF(AND(B118="SELL",H118&lt;0),H118,"")</f>
+        <v/>
+      </c>
+      <c r="L118">
+        <f>IF(K118&lt;&gt;"",A118,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -7335,6 +8256,14 @@
         <f>CurrentPositions!J114</f>
         <v/>
       </c>
+      <c r="K119">
+        <f>IF(AND(B119="SELL",H119&lt;0),H119,"")</f>
+        <v/>
+      </c>
+      <c r="L119">
+        <f>IF(K119&lt;&gt;"",A119,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -7377,6 +8306,14 @@
         <f>CurrentPositions!J115</f>
         <v/>
       </c>
+      <c r="K120">
+        <f>IF(AND(B120="SELL",H120&lt;0),H120,"")</f>
+        <v/>
+      </c>
+      <c r="L120">
+        <f>IF(K120&lt;&gt;"",A120,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -7419,6 +8356,14 @@
         <f>CurrentPositions!J116</f>
         <v/>
       </c>
+      <c r="K121">
+        <f>IF(AND(B121="SELL",H121&lt;0),H121,"")</f>
+        <v/>
+      </c>
+      <c r="L121">
+        <f>IF(K121&lt;&gt;"",A121,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -7461,6 +8406,14 @@
         <f>CurrentPositions!J117</f>
         <v/>
       </c>
+      <c r="K122">
+        <f>IF(AND(B122="SELL",H122&lt;0),H122,"")</f>
+        <v/>
+      </c>
+      <c r="L122">
+        <f>IF(K122&lt;&gt;"",A122,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -7503,6 +8456,14 @@
         <f>CurrentPositions!J118</f>
         <v/>
       </c>
+      <c r="K123">
+        <f>IF(AND(B123="SELL",H123&lt;0),H123,"")</f>
+        <v/>
+      </c>
+      <c r="L123">
+        <f>IF(K123&lt;&gt;"",A123,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -7545,6 +8506,14 @@
         <f>CurrentPositions!J119</f>
         <v/>
       </c>
+      <c r="K124">
+        <f>IF(AND(B124="SELL",H124&lt;0),H124,"")</f>
+        <v/>
+      </c>
+      <c r="L124">
+        <f>IF(K124&lt;&gt;"",A124,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -7587,6 +8556,14 @@
         <f>CurrentPositions!J120</f>
         <v/>
       </c>
+      <c r="K125">
+        <f>IF(AND(B125="SELL",H125&lt;0),H125,"")</f>
+        <v/>
+      </c>
+      <c r="L125">
+        <f>IF(K125&lt;&gt;"",A125,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -7629,6 +8606,14 @@
         <f>CurrentPositions!J121</f>
         <v/>
       </c>
+      <c r="K126">
+        <f>IF(AND(B126="SELL",H126&lt;0),H126,"")</f>
+        <v/>
+      </c>
+      <c r="L126">
+        <f>IF(K126&lt;&gt;"",A126,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -7671,6 +8656,14 @@
         <f>CurrentPositions!J122</f>
         <v/>
       </c>
+      <c r="K127">
+        <f>IF(AND(B127="SELL",H127&lt;0),H127,"")</f>
+        <v/>
+      </c>
+      <c r="L127">
+        <f>IF(K127&lt;&gt;"",A127,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -7713,6 +8706,14 @@
         <f>CurrentPositions!J123</f>
         <v/>
       </c>
+      <c r="K128">
+        <f>IF(AND(B128="SELL",H128&lt;0),H128,"")</f>
+        <v/>
+      </c>
+      <c r="L128">
+        <f>IF(K128&lt;&gt;"",A128,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -7755,6 +8756,14 @@
         <f>CurrentPositions!J124</f>
         <v/>
       </c>
+      <c r="K129">
+        <f>IF(AND(B129="SELL",H129&lt;0),H129,"")</f>
+        <v/>
+      </c>
+      <c r="L129">
+        <f>IF(K129&lt;&gt;"",A129,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -7797,6 +8806,14 @@
         <f>CurrentPositions!J125</f>
         <v/>
       </c>
+      <c r="K130">
+        <f>IF(AND(B130="SELL",H130&lt;0),H130,"")</f>
+        <v/>
+      </c>
+      <c r="L130">
+        <f>IF(K130&lt;&gt;"",A130,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -7839,6 +8856,14 @@
         <f>CurrentPositions!J126</f>
         <v/>
       </c>
+      <c r="K131">
+        <f>IF(AND(B131="SELL",H131&lt;0),H131,"")</f>
+        <v/>
+      </c>
+      <c r="L131">
+        <f>IF(K131&lt;&gt;"",A131,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -7881,6 +8906,14 @@
         <f>CurrentPositions!J127</f>
         <v/>
       </c>
+      <c r="K132">
+        <f>IF(AND(B132="SELL",H132&lt;0),H132,"")</f>
+        <v/>
+      </c>
+      <c r="L132">
+        <f>IF(K132&lt;&gt;"",A132,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -7923,6 +8956,14 @@
         <f>CurrentPositions!J128</f>
         <v/>
       </c>
+      <c r="K133">
+        <f>IF(AND(B133="SELL",H133&lt;0),H133,"")</f>
+        <v/>
+      </c>
+      <c r="L133">
+        <f>IF(K133&lt;&gt;"",A133,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -7965,6 +9006,14 @@
         <f>CurrentPositions!J129</f>
         <v/>
       </c>
+      <c r="K134">
+        <f>IF(AND(B134="SELL",H134&lt;0),H134,"")</f>
+        <v/>
+      </c>
+      <c r="L134">
+        <f>IF(K134&lt;&gt;"",A134,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -8007,6 +9056,14 @@
         <f>CurrentPositions!J130</f>
         <v/>
       </c>
+      <c r="K135">
+        <f>IF(AND(B135="SELL",H135&lt;0),H135,"")</f>
+        <v/>
+      </c>
+      <c r="L135">
+        <f>IF(K135&lt;&gt;"",A135,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -8049,6 +9106,14 @@
         <f>CurrentPositions!J131</f>
         <v/>
       </c>
+      <c r="K136">
+        <f>IF(AND(B136="SELL",H136&lt;0),H136,"")</f>
+        <v/>
+      </c>
+      <c r="L136">
+        <f>IF(K136&lt;&gt;"",A136,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -8091,6 +9156,14 @@
         <f>CurrentPositions!J132</f>
         <v/>
       </c>
+      <c r="K137">
+        <f>IF(AND(B137="SELL",H137&lt;0),H137,"")</f>
+        <v/>
+      </c>
+      <c r="L137">
+        <f>IF(K137&lt;&gt;"",A137,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -8133,6 +9206,14 @@
         <f>CurrentPositions!J133</f>
         <v/>
       </c>
+      <c r="K138">
+        <f>IF(AND(B138="SELL",H138&lt;0),H138,"")</f>
+        <v/>
+      </c>
+      <c r="L138">
+        <f>IF(K138&lt;&gt;"",A138,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -8175,6 +9256,14 @@
         <f>CurrentPositions!J134</f>
         <v/>
       </c>
+      <c r="K139">
+        <f>IF(AND(B139="SELL",H139&lt;0),H139,"")</f>
+        <v/>
+      </c>
+      <c r="L139">
+        <f>IF(K139&lt;&gt;"",A139,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -8217,6 +9306,14 @@
         <f>CurrentPositions!J135</f>
         <v/>
       </c>
+      <c r="K140">
+        <f>IF(AND(B140="SELL",H140&lt;0),H140,"")</f>
+        <v/>
+      </c>
+      <c r="L140">
+        <f>IF(K140&lt;&gt;"",A140,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -8259,6 +9356,14 @@
         <f>CurrentPositions!J136</f>
         <v/>
       </c>
+      <c r="K141">
+        <f>IF(AND(B141="SELL",H141&lt;0),H141,"")</f>
+        <v/>
+      </c>
+      <c r="L141">
+        <f>IF(K141&lt;&gt;"",A141,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -8301,6 +9406,14 @@
         <f>CurrentPositions!J137</f>
         <v/>
       </c>
+      <c r="K142">
+        <f>IF(AND(B142="SELL",H142&lt;0),H142,"")</f>
+        <v/>
+      </c>
+      <c r="L142">
+        <f>IF(K142&lt;&gt;"",A142,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -8343,6 +9456,14 @@
         <f>CurrentPositions!J138</f>
         <v/>
       </c>
+      <c r="K143">
+        <f>IF(AND(B143="SELL",H143&lt;0),H143,"")</f>
+        <v/>
+      </c>
+      <c r="L143">
+        <f>IF(K143&lt;&gt;"",A143,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -8385,6 +9506,14 @@
         <f>CurrentPositions!J139</f>
         <v/>
       </c>
+      <c r="K144">
+        <f>IF(AND(B144="SELL",H144&lt;0),H144,"")</f>
+        <v/>
+      </c>
+      <c r="L144">
+        <f>IF(K144&lt;&gt;"",A144,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -8427,6 +9556,14 @@
         <f>CurrentPositions!J140</f>
         <v/>
       </c>
+      <c r="K145">
+        <f>IF(AND(B145="SELL",H145&lt;0),H145,"")</f>
+        <v/>
+      </c>
+      <c r="L145">
+        <f>IF(K145&lt;&gt;"",A145,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -8469,6 +9606,14 @@
         <f>CurrentPositions!J141</f>
         <v/>
       </c>
+      <c r="K146">
+        <f>IF(AND(B146="SELL",H146&lt;0),H146,"")</f>
+        <v/>
+      </c>
+      <c r="L146">
+        <f>IF(K146&lt;&gt;"",A146,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -8511,6 +9656,14 @@
         <f>CurrentPositions!J142</f>
         <v/>
       </c>
+      <c r="K147">
+        <f>IF(AND(B147="SELL",H147&lt;0),H147,"")</f>
+        <v/>
+      </c>
+      <c r="L147">
+        <f>IF(K147&lt;&gt;"",A147,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -8553,6 +9706,14 @@
         <f>CurrentPositions!J143</f>
         <v/>
       </c>
+      <c r="K148">
+        <f>IF(AND(B148="SELL",H148&lt;0),H148,"")</f>
+        <v/>
+      </c>
+      <c r="L148">
+        <f>IF(K148&lt;&gt;"",A148,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -8595,6 +9756,14 @@
         <f>CurrentPositions!J144</f>
         <v/>
       </c>
+      <c r="K149">
+        <f>IF(AND(B149="SELL",H149&lt;0),H149,"")</f>
+        <v/>
+      </c>
+      <c r="L149">
+        <f>IF(K149&lt;&gt;"",A149,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -8637,6 +9806,14 @@
         <f>CurrentPositions!J145</f>
         <v/>
       </c>
+      <c r="K150">
+        <f>IF(AND(B150="SELL",H150&lt;0),H150,"")</f>
+        <v/>
+      </c>
+      <c r="L150">
+        <f>IF(K150&lt;&gt;"",A150,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -8679,6 +9856,14 @@
         <f>CurrentPositions!J146</f>
         <v/>
       </c>
+      <c r="K151">
+        <f>IF(AND(B151="SELL",H151&lt;0),H151,"")</f>
+        <v/>
+      </c>
+      <c r="L151">
+        <f>IF(K151&lt;&gt;"",A151,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -8721,6 +9906,14 @@
         <f>CurrentPositions!J147</f>
         <v/>
       </c>
+      <c r="K152">
+        <f>IF(AND(B152="SELL",H152&lt;0),H152,"")</f>
+        <v/>
+      </c>
+      <c r="L152">
+        <f>IF(K152&lt;&gt;"",A152,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -8763,6 +9956,14 @@
         <f>CurrentPositions!J148</f>
         <v/>
       </c>
+      <c r="K153">
+        <f>IF(AND(B153="SELL",H153&lt;0),H153,"")</f>
+        <v/>
+      </c>
+      <c r="L153">
+        <f>IF(K153&lt;&gt;"",A153,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -8805,6 +10006,14 @@
         <f>CurrentPositions!J149</f>
         <v/>
       </c>
+      <c r="K154">
+        <f>IF(AND(B154="SELL",H154&lt;0),H154,"")</f>
+        <v/>
+      </c>
+      <c r="L154">
+        <f>IF(K154&lt;&gt;"",A154,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -8847,6 +10056,14 @@
         <f>CurrentPositions!J150</f>
         <v/>
       </c>
+      <c r="K155">
+        <f>IF(AND(B155="SELL",H155&lt;0),H155,"")</f>
+        <v/>
+      </c>
+      <c r="L155">
+        <f>IF(K155&lt;&gt;"",A155,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -8889,6 +10106,14 @@
         <f>CurrentPositions!J151</f>
         <v/>
       </c>
+      <c r="K156">
+        <f>IF(AND(B156="SELL",H156&lt;0),H156,"")</f>
+        <v/>
+      </c>
+      <c r="L156">
+        <f>IF(K156&lt;&gt;"",A156,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -8931,6 +10156,14 @@
         <f>CurrentPositions!J152</f>
         <v/>
       </c>
+      <c r="K157">
+        <f>IF(AND(B157="SELL",H157&lt;0),H157,"")</f>
+        <v/>
+      </c>
+      <c r="L157">
+        <f>IF(K157&lt;&gt;"",A157,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -8973,6 +10206,14 @@
         <f>CurrentPositions!J153</f>
         <v/>
       </c>
+      <c r="K158">
+        <f>IF(AND(B158="SELL",H158&lt;0),H158,"")</f>
+        <v/>
+      </c>
+      <c r="L158">
+        <f>IF(K158&lt;&gt;"",A158,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -9015,6 +10256,14 @@
         <f>CurrentPositions!J154</f>
         <v/>
       </c>
+      <c r="K159">
+        <f>IF(AND(B159="SELL",H159&lt;0),H159,"")</f>
+        <v/>
+      </c>
+      <c r="L159">
+        <f>IF(K159&lt;&gt;"",A159,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -9057,6 +10306,14 @@
         <f>CurrentPositions!J155</f>
         <v/>
       </c>
+      <c r="K160">
+        <f>IF(AND(B160="SELL",H160&lt;0),H160,"")</f>
+        <v/>
+      </c>
+      <c r="L160">
+        <f>IF(K160&lt;&gt;"",A160,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -9099,6 +10356,14 @@
         <f>CurrentPositions!J156</f>
         <v/>
       </c>
+      <c r="K161">
+        <f>IF(AND(B161="SELL",H161&lt;0),H161,"")</f>
+        <v/>
+      </c>
+      <c r="L161">
+        <f>IF(K161&lt;&gt;"",A161,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -9141,6 +10406,14 @@
         <f>CurrentPositions!J157</f>
         <v/>
       </c>
+      <c r="K162">
+        <f>IF(AND(B162="SELL",H162&lt;0),H162,"")</f>
+        <v/>
+      </c>
+      <c r="L162">
+        <f>IF(K162&lt;&gt;"",A162,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -9183,6 +10456,14 @@
         <f>CurrentPositions!J158</f>
         <v/>
       </c>
+      <c r="K163">
+        <f>IF(AND(B163="SELL",H163&lt;0),H163,"")</f>
+        <v/>
+      </c>
+      <c r="L163">
+        <f>IF(K163&lt;&gt;"",A163,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -9225,6 +10506,14 @@
         <f>CurrentPositions!J159</f>
         <v/>
       </c>
+      <c r="K164">
+        <f>IF(AND(B164="SELL",H164&lt;0),H164,"")</f>
+        <v/>
+      </c>
+      <c r="L164">
+        <f>IF(K164&lt;&gt;"",A164,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -9267,6 +10556,14 @@
         <f>CurrentPositions!J160</f>
         <v/>
       </c>
+      <c r="K165">
+        <f>IF(AND(B165="SELL",H165&lt;0),H165,"")</f>
+        <v/>
+      </c>
+      <c r="L165">
+        <f>IF(K165&lt;&gt;"",A165,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -9309,6 +10606,14 @@
         <f>CurrentPositions!J161</f>
         <v/>
       </c>
+      <c r="K166">
+        <f>IF(AND(B166="SELL",H166&lt;0),H166,"")</f>
+        <v/>
+      </c>
+      <c r="L166">
+        <f>IF(K166&lt;&gt;"",A166,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -9351,6 +10656,14 @@
         <f>CurrentPositions!J162</f>
         <v/>
       </c>
+      <c r="K167">
+        <f>IF(AND(B167="SELL",H167&lt;0),H167,"")</f>
+        <v/>
+      </c>
+      <c r="L167">
+        <f>IF(K167&lt;&gt;"",A167,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -9393,6 +10706,14 @@
         <f>CurrentPositions!J163</f>
         <v/>
       </c>
+      <c r="K168">
+        <f>IF(AND(B168="SELL",H168&lt;0),H168,"")</f>
+        <v/>
+      </c>
+      <c r="L168">
+        <f>IF(K168&lt;&gt;"",A168,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -9435,6 +10756,14 @@
         <f>CurrentPositions!J164</f>
         <v/>
       </c>
+      <c r="K169">
+        <f>IF(AND(B169="SELL",H169&lt;0),H169,"")</f>
+        <v/>
+      </c>
+      <c r="L169">
+        <f>IF(K169&lt;&gt;"",A169,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -9477,6 +10806,14 @@
         <f>CurrentPositions!J165</f>
         <v/>
       </c>
+      <c r="K170">
+        <f>IF(AND(B170="SELL",H170&lt;0),H170,"")</f>
+        <v/>
+      </c>
+      <c r="L170">
+        <f>IF(K170&lt;&gt;"",A170,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -9519,6 +10856,14 @@
         <f>CurrentPositions!J166</f>
         <v/>
       </c>
+      <c r="K171">
+        <f>IF(AND(B171="SELL",H171&lt;0),H171,"")</f>
+        <v/>
+      </c>
+      <c r="L171">
+        <f>IF(K171&lt;&gt;"",A171,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -9561,6 +10906,14 @@
         <f>CurrentPositions!J167</f>
         <v/>
       </c>
+      <c r="K172">
+        <f>IF(AND(B172="SELL",H172&lt;0),H172,"")</f>
+        <v/>
+      </c>
+      <c r="L172">
+        <f>IF(K172&lt;&gt;"",A172,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -9603,6 +10956,14 @@
         <f>CurrentPositions!J168</f>
         <v/>
       </c>
+      <c r="K173">
+        <f>IF(AND(B173="SELL",H173&lt;0),H173,"")</f>
+        <v/>
+      </c>
+      <c r="L173">
+        <f>IF(K173&lt;&gt;"",A173,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -9645,6 +11006,14 @@
         <f>CurrentPositions!J169</f>
         <v/>
       </c>
+      <c r="K174">
+        <f>IF(AND(B174="SELL",H174&lt;0),H174,"")</f>
+        <v/>
+      </c>
+      <c r="L174">
+        <f>IF(K174&lt;&gt;"",A174,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -9687,6 +11056,14 @@
         <f>CurrentPositions!J170</f>
         <v/>
       </c>
+      <c r="K175">
+        <f>IF(AND(B175="SELL",H175&lt;0),H175,"")</f>
+        <v/>
+      </c>
+      <c r="L175">
+        <f>IF(K175&lt;&gt;"",A175,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -9729,6 +11106,14 @@
         <f>CurrentPositions!J171</f>
         <v/>
       </c>
+      <c r="K176">
+        <f>IF(AND(B176="SELL",H176&lt;0),H176,"")</f>
+        <v/>
+      </c>
+      <c r="L176">
+        <f>IF(K176&lt;&gt;"",A176,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -9771,6 +11156,14 @@
         <f>CurrentPositions!J172</f>
         <v/>
       </c>
+      <c r="K177">
+        <f>IF(AND(B177="SELL",H177&lt;0),H177,"")</f>
+        <v/>
+      </c>
+      <c r="L177">
+        <f>IF(K177&lt;&gt;"",A177,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -9813,6 +11206,14 @@
         <f>CurrentPositions!J173</f>
         <v/>
       </c>
+      <c r="K178">
+        <f>IF(AND(B178="SELL",H178&lt;0),H178,"")</f>
+        <v/>
+      </c>
+      <c r="L178">
+        <f>IF(K178&lt;&gt;"",A178,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -9855,6 +11256,14 @@
         <f>CurrentPositions!J174</f>
         <v/>
       </c>
+      <c r="K179">
+        <f>IF(AND(B179="SELL",H179&lt;0),H179,"")</f>
+        <v/>
+      </c>
+      <c r="L179">
+        <f>IF(K179&lt;&gt;"",A179,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -9897,6 +11306,14 @@
         <f>CurrentPositions!J175</f>
         <v/>
       </c>
+      <c r="K180">
+        <f>IF(AND(B180="SELL",H180&lt;0),H180,"")</f>
+        <v/>
+      </c>
+      <c r="L180">
+        <f>IF(K180&lt;&gt;"",A180,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -9939,6 +11356,14 @@
         <f>CurrentPositions!J176</f>
         <v/>
       </c>
+      <c r="K181">
+        <f>IF(AND(B181="SELL",H181&lt;0),H181,"")</f>
+        <v/>
+      </c>
+      <c r="L181">
+        <f>IF(K181&lt;&gt;"",A181,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -9981,6 +11406,14 @@
         <f>CurrentPositions!J177</f>
         <v/>
       </c>
+      <c r="K182">
+        <f>IF(AND(B182="SELL",H182&lt;0),H182,"")</f>
+        <v/>
+      </c>
+      <c r="L182">
+        <f>IF(K182&lt;&gt;"",A182,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -10023,6 +11456,14 @@
         <f>CurrentPositions!J178</f>
         <v/>
       </c>
+      <c r="K183">
+        <f>IF(AND(B183="SELL",H183&lt;0),H183,"")</f>
+        <v/>
+      </c>
+      <c r="L183">
+        <f>IF(K183&lt;&gt;"",A183,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -10065,6 +11506,14 @@
         <f>CurrentPositions!J179</f>
         <v/>
       </c>
+      <c r="K184">
+        <f>IF(AND(B184="SELL",H184&lt;0),H184,"")</f>
+        <v/>
+      </c>
+      <c r="L184">
+        <f>IF(K184&lt;&gt;"",A184,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -10107,6 +11556,14 @@
         <f>CurrentPositions!J180</f>
         <v/>
       </c>
+      <c r="K185">
+        <f>IF(AND(B185="SELL",H185&lt;0),H185,"")</f>
+        <v/>
+      </c>
+      <c r="L185">
+        <f>IF(K185&lt;&gt;"",A185,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -10149,6 +11606,14 @@
         <f>CurrentPositions!J181</f>
         <v/>
       </c>
+      <c r="K186">
+        <f>IF(AND(B186="SELL",H186&lt;0),H186,"")</f>
+        <v/>
+      </c>
+      <c r="L186">
+        <f>IF(K186&lt;&gt;"",A186,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -10191,6 +11656,14 @@
         <f>CurrentPositions!J182</f>
         <v/>
       </c>
+      <c r="K187">
+        <f>IF(AND(B187="SELL",H187&lt;0),H187,"")</f>
+        <v/>
+      </c>
+      <c r="L187">
+        <f>IF(K187&lt;&gt;"",A187,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -10233,6 +11706,14 @@
         <f>CurrentPositions!J183</f>
         <v/>
       </c>
+      <c r="K188">
+        <f>IF(AND(B188="SELL",H188&lt;0),H188,"")</f>
+        <v/>
+      </c>
+      <c r="L188">
+        <f>IF(K188&lt;&gt;"",A188,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -10275,6 +11756,14 @@
         <f>CurrentPositions!J184</f>
         <v/>
       </c>
+      <c r="K189">
+        <f>IF(AND(B189="SELL",H189&lt;0),H189,"")</f>
+        <v/>
+      </c>
+      <c r="L189">
+        <f>IF(K189&lt;&gt;"",A189,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -10317,6 +11806,14 @@
         <f>CurrentPositions!J185</f>
         <v/>
       </c>
+      <c r="K190">
+        <f>IF(AND(B190="SELL",H190&lt;0),H190,"")</f>
+        <v/>
+      </c>
+      <c r="L190">
+        <f>IF(K190&lt;&gt;"",A190,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -10359,6 +11856,14 @@
         <f>CurrentPositions!J186</f>
         <v/>
       </c>
+      <c r="K191">
+        <f>IF(AND(B191="SELL",H191&lt;0),H191,"")</f>
+        <v/>
+      </c>
+      <c r="L191">
+        <f>IF(K191&lt;&gt;"",A191,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -10401,6 +11906,14 @@
         <f>CurrentPositions!J187</f>
         <v/>
       </c>
+      <c r="K192">
+        <f>IF(AND(B192="SELL",H192&lt;0),H192,"")</f>
+        <v/>
+      </c>
+      <c r="L192">
+        <f>IF(K192&lt;&gt;"",A192,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -10443,6 +11956,14 @@
         <f>CurrentPositions!J188</f>
         <v/>
       </c>
+      <c r="K193">
+        <f>IF(AND(B193="SELL",H193&lt;0),H193,"")</f>
+        <v/>
+      </c>
+      <c r="L193">
+        <f>IF(K193&lt;&gt;"",A193,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -10485,6 +12006,14 @@
         <f>CurrentPositions!J189</f>
         <v/>
       </c>
+      <c r="K194">
+        <f>IF(AND(B194="SELL",H194&lt;0),H194,"")</f>
+        <v/>
+      </c>
+      <c r="L194">
+        <f>IF(K194&lt;&gt;"",A194,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -10527,6 +12056,14 @@
         <f>CurrentPositions!J190</f>
         <v/>
       </c>
+      <c r="K195">
+        <f>IF(AND(B195="SELL",H195&lt;0),H195,"")</f>
+        <v/>
+      </c>
+      <c r="L195">
+        <f>IF(K195&lt;&gt;"",A195,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -10569,6 +12106,14 @@
         <f>CurrentPositions!J191</f>
         <v/>
       </c>
+      <c r="K196">
+        <f>IF(AND(B196="SELL",H196&lt;0),H196,"")</f>
+        <v/>
+      </c>
+      <c r="L196">
+        <f>IF(K196&lt;&gt;"",A196,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -10611,6 +12156,14 @@
         <f>CurrentPositions!J192</f>
         <v/>
       </c>
+      <c r="K197">
+        <f>IF(AND(B197="SELL",H197&lt;0),H197,"")</f>
+        <v/>
+      </c>
+      <c r="L197">
+        <f>IF(K197&lt;&gt;"",A197,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -10653,6 +12206,14 @@
         <f>CurrentPositions!J193</f>
         <v/>
       </c>
+      <c r="K198">
+        <f>IF(AND(B198="SELL",H198&lt;0),H198,"")</f>
+        <v/>
+      </c>
+      <c r="L198">
+        <f>IF(K198&lt;&gt;"",A198,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -10695,6 +12256,14 @@
         <f>CurrentPositions!J194</f>
         <v/>
       </c>
+      <c r="K199">
+        <f>IF(AND(B199="SELL",H199&lt;0),H199,"")</f>
+        <v/>
+      </c>
+      <c r="L199">
+        <f>IF(K199&lt;&gt;"",A199,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -10737,6 +12306,14 @@
         <f>CurrentPositions!J195</f>
         <v/>
       </c>
+      <c r="K200">
+        <f>IF(AND(B200="SELL",H200&lt;0),H200,"")</f>
+        <v/>
+      </c>
+      <c r="L200">
+        <f>IF(K200&lt;&gt;"",A200,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -10779,6 +12356,14 @@
         <f>CurrentPositions!J196</f>
         <v/>
       </c>
+      <c r="K201">
+        <f>IF(AND(B201="SELL",H201&lt;0),H201,"")</f>
+        <v/>
+      </c>
+      <c r="L201">
+        <f>IF(K201&lt;&gt;"",A201,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -10821,6 +12406,14 @@
         <f>CurrentPositions!J197</f>
         <v/>
       </c>
+      <c r="K202">
+        <f>IF(AND(B202="SELL",H202&lt;0),H202,"")</f>
+        <v/>
+      </c>
+      <c r="L202">
+        <f>IF(K202&lt;&gt;"",A202,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -10863,6 +12456,14 @@
         <f>CurrentPositions!J198</f>
         <v/>
       </c>
+      <c r="K203">
+        <f>IF(AND(B203="SELL",H203&lt;0),H203,"")</f>
+        <v/>
+      </c>
+      <c r="L203">
+        <f>IF(K203&lt;&gt;"",A203,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -10905,6 +12506,14 @@
         <f>CurrentPositions!J199</f>
         <v/>
       </c>
+      <c r="K204">
+        <f>IF(AND(B204="SELL",H204&lt;0),H204,"")</f>
+        <v/>
+      </c>
+      <c r="L204">
+        <f>IF(K204&lt;&gt;"",A204,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -10947,6 +12556,14 @@
         <f>CurrentPositions!J200</f>
         <v/>
       </c>
+      <c r="K205">
+        <f>IF(AND(B205="SELL",H205&lt;0),H205,"")</f>
+        <v/>
+      </c>
+      <c r="L205">
+        <f>IF(K205&lt;&gt;"",A205,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -10989,6 +12606,14 @@
         <f>CurrentPositions!J201</f>
         <v/>
       </c>
+      <c r="K206">
+        <f>IF(AND(B206="SELL",H206&lt;0),H206,"")</f>
+        <v/>
+      </c>
+      <c r="L206">
+        <f>IF(K206&lt;&gt;"",A206,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11009,7 +12634,7 @@
         </is>
       </c>
       <c r="B221">
-        <f>IFERROR(MINIFS(H7:H206,B7:B206,"SELL",H7:H206,"&lt;0"),0)</f>
+        <f>IF(COUNT(K7:K206)=0,0,MIN(K7:K206))</f>
         <v/>
       </c>
     </row>
@@ -11020,7 +12645,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IFERROR(MINIFS(A7:A206,B7:B206,"SELL",H7:H206,B221),"N/A")</f>
+        <f>IF(B221=0,"N/A",MIN(L7:L206))</f>
         <v/>
       </c>
     </row>
@@ -11213,6 +12838,16 @@
           <t>SectionID</t>
         </is>
       </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>TailLossHelper</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>TailTicketHelper</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>UpperLevel3</t>
@@ -11264,6 +12899,14 @@
         <f>CurrentPositions!J2</f>
         <v/>
       </c>
+      <c r="K7">
+        <f>IF(AND(B7="BUY",H7&lt;0),H7,"")</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>IF(K7&lt;&gt;"",A7,"")</f>
+        <v/>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>UpperLevel4</t>
@@ -11315,6 +12958,14 @@
         <f>CurrentPositions!J3</f>
         <v/>
       </c>
+      <c r="K8">
+        <f>IF(AND(B8="BUY",H8&lt;0),H8,"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IF(K8&lt;&gt;"",A8,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -11357,6 +13008,14 @@
         <f>CurrentPositions!J4</f>
         <v/>
       </c>
+      <c r="K9">
+        <f>IF(AND(B9="BUY",H9&lt;0),H9,"")</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>IF(K9&lt;&gt;"",A9,"")</f>
+        <v/>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>LowerLevel1</t>
@@ -11408,6 +13067,14 @@
         <f>CurrentPositions!J5</f>
         <v/>
       </c>
+      <c r="K10">
+        <f>IF(AND(B10="BUY",H10&lt;0),H10,"")</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>IF(K10&lt;&gt;"",A10,"")</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>LowerLevel2</t>
@@ -11459,6 +13126,14 @@
         <f>CurrentPositions!J6</f>
         <v/>
       </c>
+      <c r="K11">
+        <f>IF(AND(B11="BUY",H11&lt;0),H11,"")</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>IF(K11&lt;&gt;"",A11,"")</f>
+        <v/>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>LowerLevel3</t>
@@ -11510,6 +13185,14 @@
         <f>CurrentPositions!J7</f>
         <v/>
       </c>
+      <c r="K12">
+        <f>IF(AND(B12="BUY",H12&lt;0),H12,"")</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>IF(K12&lt;&gt;"",A12,"")</f>
+        <v/>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>LowerLevel4</t>
@@ -11561,6 +13244,14 @@
         <f>CurrentPositions!J8</f>
         <v/>
       </c>
+      <c r="K13">
+        <f>IF(AND(B13="BUY",H13&lt;0),H13,"")</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>IF(K13&lt;&gt;"",A13,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -11603,6 +13294,14 @@
         <f>CurrentPositions!J9</f>
         <v/>
       </c>
+      <c r="K14">
+        <f>IF(AND(B14="BUY",H14&lt;0),H14,"")</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>IF(K14&lt;&gt;"",A14,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -11645,6 +13344,14 @@
         <f>CurrentPositions!J10</f>
         <v/>
       </c>
+      <c r="K15">
+        <f>IF(AND(B15="BUY",H15&lt;0),H15,"")</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>IF(K15&lt;&gt;"",A15,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -11687,6 +13394,14 @@
         <f>CurrentPositions!J11</f>
         <v/>
       </c>
+      <c r="K16">
+        <f>IF(AND(B16="BUY",H16&lt;0),H16,"")</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>IF(K16&lt;&gt;"",A16,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -11729,6 +13444,14 @@
         <f>CurrentPositions!J12</f>
         <v/>
       </c>
+      <c r="K17">
+        <f>IF(AND(B17="BUY",H17&lt;0),H17,"")</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>IF(K17&lt;&gt;"",A17,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -11771,6 +13494,14 @@
         <f>CurrentPositions!J13</f>
         <v/>
       </c>
+      <c r="K18">
+        <f>IF(AND(B18="BUY",H18&lt;0),H18,"")</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>IF(K18&lt;&gt;"",A18,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -11813,6 +13544,14 @@
         <f>CurrentPositions!J14</f>
         <v/>
       </c>
+      <c r="K19">
+        <f>IF(AND(B19="BUY",H19&lt;0),H19,"")</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>IF(K19&lt;&gt;"",A19,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -11855,6 +13594,14 @@
         <f>CurrentPositions!J15</f>
         <v/>
       </c>
+      <c r="K20">
+        <f>IF(AND(B20="BUY",H20&lt;0),H20,"")</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>IF(K20&lt;&gt;"",A20,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -11897,6 +13644,14 @@
         <f>CurrentPositions!J16</f>
         <v/>
       </c>
+      <c r="K21">
+        <f>IF(AND(B21="BUY",H21&lt;0),H21,"")</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>IF(K21&lt;&gt;"",A21,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -11939,6 +13694,14 @@
         <f>CurrentPositions!J17</f>
         <v/>
       </c>
+      <c r="K22">
+        <f>IF(AND(B22="BUY",H22&lt;0),H22,"")</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>IF(K22&lt;&gt;"",A22,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -11981,6 +13744,14 @@
         <f>CurrentPositions!J18</f>
         <v/>
       </c>
+      <c r="K23">
+        <f>IF(AND(B23="BUY",H23&lt;0),H23,"")</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>IF(K23&lt;&gt;"",A23,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -12023,6 +13794,14 @@
         <f>CurrentPositions!J19</f>
         <v/>
       </c>
+      <c r="K24">
+        <f>IF(AND(B24="BUY",H24&lt;0),H24,"")</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>IF(K24&lt;&gt;"",A24,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -12065,6 +13844,14 @@
         <f>CurrentPositions!J20</f>
         <v/>
       </c>
+      <c r="K25">
+        <f>IF(AND(B25="BUY",H25&lt;0),H25,"")</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>IF(K25&lt;&gt;"",A25,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -12107,6 +13894,14 @@
         <f>CurrentPositions!J21</f>
         <v/>
       </c>
+      <c r="K26">
+        <f>IF(AND(B26="BUY",H26&lt;0),H26,"")</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>IF(K26&lt;&gt;"",A26,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -12149,6 +13944,14 @@
         <f>CurrentPositions!J22</f>
         <v/>
       </c>
+      <c r="K27">
+        <f>IF(AND(B27="BUY",H27&lt;0),H27,"")</f>
+        <v/>
+      </c>
+      <c r="L27">
+        <f>IF(K27&lt;&gt;"",A27,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -12191,6 +13994,14 @@
         <f>CurrentPositions!J23</f>
         <v/>
       </c>
+      <c r="K28">
+        <f>IF(AND(B28="BUY",H28&lt;0),H28,"")</f>
+        <v/>
+      </c>
+      <c r="L28">
+        <f>IF(K28&lt;&gt;"",A28,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -12233,6 +14044,14 @@
         <f>CurrentPositions!J24</f>
         <v/>
       </c>
+      <c r="K29">
+        <f>IF(AND(B29="BUY",H29&lt;0),H29,"")</f>
+        <v/>
+      </c>
+      <c r="L29">
+        <f>IF(K29&lt;&gt;"",A29,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -12275,6 +14094,14 @@
         <f>CurrentPositions!J25</f>
         <v/>
       </c>
+      <c r="K30">
+        <f>IF(AND(B30="BUY",H30&lt;0),H30,"")</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>IF(K30&lt;&gt;"",A30,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -12317,6 +14144,14 @@
         <f>CurrentPositions!J26</f>
         <v/>
       </c>
+      <c r="K31">
+        <f>IF(AND(B31="BUY",H31&lt;0),H31,"")</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>IF(K31&lt;&gt;"",A31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -12359,6 +14194,14 @@
         <f>CurrentPositions!J27</f>
         <v/>
       </c>
+      <c r="K32">
+        <f>IF(AND(B32="BUY",H32&lt;0),H32,"")</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>IF(K32&lt;&gt;"",A32,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -12401,6 +14244,14 @@
         <f>CurrentPositions!J28</f>
         <v/>
       </c>
+      <c r="K33">
+        <f>IF(AND(B33="BUY",H33&lt;0),H33,"")</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>IF(K33&lt;&gt;"",A33,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -12443,6 +14294,14 @@
         <f>CurrentPositions!J29</f>
         <v/>
       </c>
+      <c r="K34">
+        <f>IF(AND(B34="BUY",H34&lt;0),H34,"")</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>IF(K34&lt;&gt;"",A34,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -12485,6 +14344,14 @@
         <f>CurrentPositions!J30</f>
         <v/>
       </c>
+      <c r="K35">
+        <f>IF(AND(B35="BUY",H35&lt;0),H35,"")</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>IF(K35&lt;&gt;"",A35,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -12527,6 +14394,14 @@
         <f>CurrentPositions!J31</f>
         <v/>
       </c>
+      <c r="K36">
+        <f>IF(AND(B36="BUY",H36&lt;0),H36,"")</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>IF(K36&lt;&gt;"",A36,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -12569,6 +14444,14 @@
         <f>CurrentPositions!J32</f>
         <v/>
       </c>
+      <c r="K37">
+        <f>IF(AND(B37="BUY",H37&lt;0),H37,"")</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>IF(K37&lt;&gt;"",A37,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -12611,6 +14494,14 @@
         <f>CurrentPositions!J33</f>
         <v/>
       </c>
+      <c r="K38">
+        <f>IF(AND(B38="BUY",H38&lt;0),H38,"")</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>IF(K38&lt;&gt;"",A38,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -12653,6 +14544,14 @@
         <f>CurrentPositions!J34</f>
         <v/>
       </c>
+      <c r="K39">
+        <f>IF(AND(B39="BUY",H39&lt;0),H39,"")</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>IF(K39&lt;&gt;"",A39,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -12695,6 +14594,14 @@
         <f>CurrentPositions!J35</f>
         <v/>
       </c>
+      <c r="K40">
+        <f>IF(AND(B40="BUY",H40&lt;0),H40,"")</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>IF(K40&lt;&gt;"",A40,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -12737,6 +14644,14 @@
         <f>CurrentPositions!J36</f>
         <v/>
       </c>
+      <c r="K41">
+        <f>IF(AND(B41="BUY",H41&lt;0),H41,"")</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>IF(K41&lt;&gt;"",A41,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -12779,6 +14694,14 @@
         <f>CurrentPositions!J37</f>
         <v/>
       </c>
+      <c r="K42">
+        <f>IF(AND(B42="BUY",H42&lt;0),H42,"")</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>IF(K42&lt;&gt;"",A42,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -12821,6 +14744,14 @@
         <f>CurrentPositions!J38</f>
         <v/>
       </c>
+      <c r="K43">
+        <f>IF(AND(B43="BUY",H43&lt;0),H43,"")</f>
+        <v/>
+      </c>
+      <c r="L43">
+        <f>IF(K43&lt;&gt;"",A43,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -12863,6 +14794,14 @@
         <f>CurrentPositions!J39</f>
         <v/>
       </c>
+      <c r="K44">
+        <f>IF(AND(B44="BUY",H44&lt;0),H44,"")</f>
+        <v/>
+      </c>
+      <c r="L44">
+        <f>IF(K44&lt;&gt;"",A44,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -12905,6 +14844,14 @@
         <f>CurrentPositions!J40</f>
         <v/>
       </c>
+      <c r="K45">
+        <f>IF(AND(B45="BUY",H45&lt;0),H45,"")</f>
+        <v/>
+      </c>
+      <c r="L45">
+        <f>IF(K45&lt;&gt;"",A45,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -12947,6 +14894,14 @@
         <f>CurrentPositions!J41</f>
         <v/>
       </c>
+      <c r="K46">
+        <f>IF(AND(B46="BUY",H46&lt;0),H46,"")</f>
+        <v/>
+      </c>
+      <c r="L46">
+        <f>IF(K46&lt;&gt;"",A46,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -12989,6 +14944,14 @@
         <f>CurrentPositions!J42</f>
         <v/>
       </c>
+      <c r="K47">
+        <f>IF(AND(B47="BUY",H47&lt;0),H47,"")</f>
+        <v/>
+      </c>
+      <c r="L47">
+        <f>IF(K47&lt;&gt;"",A47,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -13031,6 +14994,14 @@
         <f>CurrentPositions!J43</f>
         <v/>
       </c>
+      <c r="K48">
+        <f>IF(AND(B48="BUY",H48&lt;0),H48,"")</f>
+        <v/>
+      </c>
+      <c r="L48">
+        <f>IF(K48&lt;&gt;"",A48,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -13073,6 +15044,14 @@
         <f>CurrentPositions!J44</f>
         <v/>
       </c>
+      <c r="K49">
+        <f>IF(AND(B49="BUY",H49&lt;0),H49,"")</f>
+        <v/>
+      </c>
+      <c r="L49">
+        <f>IF(K49&lt;&gt;"",A49,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -13115,6 +15094,14 @@
         <f>CurrentPositions!J45</f>
         <v/>
       </c>
+      <c r="K50">
+        <f>IF(AND(B50="BUY",H50&lt;0),H50,"")</f>
+        <v/>
+      </c>
+      <c r="L50">
+        <f>IF(K50&lt;&gt;"",A50,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -13157,6 +15144,14 @@
         <f>CurrentPositions!J46</f>
         <v/>
       </c>
+      <c r="K51">
+        <f>IF(AND(B51="BUY",H51&lt;0),H51,"")</f>
+        <v/>
+      </c>
+      <c r="L51">
+        <f>IF(K51&lt;&gt;"",A51,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -13199,6 +15194,14 @@
         <f>CurrentPositions!J47</f>
         <v/>
       </c>
+      <c r="K52">
+        <f>IF(AND(B52="BUY",H52&lt;0),H52,"")</f>
+        <v/>
+      </c>
+      <c r="L52">
+        <f>IF(K52&lt;&gt;"",A52,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -13241,6 +15244,14 @@
         <f>CurrentPositions!J48</f>
         <v/>
       </c>
+      <c r="K53">
+        <f>IF(AND(B53="BUY",H53&lt;0),H53,"")</f>
+        <v/>
+      </c>
+      <c r="L53">
+        <f>IF(K53&lt;&gt;"",A53,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -13283,6 +15294,14 @@
         <f>CurrentPositions!J49</f>
         <v/>
       </c>
+      <c r="K54">
+        <f>IF(AND(B54="BUY",H54&lt;0),H54,"")</f>
+        <v/>
+      </c>
+      <c r="L54">
+        <f>IF(K54&lt;&gt;"",A54,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -13325,6 +15344,14 @@
         <f>CurrentPositions!J50</f>
         <v/>
       </c>
+      <c r="K55">
+        <f>IF(AND(B55="BUY",H55&lt;0),H55,"")</f>
+        <v/>
+      </c>
+      <c r="L55">
+        <f>IF(K55&lt;&gt;"",A55,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -13367,6 +15394,14 @@
         <f>CurrentPositions!J51</f>
         <v/>
       </c>
+      <c r="K56">
+        <f>IF(AND(B56="BUY",H56&lt;0),H56,"")</f>
+        <v/>
+      </c>
+      <c r="L56">
+        <f>IF(K56&lt;&gt;"",A56,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -13409,6 +15444,14 @@
         <f>CurrentPositions!J52</f>
         <v/>
       </c>
+      <c r="K57">
+        <f>IF(AND(B57="BUY",H57&lt;0),H57,"")</f>
+        <v/>
+      </c>
+      <c r="L57">
+        <f>IF(K57&lt;&gt;"",A57,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -13451,6 +15494,14 @@
         <f>CurrentPositions!J53</f>
         <v/>
       </c>
+      <c r="K58">
+        <f>IF(AND(B58="BUY",H58&lt;0),H58,"")</f>
+        <v/>
+      </c>
+      <c r="L58">
+        <f>IF(K58&lt;&gt;"",A58,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -13493,6 +15544,14 @@
         <f>CurrentPositions!J54</f>
         <v/>
       </c>
+      <c r="K59">
+        <f>IF(AND(B59="BUY",H59&lt;0),H59,"")</f>
+        <v/>
+      </c>
+      <c r="L59">
+        <f>IF(K59&lt;&gt;"",A59,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -13535,6 +15594,14 @@
         <f>CurrentPositions!J55</f>
         <v/>
       </c>
+      <c r="K60">
+        <f>IF(AND(B60="BUY",H60&lt;0),H60,"")</f>
+        <v/>
+      </c>
+      <c r="L60">
+        <f>IF(K60&lt;&gt;"",A60,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -13577,6 +15644,14 @@
         <f>CurrentPositions!J56</f>
         <v/>
       </c>
+      <c r="K61">
+        <f>IF(AND(B61="BUY",H61&lt;0),H61,"")</f>
+        <v/>
+      </c>
+      <c r="L61">
+        <f>IF(K61&lt;&gt;"",A61,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -13619,6 +15694,14 @@
         <f>CurrentPositions!J57</f>
         <v/>
       </c>
+      <c r="K62">
+        <f>IF(AND(B62="BUY",H62&lt;0),H62,"")</f>
+        <v/>
+      </c>
+      <c r="L62">
+        <f>IF(K62&lt;&gt;"",A62,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -13661,6 +15744,14 @@
         <f>CurrentPositions!J58</f>
         <v/>
       </c>
+      <c r="K63">
+        <f>IF(AND(B63="BUY",H63&lt;0),H63,"")</f>
+        <v/>
+      </c>
+      <c r="L63">
+        <f>IF(K63&lt;&gt;"",A63,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -13703,6 +15794,14 @@
         <f>CurrentPositions!J59</f>
         <v/>
       </c>
+      <c r="K64">
+        <f>IF(AND(B64="BUY",H64&lt;0),H64,"")</f>
+        <v/>
+      </c>
+      <c r="L64">
+        <f>IF(K64&lt;&gt;"",A64,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -13745,6 +15844,14 @@
         <f>CurrentPositions!J60</f>
         <v/>
       </c>
+      <c r="K65">
+        <f>IF(AND(B65="BUY",H65&lt;0),H65,"")</f>
+        <v/>
+      </c>
+      <c r="L65">
+        <f>IF(K65&lt;&gt;"",A65,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -13787,6 +15894,14 @@
         <f>CurrentPositions!J61</f>
         <v/>
       </c>
+      <c r="K66">
+        <f>IF(AND(B66="BUY",H66&lt;0),H66,"")</f>
+        <v/>
+      </c>
+      <c r="L66">
+        <f>IF(K66&lt;&gt;"",A66,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -13829,6 +15944,14 @@
         <f>CurrentPositions!J62</f>
         <v/>
       </c>
+      <c r="K67">
+        <f>IF(AND(B67="BUY",H67&lt;0),H67,"")</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f>IF(K67&lt;&gt;"",A67,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -13871,6 +15994,14 @@
         <f>CurrentPositions!J63</f>
         <v/>
       </c>
+      <c r="K68">
+        <f>IF(AND(B68="BUY",H68&lt;0),H68,"")</f>
+        <v/>
+      </c>
+      <c r="L68">
+        <f>IF(K68&lt;&gt;"",A68,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -13913,6 +16044,14 @@
         <f>CurrentPositions!J64</f>
         <v/>
       </c>
+      <c r="K69">
+        <f>IF(AND(B69="BUY",H69&lt;0),H69,"")</f>
+        <v/>
+      </c>
+      <c r="L69">
+        <f>IF(K69&lt;&gt;"",A69,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -13955,6 +16094,14 @@
         <f>CurrentPositions!J65</f>
         <v/>
       </c>
+      <c r="K70">
+        <f>IF(AND(B70="BUY",H70&lt;0),H70,"")</f>
+        <v/>
+      </c>
+      <c r="L70">
+        <f>IF(K70&lt;&gt;"",A70,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -13997,6 +16144,14 @@
         <f>CurrentPositions!J66</f>
         <v/>
       </c>
+      <c r="K71">
+        <f>IF(AND(B71="BUY",H71&lt;0),H71,"")</f>
+        <v/>
+      </c>
+      <c r="L71">
+        <f>IF(K71&lt;&gt;"",A71,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -14039,6 +16194,14 @@
         <f>CurrentPositions!J67</f>
         <v/>
       </c>
+      <c r="K72">
+        <f>IF(AND(B72="BUY",H72&lt;0),H72,"")</f>
+        <v/>
+      </c>
+      <c r="L72">
+        <f>IF(K72&lt;&gt;"",A72,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -14081,6 +16244,14 @@
         <f>CurrentPositions!J68</f>
         <v/>
       </c>
+      <c r="K73">
+        <f>IF(AND(B73="BUY",H73&lt;0),H73,"")</f>
+        <v/>
+      </c>
+      <c r="L73">
+        <f>IF(K73&lt;&gt;"",A73,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -14123,6 +16294,14 @@
         <f>CurrentPositions!J69</f>
         <v/>
       </c>
+      <c r="K74">
+        <f>IF(AND(B74="BUY",H74&lt;0),H74,"")</f>
+        <v/>
+      </c>
+      <c r="L74">
+        <f>IF(K74&lt;&gt;"",A74,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -14165,6 +16344,14 @@
         <f>CurrentPositions!J70</f>
         <v/>
       </c>
+      <c r="K75">
+        <f>IF(AND(B75="BUY",H75&lt;0),H75,"")</f>
+        <v/>
+      </c>
+      <c r="L75">
+        <f>IF(K75&lt;&gt;"",A75,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -14207,6 +16394,14 @@
         <f>CurrentPositions!J71</f>
         <v/>
       </c>
+      <c r="K76">
+        <f>IF(AND(B76="BUY",H76&lt;0),H76,"")</f>
+        <v/>
+      </c>
+      <c r="L76">
+        <f>IF(K76&lt;&gt;"",A76,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -14249,6 +16444,14 @@
         <f>CurrentPositions!J72</f>
         <v/>
       </c>
+      <c r="K77">
+        <f>IF(AND(B77="BUY",H77&lt;0),H77,"")</f>
+        <v/>
+      </c>
+      <c r="L77">
+        <f>IF(K77&lt;&gt;"",A77,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -14291,6 +16494,14 @@
         <f>CurrentPositions!J73</f>
         <v/>
       </c>
+      <c r="K78">
+        <f>IF(AND(B78="BUY",H78&lt;0),H78,"")</f>
+        <v/>
+      </c>
+      <c r="L78">
+        <f>IF(K78&lt;&gt;"",A78,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -14333,6 +16544,14 @@
         <f>CurrentPositions!J74</f>
         <v/>
       </c>
+      <c r="K79">
+        <f>IF(AND(B79="BUY",H79&lt;0),H79,"")</f>
+        <v/>
+      </c>
+      <c r="L79">
+        <f>IF(K79&lt;&gt;"",A79,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -14375,6 +16594,14 @@
         <f>CurrentPositions!J75</f>
         <v/>
       </c>
+      <c r="K80">
+        <f>IF(AND(B80="BUY",H80&lt;0),H80,"")</f>
+        <v/>
+      </c>
+      <c r="L80">
+        <f>IF(K80&lt;&gt;"",A80,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -14417,6 +16644,14 @@
         <f>CurrentPositions!J76</f>
         <v/>
       </c>
+      <c r="K81">
+        <f>IF(AND(B81="BUY",H81&lt;0),H81,"")</f>
+        <v/>
+      </c>
+      <c r="L81">
+        <f>IF(K81&lt;&gt;"",A81,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -14459,6 +16694,14 @@
         <f>CurrentPositions!J77</f>
         <v/>
       </c>
+      <c r="K82">
+        <f>IF(AND(B82="BUY",H82&lt;0),H82,"")</f>
+        <v/>
+      </c>
+      <c r="L82">
+        <f>IF(K82&lt;&gt;"",A82,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -14501,6 +16744,14 @@
         <f>CurrentPositions!J78</f>
         <v/>
       </c>
+      <c r="K83">
+        <f>IF(AND(B83="BUY",H83&lt;0),H83,"")</f>
+        <v/>
+      </c>
+      <c r="L83">
+        <f>IF(K83&lt;&gt;"",A83,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -14543,6 +16794,14 @@
         <f>CurrentPositions!J79</f>
         <v/>
       </c>
+      <c r="K84">
+        <f>IF(AND(B84="BUY",H84&lt;0),H84,"")</f>
+        <v/>
+      </c>
+      <c r="L84">
+        <f>IF(K84&lt;&gt;"",A84,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -14585,6 +16844,14 @@
         <f>CurrentPositions!J80</f>
         <v/>
       </c>
+      <c r="K85">
+        <f>IF(AND(B85="BUY",H85&lt;0),H85,"")</f>
+        <v/>
+      </c>
+      <c r="L85">
+        <f>IF(K85&lt;&gt;"",A85,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -14627,6 +16894,14 @@
         <f>CurrentPositions!J81</f>
         <v/>
       </c>
+      <c r="K86">
+        <f>IF(AND(B86="BUY",H86&lt;0),H86,"")</f>
+        <v/>
+      </c>
+      <c r="L86">
+        <f>IF(K86&lt;&gt;"",A86,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -14669,6 +16944,14 @@
         <f>CurrentPositions!J82</f>
         <v/>
       </c>
+      <c r="K87">
+        <f>IF(AND(B87="BUY",H87&lt;0),H87,"")</f>
+        <v/>
+      </c>
+      <c r="L87">
+        <f>IF(K87&lt;&gt;"",A87,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -14711,6 +16994,14 @@
         <f>CurrentPositions!J83</f>
         <v/>
       </c>
+      <c r="K88">
+        <f>IF(AND(B88="BUY",H88&lt;0),H88,"")</f>
+        <v/>
+      </c>
+      <c r="L88">
+        <f>IF(K88&lt;&gt;"",A88,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -14753,6 +17044,14 @@
         <f>CurrentPositions!J84</f>
         <v/>
       </c>
+      <c r="K89">
+        <f>IF(AND(B89="BUY",H89&lt;0),H89,"")</f>
+        <v/>
+      </c>
+      <c r="L89">
+        <f>IF(K89&lt;&gt;"",A89,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -14795,6 +17094,14 @@
         <f>CurrentPositions!J85</f>
         <v/>
       </c>
+      <c r="K90">
+        <f>IF(AND(B90="BUY",H90&lt;0),H90,"")</f>
+        <v/>
+      </c>
+      <c r="L90">
+        <f>IF(K90&lt;&gt;"",A90,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -14837,6 +17144,14 @@
         <f>CurrentPositions!J86</f>
         <v/>
       </c>
+      <c r="K91">
+        <f>IF(AND(B91="BUY",H91&lt;0),H91,"")</f>
+        <v/>
+      </c>
+      <c r="L91">
+        <f>IF(K91&lt;&gt;"",A91,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -14879,6 +17194,14 @@
         <f>CurrentPositions!J87</f>
         <v/>
       </c>
+      <c r="K92">
+        <f>IF(AND(B92="BUY",H92&lt;0),H92,"")</f>
+        <v/>
+      </c>
+      <c r="L92">
+        <f>IF(K92&lt;&gt;"",A92,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -14921,6 +17244,14 @@
         <f>CurrentPositions!J88</f>
         <v/>
       </c>
+      <c r="K93">
+        <f>IF(AND(B93="BUY",H93&lt;0),H93,"")</f>
+        <v/>
+      </c>
+      <c r="L93">
+        <f>IF(K93&lt;&gt;"",A93,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -14963,6 +17294,14 @@
         <f>CurrentPositions!J89</f>
         <v/>
       </c>
+      <c r="K94">
+        <f>IF(AND(B94="BUY",H94&lt;0),H94,"")</f>
+        <v/>
+      </c>
+      <c r="L94">
+        <f>IF(K94&lt;&gt;"",A94,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -15005,6 +17344,14 @@
         <f>CurrentPositions!J90</f>
         <v/>
       </c>
+      <c r="K95">
+        <f>IF(AND(B95="BUY",H95&lt;0),H95,"")</f>
+        <v/>
+      </c>
+      <c r="L95">
+        <f>IF(K95&lt;&gt;"",A95,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -15047,6 +17394,14 @@
         <f>CurrentPositions!J91</f>
         <v/>
       </c>
+      <c r="K96">
+        <f>IF(AND(B96="BUY",H96&lt;0),H96,"")</f>
+        <v/>
+      </c>
+      <c r="L96">
+        <f>IF(K96&lt;&gt;"",A96,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -15089,6 +17444,14 @@
         <f>CurrentPositions!J92</f>
         <v/>
       </c>
+      <c r="K97">
+        <f>IF(AND(B97="BUY",H97&lt;0),H97,"")</f>
+        <v/>
+      </c>
+      <c r="L97">
+        <f>IF(K97&lt;&gt;"",A97,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -15131,6 +17494,14 @@
         <f>CurrentPositions!J93</f>
         <v/>
       </c>
+      <c r="K98">
+        <f>IF(AND(B98="BUY",H98&lt;0),H98,"")</f>
+        <v/>
+      </c>
+      <c r="L98">
+        <f>IF(K98&lt;&gt;"",A98,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -15173,6 +17544,14 @@
         <f>CurrentPositions!J94</f>
         <v/>
       </c>
+      <c r="K99">
+        <f>IF(AND(B99="BUY",H99&lt;0),H99,"")</f>
+        <v/>
+      </c>
+      <c r="L99">
+        <f>IF(K99&lt;&gt;"",A99,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -15215,6 +17594,14 @@
         <f>CurrentPositions!J95</f>
         <v/>
       </c>
+      <c r="K100">
+        <f>IF(AND(B100="BUY",H100&lt;0),H100,"")</f>
+        <v/>
+      </c>
+      <c r="L100">
+        <f>IF(K100&lt;&gt;"",A100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -15257,6 +17644,14 @@
         <f>CurrentPositions!J96</f>
         <v/>
       </c>
+      <c r="K101">
+        <f>IF(AND(B101="BUY",H101&lt;0),H101,"")</f>
+        <v/>
+      </c>
+      <c r="L101">
+        <f>IF(K101&lt;&gt;"",A101,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -15299,6 +17694,14 @@
         <f>CurrentPositions!J97</f>
         <v/>
       </c>
+      <c r="K102">
+        <f>IF(AND(B102="BUY",H102&lt;0),H102,"")</f>
+        <v/>
+      </c>
+      <c r="L102">
+        <f>IF(K102&lt;&gt;"",A102,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -15341,6 +17744,14 @@
         <f>CurrentPositions!J98</f>
         <v/>
       </c>
+      <c r="K103">
+        <f>IF(AND(B103="BUY",H103&lt;0),H103,"")</f>
+        <v/>
+      </c>
+      <c r="L103">
+        <f>IF(K103&lt;&gt;"",A103,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -15383,6 +17794,14 @@
         <f>CurrentPositions!J99</f>
         <v/>
       </c>
+      <c r="K104">
+        <f>IF(AND(B104="BUY",H104&lt;0),H104,"")</f>
+        <v/>
+      </c>
+      <c r="L104">
+        <f>IF(K104&lt;&gt;"",A104,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -15425,6 +17844,14 @@
         <f>CurrentPositions!J100</f>
         <v/>
       </c>
+      <c r="K105">
+        <f>IF(AND(B105="BUY",H105&lt;0),H105,"")</f>
+        <v/>
+      </c>
+      <c r="L105">
+        <f>IF(K105&lt;&gt;"",A105,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -15467,6 +17894,14 @@
         <f>CurrentPositions!J101</f>
         <v/>
       </c>
+      <c r="K106">
+        <f>IF(AND(B106="BUY",H106&lt;0),H106,"")</f>
+        <v/>
+      </c>
+      <c r="L106">
+        <f>IF(K106&lt;&gt;"",A106,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -15509,6 +17944,14 @@
         <f>CurrentPositions!J102</f>
         <v/>
       </c>
+      <c r="K107">
+        <f>IF(AND(B107="BUY",H107&lt;0),H107,"")</f>
+        <v/>
+      </c>
+      <c r="L107">
+        <f>IF(K107&lt;&gt;"",A107,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -15551,6 +17994,14 @@
         <f>CurrentPositions!J103</f>
         <v/>
       </c>
+      <c r="K108">
+        <f>IF(AND(B108="BUY",H108&lt;0),H108,"")</f>
+        <v/>
+      </c>
+      <c r="L108">
+        <f>IF(K108&lt;&gt;"",A108,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -15593,6 +18044,14 @@
         <f>CurrentPositions!J104</f>
         <v/>
       </c>
+      <c r="K109">
+        <f>IF(AND(B109="BUY",H109&lt;0),H109,"")</f>
+        <v/>
+      </c>
+      <c r="L109">
+        <f>IF(K109&lt;&gt;"",A109,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -15635,6 +18094,14 @@
         <f>CurrentPositions!J105</f>
         <v/>
       </c>
+      <c r="K110">
+        <f>IF(AND(B110="BUY",H110&lt;0),H110,"")</f>
+        <v/>
+      </c>
+      <c r="L110">
+        <f>IF(K110&lt;&gt;"",A110,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -15677,6 +18144,14 @@
         <f>CurrentPositions!J106</f>
         <v/>
       </c>
+      <c r="K111">
+        <f>IF(AND(B111="BUY",H111&lt;0),H111,"")</f>
+        <v/>
+      </c>
+      <c r="L111">
+        <f>IF(K111&lt;&gt;"",A111,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -15719,6 +18194,14 @@
         <f>CurrentPositions!J107</f>
         <v/>
       </c>
+      <c r="K112">
+        <f>IF(AND(B112="BUY",H112&lt;0),H112,"")</f>
+        <v/>
+      </c>
+      <c r="L112">
+        <f>IF(K112&lt;&gt;"",A112,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -15761,6 +18244,14 @@
         <f>CurrentPositions!J108</f>
         <v/>
       </c>
+      <c r="K113">
+        <f>IF(AND(B113="BUY",H113&lt;0),H113,"")</f>
+        <v/>
+      </c>
+      <c r="L113">
+        <f>IF(K113&lt;&gt;"",A113,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -15803,6 +18294,14 @@
         <f>CurrentPositions!J109</f>
         <v/>
       </c>
+      <c r="K114">
+        <f>IF(AND(B114="BUY",H114&lt;0),H114,"")</f>
+        <v/>
+      </c>
+      <c r="L114">
+        <f>IF(K114&lt;&gt;"",A114,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -15845,6 +18344,14 @@
         <f>CurrentPositions!J110</f>
         <v/>
       </c>
+      <c r="K115">
+        <f>IF(AND(B115="BUY",H115&lt;0),H115,"")</f>
+        <v/>
+      </c>
+      <c r="L115">
+        <f>IF(K115&lt;&gt;"",A115,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -15887,6 +18394,14 @@
         <f>CurrentPositions!J111</f>
         <v/>
       </c>
+      <c r="K116">
+        <f>IF(AND(B116="BUY",H116&lt;0),H116,"")</f>
+        <v/>
+      </c>
+      <c r="L116">
+        <f>IF(K116&lt;&gt;"",A116,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -15929,6 +18444,14 @@
         <f>CurrentPositions!J112</f>
         <v/>
       </c>
+      <c r="K117">
+        <f>IF(AND(B117="BUY",H117&lt;0),H117,"")</f>
+        <v/>
+      </c>
+      <c r="L117">
+        <f>IF(K117&lt;&gt;"",A117,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -15971,6 +18494,14 @@
         <f>CurrentPositions!J113</f>
         <v/>
       </c>
+      <c r="K118">
+        <f>IF(AND(B118="BUY",H118&lt;0),H118,"")</f>
+        <v/>
+      </c>
+      <c r="L118">
+        <f>IF(K118&lt;&gt;"",A118,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -16013,6 +18544,14 @@
         <f>CurrentPositions!J114</f>
         <v/>
       </c>
+      <c r="K119">
+        <f>IF(AND(B119="BUY",H119&lt;0),H119,"")</f>
+        <v/>
+      </c>
+      <c r="L119">
+        <f>IF(K119&lt;&gt;"",A119,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -16055,6 +18594,14 @@
         <f>CurrentPositions!J115</f>
         <v/>
       </c>
+      <c r="K120">
+        <f>IF(AND(B120="BUY",H120&lt;0),H120,"")</f>
+        <v/>
+      </c>
+      <c r="L120">
+        <f>IF(K120&lt;&gt;"",A120,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -16097,6 +18644,14 @@
         <f>CurrentPositions!J116</f>
         <v/>
       </c>
+      <c r="K121">
+        <f>IF(AND(B121="BUY",H121&lt;0),H121,"")</f>
+        <v/>
+      </c>
+      <c r="L121">
+        <f>IF(K121&lt;&gt;"",A121,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -16139,6 +18694,14 @@
         <f>CurrentPositions!J117</f>
         <v/>
       </c>
+      <c r="K122">
+        <f>IF(AND(B122="BUY",H122&lt;0),H122,"")</f>
+        <v/>
+      </c>
+      <c r="L122">
+        <f>IF(K122&lt;&gt;"",A122,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -16181,6 +18744,14 @@
         <f>CurrentPositions!J118</f>
         <v/>
       </c>
+      <c r="K123">
+        <f>IF(AND(B123="BUY",H123&lt;0),H123,"")</f>
+        <v/>
+      </c>
+      <c r="L123">
+        <f>IF(K123&lt;&gt;"",A123,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -16223,6 +18794,14 @@
         <f>CurrentPositions!J119</f>
         <v/>
       </c>
+      <c r="K124">
+        <f>IF(AND(B124="BUY",H124&lt;0),H124,"")</f>
+        <v/>
+      </c>
+      <c r="L124">
+        <f>IF(K124&lt;&gt;"",A124,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -16265,6 +18844,14 @@
         <f>CurrentPositions!J120</f>
         <v/>
       </c>
+      <c r="K125">
+        <f>IF(AND(B125="BUY",H125&lt;0),H125,"")</f>
+        <v/>
+      </c>
+      <c r="L125">
+        <f>IF(K125&lt;&gt;"",A125,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -16307,6 +18894,14 @@
         <f>CurrentPositions!J121</f>
         <v/>
       </c>
+      <c r="K126">
+        <f>IF(AND(B126="BUY",H126&lt;0),H126,"")</f>
+        <v/>
+      </c>
+      <c r="L126">
+        <f>IF(K126&lt;&gt;"",A126,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -16349,6 +18944,14 @@
         <f>CurrentPositions!J122</f>
         <v/>
       </c>
+      <c r="K127">
+        <f>IF(AND(B127="BUY",H127&lt;0),H127,"")</f>
+        <v/>
+      </c>
+      <c r="L127">
+        <f>IF(K127&lt;&gt;"",A127,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -16391,6 +18994,14 @@
         <f>CurrentPositions!J123</f>
         <v/>
       </c>
+      <c r="K128">
+        <f>IF(AND(B128="BUY",H128&lt;0),H128,"")</f>
+        <v/>
+      </c>
+      <c r="L128">
+        <f>IF(K128&lt;&gt;"",A128,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -16433,6 +19044,14 @@
         <f>CurrentPositions!J124</f>
         <v/>
       </c>
+      <c r="K129">
+        <f>IF(AND(B129="BUY",H129&lt;0),H129,"")</f>
+        <v/>
+      </c>
+      <c r="L129">
+        <f>IF(K129&lt;&gt;"",A129,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -16475,6 +19094,14 @@
         <f>CurrentPositions!J125</f>
         <v/>
       </c>
+      <c r="K130">
+        <f>IF(AND(B130="BUY",H130&lt;0),H130,"")</f>
+        <v/>
+      </c>
+      <c r="L130">
+        <f>IF(K130&lt;&gt;"",A130,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -16517,6 +19144,14 @@
         <f>CurrentPositions!J126</f>
         <v/>
       </c>
+      <c r="K131">
+        <f>IF(AND(B131="BUY",H131&lt;0),H131,"")</f>
+        <v/>
+      </c>
+      <c r="L131">
+        <f>IF(K131&lt;&gt;"",A131,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -16559,6 +19194,14 @@
         <f>CurrentPositions!J127</f>
         <v/>
       </c>
+      <c r="K132">
+        <f>IF(AND(B132="BUY",H132&lt;0),H132,"")</f>
+        <v/>
+      </c>
+      <c r="L132">
+        <f>IF(K132&lt;&gt;"",A132,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -16601,6 +19244,14 @@
         <f>CurrentPositions!J128</f>
         <v/>
       </c>
+      <c r="K133">
+        <f>IF(AND(B133="BUY",H133&lt;0),H133,"")</f>
+        <v/>
+      </c>
+      <c r="L133">
+        <f>IF(K133&lt;&gt;"",A133,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -16643,6 +19294,14 @@
         <f>CurrentPositions!J129</f>
         <v/>
       </c>
+      <c r="K134">
+        <f>IF(AND(B134="BUY",H134&lt;0),H134,"")</f>
+        <v/>
+      </c>
+      <c r="L134">
+        <f>IF(K134&lt;&gt;"",A134,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -16685,6 +19344,14 @@
         <f>CurrentPositions!J130</f>
         <v/>
       </c>
+      <c r="K135">
+        <f>IF(AND(B135="BUY",H135&lt;0),H135,"")</f>
+        <v/>
+      </c>
+      <c r="L135">
+        <f>IF(K135&lt;&gt;"",A135,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -16727,6 +19394,14 @@
         <f>CurrentPositions!J131</f>
         <v/>
       </c>
+      <c r="K136">
+        <f>IF(AND(B136="BUY",H136&lt;0),H136,"")</f>
+        <v/>
+      </c>
+      <c r="L136">
+        <f>IF(K136&lt;&gt;"",A136,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -16769,6 +19444,14 @@
         <f>CurrentPositions!J132</f>
         <v/>
       </c>
+      <c r="K137">
+        <f>IF(AND(B137="BUY",H137&lt;0),H137,"")</f>
+        <v/>
+      </c>
+      <c r="L137">
+        <f>IF(K137&lt;&gt;"",A137,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -16811,6 +19494,14 @@
         <f>CurrentPositions!J133</f>
         <v/>
       </c>
+      <c r="K138">
+        <f>IF(AND(B138="BUY",H138&lt;0),H138,"")</f>
+        <v/>
+      </c>
+      <c r="L138">
+        <f>IF(K138&lt;&gt;"",A138,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -16853,6 +19544,14 @@
         <f>CurrentPositions!J134</f>
         <v/>
       </c>
+      <c r="K139">
+        <f>IF(AND(B139="BUY",H139&lt;0),H139,"")</f>
+        <v/>
+      </c>
+      <c r="L139">
+        <f>IF(K139&lt;&gt;"",A139,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -16895,6 +19594,14 @@
         <f>CurrentPositions!J135</f>
         <v/>
       </c>
+      <c r="K140">
+        <f>IF(AND(B140="BUY",H140&lt;0),H140,"")</f>
+        <v/>
+      </c>
+      <c r="L140">
+        <f>IF(K140&lt;&gt;"",A140,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -16937,6 +19644,14 @@
         <f>CurrentPositions!J136</f>
         <v/>
       </c>
+      <c r="K141">
+        <f>IF(AND(B141="BUY",H141&lt;0),H141,"")</f>
+        <v/>
+      </c>
+      <c r="L141">
+        <f>IF(K141&lt;&gt;"",A141,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -16979,6 +19694,14 @@
         <f>CurrentPositions!J137</f>
         <v/>
       </c>
+      <c r="K142">
+        <f>IF(AND(B142="BUY",H142&lt;0),H142,"")</f>
+        <v/>
+      </c>
+      <c r="L142">
+        <f>IF(K142&lt;&gt;"",A142,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -17021,6 +19744,14 @@
         <f>CurrentPositions!J138</f>
         <v/>
       </c>
+      <c r="K143">
+        <f>IF(AND(B143="BUY",H143&lt;0),H143,"")</f>
+        <v/>
+      </c>
+      <c r="L143">
+        <f>IF(K143&lt;&gt;"",A143,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -17063,6 +19794,14 @@
         <f>CurrentPositions!J139</f>
         <v/>
       </c>
+      <c r="K144">
+        <f>IF(AND(B144="BUY",H144&lt;0),H144,"")</f>
+        <v/>
+      </c>
+      <c r="L144">
+        <f>IF(K144&lt;&gt;"",A144,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -17105,6 +19844,14 @@
         <f>CurrentPositions!J140</f>
         <v/>
       </c>
+      <c r="K145">
+        <f>IF(AND(B145="BUY",H145&lt;0),H145,"")</f>
+        <v/>
+      </c>
+      <c r="L145">
+        <f>IF(K145&lt;&gt;"",A145,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -17147,6 +19894,14 @@
         <f>CurrentPositions!J141</f>
         <v/>
       </c>
+      <c r="K146">
+        <f>IF(AND(B146="BUY",H146&lt;0),H146,"")</f>
+        <v/>
+      </c>
+      <c r="L146">
+        <f>IF(K146&lt;&gt;"",A146,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -17189,6 +19944,14 @@
         <f>CurrentPositions!J142</f>
         <v/>
       </c>
+      <c r="K147">
+        <f>IF(AND(B147="BUY",H147&lt;0),H147,"")</f>
+        <v/>
+      </c>
+      <c r="L147">
+        <f>IF(K147&lt;&gt;"",A147,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -17231,6 +19994,14 @@
         <f>CurrentPositions!J143</f>
         <v/>
       </c>
+      <c r="K148">
+        <f>IF(AND(B148="BUY",H148&lt;0),H148,"")</f>
+        <v/>
+      </c>
+      <c r="L148">
+        <f>IF(K148&lt;&gt;"",A148,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -17273,6 +20044,14 @@
         <f>CurrentPositions!J144</f>
         <v/>
       </c>
+      <c r="K149">
+        <f>IF(AND(B149="BUY",H149&lt;0),H149,"")</f>
+        <v/>
+      </c>
+      <c r="L149">
+        <f>IF(K149&lt;&gt;"",A149,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -17315,6 +20094,14 @@
         <f>CurrentPositions!J145</f>
         <v/>
       </c>
+      <c r="K150">
+        <f>IF(AND(B150="BUY",H150&lt;0),H150,"")</f>
+        <v/>
+      </c>
+      <c r="L150">
+        <f>IF(K150&lt;&gt;"",A150,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -17357,6 +20144,14 @@
         <f>CurrentPositions!J146</f>
         <v/>
       </c>
+      <c r="K151">
+        <f>IF(AND(B151="BUY",H151&lt;0),H151,"")</f>
+        <v/>
+      </c>
+      <c r="L151">
+        <f>IF(K151&lt;&gt;"",A151,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -17399,6 +20194,14 @@
         <f>CurrentPositions!J147</f>
         <v/>
       </c>
+      <c r="K152">
+        <f>IF(AND(B152="BUY",H152&lt;0),H152,"")</f>
+        <v/>
+      </c>
+      <c r="L152">
+        <f>IF(K152&lt;&gt;"",A152,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -17441,6 +20244,14 @@
         <f>CurrentPositions!J148</f>
         <v/>
       </c>
+      <c r="K153">
+        <f>IF(AND(B153="BUY",H153&lt;0),H153,"")</f>
+        <v/>
+      </c>
+      <c r="L153">
+        <f>IF(K153&lt;&gt;"",A153,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -17483,6 +20294,14 @@
         <f>CurrentPositions!J149</f>
         <v/>
       </c>
+      <c r="K154">
+        <f>IF(AND(B154="BUY",H154&lt;0),H154,"")</f>
+        <v/>
+      </c>
+      <c r="L154">
+        <f>IF(K154&lt;&gt;"",A154,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -17525,6 +20344,14 @@
         <f>CurrentPositions!J150</f>
         <v/>
       </c>
+      <c r="K155">
+        <f>IF(AND(B155="BUY",H155&lt;0),H155,"")</f>
+        <v/>
+      </c>
+      <c r="L155">
+        <f>IF(K155&lt;&gt;"",A155,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -17567,6 +20394,14 @@
         <f>CurrentPositions!J151</f>
         <v/>
       </c>
+      <c r="K156">
+        <f>IF(AND(B156="BUY",H156&lt;0),H156,"")</f>
+        <v/>
+      </c>
+      <c r="L156">
+        <f>IF(K156&lt;&gt;"",A156,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -17609,6 +20444,14 @@
         <f>CurrentPositions!J152</f>
         <v/>
       </c>
+      <c r="K157">
+        <f>IF(AND(B157="BUY",H157&lt;0),H157,"")</f>
+        <v/>
+      </c>
+      <c r="L157">
+        <f>IF(K157&lt;&gt;"",A157,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -17651,6 +20494,14 @@
         <f>CurrentPositions!J153</f>
         <v/>
       </c>
+      <c r="K158">
+        <f>IF(AND(B158="BUY",H158&lt;0),H158,"")</f>
+        <v/>
+      </c>
+      <c r="L158">
+        <f>IF(K158&lt;&gt;"",A158,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -17693,6 +20544,14 @@
         <f>CurrentPositions!J154</f>
         <v/>
       </c>
+      <c r="K159">
+        <f>IF(AND(B159="BUY",H159&lt;0),H159,"")</f>
+        <v/>
+      </c>
+      <c r="L159">
+        <f>IF(K159&lt;&gt;"",A159,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -17735,6 +20594,14 @@
         <f>CurrentPositions!J155</f>
         <v/>
       </c>
+      <c r="K160">
+        <f>IF(AND(B160="BUY",H160&lt;0),H160,"")</f>
+        <v/>
+      </c>
+      <c r="L160">
+        <f>IF(K160&lt;&gt;"",A160,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -17777,6 +20644,14 @@
         <f>CurrentPositions!J156</f>
         <v/>
       </c>
+      <c r="K161">
+        <f>IF(AND(B161="BUY",H161&lt;0),H161,"")</f>
+        <v/>
+      </c>
+      <c r="L161">
+        <f>IF(K161&lt;&gt;"",A161,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -17819,6 +20694,14 @@
         <f>CurrentPositions!J157</f>
         <v/>
       </c>
+      <c r="K162">
+        <f>IF(AND(B162="BUY",H162&lt;0),H162,"")</f>
+        <v/>
+      </c>
+      <c r="L162">
+        <f>IF(K162&lt;&gt;"",A162,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -17861,6 +20744,14 @@
         <f>CurrentPositions!J158</f>
         <v/>
       </c>
+      <c r="K163">
+        <f>IF(AND(B163="BUY",H163&lt;0),H163,"")</f>
+        <v/>
+      </c>
+      <c r="L163">
+        <f>IF(K163&lt;&gt;"",A163,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -17903,6 +20794,14 @@
         <f>CurrentPositions!J159</f>
         <v/>
       </c>
+      <c r="K164">
+        <f>IF(AND(B164="BUY",H164&lt;0),H164,"")</f>
+        <v/>
+      </c>
+      <c r="L164">
+        <f>IF(K164&lt;&gt;"",A164,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -17945,6 +20844,14 @@
         <f>CurrentPositions!J160</f>
         <v/>
       </c>
+      <c r="K165">
+        <f>IF(AND(B165="BUY",H165&lt;0),H165,"")</f>
+        <v/>
+      </c>
+      <c r="L165">
+        <f>IF(K165&lt;&gt;"",A165,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -17987,6 +20894,14 @@
         <f>CurrentPositions!J161</f>
         <v/>
       </c>
+      <c r="K166">
+        <f>IF(AND(B166="BUY",H166&lt;0),H166,"")</f>
+        <v/>
+      </c>
+      <c r="L166">
+        <f>IF(K166&lt;&gt;"",A166,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -18029,6 +20944,14 @@
         <f>CurrentPositions!J162</f>
         <v/>
       </c>
+      <c r="K167">
+        <f>IF(AND(B167="BUY",H167&lt;0),H167,"")</f>
+        <v/>
+      </c>
+      <c r="L167">
+        <f>IF(K167&lt;&gt;"",A167,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -18071,6 +20994,14 @@
         <f>CurrentPositions!J163</f>
         <v/>
       </c>
+      <c r="K168">
+        <f>IF(AND(B168="BUY",H168&lt;0),H168,"")</f>
+        <v/>
+      </c>
+      <c r="L168">
+        <f>IF(K168&lt;&gt;"",A168,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -18113,6 +21044,14 @@
         <f>CurrentPositions!J164</f>
         <v/>
       </c>
+      <c r="K169">
+        <f>IF(AND(B169="BUY",H169&lt;0),H169,"")</f>
+        <v/>
+      </c>
+      <c r="L169">
+        <f>IF(K169&lt;&gt;"",A169,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -18155,6 +21094,14 @@
         <f>CurrentPositions!J165</f>
         <v/>
       </c>
+      <c r="K170">
+        <f>IF(AND(B170="BUY",H170&lt;0),H170,"")</f>
+        <v/>
+      </c>
+      <c r="L170">
+        <f>IF(K170&lt;&gt;"",A170,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -18197,6 +21144,14 @@
         <f>CurrentPositions!J166</f>
         <v/>
       </c>
+      <c r="K171">
+        <f>IF(AND(B171="BUY",H171&lt;0),H171,"")</f>
+        <v/>
+      </c>
+      <c r="L171">
+        <f>IF(K171&lt;&gt;"",A171,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -18239,6 +21194,14 @@
         <f>CurrentPositions!J167</f>
         <v/>
       </c>
+      <c r="K172">
+        <f>IF(AND(B172="BUY",H172&lt;0),H172,"")</f>
+        <v/>
+      </c>
+      <c r="L172">
+        <f>IF(K172&lt;&gt;"",A172,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -18281,6 +21244,14 @@
         <f>CurrentPositions!J168</f>
         <v/>
       </c>
+      <c r="K173">
+        <f>IF(AND(B173="BUY",H173&lt;0),H173,"")</f>
+        <v/>
+      </c>
+      <c r="L173">
+        <f>IF(K173&lt;&gt;"",A173,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -18323,6 +21294,14 @@
         <f>CurrentPositions!J169</f>
         <v/>
       </c>
+      <c r="K174">
+        <f>IF(AND(B174="BUY",H174&lt;0),H174,"")</f>
+        <v/>
+      </c>
+      <c r="L174">
+        <f>IF(K174&lt;&gt;"",A174,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -18365,6 +21344,14 @@
         <f>CurrentPositions!J170</f>
         <v/>
       </c>
+      <c r="K175">
+        <f>IF(AND(B175="BUY",H175&lt;0),H175,"")</f>
+        <v/>
+      </c>
+      <c r="L175">
+        <f>IF(K175&lt;&gt;"",A175,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -18407,6 +21394,14 @@
         <f>CurrentPositions!J171</f>
         <v/>
       </c>
+      <c r="K176">
+        <f>IF(AND(B176="BUY",H176&lt;0),H176,"")</f>
+        <v/>
+      </c>
+      <c r="L176">
+        <f>IF(K176&lt;&gt;"",A176,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -18449,6 +21444,14 @@
         <f>CurrentPositions!J172</f>
         <v/>
       </c>
+      <c r="K177">
+        <f>IF(AND(B177="BUY",H177&lt;0),H177,"")</f>
+        <v/>
+      </c>
+      <c r="L177">
+        <f>IF(K177&lt;&gt;"",A177,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -18491,6 +21494,14 @@
         <f>CurrentPositions!J173</f>
         <v/>
       </c>
+      <c r="K178">
+        <f>IF(AND(B178="BUY",H178&lt;0),H178,"")</f>
+        <v/>
+      </c>
+      <c r="L178">
+        <f>IF(K178&lt;&gt;"",A178,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -18533,6 +21544,14 @@
         <f>CurrentPositions!J174</f>
         <v/>
       </c>
+      <c r="K179">
+        <f>IF(AND(B179="BUY",H179&lt;0),H179,"")</f>
+        <v/>
+      </c>
+      <c r="L179">
+        <f>IF(K179&lt;&gt;"",A179,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -18575,6 +21594,14 @@
         <f>CurrentPositions!J175</f>
         <v/>
       </c>
+      <c r="K180">
+        <f>IF(AND(B180="BUY",H180&lt;0),H180,"")</f>
+        <v/>
+      </c>
+      <c r="L180">
+        <f>IF(K180&lt;&gt;"",A180,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -18617,6 +21644,14 @@
         <f>CurrentPositions!J176</f>
         <v/>
       </c>
+      <c r="K181">
+        <f>IF(AND(B181="BUY",H181&lt;0),H181,"")</f>
+        <v/>
+      </c>
+      <c r="L181">
+        <f>IF(K181&lt;&gt;"",A181,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -18659,6 +21694,14 @@
         <f>CurrentPositions!J177</f>
         <v/>
       </c>
+      <c r="K182">
+        <f>IF(AND(B182="BUY",H182&lt;0),H182,"")</f>
+        <v/>
+      </c>
+      <c r="L182">
+        <f>IF(K182&lt;&gt;"",A182,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -18701,6 +21744,14 @@
         <f>CurrentPositions!J178</f>
         <v/>
       </c>
+      <c r="K183">
+        <f>IF(AND(B183="BUY",H183&lt;0),H183,"")</f>
+        <v/>
+      </c>
+      <c r="L183">
+        <f>IF(K183&lt;&gt;"",A183,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -18743,6 +21794,14 @@
         <f>CurrentPositions!J179</f>
         <v/>
       </c>
+      <c r="K184">
+        <f>IF(AND(B184="BUY",H184&lt;0),H184,"")</f>
+        <v/>
+      </c>
+      <c r="L184">
+        <f>IF(K184&lt;&gt;"",A184,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -18785,6 +21844,14 @@
         <f>CurrentPositions!J180</f>
         <v/>
       </c>
+      <c r="K185">
+        <f>IF(AND(B185="BUY",H185&lt;0),H185,"")</f>
+        <v/>
+      </c>
+      <c r="L185">
+        <f>IF(K185&lt;&gt;"",A185,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -18827,6 +21894,14 @@
         <f>CurrentPositions!J181</f>
         <v/>
       </c>
+      <c r="K186">
+        <f>IF(AND(B186="BUY",H186&lt;0),H186,"")</f>
+        <v/>
+      </c>
+      <c r="L186">
+        <f>IF(K186&lt;&gt;"",A186,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -18869,6 +21944,14 @@
         <f>CurrentPositions!J182</f>
         <v/>
       </c>
+      <c r="K187">
+        <f>IF(AND(B187="BUY",H187&lt;0),H187,"")</f>
+        <v/>
+      </c>
+      <c r="L187">
+        <f>IF(K187&lt;&gt;"",A187,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -18911,6 +21994,14 @@
         <f>CurrentPositions!J183</f>
         <v/>
       </c>
+      <c r="K188">
+        <f>IF(AND(B188="BUY",H188&lt;0),H188,"")</f>
+        <v/>
+      </c>
+      <c r="L188">
+        <f>IF(K188&lt;&gt;"",A188,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -18953,6 +22044,14 @@
         <f>CurrentPositions!J184</f>
         <v/>
       </c>
+      <c r="K189">
+        <f>IF(AND(B189="BUY",H189&lt;0),H189,"")</f>
+        <v/>
+      </c>
+      <c r="L189">
+        <f>IF(K189&lt;&gt;"",A189,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -18995,6 +22094,14 @@
         <f>CurrentPositions!J185</f>
         <v/>
       </c>
+      <c r="K190">
+        <f>IF(AND(B190="BUY",H190&lt;0),H190,"")</f>
+        <v/>
+      </c>
+      <c r="L190">
+        <f>IF(K190&lt;&gt;"",A190,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -19037,6 +22144,14 @@
         <f>CurrentPositions!J186</f>
         <v/>
       </c>
+      <c r="K191">
+        <f>IF(AND(B191="BUY",H191&lt;0),H191,"")</f>
+        <v/>
+      </c>
+      <c r="L191">
+        <f>IF(K191&lt;&gt;"",A191,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -19079,6 +22194,14 @@
         <f>CurrentPositions!J187</f>
         <v/>
       </c>
+      <c r="K192">
+        <f>IF(AND(B192="BUY",H192&lt;0),H192,"")</f>
+        <v/>
+      </c>
+      <c r="L192">
+        <f>IF(K192&lt;&gt;"",A192,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -19121,6 +22244,14 @@
         <f>CurrentPositions!J188</f>
         <v/>
       </c>
+      <c r="K193">
+        <f>IF(AND(B193="BUY",H193&lt;0),H193,"")</f>
+        <v/>
+      </c>
+      <c r="L193">
+        <f>IF(K193&lt;&gt;"",A193,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -19163,6 +22294,14 @@
         <f>CurrentPositions!J189</f>
         <v/>
       </c>
+      <c r="K194">
+        <f>IF(AND(B194="BUY",H194&lt;0),H194,"")</f>
+        <v/>
+      </c>
+      <c r="L194">
+        <f>IF(K194&lt;&gt;"",A194,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -19205,6 +22344,14 @@
         <f>CurrentPositions!J190</f>
         <v/>
       </c>
+      <c r="K195">
+        <f>IF(AND(B195="BUY",H195&lt;0),H195,"")</f>
+        <v/>
+      </c>
+      <c r="L195">
+        <f>IF(K195&lt;&gt;"",A195,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -19247,6 +22394,14 @@
         <f>CurrentPositions!J191</f>
         <v/>
       </c>
+      <c r="K196">
+        <f>IF(AND(B196="BUY",H196&lt;0),H196,"")</f>
+        <v/>
+      </c>
+      <c r="L196">
+        <f>IF(K196&lt;&gt;"",A196,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -19289,6 +22444,14 @@
         <f>CurrentPositions!J192</f>
         <v/>
       </c>
+      <c r="K197">
+        <f>IF(AND(B197="BUY",H197&lt;0),H197,"")</f>
+        <v/>
+      </c>
+      <c r="L197">
+        <f>IF(K197&lt;&gt;"",A197,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -19331,6 +22494,14 @@
         <f>CurrentPositions!J193</f>
         <v/>
       </c>
+      <c r="K198">
+        <f>IF(AND(B198="BUY",H198&lt;0),H198,"")</f>
+        <v/>
+      </c>
+      <c r="L198">
+        <f>IF(K198&lt;&gt;"",A198,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -19373,6 +22544,14 @@
         <f>CurrentPositions!J194</f>
         <v/>
       </c>
+      <c r="K199">
+        <f>IF(AND(B199="BUY",H199&lt;0),H199,"")</f>
+        <v/>
+      </c>
+      <c r="L199">
+        <f>IF(K199&lt;&gt;"",A199,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -19415,6 +22594,14 @@
         <f>CurrentPositions!J195</f>
         <v/>
       </c>
+      <c r="K200">
+        <f>IF(AND(B200="BUY",H200&lt;0),H200,"")</f>
+        <v/>
+      </c>
+      <c r="L200">
+        <f>IF(K200&lt;&gt;"",A200,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -19457,6 +22644,14 @@
         <f>CurrentPositions!J196</f>
         <v/>
       </c>
+      <c r="K201">
+        <f>IF(AND(B201="BUY",H201&lt;0),H201,"")</f>
+        <v/>
+      </c>
+      <c r="L201">
+        <f>IF(K201&lt;&gt;"",A201,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -19499,6 +22694,14 @@
         <f>CurrentPositions!J197</f>
         <v/>
       </c>
+      <c r="K202">
+        <f>IF(AND(B202="BUY",H202&lt;0),H202,"")</f>
+        <v/>
+      </c>
+      <c r="L202">
+        <f>IF(K202&lt;&gt;"",A202,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -19541,6 +22744,14 @@
         <f>CurrentPositions!J198</f>
         <v/>
       </c>
+      <c r="K203">
+        <f>IF(AND(B203="BUY",H203&lt;0),H203,"")</f>
+        <v/>
+      </c>
+      <c r="L203">
+        <f>IF(K203&lt;&gt;"",A203,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -19583,6 +22794,14 @@
         <f>CurrentPositions!J199</f>
         <v/>
       </c>
+      <c r="K204">
+        <f>IF(AND(B204="BUY",H204&lt;0),H204,"")</f>
+        <v/>
+      </c>
+      <c r="L204">
+        <f>IF(K204&lt;&gt;"",A204,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -19625,6 +22844,14 @@
         <f>CurrentPositions!J200</f>
         <v/>
       </c>
+      <c r="K205">
+        <f>IF(AND(B205="BUY",H205&lt;0),H205,"")</f>
+        <v/>
+      </c>
+      <c r="L205">
+        <f>IF(K205&lt;&gt;"",A205,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -19667,6 +22894,14 @@
         <f>CurrentPositions!J201</f>
         <v/>
       </c>
+      <c r="K206">
+        <f>IF(AND(B206="BUY",H206&lt;0),H206,"")</f>
+        <v/>
+      </c>
+      <c r="L206">
+        <f>IF(K206&lt;&gt;"",A206,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -19687,7 +22922,7 @@
         </is>
       </c>
       <c r="B221">
-        <f>IFERROR(MINIFS(H7:H206,B7:B206,"BUY",H7:H206,"&lt;0"),0)</f>
+        <f>IF(COUNT(K7:K206)=0,0,MIN(K7:K206))</f>
         <v/>
       </c>
     </row>
@@ -19698,7 +22933,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IFERROR(MINIFS(A7:A206,B7:B206,"BUY",H7:H206,B221),"N/A")</f>
+        <f>IF(B221=0,"N/A",MIN(L7:L206))</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,6 +886,51 @@
       </c>
       <c r="C11">
         <f>IF(AND(ScenarioText_DOWN!B31&lt;&gt;"",ISNUMBER(ScenarioText_DOWN!B4)),"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TailTicket not mapped as lot</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tail lot reasonable</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tail остаток &lt;= исходного</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B37),ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B37&gt;ScenarioText_UP!B25),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
@@ -1279,29 +1324,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Лот хвоста</t>
-        </is>
-      </c>
-      <c r="B24" s="4">
-        <f>IFERROR(IF(TailRecovery_UP!B3&gt;0,TailRecovery_UP!B3,"Хвост не найден"),"Хвост не найден")</f>
+          <t>Тикет хвоста</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>IFERROR(TailRecovery_UP!B3,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Убыток хвоста</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>IFERROR(TailRecovery_UP!B12,0)</f>
+          <t>Лот хвоста</t>
+        </is>
+      </c>
+      <c r="B25" s="4">
+        <f>IFERROR(IF(TailRecovery_UP!B4&gt;0,TailRecovery_UP!B4,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RecoveryFund до закрытия</t>
+          <t>Убыток хвоста на 1 лот</t>
         </is>
       </c>
       <c r="B26">
@@ -1312,44 +1357,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Расчётный лот закрытия</t>
-        </is>
-      </c>
-      <c r="B27" s="4">
-        <f>IFERROR(TailRecovery_UP!B9,0)</f>
+          <t>RecoveryFund до закрытия</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IFERROR(TailRecovery_UP!B7,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Округлённый лот закрытия</t>
+          <t>Расчётный лот закрытия</t>
         </is>
       </c>
       <c r="B28" s="4">
-        <f>IFERROR(TailRecovery_UP!B10,0)</f>
+        <f>IFERROR(TailRecovery_UP!B8,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Итоговый лот закрытия</t>
+          <t>Округлённый лот закрытия</t>
         </is>
       </c>
       <c r="B29" s="4">
-        <f>IFERROR(TailRecovery_UP!B10,0)</f>
+        <f>IFERROR(TailRecovery_UP!B9,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Остаток хвоста</t>
+          <t>Итоговый лот закрытия</t>
         </is>
       </c>
       <c r="B30" s="4">
-        <f>IF(OR(B24="Хвост не найден",NOT(ISNUMBER(B24))),"Хвост не найден",MAX(B24-B29,0))</f>
+        <f>IFERROR(TailRecovery_UP!B10,0)</f>
         <v/>
       </c>
     </row>
@@ -1371,12 +1416,16 @@
       </c>
     </row>
     <row r="33"/>
-    <row r="34">
-      <c r="B34" s="4" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="n"/>
+    </row>
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
@@ -1387,7 +1436,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(B24="Хвост не найден","N/A",TEXT(Scenario_UP!B222,"0"))&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;IF(ISNUMBER(B37),TEXT(B37,"0.00"),B37)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(B37,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(B36,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1617,29 +1666,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Лот хвоста</t>
-        </is>
-      </c>
-      <c r="B24" s="4">
-        <f>IFERROR(IF(TailRecovery_DOWN!B3&gt;0,TailRecovery_DOWN!B3,"Хвост не найден"),"Хвост не найден")</f>
+          <t>Тикет хвоста</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>IFERROR(TailRecovery_DOWN!B3,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Убыток хвоста</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>IFERROR(TailRecovery_DOWN!B12,0)</f>
+          <t>Лот хвоста</t>
+        </is>
+      </c>
+      <c r="B25" s="4">
+        <f>IFERROR(IF(TailRecovery_DOWN!B4&gt;0,TailRecovery_DOWN!B4,"Хвост не найден"),"Хвост не найден")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RecoveryFund до закрытия</t>
+          <t>Убыток хвоста на 1 лот</t>
         </is>
       </c>
       <c r="B26">
@@ -1650,44 +1699,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Расчётный лот закрытия</t>
-        </is>
-      </c>
-      <c r="B27" s="4">
-        <f>IFERROR(TailRecovery_DOWN!B9,0)</f>
+          <t>RecoveryFund до закрытия</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IFERROR(TailRecovery_DOWN!B7,0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Округлённый лот закрытия</t>
+          <t>Расчётный лот закрытия</t>
         </is>
       </c>
       <c r="B28" s="4">
-        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B8,0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Итоговый лот закрытия</t>
+          <t>Округлённый лот закрытия</t>
         </is>
       </c>
       <c r="B29" s="4">
-        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B9,0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Остаток хвоста</t>
+          <t>Итоговый лот закрытия</t>
         </is>
       </c>
       <c r="B30" s="4">
-        <f>IF(OR(B24="Хвост не найден",NOT(ISNUMBER(B24))),"Хвост не найден",MAX(B24-B29,0))</f>
+        <f>IFERROR(TailRecovery_DOWN!B10,0)</f>
         <v/>
       </c>
     </row>
@@ -1709,12 +1758,16 @@
       </c>
     </row>
     <row r="33"/>
-    <row r="34">
-      <c r="B34" s="4" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="n"/>
+    </row>
     <row r="38"/>
     <row r="39"/>
     <row r="40"/>
@@ -1725,7 +1778,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Лот хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B29),TEXT(B29,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(B24="Хвост не найден","N/A",TEXT(Scenario_DOWN!B222,"0"))&amp;", до="&amp;IF(ISNUMBER(B24),TEXT(B24,"0.00"),B24)&amp;", закрыть="&amp;TEXT(B29,"0.00")&amp;", остаток="&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),B30)&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B26,"0.00")&amp;" / "&amp;TEXT(B34,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;IF(ISNUMBER(B37),TEXT(B37,"0.00"),B37)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(B37,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(B36,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -1021,11 +1021,11 @@
         </is>
       </c>
       <c r="D2">
-        <f>IF(BasketSummary!B13="WAIT","ЖДАТЬ",IF(BasketSummary!B13="SAFE","SAFE",IF(BasketSummary!B13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(AND(TailRecovery_UP!B10&gt;0,TailRecovery_UP!B10&lt;TailRecovery_UP!B3),"ЗАКРЫТЬ ХВОСТ ЧАСТИЧНО","ЗАКРЫТЬ СЕКЦИЮ"))))</f>
+        <f>IF(BasketSummary!B13="WAIT","ЖДАТЬ",IF(BasketSummary!B13="SAFE","SAFE",IF(BasketSummary!B13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(AND(TailRecovery_UP!B10&gt;0,TailRecovery_UP!B10&lt;TailRecovery_UP!B4),"ЗАКРЫТЬ ХВОСТ ЧАСТИЧНО","ЗАКРЫТЬ СЕКЦИЮ"))))</f>
         <v/>
       </c>
       <c r="E2">
-        <f>IFERROR(TailRecovery_UP!B3,0)</f>
+        <f>IFERROR(TailRecovery_UP!B4,0)</f>
         <v/>
       </c>
       <c r="F2">
@@ -1033,15 +1033,15 @@
         <v/>
       </c>
       <c r="G2">
-        <f>IF(OR(NOT(ISNUMBER(E2)),NOT(ISNUMBER(F2))),"Хвост не найден",MAX(E2-F2,0))</f>
+        <f>IFERROR(TailRecovery_UP!B14,0)</f>
         <v/>
       </c>
       <c r="H2">
-        <f>IFERROR(TailRecovery_UP!B5,0)</f>
+        <f>IFERROR(TailRecovery_UP!B7,0)</f>
         <v/>
       </c>
       <c r="I2">
-        <f>IFERROR(TailRecovery_UP!B7,0)</f>
+        <f>IFERROR(TailRecovery_UP!B13,0)</f>
         <v/>
       </c>
       <c r="J2">
@@ -1069,11 +1069,11 @@
         </is>
       </c>
       <c r="D3">
-        <f>IF(BasketSummary!C13="WAIT","ЖДАТЬ",IF(BasketSummary!C13="SAFE","SAFE",IF(BasketSummary!C13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(AND(TailRecovery_DOWN!B10&gt;0,TailRecovery_DOWN!B10&lt;TailRecovery_DOWN!B3),"ЗАКРЫТЬ ХВОСТ ЧАСТИЧНО","ЗАКРЫТЬ СЕКЦИЮ"))))</f>
+        <f>IF(BasketSummary!C13="WAIT","ЖДАТЬ",IF(BasketSummary!C13="SAFE","SAFE",IF(BasketSummary!C13="BASKET_CLOSE","ЗАКРЫТЬ ВСЮ КОРЗИНУ",IF(AND(TailRecovery_DOWN!B10&gt;0,TailRecovery_DOWN!B10&lt;TailRecovery_DOWN!B4),"ЗАКРЫТЬ ХВОСТ ЧАСТИЧНО","ЗАКРЫТЬ СЕКЦИЮ"))))</f>
         <v/>
       </c>
       <c r="E3">
-        <f>IFERROR(TailRecovery_DOWN!B3,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B4,0)</f>
         <v/>
       </c>
       <c r="F3">
@@ -1081,15 +1081,15 @@
         <v/>
       </c>
       <c r="G3">
-        <f>IF(OR(NOT(ISNUMBER(E3)),NOT(ISNUMBER(F3))),"Хвост не найден",MAX(E3-F3,0))</f>
+        <f>IFERROR(TailRecovery_DOWN!B14,0)</f>
         <v/>
       </c>
       <c r="H3">
-        <f>IFERROR(TailRecovery_DOWN!B5,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B7,0)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>IFERROR(TailRecovery_DOWN!B7,0)</f>
+        <f>IFERROR(TailRecovery_DOWN!B13,0)</f>
         <v/>
       </c>
       <c r="J3">
@@ -1436,7 +1436,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;IF(ISNUMBER(B37),TEXT(B37,"0.00"),B37)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(B37,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(B36,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;IF(ISNUMBER(B37),TEXT(B37,"0.00"),B37)&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(B34,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(B37,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(B36,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,44 +892,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TailTicket not mapped as lot</t>
+          <t>ReserveAdd mapping sync</t>
         </is>
       </c>
       <c r="B12">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B19=SectionCalculator_UP!B33,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B19=SectionCalculator_DOWN!B33,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tail lot reasonable</t>
+          <t>RecoveryAdd mapping sync</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B20=SectionCalculator_UP!B34,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B20=SectionCalculator_DOWN!B34,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>TailTicket not mapped as lot</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tail lot reasonable</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Tail остаток &lt;= исходного</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="B16">
         <f>IF(AND(ISNUMBER(ScenarioText_UP!B37),ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B37&gt;ScenarioText_UP!B25),"ERROR","OK")</f>
         <v/>
       </c>
-      <c r="C14">
+      <c r="C16">
         <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
         <v/>
       </c>
@@ -1295,7 +1325,7 @@
         </is>
       </c>
       <c r="B19">
-        <f>IFERROR(TailRecovery_UP!B6,0)</f>
+        <f>IFERROR(SectionCalculator_UP!B33,0)</f>
         <v/>
       </c>
     </row>
@@ -1306,7 +1336,29 @@
         </is>
       </c>
       <c r="B20">
-        <f>IFERROR(TailRecovery_UP!B8,0)</f>
+        <f>IFERROR(SectionCalculator_UP!B34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Резерв после</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>IFERROR(SectionCalculator_UP!B35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RecoveryFund после цикла</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>IFERROR(SectionCalculator_UP!B36,0)</f>
         <v/>
       </c>
     </row>
@@ -1436,7 +1488,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1689,7 @@
         </is>
       </c>
       <c r="B19">
-        <f>IFERROR(TailRecovery_DOWN!B6,0)</f>
+        <f>IFERROR(SectionCalculator_DOWN!B33,0)</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1700,29 @@
         </is>
       </c>
       <c r="B20">
-        <f>IFERROR(TailRecovery_DOWN!B8,0)</f>
+        <f>IFERROR(SectionCalculator_DOWN!B34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Резерв после</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>IFERROR(SectionCalculator_DOWN!B35,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RecoveryFund после цикла</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>IFERROR(SectionCalculator_DOWN!B36,0)</f>
         <v/>
       </c>
     </row>
@@ -1778,7 +1852,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;"; Резерв после: "&amp;TEXT(B19,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,6 +961,51 @@
       </c>
       <c r="C16">
         <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RecoveryFundAfter &gt;= 0</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>IF(TailRecovery_UP!B13&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>IF(TailRecovery_DOWN!B13&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CloseLotFinal &lt;= TailLot</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>IF(TailRecovery_UP!B10&gt;TailRecovery_UP!B4,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>IF(TailRecovery_DOWN!B10&gt;TailRecovery_DOWN!B4,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TailLotAfter &gt;= 0</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>IF(TailRecovery_UP!B14&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF(TailRecovery_DOWN!B14&lt;0,"ERROR","OK")</f>
         <v/>
       </c>
     </row>
@@ -1488,7 +1533,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1852,7 +1897,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"Решение: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -24536,7 +24581,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>B4-B10</f>
+        <f>MAX(0,B4-B10)</f>
         <v/>
       </c>
     </row>
@@ -24738,7 +24783,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>B4-B10</f>
+        <f>MAX(0,B4-B10)</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,6 +706,67 @@
       </c>
       <c r="C24" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MarketPriceInput</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1.2302</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MidPrice</t>
+        </is>
+      </c>
+      <c r="B33" s="2">
+        <f>(B31+B32)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SpreadPoints</t>
+        </is>
+      </c>
+      <c r="B34" s="3">
+        <f>(B32-B31)/B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PriceSourceMode</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BID_ASK</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1216,66 +1277,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Текущая цена</t>
+          <t>Текущий Bid</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>IFERROR(CurrentPositions!F2,0)</f>
+        <f>IFERROR(Scenario_UP!B2,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Сценарная цена</t>
+          <t>Текущий Ask</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>IFERROR(Scenario_UP!B4,0)</f>
+        <f>IFERROR(Scenario_UP!B3,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Следующий уровень открытия</t>
+          <t>Сценарный Bid</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!N4,IF(SectionCalculator_UP!B4=2,Scenario_UP!N5,IF(SectionCalculator_UP!B4=3,Scenario_UP!N6,IF(SectionCalculator_UP!B4=4,Scenario_UP!N7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
+        <f>IFERROR(Scenario_UP!B5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Расстояние до уровня, пунктов</t>
+          <t>Сценарный Ask</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IF(OR(B5="Уровень не рассчитан",B4=""),"Расстояние не рассчитано",ROUND(ABS(B5-B4)*10000,0))</f>
+        <f>IFERROR(Scenario_UP!B6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Большая позиция</t>
+          <t>Spread, пунктов</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <f>IFERROR(IF(TailRecovery_UP!B16&gt;0,IF("UP"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_UP!B16,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(Settings!B34,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Малая защитная позиция</t>
+          <t>Следующий уровень открытия</t>
         </is>
       </c>
       <c r="B8" s="4">
-        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!N4,IF(SectionCalculator_UP!B4=2,Scenario_UP!N5,IF(SectionCalculator_UP!B4=3,Scenario_UP!N6,IF(SectionCalculator_UP!B4=4,Scenario_UP!N7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
@@ -1298,6 +1359,17 @@
       </c>
       <c r="B10">
         <f>IF(SectionCalculator_UP!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция недоступна: уровень/риск-гейт/хвост")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Малая защитная позиция</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
@@ -1580,66 +1652,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Текущая цена</t>
+          <t>Текущий Bid</t>
         </is>
       </c>
       <c r="B3" s="2">
-        <f>IFERROR(CurrentPositions!F2,0)</f>
+        <f>IFERROR(Scenario_DOWN!B2,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Сценарная цена</t>
+          <t>Текущий Ask</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <f>IFERROR(Scenario_DOWN!B4,0)</f>
+        <f>IFERROR(Scenario_DOWN!B3,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Следующий уровень открытия</t>
+          <t>Сценарный Bid</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!N9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!N10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!N11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!N12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
+        <f>IFERROR(Scenario_DOWN!B5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Расстояние до уровня, пунктов</t>
+          <t>Сценарный Ask</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>IF(OR(B5="Уровень не рассчитан",B4=""),"Расстояние не рассчитано",ROUND(ABS(B5-B4)*10000,0))</f>
+        <f>IFERROR(Scenario_DOWN!B6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Большая позиция</t>
+          <t>Spread, пунктов</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <f>IFERROR(IF(TailRecovery_DOWN!B16&gt;0,IF("DOWN"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_DOWN!B16,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(Settings!B34,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Малая защитная позиция</t>
+          <t>Следующий уровень открытия</t>
         </is>
       </c>
       <c r="B8" s="4">
-        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!N9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!N10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!N11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!N12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
@@ -1662,6 +1734,17 @@
       </c>
       <c r="B10">
         <f>IF(SectionCalculator_DOWN!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция недоступна: уровень/риск-гейт/хвост")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Малая защитная позиция</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
@@ -2426,11 +2509,12 @@
       <c r="E2" t="n">
         <v>1.23</v>
       </c>
-      <c r="F2" t="n">
-        <v>1.23</v>
+      <c r="F2">
+        <f>IF(B2="BUY",Settings!$B$31,IF(B2="SELL",Settings!$B$32,""))</f>
+        <v/>
       </c>
       <c r="G2">
-        <f>IF(B2="BUY",(F2-E2)/Settings!$B$3,(E2-F2)/Settings!$B$3)</f>
+        <f>IF(B2="BUY",(F2-E2)/Settings!$B$3,IF(B2="SELL",(E2-F2)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2464,11 +2548,12 @@
       <c r="E3" t="n">
         <v>1.23</v>
       </c>
-      <c r="F3" t="n">
-        <v>1.23</v>
+      <c r="F3">
+        <f>IF(B3="BUY",Settings!$B$31,IF(B3="SELL",Settings!$B$32,""))</f>
+        <v/>
       </c>
       <c r="G3">
-        <f>IF(B3="BUY",(F3-E3)/Settings!$B$3,(E3-F3)/Settings!$B$3)</f>
+        <f>IF(B3="BUY",(F3-E3)/Settings!$B$3,IF(B3="SELL",(E3-F3)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2502,11 +2587,12 @@
       <c r="E4" t="n">
         <v>1.235</v>
       </c>
-      <c r="F4" t="n">
-        <v>1.23</v>
+      <c r="F4">
+        <f>IF(B4="BUY",Settings!$B$31,IF(B4="SELL",Settings!$B$32,""))</f>
+        <v/>
       </c>
       <c r="G4">
-        <f>IF(B4="BUY",(F4-E4)/Settings!$B$3,(E4-F4)/Settings!$B$3)</f>
+        <f>IF(B4="BUY",(F4-E4)/Settings!$B$3,IF(B4="SELL",(E4-F4)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2544,11 +2630,12 @@
       <c r="E5" t="n">
         <v>1.235</v>
       </c>
-      <c r="F5" t="n">
-        <v>1.23</v>
+      <c r="F5">
+        <f>IF(B5="BUY",Settings!$B$31,IF(B5="SELL",Settings!$B$32,""))</f>
+        <v/>
       </c>
       <c r="G5">
-        <f>IF(B5="BUY",(F5-E5)/Settings!$B$3,(E5-F5)/Settings!$B$3)</f>
+        <f>IF(B5="BUY",(F5-E5)/Settings!$B$3,IF(B5="SELL",(E5-F5)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2604,11 +2691,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CurrentPrice</t>
+          <t>CurrentBid</t>
         </is>
       </c>
       <c r="B2">
-        <f>CurrentPositions!F2</f>
+        <f>Settings!$B$31</f>
         <v/>
       </c>
       <c r="M2" t="inlineStr">
@@ -2624,11 +2711,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MoveUpPoints</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
+          <t>CurrentAsk</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Settings!$B$32</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2643,12 +2731,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ScenarioPrice</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>B2+B3*Settings!$B$3</f>
-        <v/>
+          <t>MoveUpPoints</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2661,6 +2748,15 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ScenarioBid</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>B2+B4*Settings!$B$3</f>
+        <v/>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>UpperLevel2</t>
@@ -2764,11 +2860,11 @@
         <v/>
       </c>
       <c r="F7">
-        <f>$B$4</f>
+        <f>IF(B7="BUY",$B$5,IF(B7="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G7">
-        <f>IF(B7="BUY",(F7-E7)/Settings!$B$3,(E7-F7)/Settings!$B$3)</f>
+        <f>IF(B7="BUY",(F7-E7)/Settings!$B$3,IF(B7="SELL",(E7-F7)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2823,11 +2919,11 @@
         <v/>
       </c>
       <c r="F8">
-        <f>$B$4</f>
+        <f>IF(B8="BUY",$B$5,IF(B8="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G8">
-        <f>IF(B8="BUY",(F8-E8)/Settings!$B$3,(E8-F8)/Settings!$B$3)</f>
+        <f>IF(B8="BUY",(F8-E8)/Settings!$B$3,IF(B8="SELL",(E8-F8)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2873,11 +2969,11 @@
         <v/>
       </c>
       <c r="F9">
-        <f>$B$4</f>
+        <f>IF(B9="BUY",$B$5,IF(B9="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G9">
-        <f>IF(B9="BUY",(F9-E9)/Settings!$B$3,(E9-F9)/Settings!$B$3)</f>
+        <f>IF(B9="BUY",(F9-E9)/Settings!$B$3,IF(B9="SELL",(E9-F9)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2932,11 +3028,11 @@
         <v/>
       </c>
       <c r="F10">
-        <f>$B$4</f>
+        <f>IF(B10="BUY",$B$5,IF(B10="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G10">
-        <f>IF(B10="BUY",(F10-E10)/Settings!$B$3,(E10-F10)/Settings!$B$3)</f>
+        <f>IF(B10="BUY",(F10-E10)/Settings!$B$3,IF(B10="SELL",(E10-F10)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2991,11 +3087,11 @@
         <v/>
       </c>
       <c r="F11">
-        <f>$B$4</f>
+        <f>IF(B11="BUY",$B$5,IF(B11="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G11">
-        <f>IF(B11="BUY",(F11-E11)/Settings!$B$3,(E11-F11)/Settings!$B$3)</f>
+        <f>IF(B11="BUY",(F11-E11)/Settings!$B$3,IF(B11="SELL",(E11-F11)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H11">
@@ -3050,11 +3146,11 @@
         <v/>
       </c>
       <c r="F12">
-        <f>$B$4</f>
+        <f>IF(B12="BUY",$B$5,IF(B12="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IF(B12="BUY",(F12-E12)/Settings!$B$3,(E12-F12)/Settings!$B$3)</f>
+        <f>IF(B12="BUY",(F12-E12)/Settings!$B$3,IF(B12="SELL",(E12-F12)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H12">
@@ -3109,11 +3205,11 @@
         <v/>
       </c>
       <c r="F13">
-        <f>$B$4</f>
+        <f>IF(B13="BUY",$B$5,IF(B13="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G13">
-        <f>IF(B13="BUY",(F13-E13)/Settings!$B$3,(E13-F13)/Settings!$B$3)</f>
+        <f>IF(B13="BUY",(F13-E13)/Settings!$B$3,IF(B13="SELL",(E13-F13)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H13">
@@ -3159,11 +3255,11 @@
         <v/>
       </c>
       <c r="F14">
-        <f>$B$4</f>
+        <f>IF(B14="BUY",$B$5,IF(B14="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G14">
-        <f>IF(B14="BUY",(F14-E14)/Settings!$B$3,(E14-F14)/Settings!$B$3)</f>
+        <f>IF(B14="BUY",(F14-E14)/Settings!$B$3,IF(B14="SELL",(E14-F14)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H14">
@@ -3209,11 +3305,11 @@
         <v/>
       </c>
       <c r="F15">
-        <f>$B$4</f>
+        <f>IF(B15="BUY",$B$5,IF(B15="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G15">
-        <f>IF(B15="BUY",(F15-E15)/Settings!$B$3,(E15-F15)/Settings!$B$3)</f>
+        <f>IF(B15="BUY",(F15-E15)/Settings!$B$3,IF(B15="SELL",(E15-F15)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3259,11 +3355,11 @@
         <v/>
       </c>
       <c r="F16">
-        <f>$B$4</f>
+        <f>IF(B16="BUY",$B$5,IF(B16="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G16">
-        <f>IF(B16="BUY",(F16-E16)/Settings!$B$3,(E16-F16)/Settings!$B$3)</f>
+        <f>IF(B16="BUY",(F16-E16)/Settings!$B$3,IF(B16="SELL",(E16-F16)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3309,11 +3405,11 @@
         <v/>
       </c>
       <c r="F17">
-        <f>$B$4</f>
+        <f>IF(B17="BUY",$B$5,IF(B17="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G17">
-        <f>IF(B17="BUY",(F17-E17)/Settings!$B$3,(E17-F17)/Settings!$B$3)</f>
+        <f>IF(B17="BUY",(F17-E17)/Settings!$B$3,IF(B17="SELL",(E17-F17)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3359,11 +3455,11 @@
         <v/>
       </c>
       <c r="F18">
-        <f>$B$4</f>
+        <f>IF(B18="BUY",$B$5,IF(B18="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G18">
-        <f>IF(B18="BUY",(F18-E18)/Settings!$B$3,(E18-F18)/Settings!$B$3)</f>
+        <f>IF(B18="BUY",(F18-E18)/Settings!$B$3,IF(B18="SELL",(E18-F18)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3409,11 +3505,11 @@
         <v/>
       </c>
       <c r="F19">
-        <f>$B$4</f>
+        <f>IF(B19="BUY",$B$5,IF(B19="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G19">
-        <f>IF(B19="BUY",(F19-E19)/Settings!$B$3,(E19-F19)/Settings!$B$3)</f>
+        <f>IF(B19="BUY",(F19-E19)/Settings!$B$3,IF(B19="SELL",(E19-F19)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3459,11 +3555,11 @@
         <v/>
       </c>
       <c r="F20">
-        <f>$B$4</f>
+        <f>IF(B20="BUY",$B$5,IF(B20="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G20">
-        <f>IF(B20="BUY",(F20-E20)/Settings!$B$3,(E20-F20)/Settings!$B$3)</f>
+        <f>IF(B20="BUY",(F20-E20)/Settings!$B$3,IF(B20="SELL",(E20-F20)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3509,11 +3605,11 @@
         <v/>
       </c>
       <c r="F21">
-        <f>$B$4</f>
+        <f>IF(B21="BUY",$B$5,IF(B21="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G21">
-        <f>IF(B21="BUY",(F21-E21)/Settings!$B$3,(E21-F21)/Settings!$B$3)</f>
+        <f>IF(B21="BUY",(F21-E21)/Settings!$B$3,IF(B21="SELL",(E21-F21)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3559,11 +3655,11 @@
         <v/>
       </c>
       <c r="F22">
-        <f>$B$4</f>
+        <f>IF(B22="BUY",$B$5,IF(B22="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G22">
-        <f>IF(B22="BUY",(F22-E22)/Settings!$B$3,(E22-F22)/Settings!$B$3)</f>
+        <f>IF(B22="BUY",(F22-E22)/Settings!$B$3,IF(B22="SELL",(E22-F22)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3609,11 +3705,11 @@
         <v/>
       </c>
       <c r="F23">
-        <f>$B$4</f>
+        <f>IF(B23="BUY",$B$5,IF(B23="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G23">
-        <f>IF(B23="BUY",(F23-E23)/Settings!$B$3,(E23-F23)/Settings!$B$3)</f>
+        <f>IF(B23="BUY",(F23-E23)/Settings!$B$3,IF(B23="SELL",(E23-F23)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3659,11 +3755,11 @@
         <v/>
       </c>
       <c r="F24">
-        <f>$B$4</f>
+        <f>IF(B24="BUY",$B$5,IF(B24="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G24">
-        <f>IF(B24="BUY",(F24-E24)/Settings!$B$3,(E24-F24)/Settings!$B$3)</f>
+        <f>IF(B24="BUY",(F24-E24)/Settings!$B$3,IF(B24="SELL",(E24-F24)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3709,11 +3805,11 @@
         <v/>
       </c>
       <c r="F25">
-        <f>$B$4</f>
+        <f>IF(B25="BUY",$B$5,IF(B25="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G25">
-        <f>IF(B25="BUY",(F25-E25)/Settings!$B$3,(E25-F25)/Settings!$B$3)</f>
+        <f>IF(B25="BUY",(F25-E25)/Settings!$B$3,IF(B25="SELL",(E25-F25)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3759,11 +3855,11 @@
         <v/>
       </c>
       <c r="F26">
-        <f>$B$4</f>
+        <f>IF(B26="BUY",$B$5,IF(B26="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G26">
-        <f>IF(B26="BUY",(F26-E26)/Settings!$B$3,(E26-F26)/Settings!$B$3)</f>
+        <f>IF(B26="BUY",(F26-E26)/Settings!$B$3,IF(B26="SELL",(E26-F26)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3809,11 +3905,11 @@
         <v/>
       </c>
       <c r="F27">
-        <f>$B$4</f>
+        <f>IF(B27="BUY",$B$5,IF(B27="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G27">
-        <f>IF(B27="BUY",(F27-E27)/Settings!$B$3,(E27-F27)/Settings!$B$3)</f>
+        <f>IF(B27="BUY",(F27-E27)/Settings!$B$3,IF(B27="SELL",(E27-F27)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3859,11 +3955,11 @@
         <v/>
       </c>
       <c r="F28">
-        <f>$B$4</f>
+        <f>IF(B28="BUY",$B$5,IF(B28="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G28">
-        <f>IF(B28="BUY",(F28-E28)/Settings!$B$3,(E28-F28)/Settings!$B$3)</f>
+        <f>IF(B28="BUY",(F28-E28)/Settings!$B$3,IF(B28="SELL",(E28-F28)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3909,11 +4005,11 @@
         <v/>
       </c>
       <c r="F29">
-        <f>$B$4</f>
+        <f>IF(B29="BUY",$B$5,IF(B29="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G29">
-        <f>IF(B29="BUY",(F29-E29)/Settings!$B$3,(E29-F29)/Settings!$B$3)</f>
+        <f>IF(B29="BUY",(F29-E29)/Settings!$B$3,IF(B29="SELL",(E29-F29)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3959,11 +4055,11 @@
         <v/>
       </c>
       <c r="F30">
-        <f>$B$4</f>
+        <f>IF(B30="BUY",$B$5,IF(B30="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G30">
-        <f>IF(B30="BUY",(F30-E30)/Settings!$B$3,(E30-F30)/Settings!$B$3)</f>
+        <f>IF(B30="BUY",(F30-E30)/Settings!$B$3,IF(B30="SELL",(E30-F30)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H30">
@@ -4009,11 +4105,11 @@
         <v/>
       </c>
       <c r="F31">
-        <f>$B$4</f>
+        <f>IF(B31="BUY",$B$5,IF(B31="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G31">
-        <f>IF(B31="BUY",(F31-E31)/Settings!$B$3,(E31-F31)/Settings!$B$3)</f>
+        <f>IF(B31="BUY",(F31-E31)/Settings!$B$3,IF(B31="SELL",(E31-F31)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H31">
@@ -4059,11 +4155,11 @@
         <v/>
       </c>
       <c r="F32">
-        <f>$B$4</f>
+        <f>IF(B32="BUY",$B$5,IF(B32="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G32">
-        <f>IF(B32="BUY",(F32-E32)/Settings!$B$3,(E32-F32)/Settings!$B$3)</f>
+        <f>IF(B32="BUY",(F32-E32)/Settings!$B$3,IF(B32="SELL",(E32-F32)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H32">
@@ -4109,11 +4205,11 @@
         <v/>
       </c>
       <c r="F33">
-        <f>$B$4</f>
+        <f>IF(B33="BUY",$B$5,IF(B33="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G33">
-        <f>IF(B33="BUY",(F33-E33)/Settings!$B$3,(E33-F33)/Settings!$B$3)</f>
+        <f>IF(B33="BUY",(F33-E33)/Settings!$B$3,IF(B33="SELL",(E33-F33)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H33">
@@ -4159,11 +4255,11 @@
         <v/>
       </c>
       <c r="F34">
-        <f>$B$4</f>
+        <f>IF(B34="BUY",$B$5,IF(B34="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G34">
-        <f>IF(B34="BUY",(F34-E34)/Settings!$B$3,(E34-F34)/Settings!$B$3)</f>
+        <f>IF(B34="BUY",(F34-E34)/Settings!$B$3,IF(B34="SELL",(E34-F34)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H34">
@@ -4209,11 +4305,11 @@
         <v/>
       </c>
       <c r="F35">
-        <f>$B$4</f>
+        <f>IF(B35="BUY",$B$5,IF(B35="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G35">
-        <f>IF(B35="BUY",(F35-E35)/Settings!$B$3,(E35-F35)/Settings!$B$3)</f>
+        <f>IF(B35="BUY",(F35-E35)/Settings!$B$3,IF(B35="SELL",(E35-F35)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H35">
@@ -4259,11 +4355,11 @@
         <v/>
       </c>
       <c r="F36">
-        <f>$B$4</f>
+        <f>IF(B36="BUY",$B$5,IF(B36="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G36">
-        <f>IF(B36="BUY",(F36-E36)/Settings!$B$3,(E36-F36)/Settings!$B$3)</f>
+        <f>IF(B36="BUY",(F36-E36)/Settings!$B$3,IF(B36="SELL",(E36-F36)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H36">
@@ -4309,11 +4405,11 @@
         <v/>
       </c>
       <c r="F37">
-        <f>$B$4</f>
+        <f>IF(B37="BUY",$B$5,IF(B37="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G37">
-        <f>IF(B37="BUY",(F37-E37)/Settings!$B$3,(E37-F37)/Settings!$B$3)</f>
+        <f>IF(B37="BUY",(F37-E37)/Settings!$B$3,IF(B37="SELL",(E37-F37)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H37">
@@ -4359,11 +4455,11 @@
         <v/>
       </c>
       <c r="F38">
-        <f>$B$4</f>
+        <f>IF(B38="BUY",$B$5,IF(B38="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G38">
-        <f>IF(B38="BUY",(F38-E38)/Settings!$B$3,(E38-F38)/Settings!$B$3)</f>
+        <f>IF(B38="BUY",(F38-E38)/Settings!$B$3,IF(B38="SELL",(E38-F38)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4409,11 +4505,11 @@
         <v/>
       </c>
       <c r="F39">
-        <f>$B$4</f>
+        <f>IF(B39="BUY",$B$5,IF(B39="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G39">
-        <f>IF(B39="BUY",(F39-E39)/Settings!$B$3,(E39-F39)/Settings!$B$3)</f>
+        <f>IF(B39="BUY",(F39-E39)/Settings!$B$3,IF(B39="SELL",(E39-F39)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4459,11 +4555,11 @@
         <v/>
       </c>
       <c r="F40">
-        <f>$B$4</f>
+        <f>IF(B40="BUY",$B$5,IF(B40="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G40">
-        <f>IF(B40="BUY",(F40-E40)/Settings!$B$3,(E40-F40)/Settings!$B$3)</f>
+        <f>IF(B40="BUY",(F40-E40)/Settings!$B$3,IF(B40="SELL",(E40-F40)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4509,11 +4605,11 @@
         <v/>
       </c>
       <c r="F41">
-        <f>$B$4</f>
+        <f>IF(B41="BUY",$B$5,IF(B41="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G41">
-        <f>IF(B41="BUY",(F41-E41)/Settings!$B$3,(E41-F41)/Settings!$B$3)</f>
+        <f>IF(B41="BUY",(F41-E41)/Settings!$B$3,IF(B41="SELL",(E41-F41)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H41">
@@ -4559,11 +4655,11 @@
         <v/>
       </c>
       <c r="F42">
-        <f>$B$4</f>
+        <f>IF(B42="BUY",$B$5,IF(B42="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G42">
-        <f>IF(B42="BUY",(F42-E42)/Settings!$B$3,(E42-F42)/Settings!$B$3)</f>
+        <f>IF(B42="BUY",(F42-E42)/Settings!$B$3,IF(B42="SELL",(E42-F42)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4609,11 +4705,11 @@
         <v/>
       </c>
       <c r="F43">
-        <f>$B$4</f>
+        <f>IF(B43="BUY",$B$5,IF(B43="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G43">
-        <f>IF(B43="BUY",(F43-E43)/Settings!$B$3,(E43-F43)/Settings!$B$3)</f>
+        <f>IF(B43="BUY",(F43-E43)/Settings!$B$3,IF(B43="SELL",(E43-F43)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4659,11 +4755,11 @@
         <v/>
       </c>
       <c r="F44">
-        <f>$B$4</f>
+        <f>IF(B44="BUY",$B$5,IF(B44="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G44">
-        <f>IF(B44="BUY",(F44-E44)/Settings!$B$3,(E44-F44)/Settings!$B$3)</f>
+        <f>IF(B44="BUY",(F44-E44)/Settings!$B$3,IF(B44="SELL",(E44-F44)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4709,11 +4805,11 @@
         <v/>
       </c>
       <c r="F45">
-        <f>$B$4</f>
+        <f>IF(B45="BUY",$B$5,IF(B45="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G45">
-        <f>IF(B45="BUY",(F45-E45)/Settings!$B$3,(E45-F45)/Settings!$B$3)</f>
+        <f>IF(B45="BUY",(F45-E45)/Settings!$B$3,IF(B45="SELL",(E45-F45)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H45">
@@ -4759,11 +4855,11 @@
         <v/>
       </c>
       <c r="F46">
-        <f>$B$4</f>
+        <f>IF(B46="BUY",$B$5,IF(B46="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G46">
-        <f>IF(B46="BUY",(F46-E46)/Settings!$B$3,(E46-F46)/Settings!$B$3)</f>
+        <f>IF(B46="BUY",(F46-E46)/Settings!$B$3,IF(B46="SELL",(E46-F46)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H46">
@@ -4809,11 +4905,11 @@
         <v/>
       </c>
       <c r="F47">
-        <f>$B$4</f>
+        <f>IF(B47="BUY",$B$5,IF(B47="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G47">
-        <f>IF(B47="BUY",(F47-E47)/Settings!$B$3,(E47-F47)/Settings!$B$3)</f>
+        <f>IF(B47="BUY",(F47-E47)/Settings!$B$3,IF(B47="SELL",(E47-F47)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H47">
@@ -4859,11 +4955,11 @@
         <v/>
       </c>
       <c r="F48">
-        <f>$B$4</f>
+        <f>IF(B48="BUY",$B$5,IF(B48="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G48">
-        <f>IF(B48="BUY",(F48-E48)/Settings!$B$3,(E48-F48)/Settings!$B$3)</f>
+        <f>IF(B48="BUY",(F48-E48)/Settings!$B$3,IF(B48="SELL",(E48-F48)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H48">
@@ -4909,11 +5005,11 @@
         <v/>
       </c>
       <c r="F49">
-        <f>$B$4</f>
+        <f>IF(B49="BUY",$B$5,IF(B49="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G49">
-        <f>IF(B49="BUY",(F49-E49)/Settings!$B$3,(E49-F49)/Settings!$B$3)</f>
+        <f>IF(B49="BUY",(F49-E49)/Settings!$B$3,IF(B49="SELL",(E49-F49)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H49">
@@ -4959,11 +5055,11 @@
         <v/>
       </c>
       <c r="F50">
-        <f>$B$4</f>
+        <f>IF(B50="BUY",$B$5,IF(B50="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G50">
-        <f>IF(B50="BUY",(F50-E50)/Settings!$B$3,(E50-F50)/Settings!$B$3)</f>
+        <f>IF(B50="BUY",(F50-E50)/Settings!$B$3,IF(B50="SELL",(E50-F50)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H50">
@@ -5009,11 +5105,11 @@
         <v/>
       </c>
       <c r="F51">
-        <f>$B$4</f>
+        <f>IF(B51="BUY",$B$5,IF(B51="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G51">
-        <f>IF(B51="BUY",(F51-E51)/Settings!$B$3,(E51-F51)/Settings!$B$3)</f>
+        <f>IF(B51="BUY",(F51-E51)/Settings!$B$3,IF(B51="SELL",(E51-F51)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H51">
@@ -5059,11 +5155,11 @@
         <v/>
       </c>
       <c r="F52">
-        <f>$B$4</f>
+        <f>IF(B52="BUY",$B$5,IF(B52="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G52">
-        <f>IF(B52="BUY",(F52-E52)/Settings!$B$3,(E52-F52)/Settings!$B$3)</f>
+        <f>IF(B52="BUY",(F52-E52)/Settings!$B$3,IF(B52="SELL",(E52-F52)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H52">
@@ -5109,11 +5205,11 @@
         <v/>
       </c>
       <c r="F53">
-        <f>$B$4</f>
+        <f>IF(B53="BUY",$B$5,IF(B53="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G53">
-        <f>IF(B53="BUY",(F53-E53)/Settings!$B$3,(E53-F53)/Settings!$B$3)</f>
+        <f>IF(B53="BUY",(F53-E53)/Settings!$B$3,IF(B53="SELL",(E53-F53)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H53">
@@ -5159,11 +5255,11 @@
         <v/>
       </c>
       <c r="F54">
-        <f>$B$4</f>
+        <f>IF(B54="BUY",$B$5,IF(B54="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G54">
-        <f>IF(B54="BUY",(F54-E54)/Settings!$B$3,(E54-F54)/Settings!$B$3)</f>
+        <f>IF(B54="BUY",(F54-E54)/Settings!$B$3,IF(B54="SELL",(E54-F54)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H54">
@@ -5209,11 +5305,11 @@
         <v/>
       </c>
       <c r="F55">
-        <f>$B$4</f>
+        <f>IF(B55="BUY",$B$5,IF(B55="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G55">
-        <f>IF(B55="BUY",(F55-E55)/Settings!$B$3,(E55-F55)/Settings!$B$3)</f>
+        <f>IF(B55="BUY",(F55-E55)/Settings!$B$3,IF(B55="SELL",(E55-F55)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H55">
@@ -5259,11 +5355,11 @@
         <v/>
       </c>
       <c r="F56">
-        <f>$B$4</f>
+        <f>IF(B56="BUY",$B$5,IF(B56="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G56">
-        <f>IF(B56="BUY",(F56-E56)/Settings!$B$3,(E56-F56)/Settings!$B$3)</f>
+        <f>IF(B56="BUY",(F56-E56)/Settings!$B$3,IF(B56="SELL",(E56-F56)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H56">
@@ -5309,11 +5405,11 @@
         <v/>
       </c>
       <c r="F57">
-        <f>$B$4</f>
+        <f>IF(B57="BUY",$B$5,IF(B57="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G57">
-        <f>IF(B57="BUY",(F57-E57)/Settings!$B$3,(E57-F57)/Settings!$B$3)</f>
+        <f>IF(B57="BUY",(F57-E57)/Settings!$B$3,IF(B57="SELL",(E57-F57)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H57">
@@ -5359,11 +5455,11 @@
         <v/>
       </c>
       <c r="F58">
-        <f>$B$4</f>
+        <f>IF(B58="BUY",$B$5,IF(B58="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G58">
-        <f>IF(B58="BUY",(F58-E58)/Settings!$B$3,(E58-F58)/Settings!$B$3)</f>
+        <f>IF(B58="BUY",(F58-E58)/Settings!$B$3,IF(B58="SELL",(E58-F58)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H58">
@@ -5409,11 +5505,11 @@
         <v/>
       </c>
       <c r="F59">
-        <f>$B$4</f>
+        <f>IF(B59="BUY",$B$5,IF(B59="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G59">
-        <f>IF(B59="BUY",(F59-E59)/Settings!$B$3,(E59-F59)/Settings!$B$3)</f>
+        <f>IF(B59="BUY",(F59-E59)/Settings!$B$3,IF(B59="SELL",(E59-F59)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H59">
@@ -5459,11 +5555,11 @@
         <v/>
       </c>
       <c r="F60">
-        <f>$B$4</f>
+        <f>IF(B60="BUY",$B$5,IF(B60="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G60">
-        <f>IF(B60="BUY",(F60-E60)/Settings!$B$3,(E60-F60)/Settings!$B$3)</f>
+        <f>IF(B60="BUY",(F60-E60)/Settings!$B$3,IF(B60="SELL",(E60-F60)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H60">
@@ -5509,11 +5605,11 @@
         <v/>
       </c>
       <c r="F61">
-        <f>$B$4</f>
+        <f>IF(B61="BUY",$B$5,IF(B61="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G61">
-        <f>IF(B61="BUY",(F61-E61)/Settings!$B$3,(E61-F61)/Settings!$B$3)</f>
+        <f>IF(B61="BUY",(F61-E61)/Settings!$B$3,IF(B61="SELL",(E61-F61)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H61">
@@ -5559,11 +5655,11 @@
         <v/>
       </c>
       <c r="F62">
-        <f>$B$4</f>
+        <f>IF(B62="BUY",$B$5,IF(B62="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G62">
-        <f>IF(B62="BUY",(F62-E62)/Settings!$B$3,(E62-F62)/Settings!$B$3)</f>
+        <f>IF(B62="BUY",(F62-E62)/Settings!$B$3,IF(B62="SELL",(E62-F62)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H62">
@@ -5609,11 +5705,11 @@
         <v/>
       </c>
       <c r="F63">
-        <f>$B$4</f>
+        <f>IF(B63="BUY",$B$5,IF(B63="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G63">
-        <f>IF(B63="BUY",(F63-E63)/Settings!$B$3,(E63-F63)/Settings!$B$3)</f>
+        <f>IF(B63="BUY",(F63-E63)/Settings!$B$3,IF(B63="SELL",(E63-F63)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H63">
@@ -5659,11 +5755,11 @@
         <v/>
       </c>
       <c r="F64">
-        <f>$B$4</f>
+        <f>IF(B64="BUY",$B$5,IF(B64="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G64">
-        <f>IF(B64="BUY",(F64-E64)/Settings!$B$3,(E64-F64)/Settings!$B$3)</f>
+        <f>IF(B64="BUY",(F64-E64)/Settings!$B$3,IF(B64="SELL",(E64-F64)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H64">
@@ -5709,11 +5805,11 @@
         <v/>
       </c>
       <c r="F65">
-        <f>$B$4</f>
+        <f>IF(B65="BUY",$B$5,IF(B65="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G65">
-        <f>IF(B65="BUY",(F65-E65)/Settings!$B$3,(E65-F65)/Settings!$B$3)</f>
+        <f>IF(B65="BUY",(F65-E65)/Settings!$B$3,IF(B65="SELL",(E65-F65)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H65">
@@ -5759,11 +5855,11 @@
         <v/>
       </c>
       <c r="F66">
-        <f>$B$4</f>
+        <f>IF(B66="BUY",$B$5,IF(B66="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G66">
-        <f>IF(B66="BUY",(F66-E66)/Settings!$B$3,(E66-F66)/Settings!$B$3)</f>
+        <f>IF(B66="BUY",(F66-E66)/Settings!$B$3,IF(B66="SELL",(E66-F66)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H66">
@@ -5809,11 +5905,11 @@
         <v/>
       </c>
       <c r="F67">
-        <f>$B$4</f>
+        <f>IF(B67="BUY",$B$5,IF(B67="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G67">
-        <f>IF(B67="BUY",(F67-E67)/Settings!$B$3,(E67-F67)/Settings!$B$3)</f>
+        <f>IF(B67="BUY",(F67-E67)/Settings!$B$3,IF(B67="SELL",(E67-F67)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H67">
@@ -5859,11 +5955,11 @@
         <v/>
       </c>
       <c r="F68">
-        <f>$B$4</f>
+        <f>IF(B68="BUY",$B$5,IF(B68="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G68">
-        <f>IF(B68="BUY",(F68-E68)/Settings!$B$3,(E68-F68)/Settings!$B$3)</f>
+        <f>IF(B68="BUY",(F68-E68)/Settings!$B$3,IF(B68="SELL",(E68-F68)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H68">
@@ -5909,11 +6005,11 @@
         <v/>
       </c>
       <c r="F69">
-        <f>$B$4</f>
+        <f>IF(B69="BUY",$B$5,IF(B69="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G69">
-        <f>IF(B69="BUY",(F69-E69)/Settings!$B$3,(E69-F69)/Settings!$B$3)</f>
+        <f>IF(B69="BUY",(F69-E69)/Settings!$B$3,IF(B69="SELL",(E69-F69)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H69">
@@ -5959,11 +6055,11 @@
         <v/>
       </c>
       <c r="F70">
-        <f>$B$4</f>
+        <f>IF(B70="BUY",$B$5,IF(B70="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G70">
-        <f>IF(B70="BUY",(F70-E70)/Settings!$B$3,(E70-F70)/Settings!$B$3)</f>
+        <f>IF(B70="BUY",(F70-E70)/Settings!$B$3,IF(B70="SELL",(E70-F70)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H70">
@@ -6009,11 +6105,11 @@
         <v/>
       </c>
       <c r="F71">
-        <f>$B$4</f>
+        <f>IF(B71="BUY",$B$5,IF(B71="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G71">
-        <f>IF(B71="BUY",(F71-E71)/Settings!$B$3,(E71-F71)/Settings!$B$3)</f>
+        <f>IF(B71="BUY",(F71-E71)/Settings!$B$3,IF(B71="SELL",(E71-F71)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H71">
@@ -6059,11 +6155,11 @@
         <v/>
       </c>
       <c r="F72">
-        <f>$B$4</f>
+        <f>IF(B72="BUY",$B$5,IF(B72="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G72">
-        <f>IF(B72="BUY",(F72-E72)/Settings!$B$3,(E72-F72)/Settings!$B$3)</f>
+        <f>IF(B72="BUY",(F72-E72)/Settings!$B$3,IF(B72="SELL",(E72-F72)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H72">
@@ -6109,11 +6205,11 @@
         <v/>
       </c>
       <c r="F73">
-        <f>$B$4</f>
+        <f>IF(B73="BUY",$B$5,IF(B73="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G73">
-        <f>IF(B73="BUY",(F73-E73)/Settings!$B$3,(E73-F73)/Settings!$B$3)</f>
+        <f>IF(B73="BUY",(F73-E73)/Settings!$B$3,IF(B73="SELL",(E73-F73)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H73">
@@ -6159,11 +6255,11 @@
         <v/>
       </c>
       <c r="F74">
-        <f>$B$4</f>
+        <f>IF(B74="BUY",$B$5,IF(B74="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G74">
-        <f>IF(B74="BUY",(F74-E74)/Settings!$B$3,(E74-F74)/Settings!$B$3)</f>
+        <f>IF(B74="BUY",(F74-E74)/Settings!$B$3,IF(B74="SELL",(E74-F74)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H74">
@@ -6209,11 +6305,11 @@
         <v/>
       </c>
       <c r="F75">
-        <f>$B$4</f>
+        <f>IF(B75="BUY",$B$5,IF(B75="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G75">
-        <f>IF(B75="BUY",(F75-E75)/Settings!$B$3,(E75-F75)/Settings!$B$3)</f>
+        <f>IF(B75="BUY",(F75-E75)/Settings!$B$3,IF(B75="SELL",(E75-F75)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H75">
@@ -6259,11 +6355,11 @@
         <v/>
       </c>
       <c r="F76">
-        <f>$B$4</f>
+        <f>IF(B76="BUY",$B$5,IF(B76="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G76">
-        <f>IF(B76="BUY",(F76-E76)/Settings!$B$3,(E76-F76)/Settings!$B$3)</f>
+        <f>IF(B76="BUY",(F76-E76)/Settings!$B$3,IF(B76="SELL",(E76-F76)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H76">
@@ -6309,11 +6405,11 @@
         <v/>
       </c>
       <c r="F77">
-        <f>$B$4</f>
+        <f>IF(B77="BUY",$B$5,IF(B77="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G77">
-        <f>IF(B77="BUY",(F77-E77)/Settings!$B$3,(E77-F77)/Settings!$B$3)</f>
+        <f>IF(B77="BUY",(F77-E77)/Settings!$B$3,IF(B77="SELL",(E77-F77)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H77">
@@ -6359,11 +6455,11 @@
         <v/>
       </c>
       <c r="F78">
-        <f>$B$4</f>
+        <f>IF(B78="BUY",$B$5,IF(B78="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G78">
-        <f>IF(B78="BUY",(F78-E78)/Settings!$B$3,(E78-F78)/Settings!$B$3)</f>
+        <f>IF(B78="BUY",(F78-E78)/Settings!$B$3,IF(B78="SELL",(E78-F78)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H78">
@@ -6409,11 +6505,11 @@
         <v/>
       </c>
       <c r="F79">
-        <f>$B$4</f>
+        <f>IF(B79="BUY",$B$5,IF(B79="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G79">
-        <f>IF(B79="BUY",(F79-E79)/Settings!$B$3,(E79-F79)/Settings!$B$3)</f>
+        <f>IF(B79="BUY",(F79-E79)/Settings!$B$3,IF(B79="SELL",(E79-F79)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H79">
@@ -6459,11 +6555,11 @@
         <v/>
       </c>
       <c r="F80">
-        <f>$B$4</f>
+        <f>IF(B80="BUY",$B$5,IF(B80="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G80">
-        <f>IF(B80="BUY",(F80-E80)/Settings!$B$3,(E80-F80)/Settings!$B$3)</f>
+        <f>IF(B80="BUY",(F80-E80)/Settings!$B$3,IF(B80="SELL",(E80-F80)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H80">
@@ -6509,11 +6605,11 @@
         <v/>
       </c>
       <c r="F81">
-        <f>$B$4</f>
+        <f>IF(B81="BUY",$B$5,IF(B81="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G81">
-        <f>IF(B81="BUY",(F81-E81)/Settings!$B$3,(E81-F81)/Settings!$B$3)</f>
+        <f>IF(B81="BUY",(F81-E81)/Settings!$B$3,IF(B81="SELL",(E81-F81)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H81">
@@ -6559,11 +6655,11 @@
         <v/>
       </c>
       <c r="F82">
-        <f>$B$4</f>
+        <f>IF(B82="BUY",$B$5,IF(B82="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G82">
-        <f>IF(B82="BUY",(F82-E82)/Settings!$B$3,(E82-F82)/Settings!$B$3)</f>
+        <f>IF(B82="BUY",(F82-E82)/Settings!$B$3,IF(B82="SELL",(E82-F82)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H82">
@@ -6609,11 +6705,11 @@
         <v/>
       </c>
       <c r="F83">
-        <f>$B$4</f>
+        <f>IF(B83="BUY",$B$5,IF(B83="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G83">
-        <f>IF(B83="BUY",(F83-E83)/Settings!$B$3,(E83-F83)/Settings!$B$3)</f>
+        <f>IF(B83="BUY",(F83-E83)/Settings!$B$3,IF(B83="SELL",(E83-F83)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H83">
@@ -6659,11 +6755,11 @@
         <v/>
       </c>
       <c r="F84">
-        <f>$B$4</f>
+        <f>IF(B84="BUY",$B$5,IF(B84="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G84">
-        <f>IF(B84="BUY",(F84-E84)/Settings!$B$3,(E84-F84)/Settings!$B$3)</f>
+        <f>IF(B84="BUY",(F84-E84)/Settings!$B$3,IF(B84="SELL",(E84-F84)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H84">
@@ -6709,11 +6805,11 @@
         <v/>
       </c>
       <c r="F85">
-        <f>$B$4</f>
+        <f>IF(B85="BUY",$B$5,IF(B85="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G85">
-        <f>IF(B85="BUY",(F85-E85)/Settings!$B$3,(E85-F85)/Settings!$B$3)</f>
+        <f>IF(B85="BUY",(F85-E85)/Settings!$B$3,IF(B85="SELL",(E85-F85)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H85">
@@ -6759,11 +6855,11 @@
         <v/>
       </c>
       <c r="F86">
-        <f>$B$4</f>
+        <f>IF(B86="BUY",$B$5,IF(B86="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G86">
-        <f>IF(B86="BUY",(F86-E86)/Settings!$B$3,(E86-F86)/Settings!$B$3)</f>
+        <f>IF(B86="BUY",(F86-E86)/Settings!$B$3,IF(B86="SELL",(E86-F86)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H86">
@@ -6809,11 +6905,11 @@
         <v/>
       </c>
       <c r="F87">
-        <f>$B$4</f>
+        <f>IF(B87="BUY",$B$5,IF(B87="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G87">
-        <f>IF(B87="BUY",(F87-E87)/Settings!$B$3,(E87-F87)/Settings!$B$3)</f>
+        <f>IF(B87="BUY",(F87-E87)/Settings!$B$3,IF(B87="SELL",(E87-F87)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H87">
@@ -6859,11 +6955,11 @@
         <v/>
       </c>
       <c r="F88">
-        <f>$B$4</f>
+        <f>IF(B88="BUY",$B$5,IF(B88="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G88">
-        <f>IF(B88="BUY",(F88-E88)/Settings!$B$3,(E88-F88)/Settings!$B$3)</f>
+        <f>IF(B88="BUY",(F88-E88)/Settings!$B$3,IF(B88="SELL",(E88-F88)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H88">
@@ -6909,11 +7005,11 @@
         <v/>
       </c>
       <c r="F89">
-        <f>$B$4</f>
+        <f>IF(B89="BUY",$B$5,IF(B89="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G89">
-        <f>IF(B89="BUY",(F89-E89)/Settings!$B$3,(E89-F89)/Settings!$B$3)</f>
+        <f>IF(B89="BUY",(F89-E89)/Settings!$B$3,IF(B89="SELL",(E89-F89)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H89">
@@ -6959,11 +7055,11 @@
         <v/>
       </c>
       <c r="F90">
-        <f>$B$4</f>
+        <f>IF(B90="BUY",$B$5,IF(B90="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G90">
-        <f>IF(B90="BUY",(F90-E90)/Settings!$B$3,(E90-F90)/Settings!$B$3)</f>
+        <f>IF(B90="BUY",(F90-E90)/Settings!$B$3,IF(B90="SELL",(E90-F90)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H90">
@@ -7009,11 +7105,11 @@
         <v/>
       </c>
       <c r="F91">
-        <f>$B$4</f>
+        <f>IF(B91="BUY",$B$5,IF(B91="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G91">
-        <f>IF(B91="BUY",(F91-E91)/Settings!$B$3,(E91-F91)/Settings!$B$3)</f>
+        <f>IF(B91="BUY",(F91-E91)/Settings!$B$3,IF(B91="SELL",(E91-F91)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H91">
@@ -7059,11 +7155,11 @@
         <v/>
       </c>
       <c r="F92">
-        <f>$B$4</f>
+        <f>IF(B92="BUY",$B$5,IF(B92="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G92">
-        <f>IF(B92="BUY",(F92-E92)/Settings!$B$3,(E92-F92)/Settings!$B$3)</f>
+        <f>IF(B92="BUY",(F92-E92)/Settings!$B$3,IF(B92="SELL",(E92-F92)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H92">
@@ -7109,11 +7205,11 @@
         <v/>
       </c>
       <c r="F93">
-        <f>$B$4</f>
+        <f>IF(B93="BUY",$B$5,IF(B93="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G93">
-        <f>IF(B93="BUY",(F93-E93)/Settings!$B$3,(E93-F93)/Settings!$B$3)</f>
+        <f>IF(B93="BUY",(F93-E93)/Settings!$B$3,IF(B93="SELL",(E93-F93)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H93">
@@ -7159,11 +7255,11 @@
         <v/>
       </c>
       <c r="F94">
-        <f>$B$4</f>
+        <f>IF(B94="BUY",$B$5,IF(B94="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G94">
-        <f>IF(B94="BUY",(F94-E94)/Settings!$B$3,(E94-F94)/Settings!$B$3)</f>
+        <f>IF(B94="BUY",(F94-E94)/Settings!$B$3,IF(B94="SELL",(E94-F94)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H94">
@@ -7209,11 +7305,11 @@
         <v/>
       </c>
       <c r="F95">
-        <f>$B$4</f>
+        <f>IF(B95="BUY",$B$5,IF(B95="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G95">
-        <f>IF(B95="BUY",(F95-E95)/Settings!$B$3,(E95-F95)/Settings!$B$3)</f>
+        <f>IF(B95="BUY",(F95-E95)/Settings!$B$3,IF(B95="SELL",(E95-F95)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H95">
@@ -7259,11 +7355,11 @@
         <v/>
       </c>
       <c r="F96">
-        <f>$B$4</f>
+        <f>IF(B96="BUY",$B$5,IF(B96="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G96">
-        <f>IF(B96="BUY",(F96-E96)/Settings!$B$3,(E96-F96)/Settings!$B$3)</f>
+        <f>IF(B96="BUY",(F96-E96)/Settings!$B$3,IF(B96="SELL",(E96-F96)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H96">
@@ -7309,11 +7405,11 @@
         <v/>
       </c>
       <c r="F97">
-        <f>$B$4</f>
+        <f>IF(B97="BUY",$B$5,IF(B97="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G97">
-        <f>IF(B97="BUY",(F97-E97)/Settings!$B$3,(E97-F97)/Settings!$B$3)</f>
+        <f>IF(B97="BUY",(F97-E97)/Settings!$B$3,IF(B97="SELL",(E97-F97)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H97">
@@ -7359,11 +7455,11 @@
         <v/>
       </c>
       <c r="F98">
-        <f>$B$4</f>
+        <f>IF(B98="BUY",$B$5,IF(B98="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G98">
-        <f>IF(B98="BUY",(F98-E98)/Settings!$B$3,(E98-F98)/Settings!$B$3)</f>
+        <f>IF(B98="BUY",(F98-E98)/Settings!$B$3,IF(B98="SELL",(E98-F98)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H98">
@@ -7409,11 +7505,11 @@
         <v/>
       </c>
       <c r="F99">
-        <f>$B$4</f>
+        <f>IF(B99="BUY",$B$5,IF(B99="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G99">
-        <f>IF(B99="BUY",(F99-E99)/Settings!$B$3,(E99-F99)/Settings!$B$3)</f>
+        <f>IF(B99="BUY",(F99-E99)/Settings!$B$3,IF(B99="SELL",(E99-F99)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H99">
@@ -7459,11 +7555,11 @@
         <v/>
       </c>
       <c r="F100">
-        <f>$B$4</f>
+        <f>IF(B100="BUY",$B$5,IF(B100="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G100">
-        <f>IF(B100="BUY",(F100-E100)/Settings!$B$3,(E100-F100)/Settings!$B$3)</f>
+        <f>IF(B100="BUY",(F100-E100)/Settings!$B$3,IF(B100="SELL",(E100-F100)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H100">
@@ -7509,11 +7605,11 @@
         <v/>
       </c>
       <c r="F101">
-        <f>$B$4</f>
+        <f>IF(B101="BUY",$B$5,IF(B101="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G101">
-        <f>IF(B101="BUY",(F101-E101)/Settings!$B$3,(E101-F101)/Settings!$B$3)</f>
+        <f>IF(B101="BUY",(F101-E101)/Settings!$B$3,IF(B101="SELL",(E101-F101)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H101">
@@ -7559,11 +7655,11 @@
         <v/>
       </c>
       <c r="F102">
-        <f>$B$4</f>
+        <f>IF(B102="BUY",$B$5,IF(B102="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G102">
-        <f>IF(B102="BUY",(F102-E102)/Settings!$B$3,(E102-F102)/Settings!$B$3)</f>
+        <f>IF(B102="BUY",(F102-E102)/Settings!$B$3,IF(B102="SELL",(E102-F102)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H102">
@@ -7609,11 +7705,11 @@
         <v/>
       </c>
       <c r="F103">
-        <f>$B$4</f>
+        <f>IF(B103="BUY",$B$5,IF(B103="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G103">
-        <f>IF(B103="BUY",(F103-E103)/Settings!$B$3,(E103-F103)/Settings!$B$3)</f>
+        <f>IF(B103="BUY",(F103-E103)/Settings!$B$3,IF(B103="SELL",(E103-F103)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H103">
@@ -7659,11 +7755,11 @@
         <v/>
       </c>
       <c r="F104">
-        <f>$B$4</f>
+        <f>IF(B104="BUY",$B$5,IF(B104="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G104">
-        <f>IF(B104="BUY",(F104-E104)/Settings!$B$3,(E104-F104)/Settings!$B$3)</f>
+        <f>IF(B104="BUY",(F104-E104)/Settings!$B$3,IF(B104="SELL",(E104-F104)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H104">
@@ -7709,11 +7805,11 @@
         <v/>
       </c>
       <c r="F105">
-        <f>$B$4</f>
+        <f>IF(B105="BUY",$B$5,IF(B105="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G105">
-        <f>IF(B105="BUY",(F105-E105)/Settings!$B$3,(E105-F105)/Settings!$B$3)</f>
+        <f>IF(B105="BUY",(F105-E105)/Settings!$B$3,IF(B105="SELL",(E105-F105)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H105">
@@ -7759,11 +7855,11 @@
         <v/>
       </c>
       <c r="F106">
-        <f>$B$4</f>
+        <f>IF(B106="BUY",$B$5,IF(B106="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G106">
-        <f>IF(B106="BUY",(F106-E106)/Settings!$B$3,(E106-F106)/Settings!$B$3)</f>
+        <f>IF(B106="BUY",(F106-E106)/Settings!$B$3,IF(B106="SELL",(E106-F106)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H106">
@@ -7809,11 +7905,11 @@
         <v/>
       </c>
       <c r="F107">
-        <f>$B$4</f>
+        <f>IF(B107="BUY",$B$5,IF(B107="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G107">
-        <f>IF(B107="BUY",(F107-E107)/Settings!$B$3,(E107-F107)/Settings!$B$3)</f>
+        <f>IF(B107="BUY",(F107-E107)/Settings!$B$3,IF(B107="SELL",(E107-F107)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H107">
@@ -7859,11 +7955,11 @@
         <v/>
       </c>
       <c r="F108">
-        <f>$B$4</f>
+        <f>IF(B108="BUY",$B$5,IF(B108="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G108">
-        <f>IF(B108="BUY",(F108-E108)/Settings!$B$3,(E108-F108)/Settings!$B$3)</f>
+        <f>IF(B108="BUY",(F108-E108)/Settings!$B$3,IF(B108="SELL",(E108-F108)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H108">
@@ -7909,11 +8005,11 @@
         <v/>
       </c>
       <c r="F109">
-        <f>$B$4</f>
+        <f>IF(B109="BUY",$B$5,IF(B109="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G109">
-        <f>IF(B109="BUY",(F109-E109)/Settings!$B$3,(E109-F109)/Settings!$B$3)</f>
+        <f>IF(B109="BUY",(F109-E109)/Settings!$B$3,IF(B109="SELL",(E109-F109)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H109">
@@ -7959,11 +8055,11 @@
         <v/>
       </c>
       <c r="F110">
-        <f>$B$4</f>
+        <f>IF(B110="BUY",$B$5,IF(B110="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G110">
-        <f>IF(B110="BUY",(F110-E110)/Settings!$B$3,(E110-F110)/Settings!$B$3)</f>
+        <f>IF(B110="BUY",(F110-E110)/Settings!$B$3,IF(B110="SELL",(E110-F110)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H110">
@@ -8009,11 +8105,11 @@
         <v/>
       </c>
       <c r="F111">
-        <f>$B$4</f>
+        <f>IF(B111="BUY",$B$5,IF(B111="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G111">
-        <f>IF(B111="BUY",(F111-E111)/Settings!$B$3,(E111-F111)/Settings!$B$3)</f>
+        <f>IF(B111="BUY",(F111-E111)/Settings!$B$3,IF(B111="SELL",(E111-F111)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H111">
@@ -8059,11 +8155,11 @@
         <v/>
       </c>
       <c r="F112">
-        <f>$B$4</f>
+        <f>IF(B112="BUY",$B$5,IF(B112="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G112">
-        <f>IF(B112="BUY",(F112-E112)/Settings!$B$3,(E112-F112)/Settings!$B$3)</f>
+        <f>IF(B112="BUY",(F112-E112)/Settings!$B$3,IF(B112="SELL",(E112-F112)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H112">
@@ -8109,11 +8205,11 @@
         <v/>
       </c>
       <c r="F113">
-        <f>$B$4</f>
+        <f>IF(B113="BUY",$B$5,IF(B113="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G113">
-        <f>IF(B113="BUY",(F113-E113)/Settings!$B$3,(E113-F113)/Settings!$B$3)</f>
+        <f>IF(B113="BUY",(F113-E113)/Settings!$B$3,IF(B113="SELL",(E113-F113)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H113">
@@ -8159,11 +8255,11 @@
         <v/>
       </c>
       <c r="F114">
-        <f>$B$4</f>
+        <f>IF(B114="BUY",$B$5,IF(B114="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G114">
-        <f>IF(B114="BUY",(F114-E114)/Settings!$B$3,(E114-F114)/Settings!$B$3)</f>
+        <f>IF(B114="BUY",(F114-E114)/Settings!$B$3,IF(B114="SELL",(E114-F114)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H114">
@@ -8209,11 +8305,11 @@
         <v/>
       </c>
       <c r="F115">
-        <f>$B$4</f>
+        <f>IF(B115="BUY",$B$5,IF(B115="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G115">
-        <f>IF(B115="BUY",(F115-E115)/Settings!$B$3,(E115-F115)/Settings!$B$3)</f>
+        <f>IF(B115="BUY",(F115-E115)/Settings!$B$3,IF(B115="SELL",(E115-F115)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H115">
@@ -8259,11 +8355,11 @@
         <v/>
       </c>
       <c r="F116">
-        <f>$B$4</f>
+        <f>IF(B116="BUY",$B$5,IF(B116="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G116">
-        <f>IF(B116="BUY",(F116-E116)/Settings!$B$3,(E116-F116)/Settings!$B$3)</f>
+        <f>IF(B116="BUY",(F116-E116)/Settings!$B$3,IF(B116="SELL",(E116-F116)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H116">
@@ -8309,11 +8405,11 @@
         <v/>
       </c>
       <c r="F117">
-        <f>$B$4</f>
+        <f>IF(B117="BUY",$B$5,IF(B117="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G117">
-        <f>IF(B117="BUY",(F117-E117)/Settings!$B$3,(E117-F117)/Settings!$B$3)</f>
+        <f>IF(B117="BUY",(F117-E117)/Settings!$B$3,IF(B117="SELL",(E117-F117)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H117">
@@ -8359,11 +8455,11 @@
         <v/>
       </c>
       <c r="F118">
-        <f>$B$4</f>
+        <f>IF(B118="BUY",$B$5,IF(B118="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G118">
-        <f>IF(B118="BUY",(F118-E118)/Settings!$B$3,(E118-F118)/Settings!$B$3)</f>
+        <f>IF(B118="BUY",(F118-E118)/Settings!$B$3,IF(B118="SELL",(E118-F118)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H118">
@@ -8409,11 +8505,11 @@
         <v/>
       </c>
       <c r="F119">
-        <f>$B$4</f>
+        <f>IF(B119="BUY",$B$5,IF(B119="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G119">
-        <f>IF(B119="BUY",(F119-E119)/Settings!$B$3,(E119-F119)/Settings!$B$3)</f>
+        <f>IF(B119="BUY",(F119-E119)/Settings!$B$3,IF(B119="SELL",(E119-F119)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H119">
@@ -8459,11 +8555,11 @@
         <v/>
       </c>
       <c r="F120">
-        <f>$B$4</f>
+        <f>IF(B120="BUY",$B$5,IF(B120="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G120">
-        <f>IF(B120="BUY",(F120-E120)/Settings!$B$3,(E120-F120)/Settings!$B$3)</f>
+        <f>IF(B120="BUY",(F120-E120)/Settings!$B$3,IF(B120="SELL",(E120-F120)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H120">
@@ -8509,11 +8605,11 @@
         <v/>
       </c>
       <c r="F121">
-        <f>$B$4</f>
+        <f>IF(B121="BUY",$B$5,IF(B121="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G121">
-        <f>IF(B121="BUY",(F121-E121)/Settings!$B$3,(E121-F121)/Settings!$B$3)</f>
+        <f>IF(B121="BUY",(F121-E121)/Settings!$B$3,IF(B121="SELL",(E121-F121)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H121">
@@ -8559,11 +8655,11 @@
         <v/>
       </c>
       <c r="F122">
-        <f>$B$4</f>
+        <f>IF(B122="BUY",$B$5,IF(B122="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G122">
-        <f>IF(B122="BUY",(F122-E122)/Settings!$B$3,(E122-F122)/Settings!$B$3)</f>
+        <f>IF(B122="BUY",(F122-E122)/Settings!$B$3,IF(B122="SELL",(E122-F122)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H122">
@@ -8609,11 +8705,11 @@
         <v/>
       </c>
       <c r="F123">
-        <f>$B$4</f>
+        <f>IF(B123="BUY",$B$5,IF(B123="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G123">
-        <f>IF(B123="BUY",(F123-E123)/Settings!$B$3,(E123-F123)/Settings!$B$3)</f>
+        <f>IF(B123="BUY",(F123-E123)/Settings!$B$3,IF(B123="SELL",(E123-F123)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H123">
@@ -8659,11 +8755,11 @@
         <v/>
       </c>
       <c r="F124">
-        <f>$B$4</f>
+        <f>IF(B124="BUY",$B$5,IF(B124="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G124">
-        <f>IF(B124="BUY",(F124-E124)/Settings!$B$3,(E124-F124)/Settings!$B$3)</f>
+        <f>IF(B124="BUY",(F124-E124)/Settings!$B$3,IF(B124="SELL",(E124-F124)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H124">
@@ -8709,11 +8805,11 @@
         <v/>
       </c>
       <c r="F125">
-        <f>$B$4</f>
+        <f>IF(B125="BUY",$B$5,IF(B125="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G125">
-        <f>IF(B125="BUY",(F125-E125)/Settings!$B$3,(E125-F125)/Settings!$B$3)</f>
+        <f>IF(B125="BUY",(F125-E125)/Settings!$B$3,IF(B125="SELL",(E125-F125)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H125">
@@ -8759,11 +8855,11 @@
         <v/>
       </c>
       <c r="F126">
-        <f>$B$4</f>
+        <f>IF(B126="BUY",$B$5,IF(B126="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G126">
-        <f>IF(B126="BUY",(F126-E126)/Settings!$B$3,(E126-F126)/Settings!$B$3)</f>
+        <f>IF(B126="BUY",(F126-E126)/Settings!$B$3,IF(B126="SELL",(E126-F126)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H126">
@@ -8809,11 +8905,11 @@
         <v/>
       </c>
       <c r="F127">
-        <f>$B$4</f>
+        <f>IF(B127="BUY",$B$5,IF(B127="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G127">
-        <f>IF(B127="BUY",(F127-E127)/Settings!$B$3,(E127-F127)/Settings!$B$3)</f>
+        <f>IF(B127="BUY",(F127-E127)/Settings!$B$3,IF(B127="SELL",(E127-F127)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H127">
@@ -8859,11 +8955,11 @@
         <v/>
       </c>
       <c r="F128">
-        <f>$B$4</f>
+        <f>IF(B128="BUY",$B$5,IF(B128="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G128">
-        <f>IF(B128="BUY",(F128-E128)/Settings!$B$3,(E128-F128)/Settings!$B$3)</f>
+        <f>IF(B128="BUY",(F128-E128)/Settings!$B$3,IF(B128="SELL",(E128-F128)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H128">
@@ -8909,11 +9005,11 @@
         <v/>
       </c>
       <c r="F129">
-        <f>$B$4</f>
+        <f>IF(B129="BUY",$B$5,IF(B129="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G129">
-        <f>IF(B129="BUY",(F129-E129)/Settings!$B$3,(E129-F129)/Settings!$B$3)</f>
+        <f>IF(B129="BUY",(F129-E129)/Settings!$B$3,IF(B129="SELL",(E129-F129)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H129">
@@ -8959,11 +9055,11 @@
         <v/>
       </c>
       <c r="F130">
-        <f>$B$4</f>
+        <f>IF(B130="BUY",$B$5,IF(B130="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G130">
-        <f>IF(B130="BUY",(F130-E130)/Settings!$B$3,(E130-F130)/Settings!$B$3)</f>
+        <f>IF(B130="BUY",(F130-E130)/Settings!$B$3,IF(B130="SELL",(E130-F130)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H130">
@@ -9009,11 +9105,11 @@
         <v/>
       </c>
       <c r="F131">
-        <f>$B$4</f>
+        <f>IF(B131="BUY",$B$5,IF(B131="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G131">
-        <f>IF(B131="BUY",(F131-E131)/Settings!$B$3,(E131-F131)/Settings!$B$3)</f>
+        <f>IF(B131="BUY",(F131-E131)/Settings!$B$3,IF(B131="SELL",(E131-F131)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H131">
@@ -9059,11 +9155,11 @@
         <v/>
       </c>
       <c r="F132">
-        <f>$B$4</f>
+        <f>IF(B132="BUY",$B$5,IF(B132="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G132">
-        <f>IF(B132="BUY",(F132-E132)/Settings!$B$3,(E132-F132)/Settings!$B$3)</f>
+        <f>IF(B132="BUY",(F132-E132)/Settings!$B$3,IF(B132="SELL",(E132-F132)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H132">
@@ -9109,11 +9205,11 @@
         <v/>
       </c>
       <c r="F133">
-        <f>$B$4</f>
+        <f>IF(B133="BUY",$B$5,IF(B133="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G133">
-        <f>IF(B133="BUY",(F133-E133)/Settings!$B$3,(E133-F133)/Settings!$B$3)</f>
+        <f>IF(B133="BUY",(F133-E133)/Settings!$B$3,IF(B133="SELL",(E133-F133)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H133">
@@ -9159,11 +9255,11 @@
         <v/>
       </c>
       <c r="F134">
-        <f>$B$4</f>
+        <f>IF(B134="BUY",$B$5,IF(B134="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G134">
-        <f>IF(B134="BUY",(F134-E134)/Settings!$B$3,(E134-F134)/Settings!$B$3)</f>
+        <f>IF(B134="BUY",(F134-E134)/Settings!$B$3,IF(B134="SELL",(E134-F134)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H134">
@@ -9209,11 +9305,11 @@
         <v/>
       </c>
       <c r="F135">
-        <f>$B$4</f>
+        <f>IF(B135="BUY",$B$5,IF(B135="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G135">
-        <f>IF(B135="BUY",(F135-E135)/Settings!$B$3,(E135-F135)/Settings!$B$3)</f>
+        <f>IF(B135="BUY",(F135-E135)/Settings!$B$3,IF(B135="SELL",(E135-F135)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H135">
@@ -9259,11 +9355,11 @@
         <v/>
       </c>
       <c r="F136">
-        <f>$B$4</f>
+        <f>IF(B136="BUY",$B$5,IF(B136="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G136">
-        <f>IF(B136="BUY",(F136-E136)/Settings!$B$3,(E136-F136)/Settings!$B$3)</f>
+        <f>IF(B136="BUY",(F136-E136)/Settings!$B$3,IF(B136="SELL",(E136-F136)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H136">
@@ -9309,11 +9405,11 @@
         <v/>
       </c>
       <c r="F137">
-        <f>$B$4</f>
+        <f>IF(B137="BUY",$B$5,IF(B137="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G137">
-        <f>IF(B137="BUY",(F137-E137)/Settings!$B$3,(E137-F137)/Settings!$B$3)</f>
+        <f>IF(B137="BUY",(F137-E137)/Settings!$B$3,IF(B137="SELL",(E137-F137)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H137">
@@ -9359,11 +9455,11 @@
         <v/>
       </c>
       <c r="F138">
-        <f>$B$4</f>
+        <f>IF(B138="BUY",$B$5,IF(B138="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G138">
-        <f>IF(B138="BUY",(F138-E138)/Settings!$B$3,(E138-F138)/Settings!$B$3)</f>
+        <f>IF(B138="BUY",(F138-E138)/Settings!$B$3,IF(B138="SELL",(E138-F138)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H138">
@@ -9409,11 +9505,11 @@
         <v/>
       </c>
       <c r="F139">
-        <f>$B$4</f>
+        <f>IF(B139="BUY",$B$5,IF(B139="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G139">
-        <f>IF(B139="BUY",(F139-E139)/Settings!$B$3,(E139-F139)/Settings!$B$3)</f>
+        <f>IF(B139="BUY",(F139-E139)/Settings!$B$3,IF(B139="SELL",(E139-F139)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H139">
@@ -9459,11 +9555,11 @@
         <v/>
       </c>
       <c r="F140">
-        <f>$B$4</f>
+        <f>IF(B140="BUY",$B$5,IF(B140="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G140">
-        <f>IF(B140="BUY",(F140-E140)/Settings!$B$3,(E140-F140)/Settings!$B$3)</f>
+        <f>IF(B140="BUY",(F140-E140)/Settings!$B$3,IF(B140="SELL",(E140-F140)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H140">
@@ -9509,11 +9605,11 @@
         <v/>
       </c>
       <c r="F141">
-        <f>$B$4</f>
+        <f>IF(B141="BUY",$B$5,IF(B141="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G141">
-        <f>IF(B141="BUY",(F141-E141)/Settings!$B$3,(E141-F141)/Settings!$B$3)</f>
+        <f>IF(B141="BUY",(F141-E141)/Settings!$B$3,IF(B141="SELL",(E141-F141)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H141">
@@ -9559,11 +9655,11 @@
         <v/>
       </c>
       <c r="F142">
-        <f>$B$4</f>
+        <f>IF(B142="BUY",$B$5,IF(B142="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G142">
-        <f>IF(B142="BUY",(F142-E142)/Settings!$B$3,(E142-F142)/Settings!$B$3)</f>
+        <f>IF(B142="BUY",(F142-E142)/Settings!$B$3,IF(B142="SELL",(E142-F142)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H142">
@@ -9609,11 +9705,11 @@
         <v/>
       </c>
       <c r="F143">
-        <f>$B$4</f>
+        <f>IF(B143="BUY",$B$5,IF(B143="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G143">
-        <f>IF(B143="BUY",(F143-E143)/Settings!$B$3,(E143-F143)/Settings!$B$3)</f>
+        <f>IF(B143="BUY",(F143-E143)/Settings!$B$3,IF(B143="SELL",(E143-F143)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H143">
@@ -9659,11 +9755,11 @@
         <v/>
       </c>
       <c r="F144">
-        <f>$B$4</f>
+        <f>IF(B144="BUY",$B$5,IF(B144="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G144">
-        <f>IF(B144="BUY",(F144-E144)/Settings!$B$3,(E144-F144)/Settings!$B$3)</f>
+        <f>IF(B144="BUY",(F144-E144)/Settings!$B$3,IF(B144="SELL",(E144-F144)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H144">
@@ -9709,11 +9805,11 @@
         <v/>
       </c>
       <c r="F145">
-        <f>$B$4</f>
+        <f>IF(B145="BUY",$B$5,IF(B145="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G145">
-        <f>IF(B145="BUY",(F145-E145)/Settings!$B$3,(E145-F145)/Settings!$B$3)</f>
+        <f>IF(B145="BUY",(F145-E145)/Settings!$B$3,IF(B145="SELL",(E145-F145)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H145">
@@ -9759,11 +9855,11 @@
         <v/>
       </c>
       <c r="F146">
-        <f>$B$4</f>
+        <f>IF(B146="BUY",$B$5,IF(B146="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G146">
-        <f>IF(B146="BUY",(F146-E146)/Settings!$B$3,(E146-F146)/Settings!$B$3)</f>
+        <f>IF(B146="BUY",(F146-E146)/Settings!$B$3,IF(B146="SELL",(E146-F146)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H146">
@@ -9809,11 +9905,11 @@
         <v/>
       </c>
       <c r="F147">
-        <f>$B$4</f>
+        <f>IF(B147="BUY",$B$5,IF(B147="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G147">
-        <f>IF(B147="BUY",(F147-E147)/Settings!$B$3,(E147-F147)/Settings!$B$3)</f>
+        <f>IF(B147="BUY",(F147-E147)/Settings!$B$3,IF(B147="SELL",(E147-F147)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H147">
@@ -9859,11 +9955,11 @@
         <v/>
       </c>
       <c r="F148">
-        <f>$B$4</f>
+        <f>IF(B148="BUY",$B$5,IF(B148="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G148">
-        <f>IF(B148="BUY",(F148-E148)/Settings!$B$3,(E148-F148)/Settings!$B$3)</f>
+        <f>IF(B148="BUY",(F148-E148)/Settings!$B$3,IF(B148="SELL",(E148-F148)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H148">
@@ -9909,11 +10005,11 @@
         <v/>
       </c>
       <c r="F149">
-        <f>$B$4</f>
+        <f>IF(B149="BUY",$B$5,IF(B149="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G149">
-        <f>IF(B149="BUY",(F149-E149)/Settings!$B$3,(E149-F149)/Settings!$B$3)</f>
+        <f>IF(B149="BUY",(F149-E149)/Settings!$B$3,IF(B149="SELL",(E149-F149)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H149">
@@ -9959,11 +10055,11 @@
         <v/>
       </c>
       <c r="F150">
-        <f>$B$4</f>
+        <f>IF(B150="BUY",$B$5,IF(B150="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G150">
-        <f>IF(B150="BUY",(F150-E150)/Settings!$B$3,(E150-F150)/Settings!$B$3)</f>
+        <f>IF(B150="BUY",(F150-E150)/Settings!$B$3,IF(B150="SELL",(E150-F150)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H150">
@@ -10009,11 +10105,11 @@
         <v/>
       </c>
       <c r="F151">
-        <f>$B$4</f>
+        <f>IF(B151="BUY",$B$5,IF(B151="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G151">
-        <f>IF(B151="BUY",(F151-E151)/Settings!$B$3,(E151-F151)/Settings!$B$3)</f>
+        <f>IF(B151="BUY",(F151-E151)/Settings!$B$3,IF(B151="SELL",(E151-F151)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H151">
@@ -10059,11 +10155,11 @@
         <v/>
       </c>
       <c r="F152">
-        <f>$B$4</f>
+        <f>IF(B152="BUY",$B$5,IF(B152="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G152">
-        <f>IF(B152="BUY",(F152-E152)/Settings!$B$3,(E152-F152)/Settings!$B$3)</f>
+        <f>IF(B152="BUY",(F152-E152)/Settings!$B$3,IF(B152="SELL",(E152-F152)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H152">
@@ -10109,11 +10205,11 @@
         <v/>
       </c>
       <c r="F153">
-        <f>$B$4</f>
+        <f>IF(B153="BUY",$B$5,IF(B153="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G153">
-        <f>IF(B153="BUY",(F153-E153)/Settings!$B$3,(E153-F153)/Settings!$B$3)</f>
+        <f>IF(B153="BUY",(F153-E153)/Settings!$B$3,IF(B153="SELL",(E153-F153)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H153">
@@ -10159,11 +10255,11 @@
         <v/>
       </c>
       <c r="F154">
-        <f>$B$4</f>
+        <f>IF(B154="BUY",$B$5,IF(B154="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G154">
-        <f>IF(B154="BUY",(F154-E154)/Settings!$B$3,(E154-F154)/Settings!$B$3)</f>
+        <f>IF(B154="BUY",(F154-E154)/Settings!$B$3,IF(B154="SELL",(E154-F154)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H154">
@@ -10209,11 +10305,11 @@
         <v/>
       </c>
       <c r="F155">
-        <f>$B$4</f>
+        <f>IF(B155="BUY",$B$5,IF(B155="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G155">
-        <f>IF(B155="BUY",(F155-E155)/Settings!$B$3,(E155-F155)/Settings!$B$3)</f>
+        <f>IF(B155="BUY",(F155-E155)/Settings!$B$3,IF(B155="SELL",(E155-F155)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H155">
@@ -10259,11 +10355,11 @@
         <v/>
       </c>
       <c r="F156">
-        <f>$B$4</f>
+        <f>IF(B156="BUY",$B$5,IF(B156="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G156">
-        <f>IF(B156="BUY",(F156-E156)/Settings!$B$3,(E156-F156)/Settings!$B$3)</f>
+        <f>IF(B156="BUY",(F156-E156)/Settings!$B$3,IF(B156="SELL",(E156-F156)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H156">
@@ -10309,11 +10405,11 @@
         <v/>
       </c>
       <c r="F157">
-        <f>$B$4</f>
+        <f>IF(B157="BUY",$B$5,IF(B157="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G157">
-        <f>IF(B157="BUY",(F157-E157)/Settings!$B$3,(E157-F157)/Settings!$B$3)</f>
+        <f>IF(B157="BUY",(F157-E157)/Settings!$B$3,IF(B157="SELL",(E157-F157)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H157">
@@ -10359,11 +10455,11 @@
         <v/>
       </c>
       <c r="F158">
-        <f>$B$4</f>
+        <f>IF(B158="BUY",$B$5,IF(B158="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G158">
-        <f>IF(B158="BUY",(F158-E158)/Settings!$B$3,(E158-F158)/Settings!$B$3)</f>
+        <f>IF(B158="BUY",(F158-E158)/Settings!$B$3,IF(B158="SELL",(E158-F158)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H158">
@@ -10409,11 +10505,11 @@
         <v/>
       </c>
       <c r="F159">
-        <f>$B$4</f>
+        <f>IF(B159="BUY",$B$5,IF(B159="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G159">
-        <f>IF(B159="BUY",(F159-E159)/Settings!$B$3,(E159-F159)/Settings!$B$3)</f>
+        <f>IF(B159="BUY",(F159-E159)/Settings!$B$3,IF(B159="SELL",(E159-F159)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H159">
@@ -10459,11 +10555,11 @@
         <v/>
       </c>
       <c r="F160">
-        <f>$B$4</f>
+        <f>IF(B160="BUY",$B$5,IF(B160="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G160">
-        <f>IF(B160="BUY",(F160-E160)/Settings!$B$3,(E160-F160)/Settings!$B$3)</f>
+        <f>IF(B160="BUY",(F160-E160)/Settings!$B$3,IF(B160="SELL",(E160-F160)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H160">
@@ -10509,11 +10605,11 @@
         <v/>
       </c>
       <c r="F161">
-        <f>$B$4</f>
+        <f>IF(B161="BUY",$B$5,IF(B161="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G161">
-        <f>IF(B161="BUY",(F161-E161)/Settings!$B$3,(E161-F161)/Settings!$B$3)</f>
+        <f>IF(B161="BUY",(F161-E161)/Settings!$B$3,IF(B161="SELL",(E161-F161)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H161">
@@ -10559,11 +10655,11 @@
         <v/>
       </c>
       <c r="F162">
-        <f>$B$4</f>
+        <f>IF(B162="BUY",$B$5,IF(B162="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G162">
-        <f>IF(B162="BUY",(F162-E162)/Settings!$B$3,(E162-F162)/Settings!$B$3)</f>
+        <f>IF(B162="BUY",(F162-E162)/Settings!$B$3,IF(B162="SELL",(E162-F162)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H162">
@@ -10609,11 +10705,11 @@
         <v/>
       </c>
       <c r="F163">
-        <f>$B$4</f>
+        <f>IF(B163="BUY",$B$5,IF(B163="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G163">
-        <f>IF(B163="BUY",(F163-E163)/Settings!$B$3,(E163-F163)/Settings!$B$3)</f>
+        <f>IF(B163="BUY",(F163-E163)/Settings!$B$3,IF(B163="SELL",(E163-F163)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H163">
@@ -10659,11 +10755,11 @@
         <v/>
       </c>
       <c r="F164">
-        <f>$B$4</f>
+        <f>IF(B164="BUY",$B$5,IF(B164="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G164">
-        <f>IF(B164="BUY",(F164-E164)/Settings!$B$3,(E164-F164)/Settings!$B$3)</f>
+        <f>IF(B164="BUY",(F164-E164)/Settings!$B$3,IF(B164="SELL",(E164-F164)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H164">
@@ -10709,11 +10805,11 @@
         <v/>
       </c>
       <c r="F165">
-        <f>$B$4</f>
+        <f>IF(B165="BUY",$B$5,IF(B165="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G165">
-        <f>IF(B165="BUY",(F165-E165)/Settings!$B$3,(E165-F165)/Settings!$B$3)</f>
+        <f>IF(B165="BUY",(F165-E165)/Settings!$B$3,IF(B165="SELL",(E165-F165)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H165">
@@ -10759,11 +10855,11 @@
         <v/>
       </c>
       <c r="F166">
-        <f>$B$4</f>
+        <f>IF(B166="BUY",$B$5,IF(B166="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G166">
-        <f>IF(B166="BUY",(F166-E166)/Settings!$B$3,(E166-F166)/Settings!$B$3)</f>
+        <f>IF(B166="BUY",(F166-E166)/Settings!$B$3,IF(B166="SELL",(E166-F166)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H166">
@@ -10809,11 +10905,11 @@
         <v/>
       </c>
       <c r="F167">
-        <f>$B$4</f>
+        <f>IF(B167="BUY",$B$5,IF(B167="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G167">
-        <f>IF(B167="BUY",(F167-E167)/Settings!$B$3,(E167-F167)/Settings!$B$3)</f>
+        <f>IF(B167="BUY",(F167-E167)/Settings!$B$3,IF(B167="SELL",(E167-F167)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H167">
@@ -10859,11 +10955,11 @@
         <v/>
       </c>
       <c r="F168">
-        <f>$B$4</f>
+        <f>IF(B168="BUY",$B$5,IF(B168="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G168">
-        <f>IF(B168="BUY",(F168-E168)/Settings!$B$3,(E168-F168)/Settings!$B$3)</f>
+        <f>IF(B168="BUY",(F168-E168)/Settings!$B$3,IF(B168="SELL",(E168-F168)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H168">
@@ -10909,11 +11005,11 @@
         <v/>
       </c>
       <c r="F169">
-        <f>$B$4</f>
+        <f>IF(B169="BUY",$B$5,IF(B169="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G169">
-        <f>IF(B169="BUY",(F169-E169)/Settings!$B$3,(E169-F169)/Settings!$B$3)</f>
+        <f>IF(B169="BUY",(F169-E169)/Settings!$B$3,IF(B169="SELL",(E169-F169)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H169">
@@ -10959,11 +11055,11 @@
         <v/>
       </c>
       <c r="F170">
-        <f>$B$4</f>
+        <f>IF(B170="BUY",$B$5,IF(B170="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G170">
-        <f>IF(B170="BUY",(F170-E170)/Settings!$B$3,(E170-F170)/Settings!$B$3)</f>
+        <f>IF(B170="BUY",(F170-E170)/Settings!$B$3,IF(B170="SELL",(E170-F170)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H170">
@@ -11009,11 +11105,11 @@
         <v/>
       </c>
       <c r="F171">
-        <f>$B$4</f>
+        <f>IF(B171="BUY",$B$5,IF(B171="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G171">
-        <f>IF(B171="BUY",(F171-E171)/Settings!$B$3,(E171-F171)/Settings!$B$3)</f>
+        <f>IF(B171="BUY",(F171-E171)/Settings!$B$3,IF(B171="SELL",(E171-F171)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H171">
@@ -11059,11 +11155,11 @@
         <v/>
       </c>
       <c r="F172">
-        <f>$B$4</f>
+        <f>IF(B172="BUY",$B$5,IF(B172="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G172">
-        <f>IF(B172="BUY",(F172-E172)/Settings!$B$3,(E172-F172)/Settings!$B$3)</f>
+        <f>IF(B172="BUY",(F172-E172)/Settings!$B$3,IF(B172="SELL",(E172-F172)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H172">
@@ -11109,11 +11205,11 @@
         <v/>
       </c>
       <c r="F173">
-        <f>$B$4</f>
+        <f>IF(B173="BUY",$B$5,IF(B173="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G173">
-        <f>IF(B173="BUY",(F173-E173)/Settings!$B$3,(E173-F173)/Settings!$B$3)</f>
+        <f>IF(B173="BUY",(F173-E173)/Settings!$B$3,IF(B173="SELL",(E173-F173)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H173">
@@ -11159,11 +11255,11 @@
         <v/>
       </c>
       <c r="F174">
-        <f>$B$4</f>
+        <f>IF(B174="BUY",$B$5,IF(B174="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G174">
-        <f>IF(B174="BUY",(F174-E174)/Settings!$B$3,(E174-F174)/Settings!$B$3)</f>
+        <f>IF(B174="BUY",(F174-E174)/Settings!$B$3,IF(B174="SELL",(E174-F174)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H174">
@@ -11209,11 +11305,11 @@
         <v/>
       </c>
       <c r="F175">
-        <f>$B$4</f>
+        <f>IF(B175="BUY",$B$5,IF(B175="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G175">
-        <f>IF(B175="BUY",(F175-E175)/Settings!$B$3,(E175-F175)/Settings!$B$3)</f>
+        <f>IF(B175="BUY",(F175-E175)/Settings!$B$3,IF(B175="SELL",(E175-F175)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H175">
@@ -11259,11 +11355,11 @@
         <v/>
       </c>
       <c r="F176">
-        <f>$B$4</f>
+        <f>IF(B176="BUY",$B$5,IF(B176="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G176">
-        <f>IF(B176="BUY",(F176-E176)/Settings!$B$3,(E176-F176)/Settings!$B$3)</f>
+        <f>IF(B176="BUY",(F176-E176)/Settings!$B$3,IF(B176="SELL",(E176-F176)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H176">
@@ -11309,11 +11405,11 @@
         <v/>
       </c>
       <c r="F177">
-        <f>$B$4</f>
+        <f>IF(B177="BUY",$B$5,IF(B177="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G177">
-        <f>IF(B177="BUY",(F177-E177)/Settings!$B$3,(E177-F177)/Settings!$B$3)</f>
+        <f>IF(B177="BUY",(F177-E177)/Settings!$B$3,IF(B177="SELL",(E177-F177)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H177">
@@ -11359,11 +11455,11 @@
         <v/>
       </c>
       <c r="F178">
-        <f>$B$4</f>
+        <f>IF(B178="BUY",$B$5,IF(B178="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G178">
-        <f>IF(B178="BUY",(F178-E178)/Settings!$B$3,(E178-F178)/Settings!$B$3)</f>
+        <f>IF(B178="BUY",(F178-E178)/Settings!$B$3,IF(B178="SELL",(E178-F178)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H178">
@@ -11409,11 +11505,11 @@
         <v/>
       </c>
       <c r="F179">
-        <f>$B$4</f>
+        <f>IF(B179="BUY",$B$5,IF(B179="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G179">
-        <f>IF(B179="BUY",(F179-E179)/Settings!$B$3,(E179-F179)/Settings!$B$3)</f>
+        <f>IF(B179="BUY",(F179-E179)/Settings!$B$3,IF(B179="SELL",(E179-F179)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H179">
@@ -11459,11 +11555,11 @@
         <v/>
       </c>
       <c r="F180">
-        <f>$B$4</f>
+        <f>IF(B180="BUY",$B$5,IF(B180="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G180">
-        <f>IF(B180="BUY",(F180-E180)/Settings!$B$3,(E180-F180)/Settings!$B$3)</f>
+        <f>IF(B180="BUY",(F180-E180)/Settings!$B$3,IF(B180="SELL",(E180-F180)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H180">
@@ -11509,11 +11605,11 @@
         <v/>
       </c>
       <c r="F181">
-        <f>$B$4</f>
+        <f>IF(B181="BUY",$B$5,IF(B181="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G181">
-        <f>IF(B181="BUY",(F181-E181)/Settings!$B$3,(E181-F181)/Settings!$B$3)</f>
+        <f>IF(B181="BUY",(F181-E181)/Settings!$B$3,IF(B181="SELL",(E181-F181)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H181">
@@ -11559,11 +11655,11 @@
         <v/>
       </c>
       <c r="F182">
-        <f>$B$4</f>
+        <f>IF(B182="BUY",$B$5,IF(B182="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G182">
-        <f>IF(B182="BUY",(F182-E182)/Settings!$B$3,(E182-F182)/Settings!$B$3)</f>
+        <f>IF(B182="BUY",(F182-E182)/Settings!$B$3,IF(B182="SELL",(E182-F182)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H182">
@@ -11609,11 +11705,11 @@
         <v/>
       </c>
       <c r="F183">
-        <f>$B$4</f>
+        <f>IF(B183="BUY",$B$5,IF(B183="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G183">
-        <f>IF(B183="BUY",(F183-E183)/Settings!$B$3,(E183-F183)/Settings!$B$3)</f>
+        <f>IF(B183="BUY",(F183-E183)/Settings!$B$3,IF(B183="SELL",(E183-F183)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H183">
@@ -11659,11 +11755,11 @@
         <v/>
       </c>
       <c r="F184">
-        <f>$B$4</f>
+        <f>IF(B184="BUY",$B$5,IF(B184="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G184">
-        <f>IF(B184="BUY",(F184-E184)/Settings!$B$3,(E184-F184)/Settings!$B$3)</f>
+        <f>IF(B184="BUY",(F184-E184)/Settings!$B$3,IF(B184="SELL",(E184-F184)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H184">
@@ -11709,11 +11805,11 @@
         <v/>
       </c>
       <c r="F185">
-        <f>$B$4</f>
+        <f>IF(B185="BUY",$B$5,IF(B185="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G185">
-        <f>IF(B185="BUY",(F185-E185)/Settings!$B$3,(E185-F185)/Settings!$B$3)</f>
+        <f>IF(B185="BUY",(F185-E185)/Settings!$B$3,IF(B185="SELL",(E185-F185)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H185">
@@ -11759,11 +11855,11 @@
         <v/>
       </c>
       <c r="F186">
-        <f>$B$4</f>
+        <f>IF(B186="BUY",$B$5,IF(B186="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G186">
-        <f>IF(B186="BUY",(F186-E186)/Settings!$B$3,(E186-F186)/Settings!$B$3)</f>
+        <f>IF(B186="BUY",(F186-E186)/Settings!$B$3,IF(B186="SELL",(E186-F186)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H186">
@@ -11809,11 +11905,11 @@
         <v/>
       </c>
       <c r="F187">
-        <f>$B$4</f>
+        <f>IF(B187="BUY",$B$5,IF(B187="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G187">
-        <f>IF(B187="BUY",(F187-E187)/Settings!$B$3,(E187-F187)/Settings!$B$3)</f>
+        <f>IF(B187="BUY",(F187-E187)/Settings!$B$3,IF(B187="SELL",(E187-F187)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H187">
@@ -11859,11 +11955,11 @@
         <v/>
       </c>
       <c r="F188">
-        <f>$B$4</f>
+        <f>IF(B188="BUY",$B$5,IF(B188="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G188">
-        <f>IF(B188="BUY",(F188-E188)/Settings!$B$3,(E188-F188)/Settings!$B$3)</f>
+        <f>IF(B188="BUY",(F188-E188)/Settings!$B$3,IF(B188="SELL",(E188-F188)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H188">
@@ -11909,11 +12005,11 @@
         <v/>
       </c>
       <c r="F189">
-        <f>$B$4</f>
+        <f>IF(B189="BUY",$B$5,IF(B189="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G189">
-        <f>IF(B189="BUY",(F189-E189)/Settings!$B$3,(E189-F189)/Settings!$B$3)</f>
+        <f>IF(B189="BUY",(F189-E189)/Settings!$B$3,IF(B189="SELL",(E189-F189)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H189">
@@ -11959,11 +12055,11 @@
         <v/>
       </c>
       <c r="F190">
-        <f>$B$4</f>
+        <f>IF(B190="BUY",$B$5,IF(B190="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G190">
-        <f>IF(B190="BUY",(F190-E190)/Settings!$B$3,(E190-F190)/Settings!$B$3)</f>
+        <f>IF(B190="BUY",(F190-E190)/Settings!$B$3,IF(B190="SELL",(E190-F190)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H190">
@@ -12009,11 +12105,11 @@
         <v/>
       </c>
       <c r="F191">
-        <f>$B$4</f>
+        <f>IF(B191="BUY",$B$5,IF(B191="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G191">
-        <f>IF(B191="BUY",(F191-E191)/Settings!$B$3,(E191-F191)/Settings!$B$3)</f>
+        <f>IF(B191="BUY",(F191-E191)/Settings!$B$3,IF(B191="SELL",(E191-F191)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H191">
@@ -12059,11 +12155,11 @@
         <v/>
       </c>
       <c r="F192">
-        <f>$B$4</f>
+        <f>IF(B192="BUY",$B$5,IF(B192="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G192">
-        <f>IF(B192="BUY",(F192-E192)/Settings!$B$3,(E192-F192)/Settings!$B$3)</f>
+        <f>IF(B192="BUY",(F192-E192)/Settings!$B$3,IF(B192="SELL",(E192-F192)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H192">
@@ -12109,11 +12205,11 @@
         <v/>
       </c>
       <c r="F193">
-        <f>$B$4</f>
+        <f>IF(B193="BUY",$B$5,IF(B193="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G193">
-        <f>IF(B193="BUY",(F193-E193)/Settings!$B$3,(E193-F193)/Settings!$B$3)</f>
+        <f>IF(B193="BUY",(F193-E193)/Settings!$B$3,IF(B193="SELL",(E193-F193)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H193">
@@ -12159,11 +12255,11 @@
         <v/>
       </c>
       <c r="F194">
-        <f>$B$4</f>
+        <f>IF(B194="BUY",$B$5,IF(B194="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G194">
-        <f>IF(B194="BUY",(F194-E194)/Settings!$B$3,(E194-F194)/Settings!$B$3)</f>
+        <f>IF(B194="BUY",(F194-E194)/Settings!$B$3,IF(B194="SELL",(E194-F194)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H194">
@@ -12209,11 +12305,11 @@
         <v/>
       </c>
       <c r="F195">
-        <f>$B$4</f>
+        <f>IF(B195="BUY",$B$5,IF(B195="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G195">
-        <f>IF(B195="BUY",(F195-E195)/Settings!$B$3,(E195-F195)/Settings!$B$3)</f>
+        <f>IF(B195="BUY",(F195-E195)/Settings!$B$3,IF(B195="SELL",(E195-F195)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H195">
@@ -12259,11 +12355,11 @@
         <v/>
       </c>
       <c r="F196">
-        <f>$B$4</f>
+        <f>IF(B196="BUY",$B$5,IF(B196="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G196">
-        <f>IF(B196="BUY",(F196-E196)/Settings!$B$3,(E196-F196)/Settings!$B$3)</f>
+        <f>IF(B196="BUY",(F196-E196)/Settings!$B$3,IF(B196="SELL",(E196-F196)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H196">
@@ -12309,11 +12405,11 @@
         <v/>
       </c>
       <c r="F197">
-        <f>$B$4</f>
+        <f>IF(B197="BUY",$B$5,IF(B197="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G197">
-        <f>IF(B197="BUY",(F197-E197)/Settings!$B$3,(E197-F197)/Settings!$B$3)</f>
+        <f>IF(B197="BUY",(F197-E197)/Settings!$B$3,IF(B197="SELL",(E197-F197)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H197">
@@ -12359,11 +12455,11 @@
         <v/>
       </c>
       <c r="F198">
-        <f>$B$4</f>
+        <f>IF(B198="BUY",$B$5,IF(B198="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G198">
-        <f>IF(B198="BUY",(F198-E198)/Settings!$B$3,(E198-F198)/Settings!$B$3)</f>
+        <f>IF(B198="BUY",(F198-E198)/Settings!$B$3,IF(B198="SELL",(E198-F198)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H198">
@@ -12409,11 +12505,11 @@
         <v/>
       </c>
       <c r="F199">
-        <f>$B$4</f>
+        <f>IF(B199="BUY",$B$5,IF(B199="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G199">
-        <f>IF(B199="BUY",(F199-E199)/Settings!$B$3,(E199-F199)/Settings!$B$3)</f>
+        <f>IF(B199="BUY",(F199-E199)/Settings!$B$3,IF(B199="SELL",(E199-F199)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H199">
@@ -12459,11 +12555,11 @@
         <v/>
       </c>
       <c r="F200">
-        <f>$B$4</f>
+        <f>IF(B200="BUY",$B$5,IF(B200="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G200">
-        <f>IF(B200="BUY",(F200-E200)/Settings!$B$3,(E200-F200)/Settings!$B$3)</f>
+        <f>IF(B200="BUY",(F200-E200)/Settings!$B$3,IF(B200="SELL",(E200-F200)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H200">
@@ -12509,11 +12605,11 @@
         <v/>
       </c>
       <c r="F201">
-        <f>$B$4</f>
+        <f>IF(B201="BUY",$B$5,IF(B201="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G201">
-        <f>IF(B201="BUY",(F201-E201)/Settings!$B$3,(E201-F201)/Settings!$B$3)</f>
+        <f>IF(B201="BUY",(F201-E201)/Settings!$B$3,IF(B201="SELL",(E201-F201)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H201">
@@ -12559,11 +12655,11 @@
         <v/>
       </c>
       <c r="F202">
-        <f>$B$4</f>
+        <f>IF(B202="BUY",$B$5,IF(B202="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G202">
-        <f>IF(B202="BUY",(F202-E202)/Settings!$B$3,(E202-F202)/Settings!$B$3)</f>
+        <f>IF(B202="BUY",(F202-E202)/Settings!$B$3,IF(B202="SELL",(E202-F202)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H202">
@@ -12609,11 +12705,11 @@
         <v/>
       </c>
       <c r="F203">
-        <f>$B$4</f>
+        <f>IF(B203="BUY",$B$5,IF(B203="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G203">
-        <f>IF(B203="BUY",(F203-E203)/Settings!$B$3,(E203-F203)/Settings!$B$3)</f>
+        <f>IF(B203="BUY",(F203-E203)/Settings!$B$3,IF(B203="SELL",(E203-F203)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H203">
@@ -12659,11 +12755,11 @@
         <v/>
       </c>
       <c r="F204">
-        <f>$B$4</f>
+        <f>IF(B204="BUY",$B$5,IF(B204="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G204">
-        <f>IF(B204="BUY",(F204-E204)/Settings!$B$3,(E204-F204)/Settings!$B$3)</f>
+        <f>IF(B204="BUY",(F204-E204)/Settings!$B$3,IF(B204="SELL",(E204-F204)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H204">
@@ -12709,11 +12805,11 @@
         <v/>
       </c>
       <c r="F205">
-        <f>$B$4</f>
+        <f>IF(B205="BUY",$B$5,IF(B205="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G205">
-        <f>IF(B205="BUY",(F205-E205)/Settings!$B$3,(E205-F205)/Settings!$B$3)</f>
+        <f>IF(B205="BUY",(F205-E205)/Settings!$B$3,IF(B205="SELL",(E205-F205)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H205">
@@ -12759,11 +12855,11 @@
         <v/>
       </c>
       <c r="F206">
-        <f>$B$4</f>
+        <f>IF(B206="BUY",$B$5,IF(B206="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G206">
-        <f>IF(B206="BUY",(F206-E206)/Settings!$B$3,(E206-F206)/Settings!$B$3)</f>
+        <f>IF(B206="BUY",(F206-E206)/Settings!$B$3,IF(B206="SELL",(E206-F206)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H206">
@@ -12892,11 +12988,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CurrentPrice</t>
+          <t>CurrentBid</t>
         </is>
       </c>
       <c r="B2">
-        <f>CurrentPositions!F2</f>
+        <f>Settings!$B$31</f>
         <v/>
       </c>
       <c r="M2" t="inlineStr">
@@ -12912,11 +13008,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MoveDownPoints</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
+          <t>CurrentAsk</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>Settings!$B$32</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -12931,12 +13028,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ScenarioPrice</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>B2-B3*Settings!$B$3</f>
-        <v/>
+          <t>MoveDownPoints</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -12949,6 +13045,15 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ScenarioBid</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>B2-B4*Settings!$B$3</f>
+        <v/>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>UpperLevel2</t>
@@ -13052,11 +13157,11 @@
         <v/>
       </c>
       <c r="F7">
-        <f>$B$4</f>
+        <f>IF(B7="BUY",$B$5,IF(B7="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G7">
-        <f>IF(B7="BUY",(F7-E7)/Settings!$B$3,(E7-F7)/Settings!$B$3)</f>
+        <f>IF(B7="BUY",(F7-E7)/Settings!$B$3,IF(B7="SELL",(E7-F7)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H7">
@@ -13111,11 +13216,11 @@
         <v/>
       </c>
       <c r="F8">
-        <f>$B$4</f>
+        <f>IF(B8="BUY",$B$5,IF(B8="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G8">
-        <f>IF(B8="BUY",(F8-E8)/Settings!$B$3,(E8-F8)/Settings!$B$3)</f>
+        <f>IF(B8="BUY",(F8-E8)/Settings!$B$3,IF(B8="SELL",(E8-F8)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H8">
@@ -13161,11 +13266,11 @@
         <v/>
       </c>
       <c r="F9">
-        <f>$B$4</f>
+        <f>IF(B9="BUY",$B$5,IF(B9="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G9">
-        <f>IF(B9="BUY",(F9-E9)/Settings!$B$3,(E9-F9)/Settings!$B$3)</f>
+        <f>IF(B9="BUY",(F9-E9)/Settings!$B$3,IF(B9="SELL",(E9-F9)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H9">
@@ -13220,11 +13325,11 @@
         <v/>
       </c>
       <c r="F10">
-        <f>$B$4</f>
+        <f>IF(B10="BUY",$B$5,IF(B10="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G10">
-        <f>IF(B10="BUY",(F10-E10)/Settings!$B$3,(E10-F10)/Settings!$B$3)</f>
+        <f>IF(B10="BUY",(F10-E10)/Settings!$B$3,IF(B10="SELL",(E10-F10)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H10">
@@ -13279,11 +13384,11 @@
         <v/>
       </c>
       <c r="F11">
-        <f>$B$4</f>
+        <f>IF(B11="BUY",$B$5,IF(B11="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G11">
-        <f>IF(B11="BUY",(F11-E11)/Settings!$B$3,(E11-F11)/Settings!$B$3)</f>
+        <f>IF(B11="BUY",(F11-E11)/Settings!$B$3,IF(B11="SELL",(E11-F11)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H11">
@@ -13338,11 +13443,11 @@
         <v/>
       </c>
       <c r="F12">
-        <f>$B$4</f>
+        <f>IF(B12="BUY",$B$5,IF(B12="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IF(B12="BUY",(F12-E12)/Settings!$B$3,(E12-F12)/Settings!$B$3)</f>
+        <f>IF(B12="BUY",(F12-E12)/Settings!$B$3,IF(B12="SELL",(E12-F12)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H12">
@@ -13397,11 +13502,11 @@
         <v/>
       </c>
       <c r="F13">
-        <f>$B$4</f>
+        <f>IF(B13="BUY",$B$5,IF(B13="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G13">
-        <f>IF(B13="BUY",(F13-E13)/Settings!$B$3,(E13-F13)/Settings!$B$3)</f>
+        <f>IF(B13="BUY",(F13-E13)/Settings!$B$3,IF(B13="SELL",(E13-F13)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H13">
@@ -13447,11 +13552,11 @@
         <v/>
       </c>
       <c r="F14">
-        <f>$B$4</f>
+        <f>IF(B14="BUY",$B$5,IF(B14="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G14">
-        <f>IF(B14="BUY",(F14-E14)/Settings!$B$3,(E14-F14)/Settings!$B$3)</f>
+        <f>IF(B14="BUY",(F14-E14)/Settings!$B$3,IF(B14="SELL",(E14-F14)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H14">
@@ -13497,11 +13602,11 @@
         <v/>
       </c>
       <c r="F15">
-        <f>$B$4</f>
+        <f>IF(B15="BUY",$B$5,IF(B15="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G15">
-        <f>IF(B15="BUY",(F15-E15)/Settings!$B$3,(E15-F15)/Settings!$B$3)</f>
+        <f>IF(B15="BUY",(F15-E15)/Settings!$B$3,IF(B15="SELL",(E15-F15)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H15">
@@ -13547,11 +13652,11 @@
         <v/>
       </c>
       <c r="F16">
-        <f>$B$4</f>
+        <f>IF(B16="BUY",$B$5,IF(B16="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G16">
-        <f>IF(B16="BUY",(F16-E16)/Settings!$B$3,(E16-F16)/Settings!$B$3)</f>
+        <f>IF(B16="BUY",(F16-E16)/Settings!$B$3,IF(B16="SELL",(E16-F16)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H16">
@@ -13597,11 +13702,11 @@
         <v/>
       </c>
       <c r="F17">
-        <f>$B$4</f>
+        <f>IF(B17="BUY",$B$5,IF(B17="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G17">
-        <f>IF(B17="BUY",(F17-E17)/Settings!$B$3,(E17-F17)/Settings!$B$3)</f>
+        <f>IF(B17="BUY",(F17-E17)/Settings!$B$3,IF(B17="SELL",(E17-F17)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H17">
@@ -13647,11 +13752,11 @@
         <v/>
       </c>
       <c r="F18">
-        <f>$B$4</f>
+        <f>IF(B18="BUY",$B$5,IF(B18="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G18">
-        <f>IF(B18="BUY",(F18-E18)/Settings!$B$3,(E18-F18)/Settings!$B$3)</f>
+        <f>IF(B18="BUY",(F18-E18)/Settings!$B$3,IF(B18="SELL",(E18-F18)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H18">
@@ -13697,11 +13802,11 @@
         <v/>
       </c>
       <c r="F19">
-        <f>$B$4</f>
+        <f>IF(B19="BUY",$B$5,IF(B19="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G19">
-        <f>IF(B19="BUY",(F19-E19)/Settings!$B$3,(E19-F19)/Settings!$B$3)</f>
+        <f>IF(B19="BUY",(F19-E19)/Settings!$B$3,IF(B19="SELL",(E19-F19)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H19">
@@ -13747,11 +13852,11 @@
         <v/>
       </c>
       <c r="F20">
-        <f>$B$4</f>
+        <f>IF(B20="BUY",$B$5,IF(B20="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G20">
-        <f>IF(B20="BUY",(F20-E20)/Settings!$B$3,(E20-F20)/Settings!$B$3)</f>
+        <f>IF(B20="BUY",(F20-E20)/Settings!$B$3,IF(B20="SELL",(E20-F20)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H20">
@@ -13797,11 +13902,11 @@
         <v/>
       </c>
       <c r="F21">
-        <f>$B$4</f>
+        <f>IF(B21="BUY",$B$5,IF(B21="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G21">
-        <f>IF(B21="BUY",(F21-E21)/Settings!$B$3,(E21-F21)/Settings!$B$3)</f>
+        <f>IF(B21="BUY",(F21-E21)/Settings!$B$3,IF(B21="SELL",(E21-F21)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H21">
@@ -13847,11 +13952,11 @@
         <v/>
       </c>
       <c r="F22">
-        <f>$B$4</f>
+        <f>IF(B22="BUY",$B$5,IF(B22="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G22">
-        <f>IF(B22="BUY",(F22-E22)/Settings!$B$3,(E22-F22)/Settings!$B$3)</f>
+        <f>IF(B22="BUY",(F22-E22)/Settings!$B$3,IF(B22="SELL",(E22-F22)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H22">
@@ -13897,11 +14002,11 @@
         <v/>
       </c>
       <c r="F23">
-        <f>$B$4</f>
+        <f>IF(B23="BUY",$B$5,IF(B23="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G23">
-        <f>IF(B23="BUY",(F23-E23)/Settings!$B$3,(E23-F23)/Settings!$B$3)</f>
+        <f>IF(B23="BUY",(F23-E23)/Settings!$B$3,IF(B23="SELL",(E23-F23)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H23">
@@ -13947,11 +14052,11 @@
         <v/>
       </c>
       <c r="F24">
-        <f>$B$4</f>
+        <f>IF(B24="BUY",$B$5,IF(B24="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G24">
-        <f>IF(B24="BUY",(F24-E24)/Settings!$B$3,(E24-F24)/Settings!$B$3)</f>
+        <f>IF(B24="BUY",(F24-E24)/Settings!$B$3,IF(B24="SELL",(E24-F24)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H24">
@@ -13997,11 +14102,11 @@
         <v/>
       </c>
       <c r="F25">
-        <f>$B$4</f>
+        <f>IF(B25="BUY",$B$5,IF(B25="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G25">
-        <f>IF(B25="BUY",(F25-E25)/Settings!$B$3,(E25-F25)/Settings!$B$3)</f>
+        <f>IF(B25="BUY",(F25-E25)/Settings!$B$3,IF(B25="SELL",(E25-F25)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H25">
@@ -14047,11 +14152,11 @@
         <v/>
       </c>
       <c r="F26">
-        <f>$B$4</f>
+        <f>IF(B26="BUY",$B$5,IF(B26="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G26">
-        <f>IF(B26="BUY",(F26-E26)/Settings!$B$3,(E26-F26)/Settings!$B$3)</f>
+        <f>IF(B26="BUY",(F26-E26)/Settings!$B$3,IF(B26="SELL",(E26-F26)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H26">
@@ -14097,11 +14202,11 @@
         <v/>
       </c>
       <c r="F27">
-        <f>$B$4</f>
+        <f>IF(B27="BUY",$B$5,IF(B27="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G27">
-        <f>IF(B27="BUY",(F27-E27)/Settings!$B$3,(E27-F27)/Settings!$B$3)</f>
+        <f>IF(B27="BUY",(F27-E27)/Settings!$B$3,IF(B27="SELL",(E27-F27)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H27">
@@ -14147,11 +14252,11 @@
         <v/>
       </c>
       <c r="F28">
-        <f>$B$4</f>
+        <f>IF(B28="BUY",$B$5,IF(B28="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G28">
-        <f>IF(B28="BUY",(F28-E28)/Settings!$B$3,(E28-F28)/Settings!$B$3)</f>
+        <f>IF(B28="BUY",(F28-E28)/Settings!$B$3,IF(B28="SELL",(E28-F28)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H28">
@@ -14197,11 +14302,11 @@
         <v/>
       </c>
       <c r="F29">
-        <f>$B$4</f>
+        <f>IF(B29="BUY",$B$5,IF(B29="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G29">
-        <f>IF(B29="BUY",(F29-E29)/Settings!$B$3,(E29-F29)/Settings!$B$3)</f>
+        <f>IF(B29="BUY",(F29-E29)/Settings!$B$3,IF(B29="SELL",(E29-F29)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H29">
@@ -14247,11 +14352,11 @@
         <v/>
       </c>
       <c r="F30">
-        <f>$B$4</f>
+        <f>IF(B30="BUY",$B$5,IF(B30="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G30">
-        <f>IF(B30="BUY",(F30-E30)/Settings!$B$3,(E30-F30)/Settings!$B$3)</f>
+        <f>IF(B30="BUY",(F30-E30)/Settings!$B$3,IF(B30="SELL",(E30-F30)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H30">
@@ -14297,11 +14402,11 @@
         <v/>
       </c>
       <c r="F31">
-        <f>$B$4</f>
+        <f>IF(B31="BUY",$B$5,IF(B31="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G31">
-        <f>IF(B31="BUY",(F31-E31)/Settings!$B$3,(E31-F31)/Settings!$B$3)</f>
+        <f>IF(B31="BUY",(F31-E31)/Settings!$B$3,IF(B31="SELL",(E31-F31)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H31">
@@ -14347,11 +14452,11 @@
         <v/>
       </c>
       <c r="F32">
-        <f>$B$4</f>
+        <f>IF(B32="BUY",$B$5,IF(B32="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G32">
-        <f>IF(B32="BUY",(F32-E32)/Settings!$B$3,(E32-F32)/Settings!$B$3)</f>
+        <f>IF(B32="BUY",(F32-E32)/Settings!$B$3,IF(B32="SELL",(E32-F32)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H32">
@@ -14397,11 +14502,11 @@
         <v/>
       </c>
       <c r="F33">
-        <f>$B$4</f>
+        <f>IF(B33="BUY",$B$5,IF(B33="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G33">
-        <f>IF(B33="BUY",(F33-E33)/Settings!$B$3,(E33-F33)/Settings!$B$3)</f>
+        <f>IF(B33="BUY",(F33-E33)/Settings!$B$3,IF(B33="SELL",(E33-F33)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H33">
@@ -14447,11 +14552,11 @@
         <v/>
       </c>
       <c r="F34">
-        <f>$B$4</f>
+        <f>IF(B34="BUY",$B$5,IF(B34="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G34">
-        <f>IF(B34="BUY",(F34-E34)/Settings!$B$3,(E34-F34)/Settings!$B$3)</f>
+        <f>IF(B34="BUY",(F34-E34)/Settings!$B$3,IF(B34="SELL",(E34-F34)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H34">
@@ -14497,11 +14602,11 @@
         <v/>
       </c>
       <c r="F35">
-        <f>$B$4</f>
+        <f>IF(B35="BUY",$B$5,IF(B35="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G35">
-        <f>IF(B35="BUY",(F35-E35)/Settings!$B$3,(E35-F35)/Settings!$B$3)</f>
+        <f>IF(B35="BUY",(F35-E35)/Settings!$B$3,IF(B35="SELL",(E35-F35)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H35">
@@ -14547,11 +14652,11 @@
         <v/>
       </c>
       <c r="F36">
-        <f>$B$4</f>
+        <f>IF(B36="BUY",$B$5,IF(B36="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G36">
-        <f>IF(B36="BUY",(F36-E36)/Settings!$B$3,(E36-F36)/Settings!$B$3)</f>
+        <f>IF(B36="BUY",(F36-E36)/Settings!$B$3,IF(B36="SELL",(E36-F36)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H36">
@@ -14597,11 +14702,11 @@
         <v/>
       </c>
       <c r="F37">
-        <f>$B$4</f>
+        <f>IF(B37="BUY",$B$5,IF(B37="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G37">
-        <f>IF(B37="BUY",(F37-E37)/Settings!$B$3,(E37-F37)/Settings!$B$3)</f>
+        <f>IF(B37="BUY",(F37-E37)/Settings!$B$3,IF(B37="SELL",(E37-F37)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H37">
@@ -14647,11 +14752,11 @@
         <v/>
       </c>
       <c r="F38">
-        <f>$B$4</f>
+        <f>IF(B38="BUY",$B$5,IF(B38="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G38">
-        <f>IF(B38="BUY",(F38-E38)/Settings!$B$3,(E38-F38)/Settings!$B$3)</f>
+        <f>IF(B38="BUY",(F38-E38)/Settings!$B$3,IF(B38="SELL",(E38-F38)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H38">
@@ -14697,11 +14802,11 @@
         <v/>
       </c>
       <c r="F39">
-        <f>$B$4</f>
+        <f>IF(B39="BUY",$B$5,IF(B39="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G39">
-        <f>IF(B39="BUY",(F39-E39)/Settings!$B$3,(E39-F39)/Settings!$B$3)</f>
+        <f>IF(B39="BUY",(F39-E39)/Settings!$B$3,IF(B39="SELL",(E39-F39)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H39">
@@ -14747,11 +14852,11 @@
         <v/>
       </c>
       <c r="F40">
-        <f>$B$4</f>
+        <f>IF(B40="BUY",$B$5,IF(B40="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G40">
-        <f>IF(B40="BUY",(F40-E40)/Settings!$B$3,(E40-F40)/Settings!$B$3)</f>
+        <f>IF(B40="BUY",(F40-E40)/Settings!$B$3,IF(B40="SELL",(E40-F40)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H40">
@@ -14797,11 +14902,11 @@
         <v/>
       </c>
       <c r="F41">
-        <f>$B$4</f>
+        <f>IF(B41="BUY",$B$5,IF(B41="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G41">
-        <f>IF(B41="BUY",(F41-E41)/Settings!$B$3,(E41-F41)/Settings!$B$3)</f>
+        <f>IF(B41="BUY",(F41-E41)/Settings!$B$3,IF(B41="SELL",(E41-F41)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H41">
@@ -14847,11 +14952,11 @@
         <v/>
       </c>
       <c r="F42">
-        <f>$B$4</f>
+        <f>IF(B42="BUY",$B$5,IF(B42="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G42">
-        <f>IF(B42="BUY",(F42-E42)/Settings!$B$3,(E42-F42)/Settings!$B$3)</f>
+        <f>IF(B42="BUY",(F42-E42)/Settings!$B$3,IF(B42="SELL",(E42-F42)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H42">
@@ -14897,11 +15002,11 @@
         <v/>
       </c>
       <c r="F43">
-        <f>$B$4</f>
+        <f>IF(B43="BUY",$B$5,IF(B43="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G43">
-        <f>IF(B43="BUY",(F43-E43)/Settings!$B$3,(E43-F43)/Settings!$B$3)</f>
+        <f>IF(B43="BUY",(F43-E43)/Settings!$B$3,IF(B43="SELL",(E43-F43)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H43">
@@ -14947,11 +15052,11 @@
         <v/>
       </c>
       <c r="F44">
-        <f>$B$4</f>
+        <f>IF(B44="BUY",$B$5,IF(B44="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G44">
-        <f>IF(B44="BUY",(F44-E44)/Settings!$B$3,(E44-F44)/Settings!$B$3)</f>
+        <f>IF(B44="BUY",(F44-E44)/Settings!$B$3,IF(B44="SELL",(E44-F44)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H44">
@@ -14997,11 +15102,11 @@
         <v/>
       </c>
       <c r="F45">
-        <f>$B$4</f>
+        <f>IF(B45="BUY",$B$5,IF(B45="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G45">
-        <f>IF(B45="BUY",(F45-E45)/Settings!$B$3,(E45-F45)/Settings!$B$3)</f>
+        <f>IF(B45="BUY",(F45-E45)/Settings!$B$3,IF(B45="SELL",(E45-F45)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H45">
@@ -15047,11 +15152,11 @@
         <v/>
       </c>
       <c r="F46">
-        <f>$B$4</f>
+        <f>IF(B46="BUY",$B$5,IF(B46="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G46">
-        <f>IF(B46="BUY",(F46-E46)/Settings!$B$3,(E46-F46)/Settings!$B$3)</f>
+        <f>IF(B46="BUY",(F46-E46)/Settings!$B$3,IF(B46="SELL",(E46-F46)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H46">
@@ -15097,11 +15202,11 @@
         <v/>
       </c>
       <c r="F47">
-        <f>$B$4</f>
+        <f>IF(B47="BUY",$B$5,IF(B47="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G47">
-        <f>IF(B47="BUY",(F47-E47)/Settings!$B$3,(E47-F47)/Settings!$B$3)</f>
+        <f>IF(B47="BUY",(F47-E47)/Settings!$B$3,IF(B47="SELL",(E47-F47)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H47">
@@ -15147,11 +15252,11 @@
         <v/>
       </c>
       <c r="F48">
-        <f>$B$4</f>
+        <f>IF(B48="BUY",$B$5,IF(B48="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G48">
-        <f>IF(B48="BUY",(F48-E48)/Settings!$B$3,(E48-F48)/Settings!$B$3)</f>
+        <f>IF(B48="BUY",(F48-E48)/Settings!$B$3,IF(B48="SELL",(E48-F48)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H48">
@@ -15197,11 +15302,11 @@
         <v/>
       </c>
       <c r="F49">
-        <f>$B$4</f>
+        <f>IF(B49="BUY",$B$5,IF(B49="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G49">
-        <f>IF(B49="BUY",(F49-E49)/Settings!$B$3,(E49-F49)/Settings!$B$3)</f>
+        <f>IF(B49="BUY",(F49-E49)/Settings!$B$3,IF(B49="SELL",(E49-F49)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H49">
@@ -15247,11 +15352,11 @@
         <v/>
       </c>
       <c r="F50">
-        <f>$B$4</f>
+        <f>IF(B50="BUY",$B$5,IF(B50="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G50">
-        <f>IF(B50="BUY",(F50-E50)/Settings!$B$3,(E50-F50)/Settings!$B$3)</f>
+        <f>IF(B50="BUY",(F50-E50)/Settings!$B$3,IF(B50="SELL",(E50-F50)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H50">
@@ -15297,11 +15402,11 @@
         <v/>
       </c>
       <c r="F51">
-        <f>$B$4</f>
+        <f>IF(B51="BUY",$B$5,IF(B51="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G51">
-        <f>IF(B51="BUY",(F51-E51)/Settings!$B$3,(E51-F51)/Settings!$B$3)</f>
+        <f>IF(B51="BUY",(F51-E51)/Settings!$B$3,IF(B51="SELL",(E51-F51)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H51">
@@ -15347,11 +15452,11 @@
         <v/>
       </c>
       <c r="F52">
-        <f>$B$4</f>
+        <f>IF(B52="BUY",$B$5,IF(B52="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G52">
-        <f>IF(B52="BUY",(F52-E52)/Settings!$B$3,(E52-F52)/Settings!$B$3)</f>
+        <f>IF(B52="BUY",(F52-E52)/Settings!$B$3,IF(B52="SELL",(E52-F52)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H52">
@@ -15397,11 +15502,11 @@
         <v/>
       </c>
       <c r="F53">
-        <f>$B$4</f>
+        <f>IF(B53="BUY",$B$5,IF(B53="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G53">
-        <f>IF(B53="BUY",(F53-E53)/Settings!$B$3,(E53-F53)/Settings!$B$3)</f>
+        <f>IF(B53="BUY",(F53-E53)/Settings!$B$3,IF(B53="SELL",(E53-F53)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H53">
@@ -15447,11 +15552,11 @@
         <v/>
       </c>
       <c r="F54">
-        <f>$B$4</f>
+        <f>IF(B54="BUY",$B$5,IF(B54="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G54">
-        <f>IF(B54="BUY",(F54-E54)/Settings!$B$3,(E54-F54)/Settings!$B$3)</f>
+        <f>IF(B54="BUY",(F54-E54)/Settings!$B$3,IF(B54="SELL",(E54-F54)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H54">
@@ -15497,11 +15602,11 @@
         <v/>
       </c>
       <c r="F55">
-        <f>$B$4</f>
+        <f>IF(B55="BUY",$B$5,IF(B55="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G55">
-        <f>IF(B55="BUY",(F55-E55)/Settings!$B$3,(E55-F55)/Settings!$B$3)</f>
+        <f>IF(B55="BUY",(F55-E55)/Settings!$B$3,IF(B55="SELL",(E55-F55)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H55">
@@ -15547,11 +15652,11 @@
         <v/>
       </c>
       <c r="F56">
-        <f>$B$4</f>
+        <f>IF(B56="BUY",$B$5,IF(B56="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G56">
-        <f>IF(B56="BUY",(F56-E56)/Settings!$B$3,(E56-F56)/Settings!$B$3)</f>
+        <f>IF(B56="BUY",(F56-E56)/Settings!$B$3,IF(B56="SELL",(E56-F56)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H56">
@@ -15597,11 +15702,11 @@
         <v/>
       </c>
       <c r="F57">
-        <f>$B$4</f>
+        <f>IF(B57="BUY",$B$5,IF(B57="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G57">
-        <f>IF(B57="BUY",(F57-E57)/Settings!$B$3,(E57-F57)/Settings!$B$3)</f>
+        <f>IF(B57="BUY",(F57-E57)/Settings!$B$3,IF(B57="SELL",(E57-F57)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H57">
@@ -15647,11 +15752,11 @@
         <v/>
       </c>
       <c r="F58">
-        <f>$B$4</f>
+        <f>IF(B58="BUY",$B$5,IF(B58="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G58">
-        <f>IF(B58="BUY",(F58-E58)/Settings!$B$3,(E58-F58)/Settings!$B$3)</f>
+        <f>IF(B58="BUY",(F58-E58)/Settings!$B$3,IF(B58="SELL",(E58-F58)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H58">
@@ -15697,11 +15802,11 @@
         <v/>
       </c>
       <c r="F59">
-        <f>$B$4</f>
+        <f>IF(B59="BUY",$B$5,IF(B59="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G59">
-        <f>IF(B59="BUY",(F59-E59)/Settings!$B$3,(E59-F59)/Settings!$B$3)</f>
+        <f>IF(B59="BUY",(F59-E59)/Settings!$B$3,IF(B59="SELL",(E59-F59)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H59">
@@ -15747,11 +15852,11 @@
         <v/>
       </c>
       <c r="F60">
-        <f>$B$4</f>
+        <f>IF(B60="BUY",$B$5,IF(B60="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G60">
-        <f>IF(B60="BUY",(F60-E60)/Settings!$B$3,(E60-F60)/Settings!$B$3)</f>
+        <f>IF(B60="BUY",(F60-E60)/Settings!$B$3,IF(B60="SELL",(E60-F60)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H60">
@@ -15797,11 +15902,11 @@
         <v/>
       </c>
       <c r="F61">
-        <f>$B$4</f>
+        <f>IF(B61="BUY",$B$5,IF(B61="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G61">
-        <f>IF(B61="BUY",(F61-E61)/Settings!$B$3,(E61-F61)/Settings!$B$3)</f>
+        <f>IF(B61="BUY",(F61-E61)/Settings!$B$3,IF(B61="SELL",(E61-F61)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H61">
@@ -15847,11 +15952,11 @@
         <v/>
       </c>
       <c r="F62">
-        <f>$B$4</f>
+        <f>IF(B62="BUY",$B$5,IF(B62="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G62">
-        <f>IF(B62="BUY",(F62-E62)/Settings!$B$3,(E62-F62)/Settings!$B$3)</f>
+        <f>IF(B62="BUY",(F62-E62)/Settings!$B$3,IF(B62="SELL",(E62-F62)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H62">
@@ -15897,11 +16002,11 @@
         <v/>
       </c>
       <c r="F63">
-        <f>$B$4</f>
+        <f>IF(B63="BUY",$B$5,IF(B63="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G63">
-        <f>IF(B63="BUY",(F63-E63)/Settings!$B$3,(E63-F63)/Settings!$B$3)</f>
+        <f>IF(B63="BUY",(F63-E63)/Settings!$B$3,IF(B63="SELL",(E63-F63)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H63">
@@ -15947,11 +16052,11 @@
         <v/>
       </c>
       <c r="F64">
-        <f>$B$4</f>
+        <f>IF(B64="BUY",$B$5,IF(B64="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G64">
-        <f>IF(B64="BUY",(F64-E64)/Settings!$B$3,(E64-F64)/Settings!$B$3)</f>
+        <f>IF(B64="BUY",(F64-E64)/Settings!$B$3,IF(B64="SELL",(E64-F64)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H64">
@@ -15997,11 +16102,11 @@
         <v/>
       </c>
       <c r="F65">
-        <f>$B$4</f>
+        <f>IF(B65="BUY",$B$5,IF(B65="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G65">
-        <f>IF(B65="BUY",(F65-E65)/Settings!$B$3,(E65-F65)/Settings!$B$3)</f>
+        <f>IF(B65="BUY",(F65-E65)/Settings!$B$3,IF(B65="SELL",(E65-F65)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H65">
@@ -16047,11 +16152,11 @@
         <v/>
       </c>
       <c r="F66">
-        <f>$B$4</f>
+        <f>IF(B66="BUY",$B$5,IF(B66="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G66">
-        <f>IF(B66="BUY",(F66-E66)/Settings!$B$3,(E66-F66)/Settings!$B$3)</f>
+        <f>IF(B66="BUY",(F66-E66)/Settings!$B$3,IF(B66="SELL",(E66-F66)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H66">
@@ -16097,11 +16202,11 @@
         <v/>
       </c>
       <c r="F67">
-        <f>$B$4</f>
+        <f>IF(B67="BUY",$B$5,IF(B67="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G67">
-        <f>IF(B67="BUY",(F67-E67)/Settings!$B$3,(E67-F67)/Settings!$B$3)</f>
+        <f>IF(B67="BUY",(F67-E67)/Settings!$B$3,IF(B67="SELL",(E67-F67)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H67">
@@ -16147,11 +16252,11 @@
         <v/>
       </c>
       <c r="F68">
-        <f>$B$4</f>
+        <f>IF(B68="BUY",$B$5,IF(B68="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G68">
-        <f>IF(B68="BUY",(F68-E68)/Settings!$B$3,(E68-F68)/Settings!$B$3)</f>
+        <f>IF(B68="BUY",(F68-E68)/Settings!$B$3,IF(B68="SELL",(E68-F68)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H68">
@@ -16197,11 +16302,11 @@
         <v/>
       </c>
       <c r="F69">
-        <f>$B$4</f>
+        <f>IF(B69="BUY",$B$5,IF(B69="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G69">
-        <f>IF(B69="BUY",(F69-E69)/Settings!$B$3,(E69-F69)/Settings!$B$3)</f>
+        <f>IF(B69="BUY",(F69-E69)/Settings!$B$3,IF(B69="SELL",(E69-F69)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H69">
@@ -16247,11 +16352,11 @@
         <v/>
       </c>
       <c r="F70">
-        <f>$B$4</f>
+        <f>IF(B70="BUY",$B$5,IF(B70="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G70">
-        <f>IF(B70="BUY",(F70-E70)/Settings!$B$3,(E70-F70)/Settings!$B$3)</f>
+        <f>IF(B70="BUY",(F70-E70)/Settings!$B$3,IF(B70="SELL",(E70-F70)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H70">
@@ -16297,11 +16402,11 @@
         <v/>
       </c>
       <c r="F71">
-        <f>$B$4</f>
+        <f>IF(B71="BUY",$B$5,IF(B71="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G71">
-        <f>IF(B71="BUY",(F71-E71)/Settings!$B$3,(E71-F71)/Settings!$B$3)</f>
+        <f>IF(B71="BUY",(F71-E71)/Settings!$B$3,IF(B71="SELL",(E71-F71)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H71">
@@ -16347,11 +16452,11 @@
         <v/>
       </c>
       <c r="F72">
-        <f>$B$4</f>
+        <f>IF(B72="BUY",$B$5,IF(B72="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G72">
-        <f>IF(B72="BUY",(F72-E72)/Settings!$B$3,(E72-F72)/Settings!$B$3)</f>
+        <f>IF(B72="BUY",(F72-E72)/Settings!$B$3,IF(B72="SELL",(E72-F72)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H72">
@@ -16397,11 +16502,11 @@
         <v/>
       </c>
       <c r="F73">
-        <f>$B$4</f>
+        <f>IF(B73="BUY",$B$5,IF(B73="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G73">
-        <f>IF(B73="BUY",(F73-E73)/Settings!$B$3,(E73-F73)/Settings!$B$3)</f>
+        <f>IF(B73="BUY",(F73-E73)/Settings!$B$3,IF(B73="SELL",(E73-F73)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H73">
@@ -16447,11 +16552,11 @@
         <v/>
       </c>
       <c r="F74">
-        <f>$B$4</f>
+        <f>IF(B74="BUY",$B$5,IF(B74="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G74">
-        <f>IF(B74="BUY",(F74-E74)/Settings!$B$3,(E74-F74)/Settings!$B$3)</f>
+        <f>IF(B74="BUY",(F74-E74)/Settings!$B$3,IF(B74="SELL",(E74-F74)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H74">
@@ -16497,11 +16602,11 @@
         <v/>
       </c>
       <c r="F75">
-        <f>$B$4</f>
+        <f>IF(B75="BUY",$B$5,IF(B75="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G75">
-        <f>IF(B75="BUY",(F75-E75)/Settings!$B$3,(E75-F75)/Settings!$B$3)</f>
+        <f>IF(B75="BUY",(F75-E75)/Settings!$B$3,IF(B75="SELL",(E75-F75)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H75">
@@ -16547,11 +16652,11 @@
         <v/>
       </c>
       <c r="F76">
-        <f>$B$4</f>
+        <f>IF(B76="BUY",$B$5,IF(B76="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G76">
-        <f>IF(B76="BUY",(F76-E76)/Settings!$B$3,(E76-F76)/Settings!$B$3)</f>
+        <f>IF(B76="BUY",(F76-E76)/Settings!$B$3,IF(B76="SELL",(E76-F76)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H76">
@@ -16597,11 +16702,11 @@
         <v/>
       </c>
       <c r="F77">
-        <f>$B$4</f>
+        <f>IF(B77="BUY",$B$5,IF(B77="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G77">
-        <f>IF(B77="BUY",(F77-E77)/Settings!$B$3,(E77-F77)/Settings!$B$3)</f>
+        <f>IF(B77="BUY",(F77-E77)/Settings!$B$3,IF(B77="SELL",(E77-F77)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H77">
@@ -16647,11 +16752,11 @@
         <v/>
       </c>
       <c r="F78">
-        <f>$B$4</f>
+        <f>IF(B78="BUY",$B$5,IF(B78="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G78">
-        <f>IF(B78="BUY",(F78-E78)/Settings!$B$3,(E78-F78)/Settings!$B$3)</f>
+        <f>IF(B78="BUY",(F78-E78)/Settings!$B$3,IF(B78="SELL",(E78-F78)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H78">
@@ -16697,11 +16802,11 @@
         <v/>
       </c>
       <c r="F79">
-        <f>$B$4</f>
+        <f>IF(B79="BUY",$B$5,IF(B79="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G79">
-        <f>IF(B79="BUY",(F79-E79)/Settings!$B$3,(E79-F79)/Settings!$B$3)</f>
+        <f>IF(B79="BUY",(F79-E79)/Settings!$B$3,IF(B79="SELL",(E79-F79)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H79">
@@ -16747,11 +16852,11 @@
         <v/>
       </c>
       <c r="F80">
-        <f>$B$4</f>
+        <f>IF(B80="BUY",$B$5,IF(B80="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G80">
-        <f>IF(B80="BUY",(F80-E80)/Settings!$B$3,(E80-F80)/Settings!$B$3)</f>
+        <f>IF(B80="BUY",(F80-E80)/Settings!$B$3,IF(B80="SELL",(E80-F80)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H80">
@@ -16797,11 +16902,11 @@
         <v/>
       </c>
       <c r="F81">
-        <f>$B$4</f>
+        <f>IF(B81="BUY",$B$5,IF(B81="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G81">
-        <f>IF(B81="BUY",(F81-E81)/Settings!$B$3,(E81-F81)/Settings!$B$3)</f>
+        <f>IF(B81="BUY",(F81-E81)/Settings!$B$3,IF(B81="SELL",(E81-F81)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H81">
@@ -16847,11 +16952,11 @@
         <v/>
       </c>
       <c r="F82">
-        <f>$B$4</f>
+        <f>IF(B82="BUY",$B$5,IF(B82="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G82">
-        <f>IF(B82="BUY",(F82-E82)/Settings!$B$3,(E82-F82)/Settings!$B$3)</f>
+        <f>IF(B82="BUY",(F82-E82)/Settings!$B$3,IF(B82="SELL",(E82-F82)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H82">
@@ -16897,11 +17002,11 @@
         <v/>
       </c>
       <c r="F83">
-        <f>$B$4</f>
+        <f>IF(B83="BUY",$B$5,IF(B83="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G83">
-        <f>IF(B83="BUY",(F83-E83)/Settings!$B$3,(E83-F83)/Settings!$B$3)</f>
+        <f>IF(B83="BUY",(F83-E83)/Settings!$B$3,IF(B83="SELL",(E83-F83)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H83">
@@ -16947,11 +17052,11 @@
         <v/>
       </c>
       <c r="F84">
-        <f>$B$4</f>
+        <f>IF(B84="BUY",$B$5,IF(B84="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G84">
-        <f>IF(B84="BUY",(F84-E84)/Settings!$B$3,(E84-F84)/Settings!$B$3)</f>
+        <f>IF(B84="BUY",(F84-E84)/Settings!$B$3,IF(B84="SELL",(E84-F84)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H84">
@@ -16997,11 +17102,11 @@
         <v/>
       </c>
       <c r="F85">
-        <f>$B$4</f>
+        <f>IF(B85="BUY",$B$5,IF(B85="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G85">
-        <f>IF(B85="BUY",(F85-E85)/Settings!$B$3,(E85-F85)/Settings!$B$3)</f>
+        <f>IF(B85="BUY",(F85-E85)/Settings!$B$3,IF(B85="SELL",(E85-F85)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H85">
@@ -17047,11 +17152,11 @@
         <v/>
       </c>
       <c r="F86">
-        <f>$B$4</f>
+        <f>IF(B86="BUY",$B$5,IF(B86="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G86">
-        <f>IF(B86="BUY",(F86-E86)/Settings!$B$3,(E86-F86)/Settings!$B$3)</f>
+        <f>IF(B86="BUY",(F86-E86)/Settings!$B$3,IF(B86="SELL",(E86-F86)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H86">
@@ -17097,11 +17202,11 @@
         <v/>
       </c>
       <c r="F87">
-        <f>$B$4</f>
+        <f>IF(B87="BUY",$B$5,IF(B87="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G87">
-        <f>IF(B87="BUY",(F87-E87)/Settings!$B$3,(E87-F87)/Settings!$B$3)</f>
+        <f>IF(B87="BUY",(F87-E87)/Settings!$B$3,IF(B87="SELL",(E87-F87)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H87">
@@ -17147,11 +17252,11 @@
         <v/>
       </c>
       <c r="F88">
-        <f>$B$4</f>
+        <f>IF(B88="BUY",$B$5,IF(B88="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G88">
-        <f>IF(B88="BUY",(F88-E88)/Settings!$B$3,(E88-F88)/Settings!$B$3)</f>
+        <f>IF(B88="BUY",(F88-E88)/Settings!$B$3,IF(B88="SELL",(E88-F88)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H88">
@@ -17197,11 +17302,11 @@
         <v/>
       </c>
       <c r="F89">
-        <f>$B$4</f>
+        <f>IF(B89="BUY",$B$5,IF(B89="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G89">
-        <f>IF(B89="BUY",(F89-E89)/Settings!$B$3,(E89-F89)/Settings!$B$3)</f>
+        <f>IF(B89="BUY",(F89-E89)/Settings!$B$3,IF(B89="SELL",(E89-F89)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H89">
@@ -17247,11 +17352,11 @@
         <v/>
       </c>
       <c r="F90">
-        <f>$B$4</f>
+        <f>IF(B90="BUY",$B$5,IF(B90="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G90">
-        <f>IF(B90="BUY",(F90-E90)/Settings!$B$3,(E90-F90)/Settings!$B$3)</f>
+        <f>IF(B90="BUY",(F90-E90)/Settings!$B$3,IF(B90="SELL",(E90-F90)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H90">
@@ -17297,11 +17402,11 @@
         <v/>
       </c>
       <c r="F91">
-        <f>$B$4</f>
+        <f>IF(B91="BUY",$B$5,IF(B91="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G91">
-        <f>IF(B91="BUY",(F91-E91)/Settings!$B$3,(E91-F91)/Settings!$B$3)</f>
+        <f>IF(B91="BUY",(F91-E91)/Settings!$B$3,IF(B91="SELL",(E91-F91)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H91">
@@ -17347,11 +17452,11 @@
         <v/>
       </c>
       <c r="F92">
-        <f>$B$4</f>
+        <f>IF(B92="BUY",$B$5,IF(B92="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G92">
-        <f>IF(B92="BUY",(F92-E92)/Settings!$B$3,(E92-F92)/Settings!$B$3)</f>
+        <f>IF(B92="BUY",(F92-E92)/Settings!$B$3,IF(B92="SELL",(E92-F92)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H92">
@@ -17397,11 +17502,11 @@
         <v/>
       </c>
       <c r="F93">
-        <f>$B$4</f>
+        <f>IF(B93="BUY",$B$5,IF(B93="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G93">
-        <f>IF(B93="BUY",(F93-E93)/Settings!$B$3,(E93-F93)/Settings!$B$3)</f>
+        <f>IF(B93="BUY",(F93-E93)/Settings!$B$3,IF(B93="SELL",(E93-F93)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H93">
@@ -17447,11 +17552,11 @@
         <v/>
       </c>
       <c r="F94">
-        <f>$B$4</f>
+        <f>IF(B94="BUY",$B$5,IF(B94="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G94">
-        <f>IF(B94="BUY",(F94-E94)/Settings!$B$3,(E94-F94)/Settings!$B$3)</f>
+        <f>IF(B94="BUY",(F94-E94)/Settings!$B$3,IF(B94="SELL",(E94-F94)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H94">
@@ -17497,11 +17602,11 @@
         <v/>
       </c>
       <c r="F95">
-        <f>$B$4</f>
+        <f>IF(B95="BUY",$B$5,IF(B95="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G95">
-        <f>IF(B95="BUY",(F95-E95)/Settings!$B$3,(E95-F95)/Settings!$B$3)</f>
+        <f>IF(B95="BUY",(F95-E95)/Settings!$B$3,IF(B95="SELL",(E95-F95)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H95">
@@ -17547,11 +17652,11 @@
         <v/>
       </c>
       <c r="F96">
-        <f>$B$4</f>
+        <f>IF(B96="BUY",$B$5,IF(B96="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G96">
-        <f>IF(B96="BUY",(F96-E96)/Settings!$B$3,(E96-F96)/Settings!$B$3)</f>
+        <f>IF(B96="BUY",(F96-E96)/Settings!$B$3,IF(B96="SELL",(E96-F96)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H96">
@@ -17597,11 +17702,11 @@
         <v/>
       </c>
       <c r="F97">
-        <f>$B$4</f>
+        <f>IF(B97="BUY",$B$5,IF(B97="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G97">
-        <f>IF(B97="BUY",(F97-E97)/Settings!$B$3,(E97-F97)/Settings!$B$3)</f>
+        <f>IF(B97="BUY",(F97-E97)/Settings!$B$3,IF(B97="SELL",(E97-F97)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H97">
@@ -17647,11 +17752,11 @@
         <v/>
       </c>
       <c r="F98">
-        <f>$B$4</f>
+        <f>IF(B98="BUY",$B$5,IF(B98="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G98">
-        <f>IF(B98="BUY",(F98-E98)/Settings!$B$3,(E98-F98)/Settings!$B$3)</f>
+        <f>IF(B98="BUY",(F98-E98)/Settings!$B$3,IF(B98="SELL",(E98-F98)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H98">
@@ -17697,11 +17802,11 @@
         <v/>
       </c>
       <c r="F99">
-        <f>$B$4</f>
+        <f>IF(B99="BUY",$B$5,IF(B99="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G99">
-        <f>IF(B99="BUY",(F99-E99)/Settings!$B$3,(E99-F99)/Settings!$B$3)</f>
+        <f>IF(B99="BUY",(F99-E99)/Settings!$B$3,IF(B99="SELL",(E99-F99)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H99">
@@ -17747,11 +17852,11 @@
         <v/>
       </c>
       <c r="F100">
-        <f>$B$4</f>
+        <f>IF(B100="BUY",$B$5,IF(B100="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G100">
-        <f>IF(B100="BUY",(F100-E100)/Settings!$B$3,(E100-F100)/Settings!$B$3)</f>
+        <f>IF(B100="BUY",(F100-E100)/Settings!$B$3,IF(B100="SELL",(E100-F100)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H100">
@@ -17797,11 +17902,11 @@
         <v/>
       </c>
       <c r="F101">
-        <f>$B$4</f>
+        <f>IF(B101="BUY",$B$5,IF(B101="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G101">
-        <f>IF(B101="BUY",(F101-E101)/Settings!$B$3,(E101-F101)/Settings!$B$3)</f>
+        <f>IF(B101="BUY",(F101-E101)/Settings!$B$3,IF(B101="SELL",(E101-F101)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H101">
@@ -17847,11 +17952,11 @@
         <v/>
       </c>
       <c r="F102">
-        <f>$B$4</f>
+        <f>IF(B102="BUY",$B$5,IF(B102="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G102">
-        <f>IF(B102="BUY",(F102-E102)/Settings!$B$3,(E102-F102)/Settings!$B$3)</f>
+        <f>IF(B102="BUY",(F102-E102)/Settings!$B$3,IF(B102="SELL",(E102-F102)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H102">
@@ -17897,11 +18002,11 @@
         <v/>
       </c>
       <c r="F103">
-        <f>$B$4</f>
+        <f>IF(B103="BUY",$B$5,IF(B103="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G103">
-        <f>IF(B103="BUY",(F103-E103)/Settings!$B$3,(E103-F103)/Settings!$B$3)</f>
+        <f>IF(B103="BUY",(F103-E103)/Settings!$B$3,IF(B103="SELL",(E103-F103)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H103">
@@ -17947,11 +18052,11 @@
         <v/>
       </c>
       <c r="F104">
-        <f>$B$4</f>
+        <f>IF(B104="BUY",$B$5,IF(B104="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G104">
-        <f>IF(B104="BUY",(F104-E104)/Settings!$B$3,(E104-F104)/Settings!$B$3)</f>
+        <f>IF(B104="BUY",(F104-E104)/Settings!$B$3,IF(B104="SELL",(E104-F104)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H104">
@@ -17997,11 +18102,11 @@
         <v/>
       </c>
       <c r="F105">
-        <f>$B$4</f>
+        <f>IF(B105="BUY",$B$5,IF(B105="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G105">
-        <f>IF(B105="BUY",(F105-E105)/Settings!$B$3,(E105-F105)/Settings!$B$3)</f>
+        <f>IF(B105="BUY",(F105-E105)/Settings!$B$3,IF(B105="SELL",(E105-F105)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H105">
@@ -18047,11 +18152,11 @@
         <v/>
       </c>
       <c r="F106">
-        <f>$B$4</f>
+        <f>IF(B106="BUY",$B$5,IF(B106="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G106">
-        <f>IF(B106="BUY",(F106-E106)/Settings!$B$3,(E106-F106)/Settings!$B$3)</f>
+        <f>IF(B106="BUY",(F106-E106)/Settings!$B$3,IF(B106="SELL",(E106-F106)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H106">
@@ -18097,11 +18202,11 @@
         <v/>
       </c>
       <c r="F107">
-        <f>$B$4</f>
+        <f>IF(B107="BUY",$B$5,IF(B107="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G107">
-        <f>IF(B107="BUY",(F107-E107)/Settings!$B$3,(E107-F107)/Settings!$B$3)</f>
+        <f>IF(B107="BUY",(F107-E107)/Settings!$B$3,IF(B107="SELL",(E107-F107)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H107">
@@ -18147,11 +18252,11 @@
         <v/>
       </c>
       <c r="F108">
-        <f>$B$4</f>
+        <f>IF(B108="BUY",$B$5,IF(B108="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G108">
-        <f>IF(B108="BUY",(F108-E108)/Settings!$B$3,(E108-F108)/Settings!$B$3)</f>
+        <f>IF(B108="BUY",(F108-E108)/Settings!$B$3,IF(B108="SELL",(E108-F108)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H108">
@@ -18197,11 +18302,11 @@
         <v/>
       </c>
       <c r="F109">
-        <f>$B$4</f>
+        <f>IF(B109="BUY",$B$5,IF(B109="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G109">
-        <f>IF(B109="BUY",(F109-E109)/Settings!$B$3,(E109-F109)/Settings!$B$3)</f>
+        <f>IF(B109="BUY",(F109-E109)/Settings!$B$3,IF(B109="SELL",(E109-F109)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H109">
@@ -18247,11 +18352,11 @@
         <v/>
       </c>
       <c r="F110">
-        <f>$B$4</f>
+        <f>IF(B110="BUY",$B$5,IF(B110="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G110">
-        <f>IF(B110="BUY",(F110-E110)/Settings!$B$3,(E110-F110)/Settings!$B$3)</f>
+        <f>IF(B110="BUY",(F110-E110)/Settings!$B$3,IF(B110="SELL",(E110-F110)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H110">
@@ -18297,11 +18402,11 @@
         <v/>
       </c>
       <c r="F111">
-        <f>$B$4</f>
+        <f>IF(B111="BUY",$B$5,IF(B111="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G111">
-        <f>IF(B111="BUY",(F111-E111)/Settings!$B$3,(E111-F111)/Settings!$B$3)</f>
+        <f>IF(B111="BUY",(F111-E111)/Settings!$B$3,IF(B111="SELL",(E111-F111)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H111">
@@ -18347,11 +18452,11 @@
         <v/>
       </c>
       <c r="F112">
-        <f>$B$4</f>
+        <f>IF(B112="BUY",$B$5,IF(B112="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G112">
-        <f>IF(B112="BUY",(F112-E112)/Settings!$B$3,(E112-F112)/Settings!$B$3)</f>
+        <f>IF(B112="BUY",(F112-E112)/Settings!$B$3,IF(B112="SELL",(E112-F112)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H112">
@@ -18397,11 +18502,11 @@
         <v/>
       </c>
       <c r="F113">
-        <f>$B$4</f>
+        <f>IF(B113="BUY",$B$5,IF(B113="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G113">
-        <f>IF(B113="BUY",(F113-E113)/Settings!$B$3,(E113-F113)/Settings!$B$3)</f>
+        <f>IF(B113="BUY",(F113-E113)/Settings!$B$3,IF(B113="SELL",(E113-F113)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H113">
@@ -18447,11 +18552,11 @@
         <v/>
       </c>
       <c r="F114">
-        <f>$B$4</f>
+        <f>IF(B114="BUY",$B$5,IF(B114="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G114">
-        <f>IF(B114="BUY",(F114-E114)/Settings!$B$3,(E114-F114)/Settings!$B$3)</f>
+        <f>IF(B114="BUY",(F114-E114)/Settings!$B$3,IF(B114="SELL",(E114-F114)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H114">
@@ -18497,11 +18602,11 @@
         <v/>
       </c>
       <c r="F115">
-        <f>$B$4</f>
+        <f>IF(B115="BUY",$B$5,IF(B115="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G115">
-        <f>IF(B115="BUY",(F115-E115)/Settings!$B$3,(E115-F115)/Settings!$B$3)</f>
+        <f>IF(B115="BUY",(F115-E115)/Settings!$B$3,IF(B115="SELL",(E115-F115)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H115">
@@ -18547,11 +18652,11 @@
         <v/>
       </c>
       <c r="F116">
-        <f>$B$4</f>
+        <f>IF(B116="BUY",$B$5,IF(B116="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G116">
-        <f>IF(B116="BUY",(F116-E116)/Settings!$B$3,(E116-F116)/Settings!$B$3)</f>
+        <f>IF(B116="BUY",(F116-E116)/Settings!$B$3,IF(B116="SELL",(E116-F116)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H116">
@@ -18597,11 +18702,11 @@
         <v/>
       </c>
       <c r="F117">
-        <f>$B$4</f>
+        <f>IF(B117="BUY",$B$5,IF(B117="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G117">
-        <f>IF(B117="BUY",(F117-E117)/Settings!$B$3,(E117-F117)/Settings!$B$3)</f>
+        <f>IF(B117="BUY",(F117-E117)/Settings!$B$3,IF(B117="SELL",(E117-F117)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H117">
@@ -18647,11 +18752,11 @@
         <v/>
       </c>
       <c r="F118">
-        <f>$B$4</f>
+        <f>IF(B118="BUY",$B$5,IF(B118="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G118">
-        <f>IF(B118="BUY",(F118-E118)/Settings!$B$3,(E118-F118)/Settings!$B$3)</f>
+        <f>IF(B118="BUY",(F118-E118)/Settings!$B$3,IF(B118="SELL",(E118-F118)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H118">
@@ -18697,11 +18802,11 @@
         <v/>
       </c>
       <c r="F119">
-        <f>$B$4</f>
+        <f>IF(B119="BUY",$B$5,IF(B119="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G119">
-        <f>IF(B119="BUY",(F119-E119)/Settings!$B$3,(E119-F119)/Settings!$B$3)</f>
+        <f>IF(B119="BUY",(F119-E119)/Settings!$B$3,IF(B119="SELL",(E119-F119)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H119">
@@ -18747,11 +18852,11 @@
         <v/>
       </c>
       <c r="F120">
-        <f>$B$4</f>
+        <f>IF(B120="BUY",$B$5,IF(B120="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G120">
-        <f>IF(B120="BUY",(F120-E120)/Settings!$B$3,(E120-F120)/Settings!$B$3)</f>
+        <f>IF(B120="BUY",(F120-E120)/Settings!$B$3,IF(B120="SELL",(E120-F120)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H120">
@@ -18797,11 +18902,11 @@
         <v/>
       </c>
       <c r="F121">
-        <f>$B$4</f>
+        <f>IF(B121="BUY",$B$5,IF(B121="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G121">
-        <f>IF(B121="BUY",(F121-E121)/Settings!$B$3,(E121-F121)/Settings!$B$3)</f>
+        <f>IF(B121="BUY",(F121-E121)/Settings!$B$3,IF(B121="SELL",(E121-F121)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H121">
@@ -18847,11 +18952,11 @@
         <v/>
       </c>
       <c r="F122">
-        <f>$B$4</f>
+        <f>IF(B122="BUY",$B$5,IF(B122="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G122">
-        <f>IF(B122="BUY",(F122-E122)/Settings!$B$3,(E122-F122)/Settings!$B$3)</f>
+        <f>IF(B122="BUY",(F122-E122)/Settings!$B$3,IF(B122="SELL",(E122-F122)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H122">
@@ -18897,11 +19002,11 @@
         <v/>
       </c>
       <c r="F123">
-        <f>$B$4</f>
+        <f>IF(B123="BUY",$B$5,IF(B123="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G123">
-        <f>IF(B123="BUY",(F123-E123)/Settings!$B$3,(E123-F123)/Settings!$B$3)</f>
+        <f>IF(B123="BUY",(F123-E123)/Settings!$B$3,IF(B123="SELL",(E123-F123)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H123">
@@ -18947,11 +19052,11 @@
         <v/>
       </c>
       <c r="F124">
-        <f>$B$4</f>
+        <f>IF(B124="BUY",$B$5,IF(B124="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G124">
-        <f>IF(B124="BUY",(F124-E124)/Settings!$B$3,(E124-F124)/Settings!$B$3)</f>
+        <f>IF(B124="BUY",(F124-E124)/Settings!$B$3,IF(B124="SELL",(E124-F124)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H124">
@@ -18997,11 +19102,11 @@
         <v/>
       </c>
       <c r="F125">
-        <f>$B$4</f>
+        <f>IF(B125="BUY",$B$5,IF(B125="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G125">
-        <f>IF(B125="BUY",(F125-E125)/Settings!$B$3,(E125-F125)/Settings!$B$3)</f>
+        <f>IF(B125="BUY",(F125-E125)/Settings!$B$3,IF(B125="SELL",(E125-F125)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H125">
@@ -19047,11 +19152,11 @@
         <v/>
       </c>
       <c r="F126">
-        <f>$B$4</f>
+        <f>IF(B126="BUY",$B$5,IF(B126="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G126">
-        <f>IF(B126="BUY",(F126-E126)/Settings!$B$3,(E126-F126)/Settings!$B$3)</f>
+        <f>IF(B126="BUY",(F126-E126)/Settings!$B$3,IF(B126="SELL",(E126-F126)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H126">
@@ -19097,11 +19202,11 @@
         <v/>
       </c>
       <c r="F127">
-        <f>$B$4</f>
+        <f>IF(B127="BUY",$B$5,IF(B127="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G127">
-        <f>IF(B127="BUY",(F127-E127)/Settings!$B$3,(E127-F127)/Settings!$B$3)</f>
+        <f>IF(B127="BUY",(F127-E127)/Settings!$B$3,IF(B127="SELL",(E127-F127)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H127">
@@ -19147,11 +19252,11 @@
         <v/>
       </c>
       <c r="F128">
-        <f>$B$4</f>
+        <f>IF(B128="BUY",$B$5,IF(B128="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G128">
-        <f>IF(B128="BUY",(F128-E128)/Settings!$B$3,(E128-F128)/Settings!$B$3)</f>
+        <f>IF(B128="BUY",(F128-E128)/Settings!$B$3,IF(B128="SELL",(E128-F128)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H128">
@@ -19197,11 +19302,11 @@
         <v/>
       </c>
       <c r="F129">
-        <f>$B$4</f>
+        <f>IF(B129="BUY",$B$5,IF(B129="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G129">
-        <f>IF(B129="BUY",(F129-E129)/Settings!$B$3,(E129-F129)/Settings!$B$3)</f>
+        <f>IF(B129="BUY",(F129-E129)/Settings!$B$3,IF(B129="SELL",(E129-F129)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H129">
@@ -19247,11 +19352,11 @@
         <v/>
       </c>
       <c r="F130">
-        <f>$B$4</f>
+        <f>IF(B130="BUY",$B$5,IF(B130="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G130">
-        <f>IF(B130="BUY",(F130-E130)/Settings!$B$3,(E130-F130)/Settings!$B$3)</f>
+        <f>IF(B130="BUY",(F130-E130)/Settings!$B$3,IF(B130="SELL",(E130-F130)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H130">
@@ -19297,11 +19402,11 @@
         <v/>
       </c>
       <c r="F131">
-        <f>$B$4</f>
+        <f>IF(B131="BUY",$B$5,IF(B131="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G131">
-        <f>IF(B131="BUY",(F131-E131)/Settings!$B$3,(E131-F131)/Settings!$B$3)</f>
+        <f>IF(B131="BUY",(F131-E131)/Settings!$B$3,IF(B131="SELL",(E131-F131)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H131">
@@ -19347,11 +19452,11 @@
         <v/>
       </c>
       <c r="F132">
-        <f>$B$4</f>
+        <f>IF(B132="BUY",$B$5,IF(B132="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G132">
-        <f>IF(B132="BUY",(F132-E132)/Settings!$B$3,(E132-F132)/Settings!$B$3)</f>
+        <f>IF(B132="BUY",(F132-E132)/Settings!$B$3,IF(B132="SELL",(E132-F132)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H132">
@@ -19397,11 +19502,11 @@
         <v/>
       </c>
       <c r="F133">
-        <f>$B$4</f>
+        <f>IF(B133="BUY",$B$5,IF(B133="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G133">
-        <f>IF(B133="BUY",(F133-E133)/Settings!$B$3,(E133-F133)/Settings!$B$3)</f>
+        <f>IF(B133="BUY",(F133-E133)/Settings!$B$3,IF(B133="SELL",(E133-F133)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H133">
@@ -19447,11 +19552,11 @@
         <v/>
       </c>
       <c r="F134">
-        <f>$B$4</f>
+        <f>IF(B134="BUY",$B$5,IF(B134="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G134">
-        <f>IF(B134="BUY",(F134-E134)/Settings!$B$3,(E134-F134)/Settings!$B$3)</f>
+        <f>IF(B134="BUY",(F134-E134)/Settings!$B$3,IF(B134="SELL",(E134-F134)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H134">
@@ -19497,11 +19602,11 @@
         <v/>
       </c>
       <c r="F135">
-        <f>$B$4</f>
+        <f>IF(B135="BUY",$B$5,IF(B135="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G135">
-        <f>IF(B135="BUY",(F135-E135)/Settings!$B$3,(E135-F135)/Settings!$B$3)</f>
+        <f>IF(B135="BUY",(F135-E135)/Settings!$B$3,IF(B135="SELL",(E135-F135)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H135">
@@ -19547,11 +19652,11 @@
         <v/>
       </c>
       <c r="F136">
-        <f>$B$4</f>
+        <f>IF(B136="BUY",$B$5,IF(B136="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G136">
-        <f>IF(B136="BUY",(F136-E136)/Settings!$B$3,(E136-F136)/Settings!$B$3)</f>
+        <f>IF(B136="BUY",(F136-E136)/Settings!$B$3,IF(B136="SELL",(E136-F136)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H136">
@@ -19597,11 +19702,11 @@
         <v/>
       </c>
       <c r="F137">
-        <f>$B$4</f>
+        <f>IF(B137="BUY",$B$5,IF(B137="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G137">
-        <f>IF(B137="BUY",(F137-E137)/Settings!$B$3,(E137-F137)/Settings!$B$3)</f>
+        <f>IF(B137="BUY",(F137-E137)/Settings!$B$3,IF(B137="SELL",(E137-F137)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H137">
@@ -19647,11 +19752,11 @@
         <v/>
       </c>
       <c r="F138">
-        <f>$B$4</f>
+        <f>IF(B138="BUY",$B$5,IF(B138="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G138">
-        <f>IF(B138="BUY",(F138-E138)/Settings!$B$3,(E138-F138)/Settings!$B$3)</f>
+        <f>IF(B138="BUY",(F138-E138)/Settings!$B$3,IF(B138="SELL",(E138-F138)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H138">
@@ -19697,11 +19802,11 @@
         <v/>
       </c>
       <c r="F139">
-        <f>$B$4</f>
+        <f>IF(B139="BUY",$B$5,IF(B139="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G139">
-        <f>IF(B139="BUY",(F139-E139)/Settings!$B$3,(E139-F139)/Settings!$B$3)</f>
+        <f>IF(B139="BUY",(F139-E139)/Settings!$B$3,IF(B139="SELL",(E139-F139)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H139">
@@ -19747,11 +19852,11 @@
         <v/>
       </c>
       <c r="F140">
-        <f>$B$4</f>
+        <f>IF(B140="BUY",$B$5,IF(B140="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G140">
-        <f>IF(B140="BUY",(F140-E140)/Settings!$B$3,(E140-F140)/Settings!$B$3)</f>
+        <f>IF(B140="BUY",(F140-E140)/Settings!$B$3,IF(B140="SELL",(E140-F140)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H140">
@@ -19797,11 +19902,11 @@
         <v/>
       </c>
       <c r="F141">
-        <f>$B$4</f>
+        <f>IF(B141="BUY",$B$5,IF(B141="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G141">
-        <f>IF(B141="BUY",(F141-E141)/Settings!$B$3,(E141-F141)/Settings!$B$3)</f>
+        <f>IF(B141="BUY",(F141-E141)/Settings!$B$3,IF(B141="SELL",(E141-F141)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H141">
@@ -19847,11 +19952,11 @@
         <v/>
       </c>
       <c r="F142">
-        <f>$B$4</f>
+        <f>IF(B142="BUY",$B$5,IF(B142="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G142">
-        <f>IF(B142="BUY",(F142-E142)/Settings!$B$3,(E142-F142)/Settings!$B$3)</f>
+        <f>IF(B142="BUY",(F142-E142)/Settings!$B$3,IF(B142="SELL",(E142-F142)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H142">
@@ -19897,11 +20002,11 @@
         <v/>
       </c>
       <c r="F143">
-        <f>$B$4</f>
+        <f>IF(B143="BUY",$B$5,IF(B143="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G143">
-        <f>IF(B143="BUY",(F143-E143)/Settings!$B$3,(E143-F143)/Settings!$B$3)</f>
+        <f>IF(B143="BUY",(F143-E143)/Settings!$B$3,IF(B143="SELL",(E143-F143)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H143">
@@ -19947,11 +20052,11 @@
         <v/>
       </c>
       <c r="F144">
-        <f>$B$4</f>
+        <f>IF(B144="BUY",$B$5,IF(B144="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G144">
-        <f>IF(B144="BUY",(F144-E144)/Settings!$B$3,(E144-F144)/Settings!$B$3)</f>
+        <f>IF(B144="BUY",(F144-E144)/Settings!$B$3,IF(B144="SELL",(E144-F144)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H144">
@@ -19997,11 +20102,11 @@
         <v/>
       </c>
       <c r="F145">
-        <f>$B$4</f>
+        <f>IF(B145="BUY",$B$5,IF(B145="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G145">
-        <f>IF(B145="BUY",(F145-E145)/Settings!$B$3,(E145-F145)/Settings!$B$3)</f>
+        <f>IF(B145="BUY",(F145-E145)/Settings!$B$3,IF(B145="SELL",(E145-F145)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H145">
@@ -20047,11 +20152,11 @@
         <v/>
       </c>
       <c r="F146">
-        <f>$B$4</f>
+        <f>IF(B146="BUY",$B$5,IF(B146="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G146">
-        <f>IF(B146="BUY",(F146-E146)/Settings!$B$3,(E146-F146)/Settings!$B$3)</f>
+        <f>IF(B146="BUY",(F146-E146)/Settings!$B$3,IF(B146="SELL",(E146-F146)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H146">
@@ -20097,11 +20202,11 @@
         <v/>
       </c>
       <c r="F147">
-        <f>$B$4</f>
+        <f>IF(B147="BUY",$B$5,IF(B147="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G147">
-        <f>IF(B147="BUY",(F147-E147)/Settings!$B$3,(E147-F147)/Settings!$B$3)</f>
+        <f>IF(B147="BUY",(F147-E147)/Settings!$B$3,IF(B147="SELL",(E147-F147)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H147">
@@ -20147,11 +20252,11 @@
         <v/>
       </c>
       <c r="F148">
-        <f>$B$4</f>
+        <f>IF(B148="BUY",$B$5,IF(B148="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G148">
-        <f>IF(B148="BUY",(F148-E148)/Settings!$B$3,(E148-F148)/Settings!$B$3)</f>
+        <f>IF(B148="BUY",(F148-E148)/Settings!$B$3,IF(B148="SELL",(E148-F148)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H148">
@@ -20197,11 +20302,11 @@
         <v/>
       </c>
       <c r="F149">
-        <f>$B$4</f>
+        <f>IF(B149="BUY",$B$5,IF(B149="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G149">
-        <f>IF(B149="BUY",(F149-E149)/Settings!$B$3,(E149-F149)/Settings!$B$3)</f>
+        <f>IF(B149="BUY",(F149-E149)/Settings!$B$3,IF(B149="SELL",(E149-F149)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H149">
@@ -20247,11 +20352,11 @@
         <v/>
       </c>
       <c r="F150">
-        <f>$B$4</f>
+        <f>IF(B150="BUY",$B$5,IF(B150="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G150">
-        <f>IF(B150="BUY",(F150-E150)/Settings!$B$3,(E150-F150)/Settings!$B$3)</f>
+        <f>IF(B150="BUY",(F150-E150)/Settings!$B$3,IF(B150="SELL",(E150-F150)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H150">
@@ -20297,11 +20402,11 @@
         <v/>
       </c>
       <c r="F151">
-        <f>$B$4</f>
+        <f>IF(B151="BUY",$B$5,IF(B151="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G151">
-        <f>IF(B151="BUY",(F151-E151)/Settings!$B$3,(E151-F151)/Settings!$B$3)</f>
+        <f>IF(B151="BUY",(F151-E151)/Settings!$B$3,IF(B151="SELL",(E151-F151)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H151">
@@ -20347,11 +20452,11 @@
         <v/>
       </c>
       <c r="F152">
-        <f>$B$4</f>
+        <f>IF(B152="BUY",$B$5,IF(B152="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G152">
-        <f>IF(B152="BUY",(F152-E152)/Settings!$B$3,(E152-F152)/Settings!$B$3)</f>
+        <f>IF(B152="BUY",(F152-E152)/Settings!$B$3,IF(B152="SELL",(E152-F152)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H152">
@@ -20397,11 +20502,11 @@
         <v/>
       </c>
       <c r="F153">
-        <f>$B$4</f>
+        <f>IF(B153="BUY",$B$5,IF(B153="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G153">
-        <f>IF(B153="BUY",(F153-E153)/Settings!$B$3,(E153-F153)/Settings!$B$3)</f>
+        <f>IF(B153="BUY",(F153-E153)/Settings!$B$3,IF(B153="SELL",(E153-F153)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H153">
@@ -20447,11 +20552,11 @@
         <v/>
       </c>
       <c r="F154">
-        <f>$B$4</f>
+        <f>IF(B154="BUY",$B$5,IF(B154="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G154">
-        <f>IF(B154="BUY",(F154-E154)/Settings!$B$3,(E154-F154)/Settings!$B$3)</f>
+        <f>IF(B154="BUY",(F154-E154)/Settings!$B$3,IF(B154="SELL",(E154-F154)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H154">
@@ -20497,11 +20602,11 @@
         <v/>
       </c>
       <c r="F155">
-        <f>$B$4</f>
+        <f>IF(B155="BUY",$B$5,IF(B155="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G155">
-        <f>IF(B155="BUY",(F155-E155)/Settings!$B$3,(E155-F155)/Settings!$B$3)</f>
+        <f>IF(B155="BUY",(F155-E155)/Settings!$B$3,IF(B155="SELL",(E155-F155)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H155">
@@ -20547,11 +20652,11 @@
         <v/>
       </c>
       <c r="F156">
-        <f>$B$4</f>
+        <f>IF(B156="BUY",$B$5,IF(B156="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G156">
-        <f>IF(B156="BUY",(F156-E156)/Settings!$B$3,(E156-F156)/Settings!$B$3)</f>
+        <f>IF(B156="BUY",(F156-E156)/Settings!$B$3,IF(B156="SELL",(E156-F156)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H156">
@@ -20597,11 +20702,11 @@
         <v/>
       </c>
       <c r="F157">
-        <f>$B$4</f>
+        <f>IF(B157="BUY",$B$5,IF(B157="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G157">
-        <f>IF(B157="BUY",(F157-E157)/Settings!$B$3,(E157-F157)/Settings!$B$3)</f>
+        <f>IF(B157="BUY",(F157-E157)/Settings!$B$3,IF(B157="SELL",(E157-F157)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H157">
@@ -20647,11 +20752,11 @@
         <v/>
       </c>
       <c r="F158">
-        <f>$B$4</f>
+        <f>IF(B158="BUY",$B$5,IF(B158="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G158">
-        <f>IF(B158="BUY",(F158-E158)/Settings!$B$3,(E158-F158)/Settings!$B$3)</f>
+        <f>IF(B158="BUY",(F158-E158)/Settings!$B$3,IF(B158="SELL",(E158-F158)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H158">
@@ -20697,11 +20802,11 @@
         <v/>
       </c>
       <c r="F159">
-        <f>$B$4</f>
+        <f>IF(B159="BUY",$B$5,IF(B159="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G159">
-        <f>IF(B159="BUY",(F159-E159)/Settings!$B$3,(E159-F159)/Settings!$B$3)</f>
+        <f>IF(B159="BUY",(F159-E159)/Settings!$B$3,IF(B159="SELL",(E159-F159)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H159">
@@ -20747,11 +20852,11 @@
         <v/>
       </c>
       <c r="F160">
-        <f>$B$4</f>
+        <f>IF(B160="BUY",$B$5,IF(B160="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G160">
-        <f>IF(B160="BUY",(F160-E160)/Settings!$B$3,(E160-F160)/Settings!$B$3)</f>
+        <f>IF(B160="BUY",(F160-E160)/Settings!$B$3,IF(B160="SELL",(E160-F160)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H160">
@@ -20797,11 +20902,11 @@
         <v/>
       </c>
       <c r="F161">
-        <f>$B$4</f>
+        <f>IF(B161="BUY",$B$5,IF(B161="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G161">
-        <f>IF(B161="BUY",(F161-E161)/Settings!$B$3,(E161-F161)/Settings!$B$3)</f>
+        <f>IF(B161="BUY",(F161-E161)/Settings!$B$3,IF(B161="SELL",(E161-F161)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H161">
@@ -20847,11 +20952,11 @@
         <v/>
       </c>
       <c r="F162">
-        <f>$B$4</f>
+        <f>IF(B162="BUY",$B$5,IF(B162="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G162">
-        <f>IF(B162="BUY",(F162-E162)/Settings!$B$3,(E162-F162)/Settings!$B$3)</f>
+        <f>IF(B162="BUY",(F162-E162)/Settings!$B$3,IF(B162="SELL",(E162-F162)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H162">
@@ -20897,11 +21002,11 @@
         <v/>
       </c>
       <c r="F163">
-        <f>$B$4</f>
+        <f>IF(B163="BUY",$B$5,IF(B163="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G163">
-        <f>IF(B163="BUY",(F163-E163)/Settings!$B$3,(E163-F163)/Settings!$B$3)</f>
+        <f>IF(B163="BUY",(F163-E163)/Settings!$B$3,IF(B163="SELL",(E163-F163)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H163">
@@ -20947,11 +21052,11 @@
         <v/>
       </c>
       <c r="F164">
-        <f>$B$4</f>
+        <f>IF(B164="BUY",$B$5,IF(B164="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G164">
-        <f>IF(B164="BUY",(F164-E164)/Settings!$B$3,(E164-F164)/Settings!$B$3)</f>
+        <f>IF(B164="BUY",(F164-E164)/Settings!$B$3,IF(B164="SELL",(E164-F164)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H164">
@@ -20997,11 +21102,11 @@
         <v/>
       </c>
       <c r="F165">
-        <f>$B$4</f>
+        <f>IF(B165="BUY",$B$5,IF(B165="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G165">
-        <f>IF(B165="BUY",(F165-E165)/Settings!$B$3,(E165-F165)/Settings!$B$3)</f>
+        <f>IF(B165="BUY",(F165-E165)/Settings!$B$3,IF(B165="SELL",(E165-F165)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H165">
@@ -21047,11 +21152,11 @@
         <v/>
       </c>
       <c r="F166">
-        <f>$B$4</f>
+        <f>IF(B166="BUY",$B$5,IF(B166="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G166">
-        <f>IF(B166="BUY",(F166-E166)/Settings!$B$3,(E166-F166)/Settings!$B$3)</f>
+        <f>IF(B166="BUY",(F166-E166)/Settings!$B$3,IF(B166="SELL",(E166-F166)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H166">
@@ -21097,11 +21202,11 @@
         <v/>
       </c>
       <c r="F167">
-        <f>$B$4</f>
+        <f>IF(B167="BUY",$B$5,IF(B167="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G167">
-        <f>IF(B167="BUY",(F167-E167)/Settings!$B$3,(E167-F167)/Settings!$B$3)</f>
+        <f>IF(B167="BUY",(F167-E167)/Settings!$B$3,IF(B167="SELL",(E167-F167)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H167">
@@ -21147,11 +21252,11 @@
         <v/>
       </c>
       <c r="F168">
-        <f>$B$4</f>
+        <f>IF(B168="BUY",$B$5,IF(B168="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G168">
-        <f>IF(B168="BUY",(F168-E168)/Settings!$B$3,(E168-F168)/Settings!$B$3)</f>
+        <f>IF(B168="BUY",(F168-E168)/Settings!$B$3,IF(B168="SELL",(E168-F168)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H168">
@@ -21197,11 +21302,11 @@
         <v/>
       </c>
       <c r="F169">
-        <f>$B$4</f>
+        <f>IF(B169="BUY",$B$5,IF(B169="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G169">
-        <f>IF(B169="BUY",(F169-E169)/Settings!$B$3,(E169-F169)/Settings!$B$3)</f>
+        <f>IF(B169="BUY",(F169-E169)/Settings!$B$3,IF(B169="SELL",(E169-F169)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H169">
@@ -21247,11 +21352,11 @@
         <v/>
       </c>
       <c r="F170">
-        <f>$B$4</f>
+        <f>IF(B170="BUY",$B$5,IF(B170="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G170">
-        <f>IF(B170="BUY",(F170-E170)/Settings!$B$3,(E170-F170)/Settings!$B$3)</f>
+        <f>IF(B170="BUY",(F170-E170)/Settings!$B$3,IF(B170="SELL",(E170-F170)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H170">
@@ -21297,11 +21402,11 @@
         <v/>
       </c>
       <c r="F171">
-        <f>$B$4</f>
+        <f>IF(B171="BUY",$B$5,IF(B171="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G171">
-        <f>IF(B171="BUY",(F171-E171)/Settings!$B$3,(E171-F171)/Settings!$B$3)</f>
+        <f>IF(B171="BUY",(F171-E171)/Settings!$B$3,IF(B171="SELL",(E171-F171)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H171">
@@ -21347,11 +21452,11 @@
         <v/>
       </c>
       <c r="F172">
-        <f>$B$4</f>
+        <f>IF(B172="BUY",$B$5,IF(B172="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G172">
-        <f>IF(B172="BUY",(F172-E172)/Settings!$B$3,(E172-F172)/Settings!$B$3)</f>
+        <f>IF(B172="BUY",(F172-E172)/Settings!$B$3,IF(B172="SELL",(E172-F172)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H172">
@@ -21397,11 +21502,11 @@
         <v/>
       </c>
       <c r="F173">
-        <f>$B$4</f>
+        <f>IF(B173="BUY",$B$5,IF(B173="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G173">
-        <f>IF(B173="BUY",(F173-E173)/Settings!$B$3,(E173-F173)/Settings!$B$3)</f>
+        <f>IF(B173="BUY",(F173-E173)/Settings!$B$3,IF(B173="SELL",(E173-F173)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H173">
@@ -21447,11 +21552,11 @@
         <v/>
       </c>
       <c r="F174">
-        <f>$B$4</f>
+        <f>IF(B174="BUY",$B$5,IF(B174="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G174">
-        <f>IF(B174="BUY",(F174-E174)/Settings!$B$3,(E174-F174)/Settings!$B$3)</f>
+        <f>IF(B174="BUY",(F174-E174)/Settings!$B$3,IF(B174="SELL",(E174-F174)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H174">
@@ -21497,11 +21602,11 @@
         <v/>
       </c>
       <c r="F175">
-        <f>$B$4</f>
+        <f>IF(B175="BUY",$B$5,IF(B175="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G175">
-        <f>IF(B175="BUY",(F175-E175)/Settings!$B$3,(E175-F175)/Settings!$B$3)</f>
+        <f>IF(B175="BUY",(F175-E175)/Settings!$B$3,IF(B175="SELL",(E175-F175)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H175">
@@ -21547,11 +21652,11 @@
         <v/>
       </c>
       <c r="F176">
-        <f>$B$4</f>
+        <f>IF(B176="BUY",$B$5,IF(B176="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G176">
-        <f>IF(B176="BUY",(F176-E176)/Settings!$B$3,(E176-F176)/Settings!$B$3)</f>
+        <f>IF(B176="BUY",(F176-E176)/Settings!$B$3,IF(B176="SELL",(E176-F176)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H176">
@@ -21597,11 +21702,11 @@
         <v/>
       </c>
       <c r="F177">
-        <f>$B$4</f>
+        <f>IF(B177="BUY",$B$5,IF(B177="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G177">
-        <f>IF(B177="BUY",(F177-E177)/Settings!$B$3,(E177-F177)/Settings!$B$3)</f>
+        <f>IF(B177="BUY",(F177-E177)/Settings!$B$3,IF(B177="SELL",(E177-F177)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H177">
@@ -21647,11 +21752,11 @@
         <v/>
       </c>
       <c r="F178">
-        <f>$B$4</f>
+        <f>IF(B178="BUY",$B$5,IF(B178="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G178">
-        <f>IF(B178="BUY",(F178-E178)/Settings!$B$3,(E178-F178)/Settings!$B$3)</f>
+        <f>IF(B178="BUY",(F178-E178)/Settings!$B$3,IF(B178="SELL",(E178-F178)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H178">
@@ -21697,11 +21802,11 @@
         <v/>
       </c>
       <c r="F179">
-        <f>$B$4</f>
+        <f>IF(B179="BUY",$B$5,IF(B179="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G179">
-        <f>IF(B179="BUY",(F179-E179)/Settings!$B$3,(E179-F179)/Settings!$B$3)</f>
+        <f>IF(B179="BUY",(F179-E179)/Settings!$B$3,IF(B179="SELL",(E179-F179)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H179">
@@ -21747,11 +21852,11 @@
         <v/>
       </c>
       <c r="F180">
-        <f>$B$4</f>
+        <f>IF(B180="BUY",$B$5,IF(B180="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G180">
-        <f>IF(B180="BUY",(F180-E180)/Settings!$B$3,(E180-F180)/Settings!$B$3)</f>
+        <f>IF(B180="BUY",(F180-E180)/Settings!$B$3,IF(B180="SELL",(E180-F180)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H180">
@@ -21797,11 +21902,11 @@
         <v/>
       </c>
       <c r="F181">
-        <f>$B$4</f>
+        <f>IF(B181="BUY",$B$5,IF(B181="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G181">
-        <f>IF(B181="BUY",(F181-E181)/Settings!$B$3,(E181-F181)/Settings!$B$3)</f>
+        <f>IF(B181="BUY",(F181-E181)/Settings!$B$3,IF(B181="SELL",(E181-F181)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H181">
@@ -21847,11 +21952,11 @@
         <v/>
       </c>
       <c r="F182">
-        <f>$B$4</f>
+        <f>IF(B182="BUY",$B$5,IF(B182="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G182">
-        <f>IF(B182="BUY",(F182-E182)/Settings!$B$3,(E182-F182)/Settings!$B$3)</f>
+        <f>IF(B182="BUY",(F182-E182)/Settings!$B$3,IF(B182="SELL",(E182-F182)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H182">
@@ -21897,11 +22002,11 @@
         <v/>
       </c>
       <c r="F183">
-        <f>$B$4</f>
+        <f>IF(B183="BUY",$B$5,IF(B183="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G183">
-        <f>IF(B183="BUY",(F183-E183)/Settings!$B$3,(E183-F183)/Settings!$B$3)</f>
+        <f>IF(B183="BUY",(F183-E183)/Settings!$B$3,IF(B183="SELL",(E183-F183)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H183">
@@ -21947,11 +22052,11 @@
         <v/>
       </c>
       <c r="F184">
-        <f>$B$4</f>
+        <f>IF(B184="BUY",$B$5,IF(B184="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G184">
-        <f>IF(B184="BUY",(F184-E184)/Settings!$B$3,(E184-F184)/Settings!$B$3)</f>
+        <f>IF(B184="BUY",(F184-E184)/Settings!$B$3,IF(B184="SELL",(E184-F184)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H184">
@@ -21997,11 +22102,11 @@
         <v/>
       </c>
       <c r="F185">
-        <f>$B$4</f>
+        <f>IF(B185="BUY",$B$5,IF(B185="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G185">
-        <f>IF(B185="BUY",(F185-E185)/Settings!$B$3,(E185-F185)/Settings!$B$3)</f>
+        <f>IF(B185="BUY",(F185-E185)/Settings!$B$3,IF(B185="SELL",(E185-F185)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H185">
@@ -22047,11 +22152,11 @@
         <v/>
       </c>
       <c r="F186">
-        <f>$B$4</f>
+        <f>IF(B186="BUY",$B$5,IF(B186="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G186">
-        <f>IF(B186="BUY",(F186-E186)/Settings!$B$3,(E186-F186)/Settings!$B$3)</f>
+        <f>IF(B186="BUY",(F186-E186)/Settings!$B$3,IF(B186="SELL",(E186-F186)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H186">
@@ -22097,11 +22202,11 @@
         <v/>
       </c>
       <c r="F187">
-        <f>$B$4</f>
+        <f>IF(B187="BUY",$B$5,IF(B187="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G187">
-        <f>IF(B187="BUY",(F187-E187)/Settings!$B$3,(E187-F187)/Settings!$B$3)</f>
+        <f>IF(B187="BUY",(F187-E187)/Settings!$B$3,IF(B187="SELL",(E187-F187)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H187">
@@ -22147,11 +22252,11 @@
         <v/>
       </c>
       <c r="F188">
-        <f>$B$4</f>
+        <f>IF(B188="BUY",$B$5,IF(B188="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G188">
-        <f>IF(B188="BUY",(F188-E188)/Settings!$B$3,(E188-F188)/Settings!$B$3)</f>
+        <f>IF(B188="BUY",(F188-E188)/Settings!$B$3,IF(B188="SELL",(E188-F188)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H188">
@@ -22197,11 +22302,11 @@
         <v/>
       </c>
       <c r="F189">
-        <f>$B$4</f>
+        <f>IF(B189="BUY",$B$5,IF(B189="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G189">
-        <f>IF(B189="BUY",(F189-E189)/Settings!$B$3,(E189-F189)/Settings!$B$3)</f>
+        <f>IF(B189="BUY",(F189-E189)/Settings!$B$3,IF(B189="SELL",(E189-F189)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H189">
@@ -22247,11 +22352,11 @@
         <v/>
       </c>
       <c r="F190">
-        <f>$B$4</f>
+        <f>IF(B190="BUY",$B$5,IF(B190="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G190">
-        <f>IF(B190="BUY",(F190-E190)/Settings!$B$3,(E190-F190)/Settings!$B$3)</f>
+        <f>IF(B190="BUY",(F190-E190)/Settings!$B$3,IF(B190="SELL",(E190-F190)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H190">
@@ -22297,11 +22402,11 @@
         <v/>
       </c>
       <c r="F191">
-        <f>$B$4</f>
+        <f>IF(B191="BUY",$B$5,IF(B191="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G191">
-        <f>IF(B191="BUY",(F191-E191)/Settings!$B$3,(E191-F191)/Settings!$B$3)</f>
+        <f>IF(B191="BUY",(F191-E191)/Settings!$B$3,IF(B191="SELL",(E191-F191)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H191">
@@ -22347,11 +22452,11 @@
         <v/>
       </c>
       <c r="F192">
-        <f>$B$4</f>
+        <f>IF(B192="BUY",$B$5,IF(B192="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G192">
-        <f>IF(B192="BUY",(F192-E192)/Settings!$B$3,(E192-F192)/Settings!$B$3)</f>
+        <f>IF(B192="BUY",(F192-E192)/Settings!$B$3,IF(B192="SELL",(E192-F192)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H192">
@@ -22397,11 +22502,11 @@
         <v/>
       </c>
       <c r="F193">
-        <f>$B$4</f>
+        <f>IF(B193="BUY",$B$5,IF(B193="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G193">
-        <f>IF(B193="BUY",(F193-E193)/Settings!$B$3,(E193-F193)/Settings!$B$3)</f>
+        <f>IF(B193="BUY",(F193-E193)/Settings!$B$3,IF(B193="SELL",(E193-F193)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H193">
@@ -22447,11 +22552,11 @@
         <v/>
       </c>
       <c r="F194">
-        <f>$B$4</f>
+        <f>IF(B194="BUY",$B$5,IF(B194="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G194">
-        <f>IF(B194="BUY",(F194-E194)/Settings!$B$3,(E194-F194)/Settings!$B$3)</f>
+        <f>IF(B194="BUY",(F194-E194)/Settings!$B$3,IF(B194="SELL",(E194-F194)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H194">
@@ -22497,11 +22602,11 @@
         <v/>
       </c>
       <c r="F195">
-        <f>$B$4</f>
+        <f>IF(B195="BUY",$B$5,IF(B195="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G195">
-        <f>IF(B195="BUY",(F195-E195)/Settings!$B$3,(E195-F195)/Settings!$B$3)</f>
+        <f>IF(B195="BUY",(F195-E195)/Settings!$B$3,IF(B195="SELL",(E195-F195)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H195">
@@ -22547,11 +22652,11 @@
         <v/>
       </c>
       <c r="F196">
-        <f>$B$4</f>
+        <f>IF(B196="BUY",$B$5,IF(B196="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G196">
-        <f>IF(B196="BUY",(F196-E196)/Settings!$B$3,(E196-F196)/Settings!$B$3)</f>
+        <f>IF(B196="BUY",(F196-E196)/Settings!$B$3,IF(B196="SELL",(E196-F196)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H196">
@@ -22597,11 +22702,11 @@
         <v/>
       </c>
       <c r="F197">
-        <f>$B$4</f>
+        <f>IF(B197="BUY",$B$5,IF(B197="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G197">
-        <f>IF(B197="BUY",(F197-E197)/Settings!$B$3,(E197-F197)/Settings!$B$3)</f>
+        <f>IF(B197="BUY",(F197-E197)/Settings!$B$3,IF(B197="SELL",(E197-F197)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H197">
@@ -22647,11 +22752,11 @@
         <v/>
       </c>
       <c r="F198">
-        <f>$B$4</f>
+        <f>IF(B198="BUY",$B$5,IF(B198="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G198">
-        <f>IF(B198="BUY",(F198-E198)/Settings!$B$3,(E198-F198)/Settings!$B$3)</f>
+        <f>IF(B198="BUY",(F198-E198)/Settings!$B$3,IF(B198="SELL",(E198-F198)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H198">
@@ -22697,11 +22802,11 @@
         <v/>
       </c>
       <c r="F199">
-        <f>$B$4</f>
+        <f>IF(B199="BUY",$B$5,IF(B199="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G199">
-        <f>IF(B199="BUY",(F199-E199)/Settings!$B$3,(E199-F199)/Settings!$B$3)</f>
+        <f>IF(B199="BUY",(F199-E199)/Settings!$B$3,IF(B199="SELL",(E199-F199)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H199">
@@ -22747,11 +22852,11 @@
         <v/>
       </c>
       <c r="F200">
-        <f>$B$4</f>
+        <f>IF(B200="BUY",$B$5,IF(B200="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G200">
-        <f>IF(B200="BUY",(F200-E200)/Settings!$B$3,(E200-F200)/Settings!$B$3)</f>
+        <f>IF(B200="BUY",(F200-E200)/Settings!$B$3,IF(B200="SELL",(E200-F200)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H200">
@@ -22797,11 +22902,11 @@
         <v/>
       </c>
       <c r="F201">
-        <f>$B$4</f>
+        <f>IF(B201="BUY",$B$5,IF(B201="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G201">
-        <f>IF(B201="BUY",(F201-E201)/Settings!$B$3,(E201-F201)/Settings!$B$3)</f>
+        <f>IF(B201="BUY",(F201-E201)/Settings!$B$3,IF(B201="SELL",(E201-F201)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H201">
@@ -22847,11 +22952,11 @@
         <v/>
       </c>
       <c r="F202">
-        <f>$B$4</f>
+        <f>IF(B202="BUY",$B$5,IF(B202="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G202">
-        <f>IF(B202="BUY",(F202-E202)/Settings!$B$3,(E202-F202)/Settings!$B$3)</f>
+        <f>IF(B202="BUY",(F202-E202)/Settings!$B$3,IF(B202="SELL",(E202-F202)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H202">
@@ -22897,11 +23002,11 @@
         <v/>
       </c>
       <c r="F203">
-        <f>$B$4</f>
+        <f>IF(B203="BUY",$B$5,IF(B203="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G203">
-        <f>IF(B203="BUY",(F203-E203)/Settings!$B$3,(E203-F203)/Settings!$B$3)</f>
+        <f>IF(B203="BUY",(F203-E203)/Settings!$B$3,IF(B203="SELL",(E203-F203)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H203">
@@ -22947,11 +23052,11 @@
         <v/>
       </c>
       <c r="F204">
-        <f>$B$4</f>
+        <f>IF(B204="BUY",$B$5,IF(B204="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G204">
-        <f>IF(B204="BUY",(F204-E204)/Settings!$B$3,(E204-F204)/Settings!$B$3)</f>
+        <f>IF(B204="BUY",(F204-E204)/Settings!$B$3,IF(B204="SELL",(E204-F204)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H204">
@@ -22997,11 +23102,11 @@
         <v/>
       </c>
       <c r="F205">
-        <f>$B$4</f>
+        <f>IF(B205="BUY",$B$5,IF(B205="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G205">
-        <f>IF(B205="BUY",(F205-E205)/Settings!$B$3,(E205-F205)/Settings!$B$3)</f>
+        <f>IF(B205="BUY",(F205-E205)/Settings!$B$3,IF(B205="SELL",(E205-F205)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H205">
@@ -23047,11 +23152,11 @@
         <v/>
       </c>
       <c r="F206">
-        <f>$B$4</f>
+        <f>IF(B206="BUY",$B$5,IF(B206="SELL",$B$6,""))</f>
         <v/>
       </c>
       <c r="G206">
-        <f>IF(B206="BUY",(F206-E206)/Settings!$B$3,(E206-F206)/Settings!$B$3)</f>
+        <f>IF(B206="BUY",(F206-E206)/Settings!$B$3,IF(B206="SELL",(E206-F206)/Settings!$B$3,0))</f>
         <v/>
       </c>
       <c r="H206">
@@ -23284,7 +23389,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>IF(Scenario_UP!B4&gt;=IF(B4=1,Scenario_UP!N4,IF(B4=2,Scenario_UP!N5,IF(B4=3,Scenario_UP!N6,Scenario_UP!N7))),"YES","NO")</f>
+        <f>IF(Scenario_UP!B7&gt;=IF(B4=1,Scenario_UP!N4,IF(B4=2,Scenario_UP!N5,IF(B4=3,Scenario_UP!N6,Scenario_UP!N7))),"YES","NO")</f>
         <v/>
       </c>
     </row>
@@ -23921,7 +24026,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>IF(Scenario_DOWN!B4&lt;=IF(B4=1,Scenario_DOWN!N9,IF(B4=2,Scenario_DOWN!N10,IF(B4=3,Scenario_DOWN!N11,Scenario_DOWN!N12))),"YES","NO")</f>
+        <f>IF(Scenario_DOWN!B7&lt;=IF(B4=1,Scenario_DOWN!N9,IF(B4=2,Scenario_DOWN!N10,IF(B4=3,Scenario_DOWN!N11,Scenario_DOWN!N12))),"YES","NO")</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="B9">
-        <f>IF(OR(ISNUMBER(ScenarioText_UP!B5),ScenarioText_UP!B5="Уровень не рассчитан"),"OK","ERROR")</f>
+        <f>IF(OR(ISNUMBER(ScenarioText_UP!B9),ScenarioText_UP!B9="Уровень не рассчитан"),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C9">
-        <f>IF(OR(ISNUMBER(ScenarioText_DOWN!B5),ScenarioText_DOWN!B5="Уровень не рассчитан"),"OK","ERROR")</f>
+        <f>IF(OR(ISNUMBER(ScenarioText_DOWN!B9),ScenarioText_DOWN!B9="Уровень не рассчитан"),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
@@ -927,145 +927,220 @@
         </is>
       </c>
       <c r="B10">
-        <f>IF(OR(ISNUMBER(ScenarioText_UP!B6),ScenarioText_UP!B6="Расстояние не рассчитано"),"OK","ERROR")</f>
+        <f>IF(OR(ISNUMBER(ScenarioText_UP!B10),ScenarioText_UP!B10="Расстояние не рассчитано"),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C10">
-        <f>IF(OR(ISNUMBER(ScenarioText_DOWN!B6),ScenarioText_DOWN!B6="Расстояние не рассчитано"),"OK","ERROR")</f>
+        <f>IF(OR(ISNUMBER(ScenarioText_DOWN!B10),ScenarioText_DOWN!B10="Расстояние не рассчитано"),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HumanReadableAction not empty</t>
+          <t>ScenarioMid is numeric</t>
         </is>
       </c>
       <c r="B11">
-        <f>IF(AND(ScenarioText_UP!B31&lt;&gt;"",ISNUMBER(ScenarioText_UP!B4)),"OK","ERROR")</f>
+        <f>IF(ISNUMBER(ScenarioText_UP!B7),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C11">
-        <f>IF(AND(ScenarioText_DOWN!B31&lt;&gt;"",ISNUMBER(ScenarioText_DOWN!B4)),"OK","ERROR")</f>
+        <f>IF(ISNUMBER(ScenarioText_DOWN!B7),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ReserveAdd mapping sync</t>
+          <t>ScenarioSpread is numeric</t>
         </is>
       </c>
       <c r="B12">
-        <f>IF(ScenarioText_UP!B19=SectionCalculator_UP!B33,"OK","ERROR")</f>
+        <f>IF(ISNUMBER(ScenarioText_UP!B8),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IF(ScenarioText_DOWN!B19=SectionCalculator_DOWN!B33,"OK","ERROR")</f>
+        <f>IF(ISNUMBER(ScenarioText_DOWN!B8),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RecoveryAdd mapping sync</t>
+          <t>Scenario_* B8 not empty</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(ScenarioText_UP!B20=SectionCalculator_UP!B34,"OK","ERROR")</f>
+        <f>IF(Scenario_UP!B8&lt;&gt;"","OK","ERROR")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>IF(ScenarioText_DOWN!B20=SectionCalculator_DOWN!B34,"OK","ERROR")</f>
+        <f>IF(Scenario_DOWN!B8&lt;&gt;"","OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TailTicket not mapped as lot</t>
+          <t>ScenarioText B9!=B5</t>
         </is>
       </c>
       <c r="B14">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B9&lt;&gt;ScenarioText_UP!B5,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B9&lt;&gt;ScenarioText_DOWN!B5,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tail lot reasonable</t>
+          <t>ScenarioText B10!=B6</t>
         </is>
       </c>
       <c r="B15">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B10&lt;&gt;ScenarioText_UP!B6,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B10&lt;&gt;ScenarioText_DOWN!B6,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tail остаток &lt;= исходного</t>
+          <t>HumanReadableAction not empty</t>
         </is>
       </c>
       <c r="B16">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B37),ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B37&gt;ScenarioText_UP!B25),"ERROR","OK")</f>
+        <f>IF(AND(ScenarioText_UP!B31&lt;&gt;"",ISNUMBER(ScenarioText_UP!B4)),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
+        <f>IF(AND(ScenarioText_DOWN!B31&lt;&gt;"",ISNUMBER(ScenarioText_DOWN!B4)),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RecoveryFundAfter &gt;= 0</t>
+          <t>ReserveAdd mapping sync</t>
         </is>
       </c>
       <c r="B17">
-        <f>IF(TailRecovery_UP!B13&lt;0,"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B19=SectionCalculator_UP!B33,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>IF(TailRecovery_DOWN!B13&lt;0,"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B19=SectionCalculator_DOWN!B33,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CloseLotFinal &lt;= TailLot</t>
+          <t>RecoveryAdd mapping sync</t>
         </is>
       </c>
       <c r="B18">
-        <f>IF(TailRecovery_UP!B10&gt;TailRecovery_UP!B4,"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B20=SectionCalculator_UP!B34,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>IF(TailRecovery_DOWN!B10&gt;TailRecovery_DOWN!B4,"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B20=SectionCalculator_DOWN!B34,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>TailTicket not mapped as lot</t>
+        </is>
+      </c>
+      <c r="B19">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tail lot reasonable</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tail остаток &lt;= исходного</t>
+        </is>
+      </c>
+      <c r="B21">
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B37),ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B37&gt;ScenarioText_UP!B25),"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C21">
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RecoveryFundAfter &gt;= 0</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>IF(TailRecovery_UP!B13&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C22">
+        <f>IF(TailRecovery_DOWN!B13&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CloseLotFinal &lt;= TailLot</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>IF(TailRecovery_UP!B10&gt;TailRecovery_UP!B4,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>IF(TailRecovery_DOWN!B10&gt;TailRecovery_DOWN!B4,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TailLotAfter &gt;= 0</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="B24">
         <f>IF(TailRecovery_UP!B14&lt;0,"ERROR","OK")</f>
         <v/>
       </c>
-      <c r="C19">
+      <c r="C24">
         <f>IF(TailRecovery_DOWN!B14&lt;0,"ERROR","OK")</f>
         <v/>
       </c>
@@ -1330,46 +1405,38 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Следующий уровень открытия</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!N4,IF(SectionCalculator_UP!B4=2,Scenario_UP!N5,IF(SectionCalculator_UP!B4=3,Scenario_UP!N6,IF(SectionCalculator_UP!B4=4,Scenario_UP!N7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
-        <v/>
-      </c>
+      <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Уровень секции</t>
+          <t>Следующий уровень открытия</t>
         </is>
       </c>
       <c r="B9">
-        <f>IFERROR(SectionCalculator_UP!B4,0)</f>
+        <f>IFERROR(IF(SectionCalculator_UP!B4=1,Scenario_UP!N4,IF(SectionCalculator_UP!B4=2,Scenario_UP!N5,IF(SectionCalculator_UP!B4=3,Scenario_UP!N6,IF(SectionCalculator_UP!B4=4,Scenario_UP!N7,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Причина</t>
+          <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
       <c r="B10">
-        <f>IF(SectionCalculator_UP!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция недоступна: уровень/риск-гейт/хвост")</f>
+        <f>IF(OR(B9="Уровень не рассчитан",B7=""),"Расстояние не рассчитано",ROUND(ABS(B9-B7)/Settings!$B$3,0))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Малая защитная позиция</t>
+          <t>Большая позиция</t>
         </is>
       </c>
       <c r="B11">
-        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(IF(TailRecovery_UP!B16&gt;0,IF("UP"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_UP!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
@@ -1378,6 +1445,10 @@
         <is>
           <t>Проверки риска</t>
         </is>
+      </c>
+      <c r="B12">
+        <f>IFERROR(IF(TailRecovery_UP!B17&gt;0,IF("UP"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_UP!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1705,46 +1776,38 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Следующий уровень открытия</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!N9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!N10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!N11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!N12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
-        <v/>
-      </c>
+      <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Уровень секции</t>
+          <t>Следующий уровень открытия</t>
         </is>
       </c>
       <c r="B9">
-        <f>IFERROR(SectionCalculator_DOWN!B4,0)</f>
+        <f>IFERROR(IF(SectionCalculator_DOWN!B4=1,Scenario_DOWN!N9,IF(SectionCalculator_DOWN!B4=2,Scenario_DOWN!N10,IF(SectionCalculator_DOWN!B4=3,Scenario_DOWN!N11,IF(SectionCalculator_DOWN!B4=4,Scenario_DOWN!N12,"Уровень не рассчитан")))),"Уровень не рассчитан")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Причина</t>
+          <t>Расстояние до уровня, пунктов</t>
         </is>
       </c>
       <c r="B10">
-        <f>IF(SectionCalculator_DOWN!B14="YES","цена достигла уровня; хвост найден; риск-лимиты OK","секция недоступна: уровень/риск-гейт/хвост")</f>
+        <f>IF(OR(B9="Уровень не рассчитан",B7=""),"Расстояние не рассчитано",ROUND(ABS(B9-B7)/Settings!$B$3,0))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Малая защитная позиция</t>
+          <t>Большая позиция</t>
         </is>
       </c>
       <c r="B11">
-        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <f>IFERROR(IF(TailRecovery_DOWN!B16&gt;0,IF("DOWN"="UP","SELL ","BUY ")&amp;TEXT(TailRecovery_DOWN!B16,"0.00"),"Не открывать"),"Не открывать")</f>
         <v/>
       </c>
     </row>
@@ -1753,6 +1816,10 @@
         <is>
           <t>Проверки риска</t>
         </is>
+      </c>
+      <c r="B12">
+        <f>IFERROR(IF(TailRecovery_DOWN!B17&gt;0,IF("DOWN"="UP","BUY ","SELL ")&amp;TEXT(TailRecovery_DOWN!B17,"0.00"),"Не открывать"),"Не открывать")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2807,6 +2874,17 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ScenarioSpread</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>(B6-B5)/Settings!$B$3</f>
+        <v/>
+      </c>
+    </row>
     <row r="9">
       <c r="M9" t="inlineStr">
         <is>
@@ -13130,6 +13208,17 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ScenarioSpread</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>(B6-B5)/Settings!$B$3</f>
+        <v/>
+      </c>
+    </row>
     <row r="9">
       <c r="M9" t="inlineStr">
         <is>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -1396,16 +1396,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spread, пунктов</t>
+          <t>Сценарный Mid</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <f>IFERROR(Settings!B34,0)</f>
+        <f>IFERROR(Scenario_UP!B7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Сценарный Spread</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>IFERROR(Scenario_UP!B8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1443,7 +1451,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Проверки риска</t>
+          <t>Малая защитная позиция</t>
         </is>
       </c>
       <c r="B12">
@@ -1454,11 +1462,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Можно открыть секцию</t>
+          <t>Уровень секции</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")</f>
+        <f>IFERROR(SectionCalculator_UP!B4,0)</f>
         <v/>
       </c>
     </row>
@@ -1676,7 +1684,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1767,16 +1775,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spread, пунктов</t>
+          <t>Сценарный Mid</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <f>IFERROR(Settings!B34,0)</f>
+        <f>IFERROR(Scenario_DOWN!B7,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Сценарный Spread</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>IFERROR(Scenario_DOWN!B8,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1814,7 +1830,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Проверки риска</t>
+          <t>Малая защитная позиция</t>
         </is>
       </c>
       <c r="B12">
@@ -1825,11 +1841,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Можно открыть секцию</t>
+          <t>Уровень секции</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")</f>
+        <f>IFERROR(SectionCalculator_DOWN!B4,0)</f>
         <v/>
       </c>
     </row>
@@ -2047,7 +2063,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущая расчетная цена: "&amp;TEXT(B3,"0.00000")&amp;"."&amp;CHAR(10)&amp;"Сценарий: "&amp;B2&amp;CHAR(10)&amp;"Текущая цена: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Сценарная цена: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B5),TEXT(B5,"0.00000"),B5)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B6),TEXT(B6,"0")&amp;" пунктов",B6)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,179 +968,209 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scenario_* B8 not empty</t>
+          <t>ScenarioSpread bounds</t>
         </is>
       </c>
       <c r="B13">
-        <f>IF(Scenario_UP!B8&lt;&gt;"","OK","ERROR")</f>
+        <f>IF(AND(ScenarioText_UP!B8&gt;0,ScenarioText_UP!B8&lt;1000),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C13">
-        <f>IF(Scenario_DOWN!B8&lt;&gt;"","OK","ERROR")</f>
+        <f>IF(AND(ScenarioText_DOWN!B8&gt;0,ScenarioText_DOWN!B8&lt;1000),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ScenarioText B9!=B5</t>
+          <t>Scenario_* B8 not empty</t>
         </is>
       </c>
       <c r="B14">
-        <f>IF(ScenarioText_UP!B9&lt;&gt;ScenarioText_UP!B5,"OK","ERROR")</f>
+        <f>IF(Scenario_UP!B8&lt;&gt;"","OK","ERROR")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>IF(ScenarioText_DOWN!B9&lt;&gt;ScenarioText_DOWN!B5,"OK","ERROR")</f>
+        <f>IF(Scenario_DOWN!B8&lt;&gt;"","OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ScenarioText B10!=B6</t>
+          <t>No legacy single-price wording</t>
         </is>
       </c>
       <c r="B15">
-        <f>IF(ScenarioText_UP!B10&lt;&gt;ScenarioText_UP!B6,"OK","ERROR")</f>
+        <f>IF(ISERROR(SEARCH("Сценарная цена",ScenarioText_UP!B46)),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>IF(ScenarioText_DOWN!B10&lt;&gt;ScenarioText_DOWN!B6,"OK","ERROR")</f>
+        <f>IF(ISERROR(SEARCH("Сценарная цена",ScenarioText_DOWN!B46)),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HumanReadableAction not empty</t>
+          <t>ScenarioText B9!=B5</t>
         </is>
       </c>
       <c r="B16">
-        <f>IF(AND(ScenarioText_UP!B31&lt;&gt;"",ISNUMBER(ScenarioText_UP!B4)),"OK","ERROR")</f>
+        <f>IF(ScenarioText_UP!B9&lt;&gt;ScenarioText_UP!B5,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C16">
-        <f>IF(AND(ScenarioText_DOWN!B31&lt;&gt;"",ISNUMBER(ScenarioText_DOWN!B4)),"OK","ERROR")</f>
+        <f>IF(ScenarioText_DOWN!B9&lt;&gt;ScenarioText_DOWN!B5,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ReserveAdd mapping sync</t>
+          <t>ScenarioText B10!=B6</t>
         </is>
       </c>
       <c r="B17">
-        <f>IF(ScenarioText_UP!B19=SectionCalculator_UP!B33,"OK","ERROR")</f>
+        <f>IF(ScenarioText_UP!B10&lt;&gt;ScenarioText_UP!B6,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C17">
-        <f>IF(ScenarioText_DOWN!B19=SectionCalculator_DOWN!B33,"OK","ERROR")</f>
+        <f>IF(ScenarioText_DOWN!B10&lt;&gt;ScenarioText_DOWN!B6,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RecoveryAdd mapping sync</t>
+          <t>HumanReadableAction not empty</t>
         </is>
       </c>
       <c r="B18">
-        <f>IF(ScenarioText_UP!B20=SectionCalculator_UP!B34,"OK","ERROR")</f>
+        <f>IF(AND(ScenarioText_UP!B31&lt;&gt;"",ISNUMBER(ScenarioText_UP!B4)),"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C18">
-        <f>IF(ScenarioText_DOWN!B20=SectionCalculator_DOWN!B34,"OK","ERROR")</f>
+        <f>IF(AND(ScenarioText_DOWN!B31&lt;&gt;"",ISNUMBER(ScenarioText_DOWN!B4)),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TailTicket not mapped as lot</t>
+          <t>ReserveAdd mapping sync</t>
         </is>
       </c>
       <c r="B19">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B19=SectionCalculator_UP!B33,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C19">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B19=SectionCalculator_DOWN!B33,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tail lot reasonable</t>
+          <t>RecoveryAdd mapping sync</t>
         </is>
       </c>
       <c r="B20">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_UP!B20=SectionCalculator_UP!B34,"OK","ERROR")</f>
         <v/>
       </c>
       <c r="C20">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
+        <f>IF(ScenarioText_DOWN!B20=SectionCalculator_DOWN!B34,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tail остаток &lt;= исходного</t>
+          <t>TailTicket not mapped as lot</t>
         </is>
       </c>
       <c r="B21">
-        <f>IF(AND(ISNUMBER(ScenarioText_UP!B37),ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B37&gt;ScenarioText_UP!B25),"ERROR","OK")</f>
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B24),ScenarioText_UP!B24&gt;1000,ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
         <v/>
       </c>
       <c r="C21">
-        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B24),ScenarioText_DOWN!B24&gt;1000,ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RecoveryFundAfter &gt;= 0</t>
+          <t>Tail lot reasonable</t>
         </is>
       </c>
       <c r="B22">
-        <f>IF(TailRecovery_UP!B13&lt;0,"ERROR","OK")</f>
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B25&gt;100),"ERROR","OK")</f>
         <v/>
       </c>
       <c r="C22">
-        <f>IF(TailRecovery_DOWN!B13&lt;0,"ERROR","OK")</f>
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B25&gt;100),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CloseLotFinal &lt;= TailLot</t>
+          <t>Tail остаток &lt;= исходного</t>
         </is>
       </c>
       <c r="B23">
-        <f>IF(TailRecovery_UP!B10&gt;TailRecovery_UP!B4,"ERROR","OK")</f>
+        <f>IF(AND(ISNUMBER(ScenarioText_UP!B37),ISNUMBER(ScenarioText_UP!B25),ScenarioText_UP!B37&gt;ScenarioText_UP!B25),"ERROR","OK")</f>
         <v/>
       </c>
       <c r="C23">
-        <f>IF(TailRecovery_DOWN!B10&gt;TailRecovery_DOWN!B4,"ERROR","OK")</f>
+        <f>IF(AND(ISNUMBER(ScenarioText_DOWN!B37),ISNUMBER(ScenarioText_DOWN!B25),ScenarioText_DOWN!B37&gt;ScenarioText_DOWN!B25),"ERROR","OK")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>RecoveryFundAfter &gt;= 0</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>IF(TailRecovery_UP!B13&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>IF(TailRecovery_DOWN!B13&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CloseLotFinal &lt;= TailLot</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>IF(TailRecovery_UP!B10&gt;TailRecovery_UP!B4,"ERROR","OK")</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>IF(TailRecovery_DOWN!B10&gt;TailRecovery_DOWN!B4,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>TailLotAfter &gt;= 0</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="B26">
         <f>IF(TailRecovery_UP!B14&lt;0,"ERROR","OK")</f>
         <v/>
       </c>
-      <c r="C24">
+      <c r="C26">
         <f>IF(TailRecovery_DOWN!B14&lt;0,"ERROR","OK")</f>
         <v/>
       </c>
@@ -1399,7 +1429,7 @@
           <t>Сценарный Mid</t>
         </is>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <f>IFERROR(Scenario_UP!B7,0)</f>
         <v/>
       </c>
@@ -1410,7 +1440,7 @@
           <t>Сценарный Spread</t>
         </is>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <f>IFERROR(Scenario_UP!B8,0)</f>
         <v/>
       </c>
@@ -1684,7 +1714,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -1778,7 +1808,7 @@
           <t>Сценарный Mid</t>
         </is>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <f>IFERROR(Scenario_DOWN!B7,0)</f>
         <v/>
       </c>
@@ -1789,7 +1819,7 @@
           <t>Сценарный Spread</t>
         </is>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <f>IFERROR(Scenario_DOWN!B8,0)</f>
         <v/>
       </c>
@@ -2063,7 +2093,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B7&amp;" / "&amp;B8&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -1290,7 +1290,7 @@
         <v/>
       </c>
       <c r="K2">
-        <f>IF(OR(SectionCalculator_UP!B14&lt;&gt;"YES",SectionCalculator_UP!B13&lt;&gt;"YES"),"YES","NO")</f>
+        <f>IF(OR(SectionCalculator_UP!B14&lt;&gt;"YES",SectionCalculator_UP!B13&lt;&gt;"YES"),"ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
       <c r="K3">
-        <f>IF(OR(SectionCalculator_DOWN!B14&lt;&gt;"YES",SectionCalculator_DOWN!B13&lt;&gt;"YES"),"YES","NO")</f>
+        <f>IF(OR(SectionCalculator_DOWN!B14&lt;&gt;"YES",SectionCalculator_DOWN!B13&lt;&gt;"YES"),"ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;B13&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2188,349 +2188,268 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scenario_UP!B2</t>
+          <t>Scenario_UP!B5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'=CurrentPositions!F2</t>
+          <t>'=B2+B4*Settings!B3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CurrentPositions!F2</t>
+          <t>Scenario_UP!B2,B4,Settings!B3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Scenario_UP!B4</t>
+          <t>Scenario_UP!B6:B8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CurrentPrice</t>
+          <t>ScenarioBid</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Scenario_UP!B4</t>
+          <t>Scenario_UP!B6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'=B2+B3*Settings!B3</t>
+          <t>'=B3+B4*Settings!B3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scenario_UP!B2,B3,Settings!B3</t>
+          <t>Scenario_UP!B3,B4,Settings!B3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B12</t>
+          <t>Scenario_UP!B8,F12:F211</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ScenarioPrice</t>
+          <t>ScenarioAsk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Scenario_UP!N1</t>
+          <t>Scenario_UP!B7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'=...</t>
+          <t>'=(B5+B6)/2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scenario_UP positions</t>
+          <t>B5,B6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Scenario_UP!N3</t>
+          <t>SectionCalculator_UP!B12,ScenarioText_UP!B7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AverageBuyPrice</t>
+          <t>ScenarioMid</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Scenario_UP!N2</t>
+          <t>Scenario_UP!B8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'=...</t>
+          <t>'=(B6-B5)/Settings!B3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scenario_UP positions</t>
+          <t>B6,B5,Settings!B3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Scenario_UP!N3</t>
+          <t>ScenarioText_UP!B8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AverageSellPrice</t>
+          <t>ScenarioSpread</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scenario_UP!N3</t>
+          <t>Scenario_UP!B221</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'=(N1+N2)/2</t>
+          <t>'=IF(COUNT(K12:K211)=0,0,MIN(K12:K211))</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N1,N2</t>
+          <t>K12:K211</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Scenario_UP!N4:N12</t>
+          <t>Scenario_UP!B222</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>TailWorstPnL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scenario_UP!B221</t>
+          <t>Scenario_UP!B222</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'=MINIFS(...)</t>
+          <t>'=IF(B221=0,"N/A",MIN(L12:L211))</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>H7:H206,B7:B206</t>
+          <t>B221,L12:L211</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Scenario_UP!B222</t>
+          <t>Scenario_UP!B223</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TailWorstPnL</t>
+          <t>TailTicket</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scenario_UP!B222</t>
+          <t>SectionCalculator_UP!B14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'=MINIFS(...)</t>
+          <t>'=IF(...)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A7:A206,H7:H206,B221</t>
+          <t>B3,B7,B8,B12,B13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Scenario_UP!B223</t>
+          <t>ScenarioText_UP!B13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TailTicket</t>
+          <t>CanOpenSection</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B7</t>
+          <t>TailRecovery_UP!B10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'=IF(B3&lt;=0,0,FLOOR(...))</t>
+          <t>'=IF(B6="YES",MIN(B9,B4),0)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B3,B5</t>
+          <t>B6,B9,B4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B14</t>
+          <t>Log!F2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BigLot</t>
+          <t>CloseLotFinal</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B8</t>
+          <t>BasketSummary!B13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>'=IF(B3&lt;=0,0,FLOOR(...))</t>
+          <t>'=IF(...)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B3,B6</t>
+          <t>B8,B9,B10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B14</t>
+          <t>ScenarioText_UP!B31</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SmallLot</t>
+          <t>NextAction</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B14</t>
+          <t>ScenarioText_UP!B31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>'=IF(...)</t>
+          <t>'=IF(BasketSummary!B13...)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B3,B7,B8,B12,B13</t>
+          <t>BasketSummary!B13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ScenarioText_UP!B13</t>
+          <t>ScenarioText_UP!B46</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>CanOpenSection</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TailRecovery_UP!B10</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>'=IF(B6="YES",MIN(B9,B4),0)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B6,B9,B4</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Log!F2</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CloseLotFinal</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BasketSummary!B13</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>'=IF(...)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B8,B9,B10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ScenarioText_UP!B31</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>NextAction</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ScenarioText_UP!B31</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>'=IF(BasketSummary!B13...)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BasketSummary!B13</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ScenarioText_UP!B46</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>HumanReadableAction</t>
         </is>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -1290,7 +1290,7 @@
         <v/>
       </c>
       <c r="K2">
-        <f>IF(OR(SectionCalculator_UP!B14&lt;&gt;"YES",SectionCalculator_UP!B13&lt;&gt;"YES"),"ДА","НЕТ")</f>
+        <f>IF(BasketSummary!B13="SAFE","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         <v/>
       </c>
       <c r="K3">
-        <f>IF(OR(SectionCalculator_DOWN!B14&lt;&gt;"YES",SectionCalculator_DOWN!B13&lt;&gt;"YES"),"ДА","НЕТ")</f>
+        <f>IF(BasketSummary!C13="SAFE","ДА","НЕТ")</f>
         <v/>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;B38&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
     <row r="45"/>
     <row r="46">
       <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;IF(B14="ДА","НЕТ","ДА")&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;B38&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,36 @@
       </c>
       <c r="C26">
         <f>IF(TailRecovery_DOWN!B14&lt;0,"ERROR","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScenarioText SAFE not empty</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>IF(ScenarioText_UP!B38&lt;&gt;"","OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>IF(ScenarioText_DOWN!B38&lt;&gt;"","OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ScenarioText SAFE equals Log SAFE</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>IF(ScenarioText_UP!B38=Log!K2,"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>IF(ScenarioText_DOWN!B38=Log!K3,"OK","ERROR")</f>
         <v/>
       </c>
     </row>
@@ -2111,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2144,314 +2174,270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scenario_UP!B4</t>
+          <t>Scenario_UP!B5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>'=Scenario_UP!B2+Scenario_UP!B3*Settings!B3</t>
+          <t>'=B2+B4*Settings!B3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scenario_UP!B2, Scenario_UP!B3, Settings!B3</t>
+          <t>Scenario_UP!B2, Scenario_UP!B4, Settings!B3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B12, ScenarioText_UP!B4</t>
+          <t>Scenario_UP!B7:B8, SectionCalculator_UP!B12, ScenarioText_UP!B5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ScenarioBid</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scenario_DOWN!B4</t>
+          <t>Scenario_UP!B6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>'=Scenario_DOWN!B2-Scenario_DOWN!B3*Settings!B3</t>
+          <t>'=B3+B4*Settings!B3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scenario_DOWN!B2, Scenario_DOWN!B3, Settings!B3</t>
+          <t>Scenario_UP!B3, Scenario_UP!B4, Settings!B3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SectionCalculator_DOWN!B12, ScenarioText_DOWN!B4</t>
+          <t>Scenario_UP!B7:B8, Scenario_UP!F12:F211, ScenarioText_UP!B6</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ScenarioAsk</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scenario_UP!B5</t>
+          <t>Scenario_UP!B7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>'=B2+B4*Settings!B3</t>
+          <t>'=(B5+B6)/2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scenario_UP!B2,B4,Settings!B3</t>
+          <t>Scenario_UP!B5, Scenario_UP!B6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Scenario_UP!B6:B8</t>
+          <t>SectionCalculator_UP!B12, ScenarioText_UP!B7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ScenarioBid</t>
+          <t>ScenarioMid</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Scenario_UP!B6</t>
+          <t>Scenario_UP!B8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'=B3+B4*Settings!B3</t>
+          <t>'=(B6-B5)/Settings!B3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scenario_UP!B3,B4,Settings!B3</t>
+          <t>Scenario_UP!B6, Scenario_UP!B5, Settings!B3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Scenario_UP!B8,F12:F211</t>
+          <t>ScenarioText_UP!B8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ScenarioAsk</t>
+          <t>ScenarioSpread</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Scenario_UP!B7</t>
+          <t>Scenario_UP!K12:L211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'=(B5+B6)/2</t>
+          <t>PnL helper range</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B5,B6</t>
+          <t>Scenario_UP!C12:F211, Settings!B3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B12,ScenarioText_UP!B7</t>
+          <t>Scenario_UP!B221:B223</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ScenarioMid</t>
+          <t>Tail helper range</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Scenario_UP!B8</t>
+          <t>Scenario_UP!B221</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'=(B6-B5)/Settings!B3</t>
+          <t>'=IF(COUNT(K12:K211)=0,0,MIN(K12:K211))</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B6,B5,Settings!B3</t>
+          <t>Scenario_UP!K12:K211</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ScenarioText_UP!B8</t>
+          <t>Scenario_UP!B222</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ScenarioSpread</t>
+          <t>TailWorstPnL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scenario_UP!B221</t>
+          <t>Scenario_UP!B222</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'=IF(COUNT(K12:K211)=0,0,MIN(K12:K211))</t>
+          <t>'=IF(B221=0,"N/A",MIN(L12:L211))</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K12:K211</t>
+          <t>Scenario_UP!B221, Scenario_UP!L12:L211</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Scenario_UP!B222</t>
+          <t>Scenario_UP!B223, ScenarioText_UP!B24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TailWorstPnL</t>
+          <t>TailTicket</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scenario_UP!B222</t>
+          <t>BasketSummary!B13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'=IF(B221=0,"N/A",MIN(L12:L211))</t>
+          <t>'=IF(...)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B221,L12:L211</t>
+          <t>BasketSummary!B8, BasketSummary!B9, BasketSummary!B10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Scenario_UP!B223</t>
+          <t>ScenarioText_UP!B31, ScenarioText_UP!B38, Log!D2, Log!K2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TailTicket</t>
+          <t>NextAction</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SectionCalculator_UP!B14</t>
+          <t>ScenarioText_UP!B31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'=IF(...)</t>
+          <t>'=IF(BasketSummary!B13...)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B3,B7,B8,B12,B13</t>
+          <t>BasketSummary!B13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ScenarioText_UP!B13</t>
+          <t>ScenarioText_UP!B46</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CanOpenSection</t>
+          <t>HumanReadableAction</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TailRecovery_UP!B10</t>
+          <t>ScenarioText_UP!B38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>'=IF(B6="YES",MIN(B9,B4),0)</t>
+          <t>'=IF(BasketSummary!B13="SAFE","ДА","НЕТ")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B6,B9,B4</t>
+          <t>BasketSummary!B13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Log!F2</t>
+          <t>ScenarioText_UP!B46, Validation</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CloseLotFinal</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BasketSummary!B13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>'=IF(...)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B8,B9,B10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ScenarioText_UP!B31</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NextAction</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ScenarioText_UP!B31</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>'=IF(BasketSummary!B13...)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BasketSummary!B13</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ScenarioText_UP!B46</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HumanReadableAction</t>
+          <t>SAFE flag</t>
         </is>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -1383,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1717,40 +1717,83 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Разрешено закрытие хвоста</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>IF(TailRecovery_UP!B11="YES","ДА","НЕТ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Убыток закрываемой части</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>IFERROR(TailRecovery_UP!B12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RecoveryFund после закрытия</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>IFERROR(TailRecovery_UP!B13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Остаток хвоста</t>
+        </is>
+      </c>
+      <c r="B37" s="4">
+        <f>IFERROR(TailRecovery_UP!B14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>IF(BasketSummary!B13="SAFE","ДА","НЕТ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5">
         <f>B46</f>
         <v/>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35">
-      <c r="B35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="n"/>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
     <row r="43"/>
     <row r="44"/>
     <row r="45"/>
-    <row r="46">
-      <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;B38&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
-        <v/>
-      </c>
-    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:H45"/>
+    <mergeCell ref="A39:H52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1762,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,40 +2139,83 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Разрешено закрытие хвоста</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>IF(TailRecovery_DOWN!B11="YES","ДА","НЕТ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Убыток закрываемой части</t>
+        </is>
+      </c>
+      <c r="B35" s="4">
+        <f>IFERROR(TailRecovery_DOWN!B12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RecoveryFund после закрытия</t>
+        </is>
+      </c>
+      <c r="B36" s="4">
+        <f>IFERROR(TailRecovery_DOWN!B13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Остаток хвоста</t>
+        </is>
+      </c>
+      <c r="B37" s="4">
+        <f>IFERROR(TailRecovery_DOWN!B14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="B38">
+        <f>IF(BasketSummary!C13="SAFE","ДА","НЕТ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5">
         <f>B46</f>
         <v/>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35">
-      <c r="B35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="n"/>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
     <row r="43"/>
     <row r="44"/>
     <row r="45"/>
-    <row r="46">
-      <c r="B46">
-        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;B38&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
-        <v/>
-      </c>
-    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:H45"/>
+    <mergeCell ref="A39:H52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,6 +1202,21 @@
       </c>
       <c r="C28">
         <f>IF(ScenarioText_DOWN!B38=Log!K3,"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Detailed recommendation block not empty</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>IF(AND(ScenarioText_UP!A39&lt;&gt;"",ScenarioText_UP!A39&lt;&gt;0),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>IF(AND(ScenarioText_DOWN!A39&lt;&gt;"",ScenarioText_DOWN!A39&lt;&gt;0),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
@@ -1774,7 +1789,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5">
-        <f>B46</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вверх."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_UP!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_UP!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_UP!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;B38&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>
@@ -2196,7 +2211,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5">
-        <f>B46</f>
+        <f>"ПОДРОБНАЯ РЕКОМЕНДАЦИЯ"&amp;CHAR(10)&amp;CHAR(10)&amp;"Сценарий: цена идет вниз."&amp;CHAR(10)&amp;"Текущий Bid: "&amp;TEXT(B3,"0.00000")&amp;CHAR(10)&amp;"Текущий Ask: "&amp;TEXT(B4,"0.00000")&amp;CHAR(10)&amp;"Сценарный Bid: "&amp;TEXT(B5,"0.00000")&amp;CHAR(10)&amp;"Сценарный Ask: "&amp;TEXT(B6,"0.00000")&amp;CHAR(10)&amp;"Сценарный Mid: "&amp;TEXT(B7,"0.00000")&amp;CHAR(10)&amp;"Spread: "&amp;TEXT(B8,"0")&amp;" пунктов"&amp;CHAR(10)&amp;"Следующий уровень: "&amp;IF(ISNUMBER(B9),TEXT(B9,"0.00000"),B9)&amp;CHAR(10)&amp;"Расстояние до уровня: "&amp;IF(ISNUMBER(B10),TEXT(B10,"0")&amp;" пунктов",B10)&amp;CHAR(10)&amp;CHAR(10)&amp;"Рекомендация по секции: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Можно открыть секцию: "&amp;IF(SectionCalculator_DOWN!B14="YES","ДА","НЕТ")&amp;CHAR(10)&amp;"Можно закрыть секцию: "&amp;B15&amp;CHAR(10)&amp;"Можно закрыть хвост: "&amp;B16&amp;CHAR(10)&amp;CHAR(10)&amp;"Тип хвоста: "&amp;B23&amp;CHAR(10)&amp;"Тикет хвоста: "&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;CHAR(10)&amp;"Лот хвоста до закрытия: "&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;CHAR(10)&amp;"Итоговый лот закрытия: "&amp;IF(ISNUMBER(B30),TEXT(B30,"0.00"),"0.00")&amp;CHAR(10)&amp;"Остаток хвоста после закрытия: "&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;CHAR(10)&amp;"RecoveryFund после: "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"ДЕЙСТВИЕ: "&amp;B31&amp;CHAR(10)&amp;"Если открывать секцию: "&amp;B11&amp;" / "&amp;B12&amp;CHAR(10)&amp;"Если закрывать хвост: тип="&amp;B23&amp;", тикет="&amp;IF(ISNUMBER(B24),TEXT(B24,"0"),B24)&amp;", до="&amp;IF(ISNUMBER(B25),TEXT(B25,"0.00"),B25)&amp;", закрыть="&amp;TEXT(B30,"0.00")&amp;", остаток="&amp;TEXT(TailRecovery_DOWN!B14,"0.00")&amp;CHAR(10)&amp;"Добавить в резерв: "&amp;TEXT(B19,"0.00")&amp;"; Добавить в RecoveryFund: "&amp;TEXT(B20,"0.00")&amp;CHAR(10)&amp;"Резерв после: "&amp;TEXT(B21,"0.00")&amp;"; RecoveryFund после цикла: "&amp;TEXT(B22,"0.00")&amp;CHAR(10)&amp;"RecoveryFund до/после закрытия хвоста: "&amp;TEXT(B27,"0.00")&amp;" / "&amp;TEXT(TailRecovery_DOWN!B13,"0.00")&amp;CHAR(10)&amp;"SAFE: "&amp;B38&amp;CHAR(10)&amp;"ИТОГОВОЕ ДЕЙСТВИЕ: "&amp;B31</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,21 @@
       </c>
       <c r="C29">
         <f>IF(AND(ScenarioText_DOWN!A39&lt;&gt;"",ScenarioText_DOWN!A39&lt;&gt;0),"OK","ERROR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TailTicket belongs to TailWorstPnL</t>
+        </is>
+      </c>
+      <c r="B30">
+        <f>IF(OR(Scenario_UP!B222="N/A",INDEX(Scenario_UP!K12:K211,MATCH(Scenario_UP!B222,Scenario_UP!A12:A211,0))=Scenario_UP!B221),"OK","ERROR")</f>
+        <v/>
+      </c>
+      <c r="C30">
+        <f>IF(OR(Scenario_DOWN!B222="N/A",INDEX(Scenario_DOWN!K12:K211,MATCH(Scenario_DOWN!B222,Scenario_DOWN!A12:A211,0))=Scenario_DOWN!B221),"OK","ERROR")</f>
         <v/>
       </c>
     </row>
@@ -2442,12 +2457,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>'=IF(B221=0,"N/A",MIN(L12:L211))</t>
+          <t>'=IF(B221=0,"N/A",MINIFS(L12:L211,K12:K211,B221))</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scenario_UP!B221, Scenario_UP!L12:L211</t>
+          <t>Scenario_UP!B221, Scenario_UP!K12:K211, Scenario_UP!L12:L211</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13069,7 +13084,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IF(B221=0,"N/A",MIN(L12:L211))</f>
+        <f>IF(B221=0,"N/A",MINIFS(L12:L211,K12:K211,B221))</f>
         <v/>
       </c>
     </row>
@@ -23403,7 +23418,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IF(B221=0,"N/A",MIN(L12:L211))</f>
+        <f>IF(B221=0,"N/A",MINIFS(L12:L211,K12:K211,B221))</f>
         <v/>
       </c>
     </row>

--- a/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
+++ b/recovery_lock_cascade_next_step/recovery_lock_cascade_next_step_ru.xlsx
@@ -2257,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2452,106 +2452,133 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Scenario_UP!O12:O211</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>'=IF(Krow=$B$221,Lrow,"")</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Scenario_UP!K12:K211, Scenario_UP!L12:L211, Scenario_UP!B221</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Scenario_UP!B222</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>'=IF(B221=0,"N/A",MINIFS(L12:L211,K12:K211,B221))</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Scenario_UP!B221, Scenario_UP!K12:K211, Scenario_UP!L12:L211</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Scenario_UP!B223, ScenarioText_UP!B24</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TailTicket</t>
+          <t>TailFinalTicketCandidates</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BasketSummary!B13</t>
+          <t>Scenario_UP!B222</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>'=IF(...)</t>
+          <t>'=IF(B221=0,"N/A",MIN(O12:O211))</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BasketSummary!B8, BasketSummary!B9, BasketSummary!B10</t>
+          <t>Scenario_UP!B221, Scenario_UP!O12:O211</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ScenarioText_UP!B31, ScenarioText_UP!B38, Log!D2, Log!K2</t>
+          <t>Scenario_UP!B223, ScenarioText_UP!B24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NextAction</t>
+          <t>TailTicket</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ScenarioText_UP!B31</t>
+          <t>BasketSummary!B13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>'=IF(BasketSummary!B13...)</t>
+          <t>'=IF(...)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BasketSummary!B13</t>
+          <t>BasketSummary!B8, BasketSummary!B9, BasketSummary!B10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ScenarioText_UP!B46</t>
+          <t>ScenarioText_UP!B31, ScenarioText_UP!B38, Log!D2, Log!K2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HumanReadableAction</t>
+          <t>NextAction</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ScenarioText_UP!B31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>'=IF(BasketSummary!B13...)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BasketSummary!B13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ScenarioText_UP!B46</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HumanReadableAction</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>ScenarioText_UP!B38</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>'=IF(BasketSummary!B13="SAFE","ДА","НЕТ")</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>BasketSummary!B13</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>ScenarioText_UP!B46, Validation</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>SAFE flag</t>
         </is>
@@ -2798,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N225"/>
+  <dimension ref="A1:O225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3103,6 +3130,10 @@
         <f>IF(N3=0,"Уровень не рассчитан",N3-4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
+      <c r="O12">
+        <f>IF(K12=$B$221,L12,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -3153,6 +3184,10 @@
         <f>IF(K13&lt;&gt;"",A13,"")</f>
         <v/>
       </c>
+      <c r="O13">
+        <f>IF(K13=$B$221,L13,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -3203,6 +3238,10 @@
         <f>IF(K14&lt;&gt;"",A14,"")</f>
         <v/>
       </c>
+      <c r="O14">
+        <f>IF(K14=$B$221,L14,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -3253,6 +3292,10 @@
         <f>IF(K15&lt;&gt;"",A15,"")</f>
         <v/>
       </c>
+      <c r="O15">
+        <f>IF(K15=$B$221,L15,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -3303,6 +3346,10 @@
         <f>IF(K16&lt;&gt;"",A16,"")</f>
         <v/>
       </c>
+      <c r="O16">
+        <f>IF(K16=$B$221,L16,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -3353,6 +3400,10 @@
         <f>IF(K17&lt;&gt;"",A17,"")</f>
         <v/>
       </c>
+      <c r="O17">
+        <f>IF(K17=$B$221,L17,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -3403,6 +3454,10 @@
         <f>IF(K18&lt;&gt;"",A18,"")</f>
         <v/>
       </c>
+      <c r="O18">
+        <f>IF(K18=$B$221,L18,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -3453,6 +3508,10 @@
         <f>IF(K19&lt;&gt;"",A19,"")</f>
         <v/>
       </c>
+      <c r="O19">
+        <f>IF(K19=$B$221,L19,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -3503,6 +3562,10 @@
         <f>IF(K20&lt;&gt;"",A20,"")</f>
         <v/>
       </c>
+      <c r="O20">
+        <f>IF(K20=$B$221,L20,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -3553,6 +3616,10 @@
         <f>IF(K21&lt;&gt;"",A21,"")</f>
         <v/>
       </c>
+      <c r="O21">
+        <f>IF(K21=$B$221,L21,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -3603,6 +3670,10 @@
         <f>IF(K22&lt;&gt;"",A22,"")</f>
         <v/>
       </c>
+      <c r="O22">
+        <f>IF(K22=$B$221,L22,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -3653,6 +3724,10 @@
         <f>IF(K23&lt;&gt;"",A23,"")</f>
         <v/>
       </c>
+      <c r="O23">
+        <f>IF(K23=$B$221,L23,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -3703,6 +3778,10 @@
         <f>IF(K24&lt;&gt;"",A24,"")</f>
         <v/>
       </c>
+      <c r="O24">
+        <f>IF(K24=$B$221,L24,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -3753,6 +3832,10 @@
         <f>IF(K25&lt;&gt;"",A25,"")</f>
         <v/>
       </c>
+      <c r="O25">
+        <f>IF(K25=$B$221,L25,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -3803,6 +3886,10 @@
         <f>IF(K26&lt;&gt;"",A26,"")</f>
         <v/>
       </c>
+      <c r="O26">
+        <f>IF(K26=$B$221,L26,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -3853,6 +3940,10 @@
         <f>IF(K27&lt;&gt;"",A27,"")</f>
         <v/>
       </c>
+      <c r="O27">
+        <f>IF(K27=$B$221,L27,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -3903,6 +3994,10 @@
         <f>IF(K28&lt;&gt;"",A28,"")</f>
         <v/>
       </c>
+      <c r="O28">
+        <f>IF(K28=$B$221,L28,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -3953,6 +4048,10 @@
         <f>IF(K29&lt;&gt;"",A29,"")</f>
         <v/>
       </c>
+      <c r="O29">
+        <f>IF(K29=$B$221,L29,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -4003,6 +4102,10 @@
         <f>IF(K30&lt;&gt;"",A30,"")</f>
         <v/>
       </c>
+      <c r="O30">
+        <f>IF(K30=$B$221,L30,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -4053,6 +4156,10 @@
         <f>IF(K31&lt;&gt;"",A31,"")</f>
         <v/>
       </c>
+      <c r="O31">
+        <f>IF(K31=$B$221,L31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -4103,6 +4210,10 @@
         <f>IF(K32&lt;&gt;"",A32,"")</f>
         <v/>
       </c>
+      <c r="O32">
+        <f>IF(K32=$B$221,L32,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -4153,6 +4264,10 @@
         <f>IF(K33&lt;&gt;"",A33,"")</f>
         <v/>
       </c>
+      <c r="O33">
+        <f>IF(K33=$B$221,L33,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -4203,6 +4318,10 @@
         <f>IF(K34&lt;&gt;"",A34,"")</f>
         <v/>
       </c>
+      <c r="O34">
+        <f>IF(K34=$B$221,L34,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -4253,6 +4372,10 @@
         <f>IF(K35&lt;&gt;"",A35,"")</f>
         <v/>
       </c>
+      <c r="O35">
+        <f>IF(K35=$B$221,L35,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -4303,6 +4426,10 @@
         <f>IF(K36&lt;&gt;"",A36,"")</f>
         <v/>
       </c>
+      <c r="O36">
+        <f>IF(K36=$B$221,L36,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -4353,6 +4480,10 @@
         <f>IF(K37&lt;&gt;"",A37,"")</f>
         <v/>
       </c>
+      <c r="O37">
+        <f>IF(K37=$B$221,L37,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -4403,6 +4534,10 @@
         <f>IF(K38&lt;&gt;"",A38,"")</f>
         <v/>
       </c>
+      <c r="O38">
+        <f>IF(K38=$B$221,L38,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -4453,6 +4588,10 @@
         <f>IF(K39&lt;&gt;"",A39,"")</f>
         <v/>
       </c>
+      <c r="O39">
+        <f>IF(K39=$B$221,L39,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -4503,6 +4642,10 @@
         <f>IF(K40&lt;&gt;"",A40,"")</f>
         <v/>
       </c>
+      <c r="O40">
+        <f>IF(K40=$B$221,L40,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -4553,6 +4696,10 @@
         <f>IF(K41&lt;&gt;"",A41,"")</f>
         <v/>
       </c>
+      <c r="O41">
+        <f>IF(K41=$B$221,L41,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -4603,6 +4750,10 @@
         <f>IF(K42&lt;&gt;"",A42,"")</f>
         <v/>
       </c>
+      <c r="O42">
+        <f>IF(K42=$B$221,L42,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -4653,6 +4804,10 @@
         <f>IF(K43&lt;&gt;"",A43,"")</f>
         <v/>
       </c>
+      <c r="O43">
+        <f>IF(K43=$B$221,L43,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -4703,6 +4858,10 @@
         <f>IF(K44&lt;&gt;"",A44,"")</f>
         <v/>
       </c>
+      <c r="O44">
+        <f>IF(K44=$B$221,L44,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -4753,6 +4912,10 @@
         <f>IF(K45&lt;&gt;"",A45,"")</f>
         <v/>
       </c>
+      <c r="O45">
+        <f>IF(K45=$B$221,L45,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -4803,6 +4966,10 @@
         <f>IF(K46&lt;&gt;"",A46,"")</f>
         <v/>
       </c>
+      <c r="O46">
+        <f>IF(K46=$B$221,L46,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -4853,6 +5020,10 @@
         <f>IF(K47&lt;&gt;"",A47,"")</f>
         <v/>
       </c>
+      <c r="O47">
+        <f>IF(K47=$B$221,L47,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -4903,6 +5074,10 @@
         <f>IF(K48&lt;&gt;"",A48,"")</f>
         <v/>
       </c>
+      <c r="O48">
+        <f>IF(K48=$B$221,L48,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -4953,6 +5128,10 @@
         <f>IF(K49&lt;&gt;"",A49,"")</f>
         <v/>
       </c>
+      <c r="O49">
+        <f>IF(K49=$B$221,L49,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -5003,6 +5182,10 @@
         <f>IF(K50&lt;&gt;"",A50,"")</f>
         <v/>
       </c>
+      <c r="O50">
+        <f>IF(K50=$B$221,L50,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -5053,6 +5236,10 @@
         <f>IF(K51&lt;&gt;"",A51,"")</f>
         <v/>
       </c>
+      <c r="O51">
+        <f>IF(K51=$B$221,L51,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -5103,6 +5290,10 @@
         <f>IF(K52&lt;&gt;"",A52,"")</f>
         <v/>
       </c>
+      <c r="O52">
+        <f>IF(K52=$B$221,L52,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -5153,6 +5344,10 @@
         <f>IF(K53&lt;&gt;"",A53,"")</f>
         <v/>
       </c>
+      <c r="O53">
+        <f>IF(K53=$B$221,L53,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -5203,6 +5398,10 @@
         <f>IF(K54&lt;&gt;"",A54,"")</f>
         <v/>
       </c>
+      <c r="O54">
+        <f>IF(K54=$B$221,L54,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -5253,6 +5452,10 @@
         <f>IF(K55&lt;&gt;"",A55,"")</f>
         <v/>
       </c>
+      <c r="O55">
+        <f>IF(K55=$B$221,L55,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -5303,6 +5506,10 @@
         <f>IF(K56&lt;&gt;"",A56,"")</f>
         <v/>
       </c>
+      <c r="O56">
+        <f>IF(K56=$B$221,L56,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -5353,6 +5560,10 @@
         <f>IF(K57&lt;&gt;"",A57,"")</f>
         <v/>
       </c>
+      <c r="O57">
+        <f>IF(K57=$B$221,L57,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -5403,6 +5614,10 @@
         <f>IF(K58&lt;&gt;"",A58,"")</f>
         <v/>
       </c>
+      <c r="O58">
+        <f>IF(K58=$B$221,L58,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -5453,6 +5668,10 @@
         <f>IF(K59&lt;&gt;"",A59,"")</f>
         <v/>
       </c>
+      <c r="O59">
+        <f>IF(K59=$B$221,L59,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -5503,6 +5722,10 @@
         <f>IF(K60&lt;&gt;"",A60,"")</f>
         <v/>
       </c>
+      <c r="O60">
+        <f>IF(K60=$B$221,L60,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -5553,6 +5776,10 @@
         <f>IF(K61&lt;&gt;"",A61,"")</f>
         <v/>
       </c>
+      <c r="O61">
+        <f>IF(K61=$B$221,L61,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -5603,6 +5830,10 @@
         <f>IF(K62&lt;&gt;"",A62,"")</f>
         <v/>
       </c>
+      <c r="O62">
+        <f>IF(K62=$B$221,L62,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -5653,6 +5884,10 @@
         <f>IF(K63&lt;&gt;"",A63,"")</f>
         <v/>
       </c>
+      <c r="O63">
+        <f>IF(K63=$B$221,L63,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -5703,6 +5938,10 @@
         <f>IF(K64&lt;&gt;"",A64,"")</f>
         <v/>
       </c>
+      <c r="O64">
+        <f>IF(K64=$B$221,L64,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -5753,6 +5992,10 @@
         <f>IF(K65&lt;&gt;"",A65,"")</f>
         <v/>
       </c>
+      <c r="O65">
+        <f>IF(K65=$B$221,L65,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -5803,6 +6046,10 @@
         <f>IF(K66&lt;&gt;"",A66,"")</f>
         <v/>
       </c>
+      <c r="O66">
+        <f>IF(K66=$B$221,L66,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -5853,6 +6100,10 @@
         <f>IF(K67&lt;&gt;"",A67,"")</f>
         <v/>
       </c>
+      <c r="O67">
+        <f>IF(K67=$B$221,L67,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -5903,6 +6154,10 @@
         <f>IF(K68&lt;&gt;"",A68,"")</f>
         <v/>
       </c>
+      <c r="O68">
+        <f>IF(K68=$B$221,L68,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -5953,6 +6208,10 @@
         <f>IF(K69&lt;&gt;"",A69,"")</f>
         <v/>
       </c>
+      <c r="O69">
+        <f>IF(K69=$B$221,L69,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -6003,6 +6262,10 @@
         <f>IF(K70&lt;&gt;"",A70,"")</f>
         <v/>
       </c>
+      <c r="O70">
+        <f>IF(K70=$B$221,L70,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -6053,6 +6316,10 @@
         <f>IF(K71&lt;&gt;"",A71,"")</f>
         <v/>
       </c>
+      <c r="O71">
+        <f>IF(K71=$B$221,L71,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -6103,6 +6370,10 @@
         <f>IF(K72&lt;&gt;"",A72,"")</f>
         <v/>
       </c>
+      <c r="O72">
+        <f>IF(K72=$B$221,L72,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -6153,6 +6424,10 @@
         <f>IF(K73&lt;&gt;"",A73,"")</f>
         <v/>
       </c>
+      <c r="O73">
+        <f>IF(K73=$B$221,L73,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -6203,6 +6478,10 @@
         <f>IF(K74&lt;&gt;"",A74,"")</f>
         <v/>
       </c>
+      <c r="O74">
+        <f>IF(K74=$B$221,L74,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -6253,6 +6532,10 @@
         <f>IF(K75&lt;&gt;"",A75,"")</f>
         <v/>
       </c>
+      <c r="O75">
+        <f>IF(K75=$B$221,L75,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -6303,6 +6586,10 @@
         <f>IF(K76&lt;&gt;"",A76,"")</f>
         <v/>
       </c>
+      <c r="O76">
+        <f>IF(K76=$B$221,L76,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -6353,6 +6640,10 @@
         <f>IF(K77&lt;&gt;"",A77,"")</f>
         <v/>
       </c>
+      <c r="O77">
+        <f>IF(K77=$B$221,L77,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -6403,6 +6694,10 @@
         <f>IF(K78&lt;&gt;"",A78,"")</f>
         <v/>
       </c>
+      <c r="O78">
+        <f>IF(K78=$B$221,L78,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -6453,6 +6748,10 @@
         <f>IF(K79&lt;&gt;"",A79,"")</f>
         <v/>
       </c>
+      <c r="O79">
+        <f>IF(K79=$B$221,L79,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -6503,6 +6802,10 @@
         <f>IF(K80&lt;&gt;"",A80,"")</f>
         <v/>
       </c>
+      <c r="O80">
+        <f>IF(K80=$B$221,L80,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -6553,6 +6856,10 @@
         <f>IF(K81&lt;&gt;"",A81,"")</f>
         <v/>
       </c>
+      <c r="O81">
+        <f>IF(K81=$B$221,L81,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -6603,6 +6910,10 @@
         <f>IF(K82&lt;&gt;"",A82,"")</f>
         <v/>
       </c>
+      <c r="O82">
+        <f>IF(K82=$B$221,L82,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -6653,6 +6964,10 @@
         <f>IF(K83&lt;&gt;"",A83,"")</f>
         <v/>
       </c>
+      <c r="O83">
+        <f>IF(K83=$B$221,L83,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -6703,6 +7018,10 @@
         <f>IF(K84&lt;&gt;"",A84,"")</f>
         <v/>
       </c>
+      <c r="O84">
+        <f>IF(K84=$B$221,L84,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -6753,6 +7072,10 @@
         <f>IF(K85&lt;&gt;"",A85,"")</f>
         <v/>
       </c>
+      <c r="O85">
+        <f>IF(K85=$B$221,L85,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -6803,6 +7126,10 @@
         <f>IF(K86&lt;&gt;"",A86,"")</f>
         <v/>
       </c>
+      <c r="O86">
+        <f>IF(K86=$B$221,L86,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -6853,6 +7180,10 @@
         <f>IF(K87&lt;&gt;"",A87,"")</f>
         <v/>
       </c>
+      <c r="O87">
+        <f>IF(K87=$B$221,L87,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -6903,6 +7234,10 @@
         <f>IF(K88&lt;&gt;"",A88,"")</f>
         <v/>
       </c>
+      <c r="O88">
+        <f>IF(K88=$B$221,L88,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -6953,6 +7288,10 @@
         <f>IF(K89&lt;&gt;"",A89,"")</f>
         <v/>
       </c>
+      <c r="O89">
+        <f>IF(K89=$B$221,L89,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -7003,6 +7342,10 @@
         <f>IF(K90&lt;&gt;"",A90,"")</f>
         <v/>
       </c>
+      <c r="O90">
+        <f>IF(K90=$B$221,L90,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -7053,6 +7396,10 @@
         <f>IF(K91&lt;&gt;"",A91,"")</f>
         <v/>
       </c>
+      <c r="O91">
+        <f>IF(K91=$B$221,L91,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -7103,6 +7450,10 @@
         <f>IF(K92&lt;&gt;"",A92,"")</f>
         <v/>
       </c>
+      <c r="O92">
+        <f>IF(K92=$B$221,L92,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -7153,6 +7504,10 @@
         <f>IF(K93&lt;&gt;"",A93,"")</f>
         <v/>
       </c>
+      <c r="O93">
+        <f>IF(K93=$B$221,L93,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -7203,6 +7558,10 @@
         <f>IF(K94&lt;&gt;"",A94,"")</f>
         <v/>
       </c>
+      <c r="O94">
+        <f>IF(K94=$B$221,L94,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -7253,6 +7612,10 @@
         <f>IF(K95&lt;&gt;"",A95,"")</f>
         <v/>
       </c>
+      <c r="O95">
+        <f>IF(K95=$B$221,L95,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -7303,6 +7666,10 @@
         <f>IF(K96&lt;&gt;"",A96,"")</f>
         <v/>
       </c>
+      <c r="O96">
+        <f>IF(K96=$B$221,L96,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -7353,6 +7720,10 @@
         <f>IF(K97&lt;&gt;"",A97,"")</f>
         <v/>
       </c>
+      <c r="O97">
+        <f>IF(K97=$B$221,L97,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -7403,6 +7774,10 @@
         <f>IF(K98&lt;&gt;"",A98,"")</f>
         <v/>
       </c>
+      <c r="O98">
+        <f>IF(K98=$B$221,L98,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -7453,6 +7828,10 @@
         <f>IF(K99&lt;&gt;"",A99,"")</f>
         <v/>
       </c>
+      <c r="O99">
+        <f>IF(K99=$B$221,L99,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -7503,6 +7882,10 @@
         <f>IF(K100&lt;&gt;"",A100,"")</f>
         <v/>
       </c>
+      <c r="O100">
+        <f>IF(K100=$B$221,L100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -7553,6 +7936,10 @@
         <f>IF(K101&lt;&gt;"",A101,"")</f>
         <v/>
       </c>
+      <c r="O101">
+        <f>IF(K101=$B$221,L101,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -7603,6 +7990,10 @@
         <f>IF(K102&lt;&gt;"",A102,"")</f>
         <v/>
       </c>
+      <c r="O102">
+        <f>IF(K102=$B$221,L102,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -7653,6 +8044,10 @@
         <f>IF(K103&lt;&gt;"",A103,"")</f>
         <v/>
       </c>
+      <c r="O103">
+        <f>IF(K103=$B$221,L103,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -7703,6 +8098,10 @@
         <f>IF(K104&lt;&gt;"",A104,"")</f>
         <v/>
       </c>
+      <c r="O104">
+        <f>IF(K104=$B$221,L104,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -7753,6 +8152,10 @@
         <f>IF(K105&lt;&gt;"",A105,"")</f>
         <v/>
       </c>
+      <c r="O105">
+        <f>IF(K105=$B$221,L105,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -7803,6 +8206,10 @@
         <f>IF(K106&lt;&gt;"",A106,"")</f>
         <v/>
       </c>
+      <c r="O106">
+        <f>IF(K106=$B$221,L106,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -7853,6 +8260,10 @@
         <f>IF(K107&lt;&gt;"",A107,"")</f>
         <v/>
       </c>
+      <c r="O107">
+        <f>IF(K107=$B$221,L107,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -7903,6 +8314,10 @@
         <f>IF(K108&lt;&gt;"",A108,"")</f>
         <v/>
       </c>
+      <c r="O108">
+        <f>IF(K108=$B$221,L108,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -7953,6 +8368,10 @@
         <f>IF(K109&lt;&gt;"",A109,"")</f>
         <v/>
       </c>
+      <c r="O109">
+        <f>IF(K109=$B$221,L109,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -8003,6 +8422,10 @@
         <f>IF(K110&lt;&gt;"",A110,"")</f>
         <v/>
       </c>
+      <c r="O110">
+        <f>IF(K110=$B$221,L110,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -8053,6 +8476,10 @@
         <f>IF(K111&lt;&gt;"",A111,"")</f>
         <v/>
       </c>
+      <c r="O111">
+        <f>IF(K111=$B$221,L111,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -8103,6 +8530,10 @@
         <f>IF(K112&lt;&gt;"",A112,"")</f>
         <v/>
       </c>
+      <c r="O112">
+        <f>IF(K112=$B$221,L112,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -8153,6 +8584,10 @@
         <f>IF(K113&lt;&gt;"",A113,"")</f>
         <v/>
       </c>
+      <c r="O113">
+        <f>IF(K113=$B$221,L113,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -8203,6 +8638,10 @@
         <f>IF(K114&lt;&gt;"",A114,"")</f>
         <v/>
       </c>
+      <c r="O114">
+        <f>IF(K114=$B$221,L114,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -8253,6 +8692,10 @@
         <f>IF(K115&lt;&gt;"",A115,"")</f>
         <v/>
       </c>
+      <c r="O115">
+        <f>IF(K115=$B$221,L115,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -8303,6 +8746,10 @@
         <f>IF(K116&lt;&gt;"",A116,"")</f>
         <v/>
       </c>
+      <c r="O116">
+        <f>IF(K116=$B$221,L116,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -8353,6 +8800,10 @@
         <f>IF(K117&lt;&gt;"",A117,"")</f>
         <v/>
       </c>
+      <c r="O117">
+        <f>IF(K117=$B$221,L117,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -8403,6 +8854,10 @@
         <f>IF(K118&lt;&gt;"",A118,"")</f>
         <v/>
       </c>
+      <c r="O118">
+        <f>IF(K118=$B$221,L118,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -8453,6 +8908,10 @@
         <f>IF(K119&lt;&gt;"",A119,"")</f>
         <v/>
       </c>
+      <c r="O119">
+        <f>IF(K119=$B$221,L119,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -8503,6 +8962,10 @@
         <f>IF(K120&lt;&gt;"",A120,"")</f>
         <v/>
       </c>
+      <c r="O120">
+        <f>IF(K120=$B$221,L120,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -8553,6 +9016,10 @@
         <f>IF(K121&lt;&gt;"",A121,"")</f>
         <v/>
       </c>
+      <c r="O121">
+        <f>IF(K121=$B$221,L121,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -8603,6 +9070,10 @@
         <f>IF(K122&lt;&gt;"",A122,"")</f>
         <v/>
       </c>
+      <c r="O122">
+        <f>IF(K122=$B$221,L122,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -8653,6 +9124,10 @@
         <f>IF(K123&lt;&gt;"",A123,"")</f>
         <v/>
       </c>
+      <c r="O123">
+        <f>IF(K123=$B$221,L123,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -8703,6 +9178,10 @@
         <f>IF(K124&lt;&gt;"",A124,"")</f>
         <v/>
       </c>
+      <c r="O124">
+        <f>IF(K124=$B$221,L124,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -8753,6 +9232,10 @@
         <f>IF(K125&lt;&gt;"",A125,"")</f>
         <v/>
       </c>
+      <c r="O125">
+        <f>IF(K125=$B$221,L125,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -8803,6 +9286,10 @@
         <f>IF(K126&lt;&gt;"",A126,"")</f>
         <v/>
       </c>
+      <c r="O126">
+        <f>IF(K126=$B$221,L126,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -8853,6 +9340,10 @@
         <f>IF(K127&lt;&gt;"",A127,"")</f>
         <v/>
       </c>
+      <c r="O127">
+        <f>IF(K127=$B$221,L127,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -8903,6 +9394,10 @@
         <f>IF(K128&lt;&gt;"",A128,"")</f>
         <v/>
       </c>
+      <c r="O128">
+        <f>IF(K128=$B$221,L128,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -8953,6 +9448,10 @@
         <f>IF(K129&lt;&gt;"",A129,"")</f>
         <v/>
       </c>
+      <c r="O129">
+        <f>IF(K129=$B$221,L129,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -9003,6 +9502,10 @@
         <f>IF(K130&lt;&gt;"",A130,"")</f>
         <v/>
       </c>
+      <c r="O130">
+        <f>IF(K130=$B$221,L130,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -9053,6 +9556,10 @@
         <f>IF(K131&lt;&gt;"",A131,"")</f>
         <v/>
       </c>
+      <c r="O131">
+        <f>IF(K131=$B$221,L131,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -9103,6 +9610,10 @@
         <f>IF(K132&lt;&gt;"",A132,"")</f>
         <v/>
       </c>
+      <c r="O132">
+        <f>IF(K132=$B$221,L132,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -9153,6 +9664,10 @@
         <f>IF(K133&lt;&gt;"",A133,"")</f>
         <v/>
       </c>
+      <c r="O133">
+        <f>IF(K133=$B$221,L133,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -9203,6 +9718,10 @@
         <f>IF(K134&lt;&gt;"",A134,"")</f>
         <v/>
       </c>
+      <c r="O134">
+        <f>IF(K134=$B$221,L134,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -9253,6 +9772,10 @@
         <f>IF(K135&lt;&gt;"",A135,"")</f>
         <v/>
       </c>
+      <c r="O135">
+        <f>IF(K135=$B$221,L135,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -9303,6 +9826,10 @@
         <f>IF(K136&lt;&gt;"",A136,"")</f>
         <v/>
       </c>
+      <c r="O136">
+        <f>IF(K136=$B$221,L136,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -9353,6 +9880,10 @@
         <f>IF(K137&lt;&gt;"",A137,"")</f>
         <v/>
       </c>
+      <c r="O137">
+        <f>IF(K137=$B$221,L137,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -9403,6 +9934,10 @@
         <f>IF(K138&lt;&gt;"",A138,"")</f>
         <v/>
       </c>
+      <c r="O138">
+        <f>IF(K138=$B$221,L138,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -9453,6 +9988,10 @@
         <f>IF(K139&lt;&gt;"",A139,"")</f>
         <v/>
       </c>
+      <c r="O139">
+        <f>IF(K139=$B$221,L139,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -9503,6 +10042,10 @@
         <f>IF(K140&lt;&gt;"",A140,"")</f>
         <v/>
       </c>
+      <c r="O140">
+        <f>IF(K140=$B$221,L140,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -9553,6 +10096,10 @@
         <f>IF(K141&lt;&gt;"",A141,"")</f>
         <v/>
       </c>
+      <c r="O141">
+        <f>IF(K141=$B$221,L141,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -9603,6 +10150,10 @@
         <f>IF(K142&lt;&gt;"",A142,"")</f>
         <v/>
       </c>
+      <c r="O142">
+        <f>IF(K142=$B$221,L142,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -9653,6 +10204,10 @@
         <f>IF(K143&lt;&gt;"",A143,"")</f>
         <v/>
       </c>
+      <c r="O143">
+        <f>IF(K143=$B$221,L143,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -9703,6 +10258,10 @@
         <f>IF(K144&lt;&gt;"",A144,"")</f>
         <v/>
       </c>
+      <c r="O144">
+        <f>IF(K144=$B$221,L144,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -9753,6 +10312,10 @@
         <f>IF(K145&lt;&gt;"",A145,"")</f>
         <v/>
       </c>
+      <c r="O145">
+        <f>IF(K145=$B$221,L145,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -9803,6 +10366,10 @@
         <f>IF(K146&lt;&gt;"",A146,"")</f>
         <v/>
       </c>
+      <c r="O146">
+        <f>IF(K146=$B$221,L146,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -9853,6 +10420,10 @@
         <f>IF(K147&lt;&gt;"",A147,"")</f>
         <v/>
       </c>
+      <c r="O147">
+        <f>IF(K147=$B$221,L147,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -9903,6 +10474,10 @@
         <f>IF(K148&lt;&gt;"",A148,"")</f>
         <v/>
       </c>
+      <c r="O148">
+        <f>IF(K148=$B$221,L148,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -9953,6 +10528,10 @@
         <f>IF(K149&lt;&gt;"",A149,"")</f>
         <v/>
       </c>
+      <c r="O149">
+        <f>IF(K149=$B$221,L149,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -10003,6 +10582,10 @@
         <f>IF(K150&lt;&gt;"",A150,"")</f>
         <v/>
       </c>
+      <c r="O150">
+        <f>IF(K150=$B$221,L150,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -10053,6 +10636,10 @@
         <f>IF(K151&lt;&gt;"",A151,"")</f>
         <v/>
       </c>
+      <c r="O151">
+        <f>IF(K151=$B$221,L151,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -10103,6 +10690,10 @@
         <f>IF(K152&lt;&gt;"",A152,"")</f>
         <v/>
       </c>
+      <c r="O152">
+        <f>IF(K152=$B$221,L152,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -10153,6 +10744,10 @@
         <f>IF(K153&lt;&gt;"",A153,"")</f>
         <v/>
       </c>
+      <c r="O153">
+        <f>IF(K153=$B$221,L153,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -10203,6 +10798,10 @@
         <f>IF(K154&lt;&gt;"",A154,"")</f>
         <v/>
       </c>
+      <c r="O154">
+        <f>IF(K154=$B$221,L154,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -10253,6 +10852,10 @@
         <f>IF(K155&lt;&gt;"",A155,"")</f>
         <v/>
       </c>
+      <c r="O155">
+        <f>IF(K155=$B$221,L155,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -10303,6 +10906,10 @@
         <f>IF(K156&lt;&gt;"",A156,"")</f>
         <v/>
       </c>
+      <c r="O156">
+        <f>IF(K156=$B$221,L156,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -10353,6 +10960,10 @@
         <f>IF(K157&lt;&gt;"",A157,"")</f>
         <v/>
       </c>
+      <c r="O157">
+        <f>IF(K157=$B$221,L157,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -10403,6 +11014,10 @@
         <f>IF(K158&lt;&gt;"",A158,"")</f>
         <v/>
       </c>
+      <c r="O158">
+        <f>IF(K158=$B$221,L158,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -10453,6 +11068,10 @@
         <f>IF(K159&lt;&gt;"",A159,"")</f>
         <v/>
       </c>
+      <c r="O159">
+        <f>IF(K159=$B$221,L159,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -10503,6 +11122,10 @@
         <f>IF(K160&lt;&gt;"",A160,"")</f>
         <v/>
       </c>
+      <c r="O160">
+        <f>IF(K160=$B$221,L160,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -10553,6 +11176,10 @@
         <f>IF(K161&lt;&gt;"",A161,"")</f>
         <v/>
       </c>
+      <c r="O161">
+        <f>IF(K161=$B$221,L161,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -10603,6 +11230,10 @@
         <f>IF(K162&lt;&gt;"",A162,"")</f>
         <v/>
       </c>
+      <c r="O162">
+        <f>IF(K162=$B$221,L162,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -10653,6 +11284,10 @@
         <f>IF(K163&lt;&gt;"",A163,"")</f>
         <v/>
       </c>
+      <c r="O163">
+        <f>IF(K163=$B$221,L163,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -10703,6 +11338,10 @@
         <f>IF(K164&lt;&gt;"",A164,"")</f>
         <v/>
       </c>
+      <c r="O164">
+        <f>IF(K164=$B$221,L164,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -10753,6 +11392,10 @@
         <f>IF(K165&lt;&gt;"",A165,"")</f>
         <v/>
       </c>
+      <c r="O165">
+        <f>IF(K165=$B$221,L165,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -10803,6 +11446,10 @@
         <f>IF(K166&lt;&gt;"",A166,"")</f>
         <v/>
       </c>
+      <c r="O166">
+        <f>IF(K166=$B$221,L166,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -10853,6 +11500,10 @@
         <f>IF(K167&lt;&gt;"",A167,"")</f>
         <v/>
       </c>
+      <c r="O167">
+        <f>IF(K167=$B$221,L167,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -10903,6 +11554,10 @@
         <f>IF(K168&lt;&gt;"",A168,"")</f>
         <v/>
       </c>
+      <c r="O168">
+        <f>IF(K168=$B$221,L168,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -10953,6 +11608,10 @@
         <f>IF(K169&lt;&gt;"",A169,"")</f>
         <v/>
       </c>
+      <c r="O169">
+        <f>IF(K169=$B$221,L169,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -11003,6 +11662,10 @@
         <f>IF(K170&lt;&gt;"",A170,"")</f>
         <v/>
       </c>
+      <c r="O170">
+        <f>IF(K170=$B$221,L170,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -11053,6 +11716,10 @@
         <f>IF(K171&lt;&gt;"",A171,"")</f>
         <v/>
       </c>
+      <c r="O171">
+        <f>IF(K171=$B$221,L171,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -11103,6 +11770,10 @@
         <f>IF(K172&lt;&gt;"",A172,"")</f>
         <v/>
       </c>
+      <c r="O172">
+        <f>IF(K172=$B$221,L172,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -11153,6 +11824,10 @@
         <f>IF(K173&lt;&gt;"",A173,"")</f>
         <v/>
       </c>
+      <c r="O173">
+        <f>IF(K173=$B$221,L173,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -11203,6 +11878,10 @@
         <f>IF(K174&lt;&gt;"",A174,"")</f>
         <v/>
       </c>
+      <c r="O174">
+        <f>IF(K174=$B$221,L174,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -11253,6 +11932,10 @@
         <f>IF(K175&lt;&gt;"",A175,"")</f>
         <v/>
       </c>
+      <c r="O175">
+        <f>IF(K175=$B$221,L175,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -11303,6 +11986,10 @@
         <f>IF(K176&lt;&gt;"",A176,"")</f>
         <v/>
       </c>
+      <c r="O176">
+        <f>IF(K176=$B$221,L176,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -11353,6 +12040,10 @@
         <f>IF(K177&lt;&gt;"",A177,"")</f>
         <v/>
       </c>
+      <c r="O177">
+        <f>IF(K177=$B$221,L177,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -11403,6 +12094,10 @@
         <f>IF(K178&lt;&gt;"",A178,"")</f>
         <v/>
       </c>
+      <c r="O178">
+        <f>IF(K178=$B$221,L178,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -11453,6 +12148,10 @@
         <f>IF(K179&lt;&gt;"",A179,"")</f>
         <v/>
       </c>
+      <c r="O179">
+        <f>IF(K179=$B$221,L179,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -11503,6 +12202,10 @@
         <f>IF(K180&lt;&gt;"",A180,"")</f>
         <v/>
       </c>
+      <c r="O180">
+        <f>IF(K180=$B$221,L180,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -11553,6 +12256,10 @@
         <f>IF(K181&lt;&gt;"",A181,"")</f>
         <v/>
       </c>
+      <c r="O181">
+        <f>IF(K181=$B$221,L181,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -11603,6 +12310,10 @@
         <f>IF(K182&lt;&gt;"",A182,"")</f>
         <v/>
       </c>
+      <c r="O182">
+        <f>IF(K182=$B$221,L182,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -11653,6 +12364,10 @@
         <f>IF(K183&lt;&gt;"",A183,"")</f>
         <v/>
       </c>
+      <c r="O183">
+        <f>IF(K183=$B$221,L183,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -11703,6 +12418,10 @@
         <f>IF(K184&lt;&gt;"",A184,"")</f>
         <v/>
       </c>
+      <c r="O184">
+        <f>IF(K184=$B$221,L184,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -11753,6 +12472,10 @@
         <f>IF(K185&lt;&gt;"",A185,"")</f>
         <v/>
       </c>
+      <c r="O185">
+        <f>IF(K185=$B$221,L185,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -11803,6 +12526,10 @@
         <f>IF(K186&lt;&gt;"",A186,"")</f>
         <v/>
       </c>
+      <c r="O186">
+        <f>IF(K186=$B$221,L186,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -11853,6 +12580,10 @@
         <f>IF(K187&lt;&gt;"",A187,"")</f>
         <v/>
       </c>
+      <c r="O187">
+        <f>IF(K187=$B$221,L187,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -11903,6 +12634,10 @@
         <f>IF(K188&lt;&gt;"",A188,"")</f>
         <v/>
       </c>
+      <c r="O188">
+        <f>IF(K188=$B$221,L188,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -11953,6 +12688,10 @@
         <f>IF(K189&lt;&gt;"",A189,"")</f>
         <v/>
       </c>
+      <c r="O189">
+        <f>IF(K189=$B$221,L189,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -12003,6 +12742,10 @@
         <f>IF(K190&lt;&gt;"",A190,"")</f>
         <v/>
       </c>
+      <c r="O190">
+        <f>IF(K190=$B$221,L190,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -12053,6 +12796,10 @@
         <f>IF(K191&lt;&gt;"",A191,"")</f>
         <v/>
       </c>
+      <c r="O191">
+        <f>IF(K191=$B$221,L191,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -12103,6 +12850,10 @@
         <f>IF(K192&lt;&gt;"",A192,"")</f>
         <v/>
       </c>
+      <c r="O192">
+        <f>IF(K192=$B$221,L192,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -12153,6 +12904,10 @@
         <f>IF(K193&lt;&gt;"",A193,"")</f>
         <v/>
       </c>
+      <c r="O193">
+        <f>IF(K193=$B$221,L193,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -12203,6 +12958,10 @@
         <f>IF(K194&lt;&gt;"",A194,"")</f>
         <v/>
       </c>
+      <c r="O194">
+        <f>IF(K194=$B$221,L194,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -12253,6 +13012,10 @@
         <f>IF(K195&lt;&gt;"",A195,"")</f>
         <v/>
       </c>
+      <c r="O195">
+        <f>IF(K195=$B$221,L195,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -12303,6 +13066,10 @@
         <f>IF(K196&lt;&gt;"",A196,"")</f>
         <v/>
       </c>
+      <c r="O196">
+        <f>IF(K196=$B$221,L196,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -12353,6 +13120,10 @@
         <f>IF(K197&lt;&gt;"",A197,"")</f>
         <v/>
       </c>
+      <c r="O197">
+        <f>IF(K197=$B$221,L197,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -12403,6 +13174,10 @@
         <f>IF(K198&lt;&gt;"",A198,"")</f>
         <v/>
       </c>
+      <c r="O198">
+        <f>IF(K198=$B$221,L198,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -12453,6 +13228,10 @@
         <f>IF(K199&lt;&gt;"",A199,"")</f>
         <v/>
       </c>
+      <c r="O199">
+        <f>IF(K199=$B$221,L199,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -12503,6 +13282,10 @@
         <f>IF(K200&lt;&gt;"",A200,"")</f>
         <v/>
       </c>
+      <c r="O200">
+        <f>IF(K200=$B$221,L200,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -12553,6 +13336,10 @@
         <f>IF(K201&lt;&gt;"",A201,"")</f>
         <v/>
       </c>
+      <c r="O201">
+        <f>IF(K201=$B$221,L201,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -12603,6 +13390,10 @@
         <f>IF(K202&lt;&gt;"",A202,"")</f>
         <v/>
       </c>
+      <c r="O202">
+        <f>IF(K202=$B$221,L202,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -12653,6 +13444,10 @@
         <f>IF(K203&lt;&gt;"",A203,"")</f>
         <v/>
       </c>
+      <c r="O203">
+        <f>IF(K203=$B$221,L203,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -12703,6 +13498,10 @@
         <f>IF(K204&lt;&gt;"",A204,"")</f>
         <v/>
       </c>
+      <c r="O204">
+        <f>IF(K204=$B$221,L204,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -12753,6 +13552,10 @@
         <f>IF(K205&lt;&gt;"",A205,"")</f>
         <v/>
       </c>
+      <c r="O205">
+        <f>IF(K205=$B$221,L205,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -12803,6 +13606,10 @@
         <f>IF(K206&lt;&gt;"",A206,"")</f>
         <v/>
       </c>
+      <c r="O206">
+        <f>IF(K206=$B$221,L206,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -12853,6 +13660,10 @@
         <f>IF(K207&lt;&gt;"",A207,"")</f>
         <v/>
       </c>
+      <c r="O207">
+        <f>IF(K207=$B$221,L207,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -12903,6 +13714,10 @@
         <f>IF(K208&lt;&gt;"",A208,"")</f>
         <v/>
       </c>
+      <c r="O208">
+        <f>IF(K208=$B$221,L208,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -12953,6 +13768,10 @@
         <f>IF(K209&lt;&gt;"",A209,"")</f>
         <v/>
       </c>
+      <c r="O209">
+        <f>IF(K209=$B$221,L209,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -13003,6 +13822,10 @@
         <f>IF(K210&lt;&gt;"",A210,"")</f>
         <v/>
       </c>
+      <c r="O210">
+        <f>IF(K210=$B$221,L210,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -13053,6 +13876,10 @@
         <f>IF(K211&lt;&gt;"",A211,"")</f>
         <v/>
       </c>
+      <c r="O211">
+        <f>IF(K211=$B$221,L211,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13084,7 +13911,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IF(B221=0,"N/A",MINIFS(L12:L211,K12:K211,B221))</f>
+        <f>IF(B221=0,"N/A",MIN(O12:O211))</f>
         <v/>
       </c>
     </row>
@@ -13132,7 +13959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N225"/>
+  <dimension ref="A1:O225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13437,6 +14264,10 @@
         <f>IF(N3=0,"Уровень не рассчитан",N3-4*Settings!$B$5*Settings!$B$3)</f>
         <v/>
       </c>
+      <c r="O12">
+        <f>IF(K12=$B$221,L12,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -13487,6 +14318,10 @@
         <f>IF(K13&lt;&gt;"",A13,"")</f>
         <v/>
       </c>
+      <c r="O13">
+        <f>IF(K13=$B$221,L13,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -13537,6 +14372,10 @@
         <f>IF(K14&lt;&gt;"",A14,"")</f>
         <v/>
       </c>
+      <c r="O14">
+        <f>IF(K14=$B$221,L14,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -13587,6 +14426,10 @@
         <f>IF(K15&lt;&gt;"",A15,"")</f>
         <v/>
       </c>
+      <c r="O15">
+        <f>IF(K15=$B$221,L15,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -13637,6 +14480,10 @@
         <f>IF(K16&lt;&gt;"",A16,"")</f>
         <v/>
       </c>
+      <c r="O16">
+        <f>IF(K16=$B$221,L16,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -13687,6 +14534,10 @@
         <f>IF(K17&lt;&gt;"",A17,"")</f>
         <v/>
       </c>
+      <c r="O17">
+        <f>IF(K17=$B$221,L17,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -13737,6 +14588,10 @@
         <f>IF(K18&lt;&gt;"",A18,"")</f>
         <v/>
       </c>
+      <c r="O18">
+        <f>IF(K18=$B$221,L18,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -13787,6 +14642,10 @@
         <f>IF(K19&lt;&gt;"",A19,"")</f>
         <v/>
       </c>
+      <c r="O19">
+        <f>IF(K19=$B$221,L19,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -13837,6 +14696,10 @@
         <f>IF(K20&lt;&gt;"",A20,"")</f>
         <v/>
       </c>
+      <c r="O20">
+        <f>IF(K20=$B$221,L20,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -13887,6 +14750,10 @@
         <f>IF(K21&lt;&gt;"",A21,"")</f>
         <v/>
       </c>
+      <c r="O21">
+        <f>IF(K21=$B$221,L21,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -13937,6 +14804,10 @@
         <f>IF(K22&lt;&gt;"",A22,"")</f>
         <v/>
       </c>
+      <c r="O22">
+        <f>IF(K22=$B$221,L22,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -13987,6 +14858,10 @@
         <f>IF(K23&lt;&gt;"",A23,"")</f>
         <v/>
       </c>
+      <c r="O23">
+        <f>IF(K23=$B$221,L23,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -14037,6 +14912,10 @@
         <f>IF(K24&lt;&gt;"",A24,"")</f>
         <v/>
       </c>
+      <c r="O24">
+        <f>IF(K24=$B$221,L24,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -14087,6 +14966,10 @@
         <f>IF(K25&lt;&gt;"",A25,"")</f>
         <v/>
       </c>
+      <c r="O25">
+        <f>IF(K25=$B$221,L25,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -14137,6 +15020,10 @@
         <f>IF(K26&lt;&gt;"",A26,"")</f>
         <v/>
       </c>
+      <c r="O26">
+        <f>IF(K26=$B$221,L26,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -14187,6 +15074,10 @@
         <f>IF(K27&lt;&gt;"",A27,"")</f>
         <v/>
       </c>
+      <c r="O27">
+        <f>IF(K27=$B$221,L27,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -14237,6 +15128,10 @@
         <f>IF(K28&lt;&gt;"",A28,"")</f>
         <v/>
       </c>
+      <c r="O28">
+        <f>IF(K28=$B$221,L28,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -14287,6 +15182,10 @@
         <f>IF(K29&lt;&gt;"",A29,"")</f>
         <v/>
       </c>
+      <c r="O29">
+        <f>IF(K29=$B$221,L29,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -14337,6 +15236,10 @@
         <f>IF(K30&lt;&gt;"",A30,"")</f>
         <v/>
       </c>
+      <c r="O30">
+        <f>IF(K30=$B$221,L30,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -14387,6 +15290,10 @@
         <f>IF(K31&lt;&gt;"",A31,"")</f>
         <v/>
       </c>
+      <c r="O31">
+        <f>IF(K31=$B$221,L31,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -14437,6 +15344,10 @@
         <f>IF(K32&lt;&gt;"",A32,"")</f>
         <v/>
       </c>
+      <c r="O32">
+        <f>IF(K32=$B$221,L32,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -14487,6 +15398,10 @@
         <f>IF(K33&lt;&gt;"",A33,"")</f>
         <v/>
       </c>
+      <c r="O33">
+        <f>IF(K33=$B$221,L33,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -14537,6 +15452,10 @@
         <f>IF(K34&lt;&gt;"",A34,"")</f>
         <v/>
       </c>
+      <c r="O34">
+        <f>IF(K34=$B$221,L34,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -14587,6 +15506,10 @@
         <f>IF(K35&lt;&gt;"",A35,"")</f>
         <v/>
       </c>
+      <c r="O35">
+        <f>IF(K35=$B$221,L35,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -14637,6 +15560,10 @@
         <f>IF(K36&lt;&gt;"",A36,"")</f>
         <v/>
       </c>
+      <c r="O36">
+        <f>IF(K36=$B$221,L36,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -14687,6 +15614,10 @@
         <f>IF(K37&lt;&gt;"",A37,"")</f>
         <v/>
       </c>
+      <c r="O37">
+        <f>IF(K37=$B$221,L37,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -14737,6 +15668,10 @@
         <f>IF(K38&lt;&gt;"",A38,"")</f>
         <v/>
       </c>
+      <c r="O38">
+        <f>IF(K38=$B$221,L38,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -14787,6 +15722,10 @@
         <f>IF(K39&lt;&gt;"",A39,"")</f>
         <v/>
       </c>
+      <c r="O39">
+        <f>IF(K39=$B$221,L39,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -14837,6 +15776,10 @@
         <f>IF(K40&lt;&gt;"",A40,"")</f>
         <v/>
       </c>
+      <c r="O40">
+        <f>IF(K40=$B$221,L40,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -14887,6 +15830,10 @@
         <f>IF(K41&lt;&gt;"",A41,"")</f>
         <v/>
       </c>
+      <c r="O41">
+        <f>IF(K41=$B$221,L41,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -14937,6 +15884,10 @@
         <f>IF(K42&lt;&gt;"",A42,"")</f>
         <v/>
       </c>
+      <c r="O42">
+        <f>IF(K42=$B$221,L42,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -14987,6 +15938,10 @@
         <f>IF(K43&lt;&gt;"",A43,"")</f>
         <v/>
       </c>
+      <c r="O43">
+        <f>IF(K43=$B$221,L43,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -15037,6 +15992,10 @@
         <f>IF(K44&lt;&gt;"",A44,"")</f>
         <v/>
       </c>
+      <c r="O44">
+        <f>IF(K44=$B$221,L44,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -15087,6 +16046,10 @@
         <f>IF(K45&lt;&gt;"",A45,"")</f>
         <v/>
       </c>
+      <c r="O45">
+        <f>IF(K45=$B$221,L45,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -15137,6 +16100,10 @@
         <f>IF(K46&lt;&gt;"",A46,"")</f>
         <v/>
       </c>
+      <c r="O46">
+        <f>IF(K46=$B$221,L46,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -15187,6 +16154,10 @@
         <f>IF(K47&lt;&gt;"",A47,"")</f>
         <v/>
       </c>
+      <c r="O47">
+        <f>IF(K47=$B$221,L47,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -15237,6 +16208,10 @@
         <f>IF(K48&lt;&gt;"",A48,"")</f>
         <v/>
       </c>
+      <c r="O48">
+        <f>IF(K48=$B$221,L48,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -15287,6 +16262,10 @@
         <f>IF(K49&lt;&gt;"",A49,"")</f>
         <v/>
       </c>
+      <c r="O49">
+        <f>IF(K49=$B$221,L49,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -15337,6 +16316,10 @@
         <f>IF(K50&lt;&gt;"",A50,"")</f>
         <v/>
       </c>
+      <c r="O50">
+        <f>IF(K50=$B$221,L50,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -15387,6 +16370,10 @@
         <f>IF(K51&lt;&gt;"",A51,"")</f>
         <v/>
       </c>
+      <c r="O51">
+        <f>IF(K51=$B$221,L51,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -15437,6 +16424,10 @@
         <f>IF(K52&lt;&gt;"",A52,"")</f>
         <v/>
       </c>
+      <c r="O52">
+        <f>IF(K52=$B$221,L52,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -15487,6 +16478,10 @@
         <f>IF(K53&lt;&gt;"",A53,"")</f>
         <v/>
       </c>
+      <c r="O53">
+        <f>IF(K53=$B$221,L53,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -15537,6 +16532,10 @@
         <f>IF(K54&lt;&gt;"",A54,"")</f>
         <v/>
       </c>
+      <c r="O54">
+        <f>IF(K54=$B$221,L54,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -15587,6 +16586,10 @@
         <f>IF(K55&lt;&gt;"",A55,"")</f>
         <v/>
       </c>
+      <c r="O55">
+        <f>IF(K55=$B$221,L55,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -15637,6 +16640,10 @@
         <f>IF(K56&lt;&gt;"",A56,"")</f>
         <v/>
       </c>
+      <c r="O56">
+        <f>IF(K56=$B$221,L56,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -15687,6 +16694,10 @@
         <f>IF(K57&lt;&gt;"",A57,"")</f>
         <v/>
       </c>
+      <c r="O57">
+        <f>IF(K57=$B$221,L57,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -15737,6 +16748,10 @@
         <f>IF(K58&lt;&gt;"",A58,"")</f>
         <v/>
       </c>
+      <c r="O58">
+        <f>IF(K58=$B$221,L58,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -15787,6 +16802,10 @@
         <f>IF(K59&lt;&gt;"",A59,"")</f>
         <v/>
       </c>
+      <c r="O59">
+        <f>IF(K59=$B$221,L59,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -15837,6 +16856,10 @@
         <f>IF(K60&lt;&gt;"",A60,"")</f>
         <v/>
       </c>
+      <c r="O60">
+        <f>IF(K60=$B$221,L60,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -15887,6 +16910,10 @@
         <f>IF(K61&lt;&gt;"",A61,"")</f>
         <v/>
       </c>
+      <c r="O61">
+        <f>IF(K61=$B$221,L61,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -15937,6 +16964,10 @@
         <f>IF(K62&lt;&gt;"",A62,"")</f>
         <v/>
       </c>
+      <c r="O62">
+        <f>IF(K62=$B$221,L62,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -15987,6 +17018,10 @@
         <f>IF(K63&lt;&gt;"",A63,"")</f>
         <v/>
       </c>
+      <c r="O63">
+        <f>IF(K63=$B$221,L63,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -16037,6 +17072,10 @@
         <f>IF(K64&lt;&gt;"",A64,"")</f>
         <v/>
       </c>
+      <c r="O64">
+        <f>IF(K64=$B$221,L64,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -16087,6 +17126,10 @@
         <f>IF(K65&lt;&gt;"",A65,"")</f>
         <v/>
       </c>
+      <c r="O65">
+        <f>IF(K65=$B$221,L65,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -16137,6 +17180,10 @@
         <f>IF(K66&lt;&gt;"",A66,"")</f>
         <v/>
       </c>
+      <c r="O66">
+        <f>IF(K66=$B$221,L66,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -16187,6 +17234,10 @@
         <f>IF(K67&lt;&gt;"",A67,"")</f>
         <v/>
       </c>
+      <c r="O67">
+        <f>IF(K67=$B$221,L67,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -16237,6 +17288,10 @@
         <f>IF(K68&lt;&gt;"",A68,"")</f>
         <v/>
       </c>
+      <c r="O68">
+        <f>IF(K68=$B$221,L68,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -16287,6 +17342,10 @@
         <f>IF(K69&lt;&gt;"",A69,"")</f>
         <v/>
       </c>
+      <c r="O69">
+        <f>IF(K69=$B$221,L69,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -16337,6 +17396,10 @@
         <f>IF(K70&lt;&gt;"",A70,"")</f>
         <v/>
       </c>
+      <c r="O70">
+        <f>IF(K70=$B$221,L70,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -16387,6 +17450,10 @@
         <f>IF(K71&lt;&gt;"",A71,"")</f>
         <v/>
       </c>
+      <c r="O71">
+        <f>IF(K71=$B$221,L71,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -16437,6 +17504,10 @@
         <f>IF(K72&lt;&gt;"",A72,"")</f>
         <v/>
       </c>
+      <c r="O72">
+        <f>IF(K72=$B$221,L72,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -16487,6 +17558,10 @@
         <f>IF(K73&lt;&gt;"",A73,"")</f>
         <v/>
       </c>
+      <c r="O73">
+        <f>IF(K73=$B$221,L73,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -16537,6 +17612,10 @@
         <f>IF(K74&lt;&gt;"",A74,"")</f>
         <v/>
       </c>
+      <c r="O74">
+        <f>IF(K74=$B$221,L74,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -16587,6 +17666,10 @@
         <f>IF(K75&lt;&gt;"",A75,"")</f>
         <v/>
       </c>
+      <c r="O75">
+        <f>IF(K75=$B$221,L75,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -16637,6 +17720,10 @@
         <f>IF(K76&lt;&gt;"",A76,"")</f>
         <v/>
       </c>
+      <c r="O76">
+        <f>IF(K76=$B$221,L76,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -16687,6 +17774,10 @@
         <f>IF(K77&lt;&gt;"",A77,"")</f>
         <v/>
       </c>
+      <c r="O77">
+        <f>IF(K77=$B$221,L77,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -16737,6 +17828,10 @@
         <f>IF(K78&lt;&gt;"",A78,"")</f>
         <v/>
       </c>
+      <c r="O78">
+        <f>IF(K78=$B$221,L78,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -16787,6 +17882,10 @@
         <f>IF(K79&lt;&gt;"",A79,"")</f>
         <v/>
       </c>
+      <c r="O79">
+        <f>IF(K79=$B$221,L79,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -16837,6 +17936,10 @@
         <f>IF(K80&lt;&gt;"",A80,"")</f>
         <v/>
       </c>
+      <c r="O80">
+        <f>IF(K80=$B$221,L80,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -16887,6 +17990,10 @@
         <f>IF(K81&lt;&gt;"",A81,"")</f>
         <v/>
       </c>
+      <c r="O81">
+        <f>IF(K81=$B$221,L81,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -16937,6 +18044,10 @@
         <f>IF(K82&lt;&gt;"",A82,"")</f>
         <v/>
       </c>
+      <c r="O82">
+        <f>IF(K82=$B$221,L82,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -16987,6 +18098,10 @@
         <f>IF(K83&lt;&gt;"",A83,"")</f>
         <v/>
       </c>
+      <c r="O83">
+        <f>IF(K83=$B$221,L83,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -17037,6 +18152,10 @@
         <f>IF(K84&lt;&gt;"",A84,"")</f>
         <v/>
       </c>
+      <c r="O84">
+        <f>IF(K84=$B$221,L84,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -17087,6 +18206,10 @@
         <f>IF(K85&lt;&gt;"",A85,"")</f>
         <v/>
       </c>
+      <c r="O85">
+        <f>IF(K85=$B$221,L85,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -17137,6 +18260,10 @@
         <f>IF(K86&lt;&gt;"",A86,"")</f>
         <v/>
       </c>
+      <c r="O86">
+        <f>IF(K86=$B$221,L86,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -17187,6 +18314,10 @@
         <f>IF(K87&lt;&gt;"",A87,"")</f>
         <v/>
       </c>
+      <c r="O87">
+        <f>IF(K87=$B$221,L87,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -17237,6 +18368,10 @@
         <f>IF(K88&lt;&gt;"",A88,"")</f>
         <v/>
       </c>
+      <c r="O88">
+        <f>IF(K88=$B$221,L88,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -17287,6 +18422,10 @@
         <f>IF(K89&lt;&gt;"",A89,"")</f>
         <v/>
       </c>
+      <c r="O89">
+        <f>IF(K89=$B$221,L89,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -17337,6 +18476,10 @@
         <f>IF(K90&lt;&gt;"",A90,"")</f>
         <v/>
       </c>
+      <c r="O90">
+        <f>IF(K90=$B$221,L90,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -17387,6 +18530,10 @@
         <f>IF(K91&lt;&gt;"",A91,"")</f>
         <v/>
       </c>
+      <c r="O91">
+        <f>IF(K91=$B$221,L91,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -17437,6 +18584,10 @@
         <f>IF(K92&lt;&gt;"",A92,"")</f>
         <v/>
       </c>
+      <c r="O92">
+        <f>IF(K92=$B$221,L92,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -17487,6 +18638,10 @@
         <f>IF(K93&lt;&gt;"",A93,"")</f>
         <v/>
       </c>
+      <c r="O93">
+        <f>IF(K93=$B$221,L93,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -17537,6 +18692,10 @@
         <f>IF(K94&lt;&gt;"",A94,"")</f>
         <v/>
       </c>
+      <c r="O94">
+        <f>IF(K94=$B$221,L94,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -17587,6 +18746,10 @@
         <f>IF(K95&lt;&gt;"",A95,"")</f>
         <v/>
       </c>
+      <c r="O95">
+        <f>IF(K95=$B$221,L95,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -17637,6 +18800,10 @@
         <f>IF(K96&lt;&gt;"",A96,"")</f>
         <v/>
       </c>
+      <c r="O96">
+        <f>IF(K96=$B$221,L96,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -17687,6 +18854,10 @@
         <f>IF(K97&lt;&gt;"",A97,"")</f>
         <v/>
       </c>
+      <c r="O97">
+        <f>IF(K97=$B$221,L97,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -17737,6 +18908,10 @@
         <f>IF(K98&lt;&gt;"",A98,"")</f>
         <v/>
       </c>
+      <c r="O98">
+        <f>IF(K98=$B$221,L98,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -17787,6 +18962,10 @@
         <f>IF(K99&lt;&gt;"",A99,"")</f>
         <v/>
       </c>
+      <c r="O99">
+        <f>IF(K99=$B$221,L99,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -17837,6 +19016,10 @@
         <f>IF(K100&lt;&gt;"",A100,"")</f>
         <v/>
       </c>
+      <c r="O100">
+        <f>IF(K100=$B$221,L100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -17887,6 +19070,10 @@
         <f>IF(K101&lt;&gt;"",A101,"")</f>
         <v/>
       </c>
+      <c r="O101">
+        <f>IF(K101=$B$221,L101,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -17937,6 +19124,10 @@
         <f>IF(K102&lt;&gt;"",A102,"")</f>
         <v/>
       </c>
+      <c r="O102">
+        <f>IF(K102=$B$221,L102,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -17987,6 +19178,10 @@
         <f>IF(K103&lt;&gt;"",A103,"")</f>
         <v/>
       </c>
+      <c r="O103">
+        <f>IF(K103=$B$221,L103,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -18037,6 +19232,10 @@
         <f>IF(K104&lt;&gt;"",A104,"")</f>
         <v/>
       </c>
+      <c r="O104">
+        <f>IF(K104=$B$221,L104,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -18087,6 +19286,10 @@
         <f>IF(K105&lt;&gt;"",A105,"")</f>
         <v/>
       </c>
+      <c r="O105">
+        <f>IF(K105=$B$221,L105,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -18137,6 +19340,10 @@
         <f>IF(K106&lt;&gt;"",A106,"")</f>
         <v/>
       </c>
+      <c r="O106">
+        <f>IF(K106=$B$221,L106,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -18187,6 +19394,10 @@
         <f>IF(K107&lt;&gt;"",A107,"")</f>
         <v/>
       </c>
+      <c r="O107">
+        <f>IF(K107=$B$221,L107,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -18237,6 +19448,10 @@
         <f>IF(K108&lt;&gt;"",A108,"")</f>
         <v/>
       </c>
+      <c r="O108">
+        <f>IF(K108=$B$221,L108,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -18287,6 +19502,10 @@
         <f>IF(K109&lt;&gt;"",A109,"")</f>
         <v/>
       </c>
+      <c r="O109">
+        <f>IF(K109=$B$221,L109,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -18337,6 +19556,10 @@
         <f>IF(K110&lt;&gt;"",A110,"")</f>
         <v/>
       </c>
+      <c r="O110">
+        <f>IF(K110=$B$221,L110,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -18387,6 +19610,10 @@
         <f>IF(K111&lt;&gt;"",A111,"")</f>
         <v/>
       </c>
+      <c r="O111">
+        <f>IF(K111=$B$221,L111,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -18437,6 +19664,10 @@
         <f>IF(K112&lt;&gt;"",A112,"")</f>
         <v/>
       </c>
+      <c r="O112">
+        <f>IF(K112=$B$221,L112,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -18487,6 +19718,10 @@
         <f>IF(K113&lt;&gt;"",A113,"")</f>
         <v/>
       </c>
+      <c r="O113">
+        <f>IF(K113=$B$221,L113,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -18537,6 +19772,10 @@
         <f>IF(K114&lt;&gt;"",A114,"")</f>
         <v/>
       </c>
+      <c r="O114">
+        <f>IF(K114=$B$221,L114,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -18587,6 +19826,10 @@
         <f>IF(K115&lt;&gt;"",A115,"")</f>
         <v/>
       </c>
+      <c r="O115">
+        <f>IF(K115=$B$221,L115,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -18637,6 +19880,10 @@
         <f>IF(K116&lt;&gt;"",A116,"")</f>
         <v/>
       </c>
+      <c r="O116">
+        <f>IF(K116=$B$221,L116,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -18687,6 +19934,10 @@
         <f>IF(K117&lt;&gt;"",A117,"")</f>
         <v/>
       </c>
+      <c r="O117">
+        <f>IF(K117=$B$221,L117,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -18737,6 +19988,10 @@
         <f>IF(K118&lt;&gt;"",A118,"")</f>
         <v/>
       </c>
+      <c r="O118">
+        <f>IF(K118=$B$221,L118,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -18787,6 +20042,10 @@
         <f>IF(K119&lt;&gt;"",A119,"")</f>
         <v/>
       </c>
+      <c r="O119">
+        <f>IF(K119=$B$221,L119,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -18837,6 +20096,10 @@
         <f>IF(K120&lt;&gt;"",A120,"")</f>
         <v/>
       </c>
+      <c r="O120">
+        <f>IF(K120=$B$221,L120,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -18887,6 +20150,10 @@
         <f>IF(K121&lt;&gt;"",A121,"")</f>
         <v/>
       </c>
+      <c r="O121">
+        <f>IF(K121=$B$221,L121,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -18937,6 +20204,10 @@
         <f>IF(K122&lt;&gt;"",A122,"")</f>
         <v/>
       </c>
+      <c r="O122">
+        <f>IF(K122=$B$221,L122,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -18987,6 +20258,10 @@
         <f>IF(K123&lt;&gt;"",A123,"")</f>
         <v/>
       </c>
+      <c r="O123">
+        <f>IF(K123=$B$221,L123,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -19037,6 +20312,10 @@
         <f>IF(K124&lt;&gt;"",A124,"")</f>
         <v/>
       </c>
+      <c r="O124">
+        <f>IF(K124=$B$221,L124,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -19087,6 +20366,10 @@
         <f>IF(K125&lt;&gt;"",A125,"")</f>
         <v/>
       </c>
+      <c r="O125">
+        <f>IF(K125=$B$221,L125,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -19137,6 +20420,10 @@
         <f>IF(K126&lt;&gt;"",A126,"")</f>
         <v/>
       </c>
+      <c r="O126">
+        <f>IF(K126=$B$221,L126,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -19187,6 +20474,10 @@
         <f>IF(K127&lt;&gt;"",A127,"")</f>
         <v/>
       </c>
+      <c r="O127">
+        <f>IF(K127=$B$221,L127,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -19237,6 +20528,10 @@
         <f>IF(K128&lt;&gt;"",A128,"")</f>
         <v/>
       </c>
+      <c r="O128">
+        <f>IF(K128=$B$221,L128,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -19287,6 +20582,10 @@
         <f>IF(K129&lt;&gt;"",A129,"")</f>
         <v/>
       </c>
+      <c r="O129">
+        <f>IF(K129=$B$221,L129,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -19337,6 +20636,10 @@
         <f>IF(K130&lt;&gt;"",A130,"")</f>
         <v/>
       </c>
+      <c r="O130">
+        <f>IF(K130=$B$221,L130,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -19387,6 +20690,10 @@
         <f>IF(K131&lt;&gt;"",A131,"")</f>
         <v/>
       </c>
+      <c r="O131">
+        <f>IF(K131=$B$221,L131,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -19437,6 +20744,10 @@
         <f>IF(K132&lt;&gt;"",A132,"")</f>
         <v/>
       </c>
+      <c r="O132">
+        <f>IF(K132=$B$221,L132,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -19487,6 +20798,10 @@
         <f>IF(K133&lt;&gt;"",A133,"")</f>
         <v/>
       </c>
+      <c r="O133">
+        <f>IF(K133=$B$221,L133,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -19537,6 +20852,10 @@
         <f>IF(K134&lt;&gt;"",A134,"")</f>
         <v/>
       </c>
+      <c r="O134">
+        <f>IF(K134=$B$221,L134,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -19587,6 +20906,10 @@
         <f>IF(K135&lt;&gt;"",A135,"")</f>
         <v/>
       </c>
+      <c r="O135">
+        <f>IF(K135=$B$221,L135,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -19637,6 +20960,10 @@
         <f>IF(K136&lt;&gt;"",A136,"")</f>
         <v/>
       </c>
+      <c r="O136">
+        <f>IF(K136=$B$221,L136,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -19687,6 +21014,10 @@
         <f>IF(K137&lt;&gt;"",A137,"")</f>
         <v/>
       </c>
+      <c r="O137">
+        <f>IF(K137=$B$221,L137,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -19737,6 +21068,10 @@
         <f>IF(K138&lt;&gt;"",A138,"")</f>
         <v/>
       </c>
+      <c r="O138">
+        <f>IF(K138=$B$221,L138,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -19787,6 +21122,10 @@
         <f>IF(K139&lt;&gt;"",A139,"")</f>
         <v/>
       </c>
+      <c r="O139">
+        <f>IF(K139=$B$221,L139,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -19837,6 +21176,10 @@
         <f>IF(K140&lt;&gt;"",A140,"")</f>
         <v/>
       </c>
+      <c r="O140">
+        <f>IF(K140=$B$221,L140,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -19887,6 +21230,10 @@
         <f>IF(K141&lt;&gt;"",A141,"")</f>
         <v/>
       </c>
+      <c r="O141">
+        <f>IF(K141=$B$221,L141,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -19937,6 +21284,10 @@
         <f>IF(K142&lt;&gt;"",A142,"")</f>
         <v/>
       </c>
+      <c r="O142">
+        <f>IF(K142=$B$221,L142,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -19987,6 +21338,10 @@
         <f>IF(K143&lt;&gt;"",A143,"")</f>
         <v/>
       </c>
+      <c r="O143">
+        <f>IF(K143=$B$221,L143,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -20037,6 +21392,10 @@
         <f>IF(K144&lt;&gt;"",A144,"")</f>
         <v/>
       </c>
+      <c r="O144">
+        <f>IF(K144=$B$221,L144,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -20087,6 +21446,10 @@
         <f>IF(K145&lt;&gt;"",A145,"")</f>
         <v/>
       </c>
+      <c r="O145">
+        <f>IF(K145=$B$221,L145,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -20137,6 +21500,10 @@
         <f>IF(K146&lt;&gt;"",A146,"")</f>
         <v/>
       </c>
+      <c r="O146">
+        <f>IF(K146=$B$221,L146,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -20187,6 +21554,10 @@
         <f>IF(K147&lt;&gt;"",A147,"")</f>
         <v/>
       </c>
+      <c r="O147">
+        <f>IF(K147=$B$221,L147,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -20237,6 +21608,10 @@
         <f>IF(K148&lt;&gt;"",A148,"")</f>
         <v/>
       </c>
+      <c r="O148">
+        <f>IF(K148=$B$221,L148,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -20287,6 +21662,10 @@
         <f>IF(K149&lt;&gt;"",A149,"")</f>
         <v/>
       </c>
+      <c r="O149">
+        <f>IF(K149=$B$221,L149,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -20337,6 +21716,10 @@
         <f>IF(K150&lt;&gt;"",A150,"")</f>
         <v/>
       </c>
+      <c r="O150">
+        <f>IF(K150=$B$221,L150,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -20387,6 +21770,10 @@
         <f>IF(K151&lt;&gt;"",A151,"")</f>
         <v/>
       </c>
+      <c r="O151">
+        <f>IF(K151=$B$221,L151,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -20437,6 +21824,10 @@
         <f>IF(K152&lt;&gt;"",A152,"")</f>
         <v/>
       </c>
+      <c r="O152">
+        <f>IF(K152=$B$221,L152,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -20487,6 +21878,10 @@
         <f>IF(K153&lt;&gt;"",A153,"")</f>
         <v/>
       </c>
+      <c r="O153">
+        <f>IF(K153=$B$221,L153,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -20537,6 +21932,10 @@
         <f>IF(K154&lt;&gt;"",A154,"")</f>
         <v/>
       </c>
+      <c r="O154">
+        <f>IF(K154=$B$221,L154,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -20587,6 +21986,10 @@
         <f>IF(K155&lt;&gt;"",A155,"")</f>
         <v/>
       </c>
+      <c r="O155">
+        <f>IF(K155=$B$221,L155,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -20637,6 +22040,10 @@
         <f>IF(K156&lt;&gt;"",A156,"")</f>
         <v/>
       </c>
+      <c r="O156">
+        <f>IF(K156=$B$221,L156,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -20687,6 +22094,10 @@
         <f>IF(K157&lt;&gt;"",A157,"")</f>
         <v/>
       </c>
+      <c r="O157">
+        <f>IF(K157=$B$221,L157,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -20737,6 +22148,10 @@
         <f>IF(K158&lt;&gt;"",A158,"")</f>
         <v/>
       </c>
+      <c r="O158">
+        <f>IF(K158=$B$221,L158,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -20787,6 +22202,10 @@
         <f>IF(K159&lt;&gt;"",A159,"")</f>
         <v/>
       </c>
+      <c r="O159">
+        <f>IF(K159=$B$221,L159,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -20837,6 +22256,10 @@
         <f>IF(K160&lt;&gt;"",A160,"")</f>
         <v/>
       </c>
+      <c r="O160">
+        <f>IF(K160=$B$221,L160,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -20887,6 +22310,10 @@
         <f>IF(K161&lt;&gt;"",A161,"")</f>
         <v/>
       </c>
+      <c r="O161">
+        <f>IF(K161=$B$221,L161,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -20937,6 +22364,10 @@
         <f>IF(K162&lt;&gt;"",A162,"")</f>
         <v/>
       </c>
+      <c r="O162">
+        <f>IF(K162=$B$221,L162,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -20987,6 +22418,10 @@
         <f>IF(K163&lt;&gt;"",A163,"")</f>
         <v/>
       </c>
+      <c r="O163">
+        <f>IF(K163=$B$221,L163,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -21037,6 +22472,10 @@
         <f>IF(K164&lt;&gt;"",A164,"")</f>
         <v/>
       </c>
+      <c r="O164">
+        <f>IF(K164=$B$221,L164,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -21087,6 +22526,10 @@
         <f>IF(K165&lt;&gt;"",A165,"")</f>
         <v/>
       </c>
+      <c r="O165">
+        <f>IF(K165=$B$221,L165,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -21137,6 +22580,10 @@
         <f>IF(K166&lt;&gt;"",A166,"")</f>
         <v/>
       </c>
+      <c r="O166">
+        <f>IF(K166=$B$221,L166,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -21187,6 +22634,10 @@
         <f>IF(K167&lt;&gt;"",A167,"")</f>
         <v/>
       </c>
+      <c r="O167">
+        <f>IF(K167=$B$221,L167,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -21237,6 +22688,10 @@
         <f>IF(K168&lt;&gt;"",A168,"")</f>
         <v/>
       </c>
+      <c r="O168">
+        <f>IF(K168=$B$221,L168,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -21287,6 +22742,10 @@
         <f>IF(K169&lt;&gt;"",A169,"")</f>
         <v/>
       </c>
+      <c r="O169">
+        <f>IF(K169=$B$221,L169,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -21337,6 +22796,10 @@
         <f>IF(K170&lt;&gt;"",A170,"")</f>
         <v/>
       </c>
+      <c r="O170">
+        <f>IF(K170=$B$221,L170,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -21387,6 +22850,10 @@
         <f>IF(K171&lt;&gt;"",A171,"")</f>
         <v/>
       </c>
+      <c r="O171">
+        <f>IF(K171=$B$221,L171,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -21437,6 +22904,10 @@
         <f>IF(K172&lt;&gt;"",A172,"")</f>
         <v/>
       </c>
+      <c r="O172">
+        <f>IF(K172=$B$221,L172,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -21487,6 +22958,10 @@
         <f>IF(K173&lt;&gt;"",A173,"")</f>
         <v/>
       </c>
+      <c r="O173">
+        <f>IF(K173=$B$221,L173,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -21537,6 +23012,10 @@
         <f>IF(K174&lt;&gt;"",A174,"")</f>
         <v/>
       </c>
+      <c r="O174">
+        <f>IF(K174=$B$221,L174,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -21587,6 +23066,10 @@
         <f>IF(K175&lt;&gt;"",A175,"")</f>
         <v/>
       </c>
+      <c r="O175">
+        <f>IF(K175=$B$221,L175,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -21637,6 +23120,10 @@
         <f>IF(K176&lt;&gt;"",A176,"")</f>
         <v/>
       </c>
+      <c r="O176">
+        <f>IF(K176=$B$221,L176,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -21687,6 +23174,10 @@
         <f>IF(K177&lt;&gt;"",A177,"")</f>
         <v/>
       </c>
+      <c r="O177">
+        <f>IF(K177=$B$221,L177,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -21737,6 +23228,10 @@
         <f>IF(K178&lt;&gt;"",A178,"")</f>
         <v/>
       </c>
+      <c r="O178">
+        <f>IF(K178=$B$221,L178,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -21787,6 +23282,10 @@
         <f>IF(K179&lt;&gt;"",A179,"")</f>
         <v/>
       </c>
+      <c r="O179">
+        <f>IF(K179=$B$221,L179,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -21837,6 +23336,10 @@
         <f>IF(K180&lt;&gt;"",A180,"")</f>
         <v/>
       </c>
+      <c r="O180">
+        <f>IF(K180=$B$221,L180,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -21887,6 +23390,10 @@
         <f>IF(K181&lt;&gt;"",A181,"")</f>
         <v/>
       </c>
+      <c r="O181">
+        <f>IF(K181=$B$221,L181,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -21937,6 +23444,10 @@
         <f>IF(K182&lt;&gt;"",A182,"")</f>
         <v/>
       </c>
+      <c r="O182">
+        <f>IF(K182=$B$221,L182,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -21987,6 +23498,10 @@
         <f>IF(K183&lt;&gt;"",A183,"")</f>
         <v/>
       </c>
+      <c r="O183">
+        <f>IF(K183=$B$221,L183,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -22037,6 +23552,10 @@
         <f>IF(K184&lt;&gt;"",A184,"")</f>
         <v/>
       </c>
+      <c r="O184">
+        <f>IF(K184=$B$221,L184,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -22087,6 +23606,10 @@
         <f>IF(K185&lt;&gt;"",A185,"")</f>
         <v/>
       </c>
+      <c r="O185">
+        <f>IF(K185=$B$221,L185,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -22137,6 +23660,10 @@
         <f>IF(K186&lt;&gt;"",A186,"")</f>
         <v/>
       </c>
+      <c r="O186">
+        <f>IF(K186=$B$221,L186,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -22187,6 +23714,10 @@
         <f>IF(K187&lt;&gt;"",A187,"")</f>
         <v/>
       </c>
+      <c r="O187">
+        <f>IF(K187=$B$221,L187,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -22237,6 +23768,10 @@
         <f>IF(K188&lt;&gt;"",A188,"")</f>
         <v/>
       </c>
+      <c r="O188">
+        <f>IF(K188=$B$221,L188,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -22287,6 +23822,10 @@
         <f>IF(K189&lt;&gt;"",A189,"")</f>
         <v/>
       </c>
+      <c r="O189">
+        <f>IF(K189=$B$221,L189,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -22337,6 +23876,10 @@
         <f>IF(K190&lt;&gt;"",A190,"")</f>
         <v/>
       </c>
+      <c r="O190">
+        <f>IF(K190=$B$221,L190,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -22387,6 +23930,10 @@
         <f>IF(K191&lt;&gt;"",A191,"")</f>
         <v/>
       </c>
+      <c r="O191">
+        <f>IF(K191=$B$221,L191,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -22437,6 +23984,10 @@
         <f>IF(K192&lt;&gt;"",A192,"")</f>
         <v/>
       </c>
+      <c r="O192">
+        <f>IF(K192=$B$221,L192,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -22487,6 +24038,10 @@
         <f>IF(K193&lt;&gt;"",A193,"")</f>
         <v/>
       </c>
+      <c r="O193">
+        <f>IF(K193=$B$221,L193,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -22537,6 +24092,10 @@
         <f>IF(K194&lt;&gt;"",A194,"")</f>
         <v/>
       </c>
+      <c r="O194">
+        <f>IF(K194=$B$221,L194,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -22587,6 +24146,10 @@
         <f>IF(K195&lt;&gt;"",A195,"")</f>
         <v/>
       </c>
+      <c r="O195">
+        <f>IF(K195=$B$221,L195,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -22637,6 +24200,10 @@
         <f>IF(K196&lt;&gt;"",A196,"")</f>
         <v/>
       </c>
+      <c r="O196">
+        <f>IF(K196=$B$221,L196,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -22687,6 +24254,10 @@
         <f>IF(K197&lt;&gt;"",A197,"")</f>
         <v/>
       </c>
+      <c r="O197">
+        <f>IF(K197=$B$221,L197,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -22737,6 +24308,10 @@
         <f>IF(K198&lt;&gt;"",A198,"")</f>
         <v/>
       </c>
+      <c r="O198">
+        <f>IF(K198=$B$221,L198,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -22787,6 +24362,10 @@
         <f>IF(K199&lt;&gt;"",A199,"")</f>
         <v/>
       </c>
+      <c r="O199">
+        <f>IF(K199=$B$221,L199,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -22837,6 +24416,10 @@
         <f>IF(K200&lt;&gt;"",A200,"")</f>
         <v/>
       </c>
+      <c r="O200">
+        <f>IF(K200=$B$221,L200,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -22887,6 +24470,10 @@
         <f>IF(K201&lt;&gt;"",A201,"")</f>
         <v/>
       </c>
+      <c r="O201">
+        <f>IF(K201=$B$221,L201,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -22937,6 +24524,10 @@
         <f>IF(K202&lt;&gt;"",A202,"")</f>
         <v/>
       </c>
+      <c r="O202">
+        <f>IF(K202=$B$221,L202,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -22987,6 +24578,10 @@
         <f>IF(K203&lt;&gt;"",A203,"")</f>
         <v/>
       </c>
+      <c r="O203">
+        <f>IF(K203=$B$221,L203,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -23037,6 +24632,10 @@
         <f>IF(K204&lt;&gt;"",A204,"")</f>
         <v/>
       </c>
+      <c r="O204">
+        <f>IF(K204=$B$221,L204,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -23087,6 +24686,10 @@
         <f>IF(K205&lt;&gt;"",A205,"")</f>
         <v/>
       </c>
+      <c r="O205">
+        <f>IF(K205=$B$221,L205,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -23137,6 +24740,10 @@
         <f>IF(K206&lt;&gt;"",A206,"")</f>
         <v/>
       </c>
+      <c r="O206">
+        <f>IF(K206=$B$221,L206,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -23187,6 +24794,10 @@
         <f>IF(K207&lt;&gt;"",A207,"")</f>
         <v/>
       </c>
+      <c r="O207">
+        <f>IF(K207=$B$221,L207,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -23237,6 +24848,10 @@
         <f>IF(K208&lt;&gt;"",A208,"")</f>
         <v/>
       </c>
+      <c r="O208">
+        <f>IF(K208=$B$221,L208,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -23287,6 +24902,10 @@
         <f>IF(K209&lt;&gt;"",A209,"")</f>
         <v/>
       </c>
+      <c r="O209">
+        <f>IF(K209=$B$221,L209,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -23337,6 +24956,10 @@
         <f>IF(K210&lt;&gt;"",A210,"")</f>
         <v/>
       </c>
+      <c r="O210">
+        <f>IF(K210=$B$221,L210,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -23387,6 +25010,10 @@
         <f>IF(K211&lt;&gt;"",A211,"")</f>
         <v/>
       </c>
+      <c r="O211">
+        <f>IF(K211=$B$221,L211,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -23418,7 +25045,7 @@
         </is>
       </c>
       <c r="B222">
-        <f>IF(B221=0,"N/A",MINIFS(L12:L211,K12:K211,B221))</f>
+        <f>IF(B221=0,"N/A",MIN(O12:O211))</f>
         <v/>
       </c>
     </row>
